--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180CE3CC-B40A-48FC-BCC9-5CBED237410D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F61A25-B5C7-B24D-99B8-CAA5E8DA2A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25500" yWindow="1380" windowWidth="23400" windowHeight="19300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -112,7 +112,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2605,6 +2605,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4940,7 +4943,10 @@
                   <c:v>3968.87</c:v>
                 </c:pt>
                 <c:pt idx="775">
-                  <c:v>4166</c:v>
+                  <c:v>4165.57</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>4530.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7313,6 +7319,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9649,6 +9658,9 @@
                 </c:pt>
                 <c:pt idx="775">
                   <c:v>4392</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>4682</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12021,6 +12033,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14357,6 +14372,9 @@
                 </c:pt>
                 <c:pt idx="775">
                   <c:v>5759</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>6360</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16729,6 +16747,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19065,6 +19086,9 @@
                 </c:pt>
                 <c:pt idx="775">
                   <c:v>5750</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>6349</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21437,6 +21461,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23773,6 +23800,9 @@
                 </c:pt>
                 <c:pt idx="775">
                   <c:v>7149</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>7902</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26145,6 +26175,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28481,6 +28514,9 @@
                 </c:pt>
                 <c:pt idx="775">
                   <c:v>648</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>647</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30855,6 +30891,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33190,6 +33229,9 @@
                   <c:v>822</c:v>
                 </c:pt>
                 <c:pt idx="775">
+                  <c:v>828</c:v>
+                </c:pt>
+                <c:pt idx="776">
                   <c:v>828</c:v>
                 </c:pt>
               </c:numCache>
@@ -35565,6 +35607,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37901,6 +37946,9 @@
                 </c:pt>
                 <c:pt idx="775">
                   <c:v>1011</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>1015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40275,6 +40323,9 @@
                 <c:pt idx="775">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="776">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42611,6 +42662,9 @@
                 </c:pt>
                 <c:pt idx="775">
                   <c:v>2584</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>2602</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43688,19 +43742,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M777"/>
-  <sheetFormatPr defaultColWidth="7.453125" defaultRowHeight="14.5"/>
+  <dimension ref="A1:M778"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="10.453125" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="7.453125" style="8"/>
+    <col min="5" max="5" width="15.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="10.5" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="7.5" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1">
+    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -43741,7 +43795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>40716</v>
       </c>
@@ -43782,7 +43836,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>40723</v>
       </c>
@@ -43823,7 +43877,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>40730</v>
       </c>
@@ -43864,7 +43918,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>40737</v>
       </c>
@@ -43905,7 +43959,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>40744</v>
       </c>
@@ -43946,7 +44000,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>40751</v>
       </c>
@@ -43987,7 +44041,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>40758</v>
       </c>
@@ -44028,7 +44082,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>40765</v>
       </c>
@@ -44069,7 +44123,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>40772</v>
       </c>
@@ -44110,7 +44164,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>40779</v>
       </c>
@@ -44151,7 +44205,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>40786</v>
       </c>
@@ -44192,7 +44246,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>40793</v>
       </c>
@@ -44233,7 +44287,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>40800</v>
       </c>
@@ -44274,7 +44328,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>40807</v>
       </c>
@@ -44315,7 +44369,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>40814</v>
       </c>
@@ -44356,7 +44410,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>40821</v>
       </c>
@@ -44397,7 +44451,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>40828</v>
       </c>
@@ -44438,7 +44492,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>40835</v>
       </c>
@@ -44479,7 +44533,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>40842</v>
       </c>
@@ -44520,7 +44574,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>40849</v>
       </c>
@@ -44561,7 +44615,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>40856</v>
       </c>
@@ -44602,7 +44656,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>40863</v>
       </c>
@@ -44643,7 +44697,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>40870</v>
       </c>
@@ -44684,7 +44738,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>40877</v>
       </c>
@@ -44725,7 +44779,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>40884</v>
       </c>
@@ -44766,7 +44820,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>40891</v>
       </c>
@@ -44807,7 +44861,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>40898</v>
       </c>
@@ -44848,7 +44902,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>40905</v>
       </c>
@@ -44889,7 +44943,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>40912</v>
       </c>
@@ -44930,7 +44984,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>40919</v>
       </c>
@@ -44971,7 +45025,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>40926</v>
       </c>
@@ -45012,7 +45066,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>40933</v>
       </c>
@@ -45053,7 +45107,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>40940</v>
       </c>
@@ -45094,7 +45148,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>40947</v>
       </c>
@@ -45135,7 +45189,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>40954</v>
       </c>
@@ -45176,7 +45230,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>40961</v>
       </c>
@@ -45217,7 +45271,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>40968</v>
       </c>
@@ -45258,7 +45312,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>40975</v>
       </c>
@@ -45299,7 +45353,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>40982</v>
       </c>
@@ -45340,7 +45394,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>40989</v>
       </c>
@@ -45381,7 +45435,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>40996</v>
       </c>
@@ -45422,7 +45476,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>41003</v>
       </c>
@@ -45463,7 +45517,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>41010</v>
       </c>
@@ -45504,7 +45558,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>41017</v>
       </c>
@@ -45545,7 +45599,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <v>41024</v>
       </c>
@@ -45586,7 +45640,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <v>41031</v>
       </c>
@@ -45627,7 +45681,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <v>41038</v>
       </c>
@@ -45668,7 +45722,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>41045</v>
       </c>
@@ -45709,7 +45763,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>41052</v>
       </c>
@@ -45750,7 +45804,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>41059</v>
       </c>
@@ -45791,7 +45845,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>41066</v>
       </c>
@@ -45832,7 +45886,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>41073</v>
       </c>
@@ -45873,7 +45927,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>41080</v>
       </c>
@@ -45914,7 +45968,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>41087</v>
       </c>
@@ -45955,7 +46009,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>41094</v>
       </c>
@@ -45996,7 +46050,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>41101</v>
       </c>
@@ -46037,7 +46091,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>41108</v>
       </c>
@@ -46078,7 +46132,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>41115</v>
       </c>
@@ -46119,7 +46173,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>41122</v>
       </c>
@@ -46160,7 +46214,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>41129</v>
       </c>
@@ -46201,7 +46255,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>41136</v>
       </c>
@@ -46242,7 +46296,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>41143</v>
       </c>
@@ -46283,7 +46337,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>41150</v>
       </c>
@@ -46324,7 +46378,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>41157</v>
       </c>
@@ -46365,7 +46419,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>41164</v>
       </c>
@@ -46406,7 +46460,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>41171</v>
       </c>
@@ -46447,7 +46501,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>41178</v>
       </c>
@@ -46488,7 +46542,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>41185</v>
       </c>
@@ -46529,7 +46583,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>41192</v>
       </c>
@@ -46570,7 +46624,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>41199</v>
       </c>
@@ -46611,7 +46665,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>41206</v>
       </c>
@@ -46652,7 +46706,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>41213</v>
       </c>
@@ -46693,7 +46747,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <v>41220</v>
       </c>
@@ -46734,7 +46788,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>41227</v>
       </c>
@@ -46775,7 +46829,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>41234</v>
       </c>
@@ -46816,7 +46870,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>41241</v>
       </c>
@@ -46857,7 +46911,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>41248</v>
       </c>
@@ -46898,7 +46952,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>41255</v>
       </c>
@@ -46939,7 +46993,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>41262</v>
       </c>
@@ -46980,7 +47034,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <v>41269</v>
       </c>
@@ -47021,7 +47075,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <v>41276</v>
       </c>
@@ -47062,7 +47116,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <v>41283</v>
       </c>
@@ -47103,7 +47157,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>41290</v>
       </c>
@@ -47144,7 +47198,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>41297</v>
       </c>
@@ -47185,7 +47239,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>41304</v>
       </c>
@@ -47226,7 +47280,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <v>41311</v>
       </c>
@@ -47267,7 +47321,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <v>41318</v>
       </c>
@@ -47308,7 +47362,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <v>41325</v>
       </c>
@@ -47349,7 +47403,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <v>41332</v>
       </c>
@@ -47390,7 +47444,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <v>41339</v>
       </c>
@@ -47431,7 +47485,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <v>41346</v>
       </c>
@@ -47472,7 +47526,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <v>41353</v>
       </c>
@@ -47513,7 +47567,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <v>41360</v>
       </c>
@@ -47554,7 +47608,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <v>41367</v>
       </c>
@@ -47595,7 +47649,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <v>41374</v>
       </c>
@@ -47636,7 +47690,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="5">
         <v>41381</v>
       </c>
@@ -47677,7 +47731,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="5">
         <v>41388</v>
       </c>
@@ -47718,7 +47772,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <v>41395</v>
       </c>
@@ -47759,7 +47813,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <v>41402</v>
       </c>
@@ -47800,7 +47854,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="5">
         <v>41409</v>
       </c>
@@ -47841,7 +47895,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="5">
         <v>41416</v>
       </c>
@@ -47882,7 +47936,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="5">
         <v>41423</v>
       </c>
@@ -47923,7 +47977,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="5">
         <v>41430</v>
       </c>
@@ -47964,7 +48018,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="5">
         <v>41437</v>
       </c>
@@ -48005,7 +48059,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="5">
         <v>41444</v>
       </c>
@@ -48046,7 +48100,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="5">
         <v>41451</v>
       </c>
@@ -48087,7 +48141,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="5">
         <v>41458</v>
       </c>
@@ -48128,7 +48182,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="5">
         <v>41465</v>
       </c>
@@ -48169,7 +48223,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="5">
         <v>41472</v>
       </c>
@@ -48210,7 +48264,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="5">
         <v>41479</v>
       </c>
@@ -48251,7 +48305,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="5">
         <v>41486</v>
       </c>
@@ -48292,7 +48346,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="5">
         <v>41493</v>
       </c>
@@ -48333,7 +48387,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>41500</v>
       </c>
@@ -48374,7 +48428,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="5">
         <v>41507</v>
       </c>
@@ -48415,7 +48469,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="5">
         <v>41514</v>
       </c>
@@ -48456,7 +48510,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="5">
         <v>41521</v>
       </c>
@@ -48497,7 +48551,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <v>41528</v>
       </c>
@@ -48538,7 +48592,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <v>41535</v>
       </c>
@@ -48579,7 +48633,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="5">
         <v>41542</v>
       </c>
@@ -48620,7 +48674,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="5">
         <v>41549</v>
       </c>
@@ -48661,7 +48715,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <v>41556</v>
       </c>
@@ -48702,7 +48756,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="5">
         <v>41563</v>
       </c>
@@ -48743,7 +48797,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <v>41570</v>
       </c>
@@ -48784,7 +48838,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <v>41577</v>
       </c>
@@ -48825,7 +48879,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="5">
         <v>41584</v>
       </c>
@@ -48866,7 +48920,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="5">
         <v>41591</v>
       </c>
@@ -48907,7 +48961,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="5">
         <v>41598</v>
       </c>
@@ -48948,7 +49002,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="5">
         <v>41605</v>
       </c>
@@ -48989,7 +49043,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="5">
         <v>41612</v>
       </c>
@@ -49030,7 +49084,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <v>41619</v>
       </c>
@@ -49071,7 +49125,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="5">
         <v>41626</v>
       </c>
@@ -49112,7 +49166,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="5">
         <v>41640</v>
       </c>
@@ -49153,7 +49207,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <v>41647</v>
       </c>
@@ -49194,7 +49248,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <v>41654</v>
       </c>
@@ -49235,7 +49289,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <v>41661</v>
       </c>
@@ -49276,7 +49330,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <v>41668</v>
       </c>
@@ -49317,7 +49371,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <v>41675</v>
       </c>
@@ -49358,7 +49412,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="5">
         <v>41682</v>
       </c>
@@ -49399,7 +49453,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <v>41689</v>
       </c>
@@ -49440,7 +49494,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <v>41696</v>
       </c>
@@ -49481,7 +49535,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <v>41703</v>
       </c>
@@ -49522,7 +49576,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <v>41710</v>
       </c>
@@ -49563,7 +49617,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="5">
         <v>41717</v>
       </c>
@@ -49604,7 +49658,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="5">
         <v>41724</v>
       </c>
@@ -49645,7 +49699,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>41731</v>
       </c>
@@ -49686,7 +49740,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>41738</v>
       </c>
@@ -49727,7 +49781,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="5">
         <v>41745</v>
       </c>
@@ -49768,7 +49822,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="5">
         <v>41752</v>
       </c>
@@ -49809,7 +49863,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="5">
         <v>41759</v>
       </c>
@@ -49850,7 +49904,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="5">
         <v>41766</v>
       </c>
@@ -49891,7 +49945,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="5">
         <v>41773</v>
       </c>
@@ -49932,7 +49986,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="5">
         <v>41780</v>
       </c>
@@ -49973,7 +50027,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="5">
         <v>41787</v>
       </c>
@@ -50014,7 +50068,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="5">
         <v>41794</v>
       </c>
@@ -50055,7 +50109,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="5">
         <v>41801</v>
       </c>
@@ -50096,7 +50150,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="5">
         <v>41808</v>
       </c>
@@ -50137,7 +50191,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <v>41815</v>
       </c>
@@ -50178,7 +50232,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <v>41822</v>
       </c>
@@ -50219,7 +50273,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <v>41829</v>
       </c>
@@ -50260,7 +50314,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>41836</v>
       </c>
@@ -50301,7 +50355,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <v>41843</v>
       </c>
@@ -50342,7 +50396,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <v>41850</v>
       </c>
@@ -50383,7 +50437,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <v>41857</v>
       </c>
@@ -50424,7 +50478,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <v>41864</v>
       </c>
@@ -50465,7 +50519,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <v>41871</v>
       </c>
@@ -50506,7 +50560,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <v>41878</v>
       </c>
@@ -50547,7 +50601,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <v>41885</v>
       </c>
@@ -50588,7 +50642,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <v>41892</v>
       </c>
@@ -50629,7 +50683,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <v>41899</v>
       </c>
@@ -50670,7 +50724,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <v>41906</v>
       </c>
@@ -50711,7 +50765,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <v>41913</v>
       </c>
@@ -50752,7 +50806,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <v>41920</v>
       </c>
@@ -50793,7 +50847,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <v>41927</v>
       </c>
@@ -50834,7 +50888,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <v>41934</v>
       </c>
@@ -50875,7 +50929,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <v>41941</v>
       </c>
@@ -50916,7 +50970,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="5">
         <v>41948</v>
       </c>
@@ -50957,7 +51011,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" s="5">
         <v>41955</v>
       </c>
@@ -50998,7 +51052,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" s="5">
         <v>41962</v>
       </c>
@@ -51039,7 +51093,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" s="5">
         <v>41969</v>
       </c>
@@ -51080,7 +51134,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="5">
         <v>41976</v>
       </c>
@@ -51121,7 +51175,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>41983</v>
       </c>
@@ -51162,7 +51216,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>41990</v>
       </c>
@@ -51203,7 +51257,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" s="5">
         <v>42011</v>
       </c>
@@ -51244,7 +51298,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" s="5">
         <v>42018</v>
       </c>
@@ -51285,7 +51339,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" s="5">
         <v>42025</v>
       </c>
@@ -51326,7 +51380,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="5">
         <v>42032</v>
       </c>
@@ -51367,7 +51421,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="5">
         <v>42039</v>
       </c>
@@ -51408,7 +51462,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" s="5">
         <v>42046</v>
       </c>
@@ -51449,7 +51503,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="5">
         <v>42053</v>
       </c>
@@ -51490,7 +51544,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" s="5">
         <v>42060</v>
       </c>
@@ -51531,7 +51585,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" s="5">
         <v>42067</v>
       </c>
@@ -51572,7 +51626,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" s="5">
         <v>42074</v>
       </c>
@@ -51613,7 +51667,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" s="5">
         <v>42081</v>
       </c>
@@ -51654,7 +51708,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" s="5">
         <v>42088</v>
       </c>
@@ -51695,7 +51749,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>42095</v>
       </c>
@@ -51736,7 +51790,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" s="5">
         <v>42102</v>
       </c>
@@ -51777,7 +51831,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" s="5">
         <v>42109</v>
       </c>
@@ -51818,7 +51872,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="5">
         <v>42116</v>
       </c>
@@ -51859,7 +51913,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" s="5">
         <v>42123</v>
       </c>
@@ -51900,7 +51954,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" s="5">
         <v>42130</v>
       </c>
@@ -51941,7 +51995,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" s="5">
         <v>42137</v>
       </c>
@@ -51982,7 +52036,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>42144</v>
       </c>
@@ -52023,7 +52077,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>42151</v>
       </c>
@@ -52064,7 +52118,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" s="5">
         <v>42158</v>
       </c>
@@ -52105,7 +52159,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" s="5">
         <v>42165</v>
       </c>
@@ -52146,7 +52200,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" s="5">
         <v>42172</v>
       </c>
@@ -52187,7 +52241,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="5">
         <v>42179</v>
       </c>
@@ -52228,7 +52282,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="5">
         <v>42186</v>
       </c>
@@ -52269,7 +52323,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" s="5">
         <v>42193</v>
       </c>
@@ -52310,7 +52364,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" s="5">
         <v>42200</v>
       </c>
@@ -52351,7 +52405,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" s="5">
         <v>42207</v>
       </c>
@@ -52392,7 +52446,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" s="5">
         <v>42214</v>
       </c>
@@ -52433,7 +52487,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" s="5">
         <v>42221</v>
       </c>
@@ -52474,7 +52528,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
         <v>42228</v>
       </c>
@@ -52515,7 +52569,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" s="5">
         <v>42235</v>
       </c>
@@ -52556,7 +52610,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217" s="5">
         <v>42242</v>
       </c>
@@ -52597,7 +52651,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="5">
         <v>42249</v>
       </c>
@@ -52638,7 +52692,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" s="5">
         <v>42256</v>
       </c>
@@ -52679,7 +52733,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" s="5">
         <v>42263</v>
       </c>
@@ -52720,7 +52774,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221" s="5">
         <v>42270</v>
       </c>
@@ -52761,7 +52815,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222" s="5">
         <v>42277</v>
       </c>
@@ -52802,7 +52856,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="5">
         <v>42284</v>
       </c>
@@ -52843,7 +52897,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="5">
         <v>42291</v>
       </c>
@@ -52884,7 +52938,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="5">
         <v>42298</v>
       </c>
@@ -52925,7 +52979,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226" s="5">
         <v>42305</v>
       </c>
@@ -52966,7 +53020,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="5">
         <v>42312</v>
       </c>
@@ -53007,7 +53061,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>42319</v>
       </c>
@@ -53048,7 +53102,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" s="5">
         <v>42326</v>
       </c>
@@ -53089,7 +53143,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" s="5">
         <v>42333</v>
       </c>
@@ -53130,7 +53184,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" s="5">
         <v>42340</v>
       </c>
@@ -53171,7 +53225,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" s="5">
         <v>42347</v>
       </c>
@@ -53212,7 +53266,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="5">
         <v>42354</v>
       </c>
@@ -53253,7 +53307,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="5">
         <v>42361</v>
       </c>
@@ -53294,7 +53348,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="5">
         <v>42368</v>
       </c>
@@ -53335,7 +53389,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
         <v>42375</v>
       </c>
@@ -53376,7 +53430,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" s="5">
         <v>42382</v>
       </c>
@@ -53417,7 +53471,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" s="5">
         <v>42389</v>
       </c>
@@ -53458,7 +53512,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" s="5">
         <v>42396</v>
       </c>
@@ -53499,7 +53553,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="5">
         <v>42403</v>
       </c>
@@ -53540,7 +53594,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="5">
         <v>42410</v>
       </c>
@@ -53581,7 +53635,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="5">
         <v>42417</v>
       </c>
@@ -53622,7 +53676,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243" s="5">
         <v>42424</v>
       </c>
@@ -53663,7 +53717,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="5">
         <v>42431</v>
       </c>
@@ -53704,7 +53758,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="5">
         <v>42438</v>
       </c>
@@ -53745,7 +53799,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="5">
         <v>42445</v>
       </c>
@@ -53786,7 +53840,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247" s="5">
         <v>42452</v>
       </c>
@@ -53827,7 +53881,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248" s="5">
         <v>42459</v>
       </c>
@@ -53868,7 +53922,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249" s="5">
         <v>42466</v>
       </c>
@@ -53909,7 +53963,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250" s="5">
         <v>42473</v>
       </c>
@@ -53950,7 +54004,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251" s="5">
         <v>42480</v>
       </c>
@@ -53991,7 +54045,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252" s="5">
         <v>42487</v>
       </c>
@@ -54032,7 +54086,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="5">
         <v>42494</v>
       </c>
@@ -54073,7 +54127,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254" s="5">
         <v>42501</v>
       </c>
@@ -54114,7 +54168,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="5">
         <v>42508</v>
       </c>
@@ -54155,7 +54209,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256" s="5">
         <v>42515</v>
       </c>
@@ -54196,7 +54250,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" s="5">
         <v>42522</v>
       </c>
@@ -54237,7 +54291,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" s="5">
         <v>42529</v>
       </c>
@@ -54278,7 +54332,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="5">
         <v>42536</v>
       </c>
@@ -54319,7 +54373,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" s="5">
         <v>42543</v>
       </c>
@@ -54360,7 +54414,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" s="5">
         <v>42550</v>
       </c>
@@ -54401,7 +54455,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262" s="5">
         <v>42557</v>
       </c>
@@ -54442,7 +54496,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="5">
         <v>42564</v>
       </c>
@@ -54483,7 +54537,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" s="5">
         <v>42571</v>
       </c>
@@ -54524,7 +54578,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" s="5">
         <v>42578</v>
       </c>
@@ -54565,7 +54619,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" s="5">
         <v>42585</v>
       </c>
@@ -54606,7 +54660,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" s="5">
         <v>42592</v>
       </c>
@@ -54647,7 +54701,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" s="5">
         <v>42599</v>
       </c>
@@ -54688,7 +54742,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" s="5">
         <v>42606</v>
       </c>
@@ -54729,7 +54783,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270" s="5">
         <v>42613</v>
       </c>
@@ -54770,7 +54824,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" s="5">
         <v>42620</v>
       </c>
@@ -54811,7 +54865,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" s="5">
         <v>42627</v>
       </c>
@@ -54852,7 +54906,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="5">
         <v>42634</v>
       </c>
@@ -54893,7 +54947,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" s="5">
         <v>42641</v>
       </c>
@@ -54934,7 +54988,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A275" s="5">
         <v>42648</v>
       </c>
@@ -54975,7 +55029,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A276" s="5">
         <v>42655</v>
       </c>
@@ -55016,7 +55070,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277" s="5">
         <v>42662</v>
       </c>
@@ -55057,7 +55111,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A278" s="5">
         <v>42669</v>
       </c>
@@ -55098,7 +55152,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A279" s="5">
         <v>42676</v>
       </c>
@@ -55139,7 +55193,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280" s="5">
         <v>42683</v>
       </c>
@@ -55180,7 +55234,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A281" s="5">
         <v>42690</v>
       </c>
@@ -55221,7 +55275,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
         <v>42697</v>
       </c>
@@ -55262,7 +55316,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A283" s="5">
         <v>42704</v>
       </c>
@@ -55303,7 +55357,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
         <v>42711</v>
       </c>
@@ -55344,7 +55398,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A285" s="5">
         <v>42718</v>
       </c>
@@ -55385,7 +55439,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A286" s="5">
         <v>42725</v>
       </c>
@@ -55426,7 +55480,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A287" s="5">
         <v>42732</v>
       </c>
@@ -55467,7 +55521,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A288" s="5">
         <v>42739</v>
       </c>
@@ -55508,7 +55562,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289" s="5">
         <v>42746</v>
       </c>
@@ -55549,7 +55603,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290" s="5">
         <v>42753</v>
       </c>
@@ -55590,7 +55644,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291" s="5">
         <v>42760</v>
       </c>
@@ -55631,7 +55685,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" s="5">
         <v>42767</v>
       </c>
@@ -55672,7 +55726,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293" s="5">
         <v>42774</v>
       </c>
@@ -55713,7 +55767,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294" s="5">
         <v>42781</v>
       </c>
@@ -55754,7 +55808,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295" s="5">
         <v>42788</v>
       </c>
@@ -55795,7 +55849,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296" s="5">
         <v>42795</v>
       </c>
@@ -55836,7 +55890,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297" s="5">
         <v>42802</v>
       </c>
@@ -55877,7 +55931,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298" s="5">
         <v>42809</v>
       </c>
@@ -55918,7 +55972,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299" s="5">
         <v>42816</v>
       </c>
@@ -55959,7 +56013,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300" s="5">
         <v>42823</v>
       </c>
@@ -56000,7 +56054,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301" s="5">
         <v>42830</v>
       </c>
@@ -56041,7 +56095,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302" s="5">
         <v>42837</v>
       </c>
@@ -56082,7 +56136,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303" s="5">
         <v>42844</v>
       </c>
@@ -56123,7 +56177,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304" s="5">
         <v>42851</v>
       </c>
@@ -56164,7 +56218,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305" s="5">
         <v>42858</v>
       </c>
@@ -56205,7 +56259,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306" s="5">
         <v>42865</v>
       </c>
@@ -56246,7 +56300,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307" s="5">
         <v>42872</v>
       </c>
@@ -56287,7 +56341,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308" s="5">
         <v>42879</v>
       </c>
@@ -56328,7 +56382,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309" s="5">
         <v>42886</v>
       </c>
@@ -56369,7 +56423,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310" s="5">
         <v>42893</v>
       </c>
@@ -56410,7 +56464,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" s="5">
         <v>42900</v>
       </c>
@@ -56451,7 +56505,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312" s="5">
         <v>42907</v>
       </c>
@@ -56492,7 +56546,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313" s="5">
         <v>42914</v>
       </c>
@@ -56533,7 +56587,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314" s="5">
         <v>42921</v>
       </c>
@@ -56574,7 +56628,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315" s="5">
         <v>42928</v>
       </c>
@@ -56615,7 +56669,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316" s="5">
         <v>42935</v>
       </c>
@@ -56656,7 +56710,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317" s="5">
         <v>42942</v>
       </c>
@@ -56697,7 +56751,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318" s="5">
         <v>42949</v>
       </c>
@@ -56738,7 +56792,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319" s="5">
         <v>42956</v>
       </c>
@@ -56779,7 +56833,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320" s="5">
         <v>42963</v>
       </c>
@@ -56820,7 +56874,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321" s="5">
         <v>42970</v>
       </c>
@@ -56861,7 +56915,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" s="5">
         <v>42977</v>
       </c>
@@ -56902,7 +56956,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" s="5">
         <v>42984</v>
       </c>
@@ -56943,7 +56997,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" s="5">
         <v>42991</v>
       </c>
@@ -56984,7 +57038,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325" s="5">
         <v>42998</v>
       </c>
@@ -57025,7 +57079,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A326" s="5">
         <v>43005</v>
       </c>
@@ -57066,7 +57120,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
         <v>43012</v>
       </c>
@@ -57107,7 +57161,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A328" s="5">
         <v>43019</v>
       </c>
@@ -57148,7 +57202,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" s="5">
         <v>43026</v>
       </c>
@@ -57189,7 +57243,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330" s="5">
         <v>43033</v>
       </c>
@@ -57230,7 +57284,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331" s="5">
         <v>43040</v>
       </c>
@@ -57271,7 +57325,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332" s="5">
         <v>43047</v>
       </c>
@@ -57312,7 +57366,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333" s="5">
         <v>43054</v>
       </c>
@@ -57353,7 +57407,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" s="5">
         <v>43061</v>
       </c>
@@ -57394,7 +57448,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" s="5">
         <v>43068</v>
       </c>
@@ -57435,7 +57489,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" s="5">
         <v>43075</v>
       </c>
@@ -57476,7 +57530,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337" s="5">
         <v>43082</v>
       </c>
@@ -57517,7 +57571,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" s="5">
         <v>43089</v>
       </c>
@@ -57558,7 +57612,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339" s="5">
         <v>43096</v>
       </c>
@@ -57599,7 +57653,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" s="5">
         <v>43103</v>
       </c>
@@ -57640,7 +57694,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341" s="5">
         <v>43110</v>
       </c>
@@ -57681,7 +57735,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342" s="5">
         <v>43117</v>
       </c>
@@ -57722,7 +57776,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="5">
         <v>43124</v>
       </c>
@@ -57763,7 +57817,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344" s="5">
         <v>43131</v>
       </c>
@@ -57804,7 +57858,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345" s="5">
         <v>43138</v>
       </c>
@@ -57845,7 +57899,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346" s="5">
         <v>43145</v>
       </c>
@@ -57886,7 +57940,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347" s="5">
         <v>43152</v>
       </c>
@@ -57927,7 +57981,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348" s="5">
         <v>43159</v>
       </c>
@@ -57968,7 +58022,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" s="5">
         <v>43166</v>
       </c>
@@ -58009,7 +58063,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350" s="5">
         <v>43173</v>
       </c>
@@ -58050,7 +58104,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" s="5">
         <v>43180</v>
       </c>
@@ -58091,7 +58145,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="5">
         <v>43187</v>
       </c>
@@ -58132,7 +58186,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="5">
         <v>43194</v>
       </c>
@@ -58173,7 +58227,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="5">
         <v>43201</v>
       </c>
@@ -58214,7 +58268,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="5">
         <v>43208</v>
       </c>
@@ -58255,7 +58309,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="5">
         <v>43215</v>
       </c>
@@ -58296,7 +58350,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="5">
         <v>43222</v>
       </c>
@@ -58337,7 +58391,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="5">
         <v>43229</v>
       </c>
@@ -58378,7 +58432,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="5">
         <v>43236</v>
       </c>
@@ -58419,7 +58473,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" s="5">
         <v>43243</v>
       </c>
@@ -58460,7 +58514,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" s="5">
         <v>43250</v>
       </c>
@@ -58501,7 +58555,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" s="5">
         <v>43257</v>
       </c>
@@ -58542,7 +58596,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" s="5">
         <v>43264</v>
       </c>
@@ -58583,7 +58637,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364" s="5">
         <v>43271</v>
       </c>
@@ -58624,7 +58678,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365" s="5">
         <v>43278</v>
       </c>
@@ -58665,7 +58719,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" s="5">
         <v>43285</v>
       </c>
@@ -58706,7 +58760,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" s="5">
         <v>43292</v>
       </c>
@@ -58747,7 +58801,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" s="5">
         <v>43299</v>
       </c>
@@ -58788,7 +58842,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A369" s="5">
         <v>43306</v>
       </c>
@@ -58829,7 +58883,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370" s="5">
         <v>43313</v>
       </c>
@@ -58870,7 +58924,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A371" s="5">
         <v>43320</v>
       </c>
@@ -58911,7 +58965,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A372" s="5">
         <v>43327</v>
       </c>
@@ -58952,7 +59006,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A373" s="5">
         <v>43334</v>
       </c>
@@ -58993,7 +59047,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A374" s="5">
         <v>43341</v>
       </c>
@@ -59034,7 +59088,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="5">
         <v>43348</v>
       </c>
@@ -59075,7 +59129,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="5">
         <v>43355</v>
       </c>
@@ -59116,7 +59170,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="5">
         <v>43362</v>
       </c>
@@ -59157,7 +59211,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="5">
         <v>43369</v>
       </c>
@@ -59198,7 +59252,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="5">
         <v>43376</v>
       </c>
@@ -59239,7 +59293,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="5">
         <v>43383</v>
       </c>
@@ -59280,7 +59334,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A381" s="5">
         <v>43390</v>
       </c>
@@ -59321,7 +59375,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A382" s="5">
         <v>43397</v>
       </c>
@@ -59362,7 +59416,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A383" s="5">
         <v>43404</v>
       </c>
@@ -59403,7 +59457,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A384" s="5">
         <v>43411</v>
       </c>
@@ -59444,7 +59498,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="5">
         <v>43418</v>
       </c>
@@ -59485,7 +59539,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="5">
         <v>43425</v>
       </c>
@@ -59526,7 +59580,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387" s="5">
         <v>43432</v>
       </c>
@@ -59567,7 +59621,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="5">
         <v>43439</v>
       </c>
@@ -59608,7 +59662,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389" s="5">
         <v>43446</v>
       </c>
@@ -59649,7 +59703,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390" s="5">
         <v>43453</v>
       </c>
@@ -59690,7 +59744,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A391" s="5">
         <v>43460</v>
       </c>
@@ -59731,7 +59785,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="5">
         <v>43467</v>
       </c>
@@ -59772,7 +59826,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="5">
         <v>43474</v>
       </c>
@@ -59813,7 +59867,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="5">
         <v>43481</v>
       </c>
@@ -59854,7 +59908,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="5">
         <v>43488</v>
       </c>
@@ -59895,7 +59949,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="5">
         <v>43495</v>
       </c>
@@ -59936,7 +59990,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="5">
         <v>43502</v>
       </c>
@@ -59977,7 +60031,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="5">
         <v>43509</v>
       </c>
@@ -60018,7 +60072,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="5">
         <v>43516</v>
       </c>
@@ -60059,7 +60113,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="5">
         <v>43523</v>
       </c>
@@ -60100,7 +60154,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="5">
         <v>43530</v>
       </c>
@@ -60141,7 +60195,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="5">
         <v>43537</v>
       </c>
@@ -60182,7 +60236,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="5">
         <v>43544</v>
       </c>
@@ -60223,7 +60277,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="5">
         <v>43551</v>
       </c>
@@ -60264,7 +60318,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="5">
         <v>43558</v>
       </c>
@@ -60305,7 +60359,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="5">
         <v>43565</v>
       </c>
@@ -60346,7 +60400,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A407" s="5">
         <v>43572</v>
       </c>
@@ -60387,7 +60441,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408" s="5">
         <v>43579</v>
       </c>
@@ -60428,7 +60482,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409" s="5">
         <v>43586</v>
       </c>
@@ -60469,7 +60523,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" s="5">
         <v>43593</v>
       </c>
@@ -60510,7 +60564,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="5">
         <v>43600</v>
       </c>
@@ -60551,7 +60605,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="5">
         <v>43607</v>
       </c>
@@ -60592,7 +60646,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="5">
         <v>43614</v>
       </c>
@@ -60633,7 +60687,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="5">
         <v>43621</v>
       </c>
@@ -60674,7 +60728,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A415" s="5">
         <v>43628</v>
       </c>
@@ -60715,7 +60769,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A416" s="5">
         <v>43635</v>
       </c>
@@ -60756,7 +60810,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A417" s="5">
         <v>43642</v>
       </c>
@@ -60797,7 +60851,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" s="5">
         <v>43649</v>
       </c>
@@ -60838,7 +60892,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419" s="5">
         <v>43656</v>
       </c>
@@ -60879,7 +60933,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420" s="5">
         <v>43663</v>
       </c>
@@ -60920,7 +60974,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" s="5">
         <v>43670</v>
       </c>
@@ -60961,7 +61015,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" s="5">
         <v>43677</v>
       </c>
@@ -61002,7 +61056,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423" s="5">
         <v>43684</v>
       </c>
@@ -61043,7 +61097,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424" s="5">
         <v>43691</v>
       </c>
@@ -61084,7 +61138,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425" s="5">
         <v>43698</v>
       </c>
@@ -61125,7 +61179,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426" s="5">
         <v>43705</v>
       </c>
@@ -61166,7 +61220,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" s="5">
         <v>43712</v>
       </c>
@@ -61207,7 +61261,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" s="5">
         <v>43719</v>
       </c>
@@ -61248,7 +61302,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429" s="5">
         <v>43726</v>
       </c>
@@ -61289,7 +61343,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430" s="5">
         <v>43733</v>
       </c>
@@ -61330,7 +61384,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A431" s="5">
         <v>43740</v>
       </c>
@@ -61371,7 +61425,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A432" s="5">
         <v>43747</v>
       </c>
@@ -61412,7 +61466,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A433" s="5">
         <v>43754</v>
       </c>
@@ -61453,7 +61507,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A434" s="5">
         <v>43761</v>
       </c>
@@ -61494,7 +61548,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A435" s="5">
         <v>43768</v>
       </c>
@@ -61535,7 +61589,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436" s="5">
         <v>43775</v>
       </c>
@@ -61576,7 +61630,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A437" s="5">
         <v>43782</v>
       </c>
@@ -61617,7 +61671,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="5">
         <v>43789</v>
       </c>
@@ -61658,7 +61712,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="5">
         <v>43796</v>
       </c>
@@ -61699,7 +61753,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A440" s="5">
         <v>43803</v>
       </c>
@@ -61740,7 +61794,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A441" s="5">
         <v>43810</v>
       </c>
@@ -61781,7 +61835,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A442" s="5">
         <v>43817</v>
       </c>
@@ -61822,7 +61876,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A443" s="5">
         <v>43831</v>
       </c>
@@ -61863,7 +61917,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A444" s="5">
         <v>43838</v>
       </c>
@@ -61904,7 +61958,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="5">
         <v>43845</v>
       </c>
@@ -61945,7 +61999,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="5">
         <v>43852</v>
       </c>
@@ -61986,7 +62040,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="5">
         <v>43859</v>
       </c>
@@ -62027,7 +62081,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A448" s="5">
         <v>43866</v>
       </c>
@@ -62068,7 +62122,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A449" s="5">
         <v>43873</v>
       </c>
@@ -62109,7 +62163,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A450" s="5">
         <v>43880</v>
       </c>
@@ -62150,7 +62204,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A451" s="5">
         <v>43887</v>
       </c>
@@ -62191,7 +62245,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="5">
         <v>43894</v>
       </c>
@@ -62232,7 +62286,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453" s="5">
         <v>43901</v>
       </c>
@@ -62273,7 +62327,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A454" s="5">
         <v>43908</v>
       </c>
@@ -62314,7 +62368,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A455" s="5">
         <v>43915</v>
       </c>
@@ -62355,7 +62409,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456" s="5">
         <v>43922</v>
       </c>
@@ -62396,7 +62450,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457" s="5">
         <v>43929</v>
       </c>
@@ -62437,7 +62491,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458" s="5">
         <v>43936</v>
       </c>
@@ -62478,7 +62532,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459" s="5">
         <v>43943</v>
       </c>
@@ -62519,7 +62573,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460" s="5">
         <v>43950</v>
       </c>
@@ -62560,7 +62614,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461" s="5">
         <v>43957</v>
       </c>
@@ -62601,7 +62655,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462" s="5">
         <v>43964</v>
       </c>
@@ -62642,7 +62696,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463" s="5">
         <v>43971</v>
       </c>
@@ -62683,7 +62737,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464" s="5">
         <v>43978</v>
       </c>
@@ -62724,7 +62778,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A465" s="5">
         <v>43985</v>
       </c>
@@ -62765,7 +62819,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A466" s="5">
         <v>43992</v>
       </c>
@@ -62806,7 +62860,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A467" s="5">
         <v>43999</v>
       </c>
@@ -62847,7 +62901,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A468" s="5">
         <v>44006</v>
       </c>
@@ -62888,7 +62942,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A469" s="5">
         <v>44013</v>
       </c>
@@ -62929,7 +62983,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A470" s="5">
         <v>44020</v>
       </c>
@@ -62970,7 +63024,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A471" s="5">
         <v>44027</v>
       </c>
@@ -63011,7 +63065,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="5">
         <v>44034</v>
       </c>
@@ -63052,7 +63106,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A473" s="5">
         <v>44041</v>
       </c>
@@ -63093,7 +63147,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="5">
         <v>44048</v>
       </c>
@@ -63134,7 +63188,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A475" s="5">
         <v>44055</v>
       </c>
@@ -63175,7 +63229,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="5">
         <v>44062</v>
       </c>
@@ -63216,7 +63270,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A477" s="5">
         <v>44069</v>
       </c>
@@ -63257,7 +63311,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A478" s="5">
         <v>44076</v>
       </c>
@@ -63298,7 +63352,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A479" s="5">
         <v>44083</v>
       </c>
@@ -63339,7 +63393,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A480" s="5">
         <v>44090</v>
       </c>
@@ -63380,7 +63434,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A481" s="5">
         <v>44097</v>
       </c>
@@ -63421,7 +63475,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A482" s="5">
         <v>44104</v>
       </c>
@@ -63462,7 +63516,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="5">
         <v>44111</v>
       </c>
@@ -63503,7 +63557,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A484" s="5">
         <v>44118</v>
       </c>
@@ -63544,7 +63598,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A485" s="5">
         <v>44125</v>
       </c>
@@ -63585,7 +63639,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="5">
         <v>44132</v>
       </c>
@@ -63626,7 +63680,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A487" s="5">
         <v>44139</v>
       </c>
@@ -63667,7 +63721,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A488" s="5">
         <v>44146</v>
       </c>
@@ -63708,7 +63762,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A489" s="5">
         <v>44153</v>
       </c>
@@ -63749,7 +63803,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A490" s="5">
         <v>44160</v>
       </c>
@@ -63790,7 +63844,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="5">
         <v>44167</v>
       </c>
@@ -63831,7 +63885,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A492" s="5">
         <v>44174</v>
       </c>
@@ -63872,7 +63926,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A493" s="5">
         <v>44181</v>
       </c>
@@ -63913,7 +63967,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A494" s="5">
         <v>44188</v>
       </c>
@@ -63954,7 +64008,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A495" s="5">
         <v>44195</v>
       </c>
@@ -63995,7 +64049,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A496" s="5">
         <v>44202</v>
       </c>
@@ -64036,7 +64090,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A497" s="5">
         <v>44209</v>
       </c>
@@ -64077,7 +64131,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A498" s="5">
         <v>44216</v>
       </c>
@@ -64118,7 +64172,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A499" s="5">
         <v>44223</v>
       </c>
@@ -64159,7 +64213,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A500" s="5">
         <v>44230</v>
       </c>
@@ -64200,7 +64254,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A501" s="5">
         <v>44237</v>
       </c>
@@ -64241,7 +64295,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A502" s="5">
         <v>44244</v>
       </c>
@@ -64282,7 +64336,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A503" s="5">
         <v>44251</v>
       </c>
@@ -64323,7 +64377,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A504" s="5">
         <v>44258</v>
       </c>
@@ -64364,7 +64418,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A505" s="5">
         <v>44265</v>
       </c>
@@ -64405,7 +64459,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A506" s="5">
         <v>44272</v>
       </c>
@@ -64446,7 +64500,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A507" s="5">
         <v>44279</v>
       </c>
@@ -64487,7 +64541,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="5">
         <v>44286</v>
       </c>
@@ -64528,7 +64582,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="5">
         <v>44293</v>
       </c>
@@ -64569,7 +64623,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A510" s="5">
         <v>44300</v>
       </c>
@@ -64610,7 +64664,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A511" s="5">
         <v>44307</v>
       </c>
@@ -64651,7 +64705,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A512" s="5">
         <v>44314</v>
       </c>
@@ -64692,7 +64746,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A513" s="5">
         <v>44321</v>
       </c>
@@ -64733,7 +64787,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A514" s="5">
         <v>44328</v>
       </c>
@@ -64774,7 +64828,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A515" s="5">
         <v>44335</v>
       </c>
@@ -64815,7 +64869,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A516" s="5">
         <v>44342</v>
       </c>
@@ -64856,7 +64910,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A517" s="5">
         <v>44349</v>
       </c>
@@ -64897,7 +64951,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A518" s="5">
         <v>44356</v>
       </c>
@@ -64938,7 +64992,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A519" s="5">
         <v>44363</v>
       </c>
@@ -64979,7 +65033,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A520" s="5">
         <v>44370</v>
       </c>
@@ -65020,7 +65074,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A521" s="5">
         <v>44377</v>
       </c>
@@ -65061,7 +65115,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A522" s="5">
         <v>44384</v>
       </c>
@@ -65102,7 +65156,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A523" s="5">
         <v>44391</v>
       </c>
@@ -65143,7 +65197,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A524" s="5">
         <v>44398</v>
       </c>
@@ -65184,7 +65238,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A525" s="5">
         <v>44405</v>
       </c>
@@ -65225,7 +65279,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A526" s="5">
         <v>44412</v>
       </c>
@@ -65266,7 +65320,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A527" s="5">
         <v>44419</v>
       </c>
@@ -65307,7 +65361,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A528" s="5">
         <v>44426</v>
       </c>
@@ -65348,7 +65402,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A529" s="5">
         <v>44433</v>
       </c>
@@ -65389,7 +65443,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A530" s="5">
         <v>44440</v>
       </c>
@@ -65430,7 +65484,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A531" s="5">
         <v>44447</v>
       </c>
@@ -65471,7 +65525,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A532" s="5">
         <v>44454</v>
       </c>
@@ -65512,7 +65566,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A533" s="5">
         <v>44461</v>
       </c>
@@ -65553,7 +65607,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A534" s="5">
         <v>44468</v>
       </c>
@@ -65594,7 +65648,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A535" s="5">
         <v>44475</v>
       </c>
@@ -65635,7 +65689,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A536" s="5">
         <v>44482</v>
       </c>
@@ -65676,7 +65730,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A537" s="5">
         <v>44489</v>
       </c>
@@ -65717,7 +65771,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A538" s="5">
         <v>44496</v>
       </c>
@@ -65758,7 +65812,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A539" s="5">
         <v>44503</v>
       </c>
@@ -65799,7 +65853,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A540" s="5">
         <v>44510</v>
       </c>
@@ -65840,7 +65894,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" s="5">
         <v>44517</v>
       </c>
@@ -65881,7 +65935,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A542" s="5">
         <v>44524</v>
       </c>
@@ -65922,7 +65976,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A543" s="5">
         <v>44531</v>
       </c>
@@ -65963,7 +66017,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A544" s="5">
         <v>44538</v>
       </c>
@@ -66004,7 +66058,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" s="5">
         <v>44545</v>
       </c>
@@ -66045,7 +66099,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" s="5">
         <v>44552</v>
       </c>
@@ -66086,7 +66140,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" s="5">
         <v>44566</v>
       </c>
@@ -66127,7 +66181,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" s="5">
         <v>44573</v>
       </c>
@@ -66168,7 +66222,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" s="5">
         <v>44580</v>
       </c>
@@ -66209,7 +66263,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" s="5">
         <v>44587</v>
       </c>
@@ -66250,7 +66304,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" s="5">
         <v>44594</v>
       </c>
@@ -66291,7 +66345,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A552" s="5">
         <v>44601</v>
       </c>
@@ -66332,7 +66386,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A553" s="5">
         <v>44608</v>
       </c>
@@ -66373,7 +66427,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A554" s="5">
         <v>44615</v>
       </c>
@@ -66414,7 +66468,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A555" s="5">
         <v>44622</v>
       </c>
@@ -66455,7 +66509,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A556" s="5">
         <v>44629</v>
       </c>
@@ -66496,7 +66550,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A557" s="5">
         <v>44636</v>
       </c>
@@ -66537,7 +66591,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A558" s="5">
         <v>44643</v>
       </c>
@@ -66578,7 +66632,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A559" s="5">
         <v>44650</v>
       </c>
@@ -66619,7 +66673,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A560" s="5">
         <v>44657</v>
       </c>
@@ -66660,7 +66714,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A561" s="5">
         <v>44664</v>
       </c>
@@ -66701,7 +66755,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A562" s="5">
         <v>44671</v>
       </c>
@@ -66742,7 +66796,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A563" s="5">
         <v>44678</v>
       </c>
@@ -66783,7 +66837,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A564" s="5">
         <v>44685</v>
       </c>
@@ -66824,7 +66878,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A565" s="5">
         <v>44692</v>
       </c>
@@ -66865,7 +66919,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A566" s="5">
         <v>44699</v>
       </c>
@@ -66906,7 +66960,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A567" s="5">
         <v>44706</v>
       </c>
@@ -66947,7 +67001,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A568" s="5">
         <v>44713</v>
       </c>
@@ -66988,7 +67042,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A569" s="5">
         <v>44720</v>
       </c>
@@ -67029,7 +67083,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A570" s="5">
         <v>44727</v>
       </c>
@@ -67070,7 +67124,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A571" s="5">
         <v>44734</v>
       </c>
@@ -67111,7 +67165,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A572" s="5">
         <v>44741</v>
       </c>
@@ -67152,7 +67206,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A573" s="5">
         <v>44748</v>
       </c>
@@ -67193,7 +67247,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A574" s="5">
         <v>44755</v>
       </c>
@@ -67234,7 +67288,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A575" s="5">
         <v>44762</v>
       </c>
@@ -67275,7 +67329,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A576" s="5">
         <v>44769</v>
       </c>
@@ -67316,7 +67370,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A577" s="5">
         <v>44776</v>
       </c>
@@ -67357,7 +67411,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A578" s="5">
         <v>44783</v>
       </c>
@@ -67398,7 +67452,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A579" s="5">
         <v>44790</v>
       </c>
@@ -67439,7 +67493,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A580" s="5">
         <v>44797</v>
       </c>
@@ -67480,7 +67534,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A581" s="5">
         <v>44804</v>
       </c>
@@ -67521,7 +67575,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A582" s="5">
         <v>44811</v>
       </c>
@@ -67562,7 +67616,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A583" s="5">
         <v>44818</v>
       </c>
@@ -67603,7 +67657,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A584" s="5">
         <v>44825</v>
       </c>
@@ -67644,7 +67698,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A585" s="5">
         <v>44832</v>
       </c>
@@ -67685,7 +67739,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A586" s="5">
         <v>44839</v>
       </c>
@@ -67726,7 +67780,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A587" s="5">
         <v>44846</v>
       </c>
@@ -67767,7 +67821,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A588" s="5">
         <v>44853</v>
       </c>
@@ -67808,7 +67862,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A589" s="5">
         <v>44860</v>
       </c>
@@ -67849,7 +67903,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A590" s="5">
         <v>44867</v>
       </c>
@@ -67890,7 +67944,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A591" s="5">
         <v>44874</v>
       </c>
@@ -67931,7 +67985,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A592" s="5">
         <v>44881</v>
       </c>
@@ -67972,7 +68026,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A593" s="5">
         <v>44888</v>
       </c>
@@ -68013,7 +68067,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A594" s="5">
         <v>44895</v>
       </c>
@@ -68054,7 +68108,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A595" s="5">
         <v>44902</v>
       </c>
@@ -68095,7 +68149,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A596" s="5">
         <v>44909</v>
       </c>
@@ -68136,7 +68190,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A597" s="5">
         <v>44916</v>
       </c>
@@ -68177,7 +68231,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A598" s="5">
         <v>44930</v>
       </c>
@@ -68218,7 +68272,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A599" s="5">
         <v>44937</v>
       </c>
@@ -68259,7 +68313,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A600" s="5">
         <v>44944</v>
       </c>
@@ -68300,7 +68354,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A601" s="5">
         <v>44951</v>
       </c>
@@ -68341,7 +68395,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A602" s="5">
         <v>44958</v>
       </c>
@@ -68382,7 +68436,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A603" s="5">
         <v>44965</v>
       </c>
@@ -68423,7 +68477,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A604" s="5">
         <v>44972</v>
       </c>
@@ -68464,7 +68518,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A605" s="5">
         <v>44979</v>
       </c>
@@ -68505,7 +68559,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A606" s="5">
         <v>44986</v>
       </c>
@@ -68546,7 +68600,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A607" s="5">
         <v>44993</v>
       </c>
@@ -68587,7 +68641,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A608" s="5">
         <v>45000</v>
       </c>
@@ -68628,7 +68682,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A609" s="5">
         <v>45007</v>
       </c>
@@ -68669,7 +68723,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A610" s="5">
         <v>45014</v>
       </c>
@@ -68710,7 +68764,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A611" s="5">
         <v>45021</v>
       </c>
@@ -68751,7 +68805,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A612" s="5">
         <v>45028</v>
       </c>
@@ -68792,7 +68846,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A613" s="5">
         <v>45035</v>
       </c>
@@ -68833,7 +68887,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A614" s="5">
         <v>45042</v>
       </c>
@@ -68874,7 +68928,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A615" s="5">
         <v>45049</v>
       </c>
@@ -68915,7 +68969,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A616" s="5">
         <v>45056</v>
       </c>
@@ -68956,7 +69010,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A617" s="5">
         <v>45063</v>
       </c>
@@ -68997,7 +69051,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A618" s="5">
         <v>45070</v>
       </c>
@@ -69038,7 +69092,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A619" s="5">
         <v>45077</v>
       </c>
@@ -69079,7 +69133,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A620" s="5">
         <v>45084</v>
       </c>
@@ -69120,7 +69174,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A621" s="5">
         <v>45091</v>
       </c>
@@ -69161,7 +69215,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A622" s="5">
         <v>45098</v>
       </c>
@@ -69202,7 +69256,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A623" s="5">
         <v>45105</v>
       </c>
@@ -69243,7 +69297,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A624" s="5">
         <v>45112</v>
       </c>
@@ -69284,7 +69338,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A625" s="5">
         <v>45119</v>
       </c>
@@ -69325,7 +69379,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A626" s="5">
         <v>45126</v>
       </c>
@@ -69366,7 +69420,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A627" s="5">
         <v>45133</v>
       </c>
@@ -69407,7 +69461,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A628" s="5">
         <v>45140</v>
       </c>
@@ -69448,7 +69502,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A629" s="5">
         <v>45147</v>
       </c>
@@ -69489,7 +69543,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="5">
         <v>45154</v>
       </c>
@@ -69530,7 +69584,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A631" s="5">
         <v>45161</v>
       </c>
@@ -69571,7 +69625,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A632" s="5">
         <v>45168</v>
       </c>
@@ -69612,7 +69666,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A633" s="5">
         <v>45175</v>
       </c>
@@ -69653,7 +69707,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A634" s="5">
         <v>45182</v>
       </c>
@@ -69694,7 +69748,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" s="5">
         <v>45189</v>
       </c>
@@ -69735,7 +69789,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A636" s="5">
         <v>45196</v>
       </c>
@@ -69776,7 +69830,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A637" s="5">
         <v>45203</v>
       </c>
@@ -69817,7 +69871,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A638" s="5">
         <v>45210</v>
       </c>
@@ -69858,7 +69912,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A639" s="5">
         <v>45217</v>
       </c>
@@ -69899,7 +69953,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" s="5">
         <v>45224</v>
       </c>
@@ -69940,7 +69994,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A641" s="5">
         <v>45231</v>
       </c>
@@ -69981,7 +70035,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A642" s="5">
         <v>45238</v>
       </c>
@@ -70022,7 +70076,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A643" s="5">
         <v>45245</v>
       </c>
@@ -70063,7 +70117,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A644" s="5">
         <v>45252</v>
       </c>
@@ -70104,7 +70158,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A645" s="5">
         <v>45259</v>
       </c>
@@ -70145,7 +70199,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" s="5">
         <v>45266</v>
       </c>
@@ -70186,7 +70240,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" s="5">
         <v>45273</v>
       </c>
@@ -70227,7 +70281,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" s="5">
         <v>45280</v>
       </c>
@@ -70268,7 +70322,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" s="5">
         <v>45294</v>
       </c>
@@ -70309,7 +70363,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" s="5">
         <v>45301</v>
       </c>
@@ -70350,7 +70404,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" s="5">
         <v>45308</v>
       </c>
@@ -70391,7 +70445,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A652" s="5">
         <v>45315</v>
       </c>
@@ -70432,7 +70486,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A653" s="5">
         <v>45322</v>
       </c>
@@ -70473,7 +70527,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A654" s="5">
         <v>45329</v>
       </c>
@@ -70514,7 +70568,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A655" s="5">
         <v>45336</v>
       </c>
@@ -70555,7 +70609,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A656" s="5">
         <v>45343</v>
       </c>
@@ -70596,7 +70650,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A657" s="5">
         <v>45350</v>
       </c>
@@ -70637,7 +70691,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A658" s="5">
         <v>45357</v>
       </c>
@@ -70678,7 +70732,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A659" s="5">
         <v>45364</v>
       </c>
@@ -70719,7 +70773,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="5">
         <v>45371</v>
       </c>
@@ -70760,7 +70814,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A661" s="5">
         <v>45378</v>
       </c>
@@ -70801,7 +70855,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A662" s="5">
         <v>45385</v>
       </c>
@@ -70842,7 +70896,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A663" s="5">
         <v>45392</v>
       </c>
@@ -70883,7 +70937,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A664" s="5">
         <v>45399</v>
       </c>
@@ -70924,7 +70978,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A665" s="5">
         <v>45406</v>
       </c>
@@ -70965,7 +71019,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A666" s="5">
         <v>45413</v>
       </c>
@@ -71006,7 +71060,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A667" s="5">
         <v>45420</v>
       </c>
@@ -71047,7 +71101,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A668" s="5">
         <v>45427</v>
       </c>
@@ -71088,7 +71142,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A669" s="5">
         <v>45434</v>
       </c>
@@ -71129,7 +71183,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A670" s="5">
         <v>45441</v>
       </c>
@@ -71170,7 +71224,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A671" s="5">
         <v>45448</v>
       </c>
@@ -71211,7 +71265,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A672" s="5">
         <v>45455</v>
       </c>
@@ -71252,7 +71306,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A673" s="5">
         <v>45462</v>
       </c>
@@ -71293,7 +71347,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A674" s="5">
         <v>45469</v>
       </c>
@@ -71334,7 +71388,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A675" s="5">
         <v>45476</v>
       </c>
@@ -71375,7 +71429,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A676" s="5">
         <v>45483</v>
       </c>
@@ -71416,7 +71470,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A677" s="5">
         <v>45490</v>
       </c>
@@ -71457,7 +71511,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A678" s="5">
         <v>45497</v>
       </c>
@@ -71498,7 +71552,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A679" s="5">
         <v>45504</v>
       </c>
@@ -71539,7 +71593,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A680" s="5">
         <v>45511</v>
       </c>
@@ -71580,7 +71634,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A681" s="5">
         <v>45518</v>
       </c>
@@ -71621,7 +71675,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A682" s="5">
         <v>45525</v>
       </c>
@@ -71662,7 +71716,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A683" s="5">
         <v>45532</v>
       </c>
@@ -71703,7 +71757,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A684" s="5">
         <v>45539</v>
       </c>
@@ -71744,7 +71798,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A685" s="5">
         <v>45546</v>
       </c>
@@ -71785,7 +71839,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A686" s="5">
         <v>45553</v>
       </c>
@@ -71826,7 +71880,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A687" s="5">
         <v>45560</v>
       </c>
@@ -71867,7 +71921,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A688" s="5">
         <v>45567</v>
       </c>
@@ -71908,7 +71962,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A689" s="5">
         <v>45574</v>
       </c>
@@ -71949,7 +72003,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A690" s="5">
         <v>45581</v>
       </c>
@@ -71990,7 +72044,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A691" s="5">
         <v>45588</v>
       </c>
@@ -72031,7 +72085,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A692" s="5">
         <v>45595</v>
       </c>
@@ -72072,7 +72126,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A693" s="5">
         <v>45602</v>
       </c>
@@ -72113,7 +72167,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A694" s="5">
         <v>45609</v>
       </c>
@@ -72154,7 +72208,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A695" s="5">
         <v>45616</v>
       </c>
@@ -72195,7 +72249,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A696" s="5">
         <v>45623</v>
       </c>
@@ -72236,7 +72290,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A697" s="5">
         <v>45630</v>
       </c>
@@ -72277,7 +72331,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="5">
         <v>45637</v>
       </c>
@@ -72318,7 +72372,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="5">
         <v>45644</v>
       </c>
@@ -72359,7 +72413,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="5">
         <v>45658</v>
       </c>
@@ -72400,7 +72454,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="5">
         <v>45665</v>
       </c>
@@ -72441,7 +72495,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="5">
         <v>45672</v>
       </c>
@@ -72482,7 +72536,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="5">
         <v>45679</v>
       </c>
@@ -72523,7 +72577,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="5">
         <v>45686</v>
       </c>
@@ -72564,7 +72618,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="5">
         <v>45693</v>
       </c>
@@ -72605,7 +72659,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="5">
         <v>45700</v>
       </c>
@@ -72646,7 +72700,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="5">
         <v>45707</v>
       </c>
@@ -72687,7 +72741,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="5">
         <v>45714</v>
       </c>
@@ -72728,7 +72782,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="5">
         <v>45721</v>
       </c>
@@ -72769,7 +72823,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="5">
         <v>45728</v>
       </c>
@@ -72810,7 +72864,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="5">
         <v>45735</v>
       </c>
@@ -72851,7 +72905,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="5">
         <v>45742</v>
       </c>
@@ -72892,7 +72946,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="5">
         <v>45749</v>
       </c>
@@ -72933,7 +72987,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A714" s="5">
         <v>45756</v>
       </c>
@@ -72974,7 +73028,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A715" s="5">
         <v>45763</v>
       </c>
@@ -73015,7 +73069,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A716" s="5">
         <v>45770</v>
       </c>
@@ -73056,7 +73110,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A717" s="5">
         <v>45777</v>
       </c>
@@ -73097,7 +73151,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A718" s="5">
         <v>45784</v>
       </c>
@@ -73138,7 +73192,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A719" s="5">
         <v>45791</v>
       </c>
@@ -73179,7 +73233,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A720" s="5">
         <v>45798</v>
       </c>
@@ -73220,7 +73274,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A721" s="5">
         <v>45805</v>
       </c>
@@ -73261,7 +73315,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A722" s="5">
         <v>45812</v>
       </c>
@@ -73302,7 +73356,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A723" s="5">
         <v>45819</v>
       </c>
@@ -73343,7 +73397,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A724" s="5">
         <v>45826</v>
       </c>
@@ -73384,7 +73438,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A725" s="5">
         <v>45833</v>
       </c>
@@ -73425,7 +73479,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A726" s="5">
         <v>45840</v>
       </c>
@@ -73466,7 +73520,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A727" s="5">
         <v>45847</v>
       </c>
@@ -73507,7 +73561,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A728" s="5">
         <v>45854</v>
       </c>
@@ -73548,7 +73602,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A729" s="5">
         <v>45861</v>
       </c>
@@ -73589,7 +73643,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A730" s="5">
         <v>45868</v>
       </c>
@@ -73630,7 +73684,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A731" s="5">
         <v>45875</v>
       </c>
@@ -73671,7 +73725,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A732" s="5">
         <v>45882</v>
       </c>
@@ -73712,7 +73766,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A733" s="5">
         <v>45889</v>
       </c>
@@ -73753,7 +73807,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A734" s="5">
         <v>45896</v>
       </c>
@@ -73794,7 +73848,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A735" s="5">
         <v>45903</v>
       </c>
@@ -73835,7 +73889,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A736" s="5">
         <v>45910</v>
       </c>
@@ -73876,7 +73930,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A737" s="5">
         <v>45917</v>
       </c>
@@ -73917,7 +73971,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A738" s="5">
         <v>45924</v>
       </c>
@@ -73958,7 +74012,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A739" s="5">
         <v>45931</v>
       </c>
@@ -73999,7 +74053,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A740" s="5">
         <v>45938</v>
       </c>
@@ -74040,7 +74094,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A741" s="5">
         <v>45945</v>
       </c>
@@ -74081,7 +74135,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A742" s="5">
         <v>45952</v>
       </c>
@@ -74122,7 +74176,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A743" s="5">
         <v>45959</v>
       </c>
@@ -74163,7 +74217,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A744" s="5">
         <v>45966</v>
       </c>
@@ -74204,7 +74258,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A745" s="5">
         <v>45973</v>
       </c>
@@ -74245,7 +74299,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A746" s="5">
         <v>45980</v>
       </c>
@@ -74286,7 +74340,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A747" s="5">
         <v>45987</v>
       </c>
@@ -74327,7 +74381,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A748" s="5">
         <v>45994</v>
       </c>
@@ -74368,7 +74422,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A749" s="5">
         <v>46001</v>
       </c>
@@ -74409,7 +74463,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A750" s="5">
         <v>46008</v>
       </c>
@@ -74450,7 +74504,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A751" s="5">
         <v>46015</v>
       </c>
@@ -74491,7 +74545,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A752" s="5">
         <v>46022</v>
       </c>
@@ -74532,7 +74586,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A753" s="5">
         <v>46029</v>
       </c>
@@ -74573,7 +74627,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A754" s="5">
         <v>46036</v>
       </c>
@@ -74614,7 +74668,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A755" s="5">
         <v>46043</v>
       </c>
@@ -74655,7 +74709,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A756" s="5">
         <v>46050</v>
       </c>
@@ -74696,7 +74750,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A757" s="5">
         <v>46057</v>
       </c>
@@ -74737,7 +74791,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A758" s="5">
         <v>46064</v>
       </c>
@@ -74778,7 +74832,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A759" s="5">
         <v>46071</v>
       </c>
@@ -74819,7 +74873,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A760" s="5">
         <v>46078</v>
       </c>
@@ -74860,7 +74914,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A761" s="5">
         <v>46085</v>
       </c>
@@ -74901,7 +74955,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A762" s="5">
         <v>46092</v>
       </c>
@@ -74942,7 +74996,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A763" s="5">
         <v>46099</v>
       </c>
@@ -74983,7 +75037,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A764" s="5">
         <v>46106</v>
       </c>
@@ -75024,7 +75078,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A765" s="5">
         <v>46113</v>
       </c>
@@ -75065,7 +75119,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A766" s="5">
         <v>46120</v>
       </c>
@@ -75106,7 +75160,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A767" s="5">
         <v>46127</v>
       </c>
@@ -75147,7 +75201,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13">
+    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A768" s="5">
         <v>46134</v>
       </c>
@@ -75188,7 +75242,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13">
+    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A769" s="5">
         <v>46141</v>
       </c>
@@ -75229,7 +75283,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13">
+    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A770" s="5">
         <v>46148</v>
       </c>
@@ -75270,7 +75324,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13">
+    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A771" s="5">
         <v>46155</v>
       </c>
@@ -75311,7 +75365,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13">
+    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A772" s="5">
         <v>46162</v>
       </c>
@@ -75352,7 +75406,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13">
+    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A773" s="5">
         <v>46169</v>
       </c>
@@ -75393,7 +75447,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13">
+    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A774" s="5">
         <v>46176</v>
       </c>
@@ -75434,7 +75488,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13">
+    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A775" s="5">
         <v>46183</v>
       </c>
@@ -75475,7 +75529,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13">
+    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A776" s="5">
         <v>46190</v>
       </c>
@@ -75516,7 +75570,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="777" spans="1:13">
+    <row r="777" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A777" s="5">
         <v>46197</v>
       </c>
@@ -75530,7 +75584,7 @@
         <v>15</v>
       </c>
       <c r="E777" s="7">
-        <v>4166</v>
+        <v>4165.57</v>
       </c>
       <c r="F777" s="8">
         <v>4392</v>
@@ -75555,6 +75609,47 @@
       </c>
       <c r="M777" s="8">
         <v>2584</v>
+      </c>
+    </row>
+    <row r="778" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A778" s="5">
+        <v>46204</v>
+      </c>
+      <c r="B778" s="5">
+        <v>46205</v>
+      </c>
+      <c r="C778" s="6">
+        <v>0.58333333333676496</v>
+      </c>
+      <c r="D778" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E778" s="7">
+        <v>4530.42</v>
+      </c>
+      <c r="F778" s="8">
+        <v>4682</v>
+      </c>
+      <c r="G778" s="8">
+        <v>6360</v>
+      </c>
+      <c r="H778" s="8">
+        <v>6349</v>
+      </c>
+      <c r="I778" s="8">
+        <v>7902</v>
+      </c>
+      <c r="J778" s="8">
+        <v>647</v>
+      </c>
+      <c r="K778" s="8">
+        <v>828</v>
+      </c>
+      <c r="L778" s="8">
+        <v>1015</v>
+      </c>
+      <c r="M778" s="8">
+        <v>2602</v>
       </c>
     </row>
   </sheetData>
@@ -75567,7 +75662,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75578,12 +75673,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
@@ -75602,7 +75697,7 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="2:14">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="9" t="s">
         <v>10</v>
       </c>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A61BC4-6E32-4558-9C94-AD81B46E3991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78C7F48-DB6B-465D-9231-8F0BE61F8621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -2621,6 +2621,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4960,6 +4963,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>4530.42</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>4638.59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7335,6 +7341,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9674,6 +9683,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>4682</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>4933</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12049,6 +12061,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14388,6 +14403,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>6360</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>6463</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16763,6 +16781,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19102,6 +19123,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>6349</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>6482</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21477,6 +21501,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23816,6 +23843,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>7902</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>7904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26191,6 +26221,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28530,6 +28563,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>647</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>612</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30907,6 +30943,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33246,6 +33285,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>828</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>825</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35623,6 +35665,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -37962,6 +38007,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>1015</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>1022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40339,6 +40387,9 @@
                 <c:pt idx="776">
                   <c:v>46205</c:v>
                 </c:pt>
+                <c:pt idx="777">
+                  <c:v>46212</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42678,6 +42729,9 @@
                 </c:pt>
                 <c:pt idx="776">
                   <c:v>2602</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>2723</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43755,7 +43809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M778"/>
+  <dimension ref="A1:M779"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
@@ -75663,6 +75717,47 @@
       </c>
       <c r="M778" s="11">
         <v>2602</v>
+      </c>
+    </row>
+    <row r="779" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A779" s="8">
+        <v>46211</v>
+      </c>
+      <c r="B779" s="8">
+        <v>46212</v>
+      </c>
+      <c r="C779" s="9">
+        <v>0.583333333338105</v>
+      </c>
+      <c r="D779" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E779" s="10">
+        <v>4638.59</v>
+      </c>
+      <c r="F779" s="11">
+        <v>4933</v>
+      </c>
+      <c r="G779" s="11">
+        <v>6463</v>
+      </c>
+      <c r="H779" s="11">
+        <v>6482</v>
+      </c>
+      <c r="I779" s="11">
+        <v>7904</v>
+      </c>
+      <c r="J779" s="11">
+        <v>612</v>
+      </c>
+      <c r="K779" s="11">
+        <v>825</v>
+      </c>
+      <c r="L779" s="11">
+        <v>1022</v>
+      </c>
+      <c r="M779" s="11">
+        <v>2723</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78C7F48-DB6B-465D-9231-8F0BE61F8621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70403B94-C581-574D-A99F-E166A860129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25480" yWindow="600" windowWidth="25720" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -107,29 +107,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,7 +138,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,7 +146,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -195,35 +195,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -241,7 +241,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2624,6 +2624,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4966,6 +4969,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>4638.59</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>4546.6400000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7344,6 +7350,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9686,6 +9695,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>4933</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>4873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12064,6 +12076,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14406,6 +14421,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>6463</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>6300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16784,6 +16802,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19126,6 +19147,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>6482</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>6272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21504,6 +21528,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23846,6 +23873,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>7904</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>7879</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26224,6 +26254,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28566,6 +28599,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>612</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>605</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30946,6 +30982,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33287,6 +33326,9 @@
                   <c:v>828</c:v>
                 </c:pt>
                 <c:pt idx="777">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="778">
                   <c:v>825</c:v>
                 </c:pt>
               </c:numCache>
@@ -35668,6 +35710,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -38010,6 +38055,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>1022</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>1037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40390,6 +40438,9 @@
                 <c:pt idx="777">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="778">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42732,6 +42783,9 @@
                 </c:pt>
                 <c:pt idx="777">
                   <c:v>2723</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>2667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43809,19 +43863,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M779"/>
-  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M780"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="10.5" style="11" customWidth="1"/>
     <col min="14" max="16384" width="7.5" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -43862,7 +43916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>40716</v>
       </c>
@@ -43903,7 +43957,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>40723</v>
       </c>
@@ -43944,7 +43998,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>40730</v>
       </c>
@@ -43985,7 +44039,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>40737</v>
       </c>
@@ -44026,7 +44080,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>40744</v>
       </c>
@@ -44067,7 +44121,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>40751</v>
       </c>
@@ -44108,7 +44162,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>40758</v>
       </c>
@@ -44149,7 +44203,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>40765</v>
       </c>
@@ -44190,7 +44244,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>40772</v>
       </c>
@@ -44231,7 +44285,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>40779</v>
       </c>
@@ -44272,7 +44326,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>40786</v>
       </c>
@@ -44313,7 +44367,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>40793</v>
       </c>
@@ -44354,7 +44408,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>40800</v>
       </c>
@@ -44395,7 +44449,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>40807</v>
       </c>
@@ -44436,7 +44490,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>40814</v>
       </c>
@@ -44477,7 +44531,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>40821</v>
       </c>
@@ -44518,7 +44572,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>40828</v>
       </c>
@@ -44559,7 +44613,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>40835</v>
       </c>
@@ -44600,7 +44654,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>40842</v>
       </c>
@@ -44641,7 +44695,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>40849</v>
       </c>
@@ -44682,7 +44736,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>40856</v>
       </c>
@@ -44723,7 +44777,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>40863</v>
       </c>
@@ -44764,7 +44818,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>40870</v>
       </c>
@@ -44805,7 +44859,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>40877</v>
       </c>
@@ -44846,7 +44900,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>40884</v>
       </c>
@@ -44887,7 +44941,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>40891</v>
       </c>
@@ -44928,7 +44982,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>40898</v>
       </c>
@@ -44969,7 +45023,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>40905</v>
       </c>
@@ -45010,7 +45064,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>40912</v>
       </c>
@@ -45051,7 +45105,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>40919</v>
       </c>
@@ -45092,7 +45146,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>40926</v>
       </c>
@@ -45133,7 +45187,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>40933</v>
       </c>
@@ -45174,7 +45228,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>40940</v>
       </c>
@@ -45215,7 +45269,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>40947</v>
       </c>
@@ -45256,7 +45310,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>40954</v>
       </c>
@@ -45297,7 +45351,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>40961</v>
       </c>
@@ -45338,7 +45392,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>40968</v>
       </c>
@@ -45379,7 +45433,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>40975</v>
       </c>
@@ -45420,7 +45474,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>40982</v>
       </c>
@@ -45461,7 +45515,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>40989</v>
       </c>
@@ -45502,7 +45556,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>40996</v>
       </c>
@@ -45543,7 +45597,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>41003</v>
       </c>
@@ -45584,7 +45638,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>41010</v>
       </c>
@@ -45625,7 +45679,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>41017</v>
       </c>
@@ -45666,7 +45720,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>41024</v>
       </c>
@@ -45707,7 +45761,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>41031</v>
       </c>
@@ -45748,7 +45802,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>41038</v>
       </c>
@@ -45789,7 +45843,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>41045</v>
       </c>
@@ -45830,7 +45884,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>41052</v>
       </c>
@@ -45871,7 +45925,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>41059</v>
       </c>
@@ -45912,7 +45966,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>41066</v>
       </c>
@@ -45953,7 +46007,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>41073</v>
       </c>
@@ -45994,7 +46048,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>41080</v>
       </c>
@@ -46035,7 +46089,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>41087</v>
       </c>
@@ -46076,7 +46130,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>41094</v>
       </c>
@@ -46117,7 +46171,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>41101</v>
       </c>
@@ -46158,7 +46212,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>41108</v>
       </c>
@@ -46199,7 +46253,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>41115</v>
       </c>
@@ -46240,7 +46294,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>41122</v>
       </c>
@@ -46281,7 +46335,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>41129</v>
       </c>
@@ -46322,7 +46376,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>41136</v>
       </c>
@@ -46363,7 +46417,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>41143</v>
       </c>
@@ -46404,7 +46458,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>41150</v>
       </c>
@@ -46445,7 +46499,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>41157</v>
       </c>
@@ -46486,7 +46540,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>41164</v>
       </c>
@@ -46527,7 +46581,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>41171</v>
       </c>
@@ -46568,7 +46622,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>41178</v>
       </c>
@@ -46609,7 +46663,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>41185</v>
       </c>
@@ -46650,7 +46704,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>41192</v>
       </c>
@@ -46691,7 +46745,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>41199</v>
       </c>
@@ -46732,7 +46786,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>41206</v>
       </c>
@@ -46773,7 +46827,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>41213</v>
       </c>
@@ -46814,7 +46868,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>41220</v>
       </c>
@@ -46855,7 +46909,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>41227</v>
       </c>
@@ -46896,7 +46950,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>41234</v>
       </c>
@@ -46937,7 +46991,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>41241</v>
       </c>
@@ -46978,7 +47032,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>41248</v>
       </c>
@@ -47019,7 +47073,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>41255</v>
       </c>
@@ -47060,7 +47114,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>41262</v>
       </c>
@@ -47101,7 +47155,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>41269</v>
       </c>
@@ -47142,7 +47196,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>41276</v>
       </c>
@@ -47183,7 +47237,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>41283</v>
       </c>
@@ -47224,7 +47278,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>41290</v>
       </c>
@@ -47265,7 +47319,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>41297</v>
       </c>
@@ -47306,7 +47360,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>41304</v>
       </c>
@@ -47347,7 +47401,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>41311</v>
       </c>
@@ -47388,7 +47442,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>41318</v>
       </c>
@@ -47429,7 +47483,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>41325</v>
       </c>
@@ -47470,7 +47524,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>41332</v>
       </c>
@@ -47511,7 +47565,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>41339</v>
       </c>
@@ -47552,7 +47606,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>41346</v>
       </c>
@@ -47593,7 +47647,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>41353</v>
       </c>
@@ -47634,7 +47688,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>41360</v>
       </c>
@@ -47675,7 +47729,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>41367</v>
       </c>
@@ -47716,7 +47770,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>41374</v>
       </c>
@@ -47757,7 +47811,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>41381</v>
       </c>
@@ -47798,7 +47852,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>41388</v>
       </c>
@@ -47839,7 +47893,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>41395</v>
       </c>
@@ -47880,7 +47934,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>41402</v>
       </c>
@@ -47921,7 +47975,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>41409</v>
       </c>
@@ -47962,7 +48016,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>41416</v>
       </c>
@@ -48003,7 +48057,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>41423</v>
       </c>
@@ -48044,7 +48098,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>41430</v>
       </c>
@@ -48085,7 +48139,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>41437</v>
       </c>
@@ -48126,7 +48180,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>41444</v>
       </c>
@@ -48167,7 +48221,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>41451</v>
       </c>
@@ -48208,7 +48262,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>41458</v>
       </c>
@@ -48249,7 +48303,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>41465</v>
       </c>
@@ -48290,7 +48344,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>41472</v>
       </c>
@@ -48331,7 +48385,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>41479</v>
       </c>
@@ -48372,7 +48426,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>41486</v>
       </c>
@@ -48413,7 +48467,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>41493</v>
       </c>
@@ -48454,7 +48508,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="8">
         <v>41500</v>
       </c>
@@ -48495,7 +48549,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="8">
         <v>41507</v>
       </c>
@@ -48536,7 +48590,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="8">
         <v>41514</v>
       </c>
@@ -48577,7 +48631,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="8">
         <v>41521</v>
       </c>
@@ -48618,7 +48672,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="8">
         <v>41528</v>
       </c>
@@ -48659,7 +48713,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="8">
         <v>41535</v>
       </c>
@@ -48700,7 +48754,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="8">
         <v>41542</v>
       </c>
@@ -48741,7 +48795,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="8">
         <v>41549</v>
       </c>
@@ -48782,7 +48836,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="8">
         <v>41556</v>
       </c>
@@ -48823,7 +48877,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="8">
         <v>41563</v>
       </c>
@@ -48864,7 +48918,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="8">
         <v>41570</v>
       </c>
@@ -48905,7 +48959,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
         <v>41577</v>
       </c>
@@ -48946,7 +49000,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
         <v>41584</v>
       </c>
@@ -48987,7 +49041,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
         <v>41591</v>
       </c>
@@ -49028,7 +49082,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
         <v>41598</v>
       </c>
@@ -49069,7 +49123,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
         <v>41605</v>
       </c>
@@ -49110,7 +49164,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
         <v>41612</v>
       </c>
@@ -49151,7 +49205,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <v>41619</v>
       </c>
@@ -49192,7 +49246,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <v>41626</v>
       </c>
@@ -49233,7 +49287,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <v>41640</v>
       </c>
@@ -49274,7 +49328,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <v>41647</v>
       </c>
@@ -49315,7 +49369,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <v>41654</v>
       </c>
@@ -49356,7 +49410,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <v>41661</v>
       </c>
@@ -49397,7 +49451,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <v>41668</v>
       </c>
@@ -49438,7 +49492,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <v>41675</v>
       </c>
@@ -49479,7 +49533,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
         <v>41682</v>
       </c>
@@ -49520,7 +49574,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
         <v>41689</v>
       </c>
@@ -49561,7 +49615,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
         <v>41696</v>
       </c>
@@ -49602,7 +49656,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
         <v>41703</v>
       </c>
@@ -49643,7 +49697,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
         <v>41710</v>
       </c>
@@ -49684,7 +49738,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
         <v>41717</v>
       </c>
@@ -49725,7 +49779,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
         <v>41724</v>
       </c>
@@ -49766,7 +49820,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <v>41731</v>
       </c>
@@ -49807,7 +49861,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <v>41738</v>
       </c>
@@ -49848,7 +49902,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <v>41745</v>
       </c>
@@ -49889,7 +49943,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <v>41752</v>
       </c>
@@ -49930,7 +49984,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <v>41759</v>
       </c>
@@ -49971,7 +50025,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <v>41766</v>
       </c>
@@ -50012,7 +50066,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <v>41773</v>
       </c>
@@ -50053,7 +50107,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <v>41780</v>
       </c>
@@ -50094,7 +50148,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <v>41787</v>
       </c>
@@ -50135,7 +50189,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>41794</v>
       </c>
@@ -50176,7 +50230,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <v>41801</v>
       </c>
@@ -50217,7 +50271,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>41808</v>
       </c>
@@ -50258,7 +50312,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <v>41815</v>
       </c>
@@ -50299,7 +50353,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>41822</v>
       </c>
@@ -50340,7 +50394,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <v>41829</v>
       </c>
@@ -50381,7 +50435,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>41836</v>
       </c>
@@ -50422,7 +50476,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <v>41843</v>
       </c>
@@ -50463,7 +50517,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>41850</v>
       </c>
@@ -50504,7 +50558,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <v>41857</v>
       </c>
@@ -50545,7 +50599,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>41864</v>
       </c>
@@ -50586,7 +50640,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="8">
         <v>41871</v>
       </c>
@@ -50627,7 +50681,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>41878</v>
       </c>
@@ -50668,7 +50722,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
         <v>41885</v>
       </c>
@@ -50709,7 +50763,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>41892</v>
       </c>
@@ -50750,7 +50804,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="8">
         <v>41899</v>
       </c>
@@ -50791,7 +50845,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>41906</v>
       </c>
@@ -50832,7 +50886,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="8">
         <v>41913</v>
       </c>
@@ -50873,7 +50927,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" s="8">
         <v>41920</v>
       </c>
@@ -50914,7 +50968,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" s="8">
         <v>41927</v>
       </c>
@@ -50955,7 +51009,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" s="8">
         <v>41934</v>
       </c>
@@ -50996,7 +51050,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" s="8">
         <v>41941</v>
       </c>
@@ -51037,7 +51091,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <v>41948</v>
       </c>
@@ -51078,7 +51132,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" s="8">
         <v>41955</v>
       </c>
@@ -51119,7 +51173,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" s="8">
         <v>41962</v>
       </c>
@@ -51160,7 +51214,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" s="8">
         <v>41969</v>
       </c>
@@ -51201,7 +51255,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <v>41976</v>
       </c>
@@ -51242,7 +51296,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <v>41983</v>
       </c>
@@ -51283,7 +51337,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <v>41990</v>
       </c>
@@ -51324,7 +51378,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" s="8">
         <v>42011</v>
       </c>
@@ -51365,7 +51419,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <v>42018</v>
       </c>
@@ -51406,7 +51460,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <v>42025</v>
       </c>
@@ -51447,7 +51501,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <v>42032</v>
       </c>
@@ -51488,7 +51542,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <v>42039</v>
       </c>
@@ -51529,7 +51583,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <v>42046</v>
       </c>
@@ -51570,7 +51624,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <v>42053</v>
       </c>
@@ -51611,7 +51665,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <v>42060</v>
       </c>
@@ -51652,7 +51706,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <v>42067</v>
       </c>
@@ -51693,7 +51747,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <v>42074</v>
       </c>
@@ -51734,7 +51788,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <v>42081</v>
       </c>
@@ -51775,7 +51829,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <v>42088</v>
       </c>
@@ -51816,7 +51870,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <v>42095</v>
       </c>
@@ -51857,7 +51911,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <v>42102</v>
       </c>
@@ -51898,7 +51952,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <v>42109</v>
       </c>
@@ -51939,7 +51993,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <v>42116</v>
       </c>
@@ -51980,7 +52034,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <v>42123</v>
       </c>
@@ -52021,7 +52075,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <v>42130</v>
       </c>
@@ -52062,7 +52116,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <v>42137</v>
       </c>
@@ -52103,7 +52157,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <v>42144</v>
       </c>
@@ -52144,7 +52198,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <v>42151</v>
       </c>
@@ -52185,7 +52239,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <v>42158</v>
       </c>
@@ -52226,7 +52280,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <v>42165</v>
       </c>
@@ -52267,7 +52321,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <v>42172</v>
       </c>
@@ -52308,7 +52362,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <v>42179</v>
       </c>
@@ -52349,7 +52403,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <v>42186</v>
       </c>
@@ -52390,7 +52444,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <v>42193</v>
       </c>
@@ -52431,7 +52485,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <v>42200</v>
       </c>
@@ -52472,7 +52526,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <v>42207</v>
       </c>
@@ -52513,7 +52567,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <v>42214</v>
       </c>
@@ -52554,7 +52608,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <v>42221</v>
       </c>
@@ -52595,7 +52649,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <v>42228</v>
       </c>
@@ -52636,7 +52690,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <v>42235</v>
       </c>
@@ -52677,7 +52731,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <v>42242</v>
       </c>
@@ -52718,7 +52772,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <v>42249</v>
       </c>
@@ -52759,7 +52813,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <v>42256</v>
       </c>
@@ -52800,7 +52854,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <v>42263</v>
       </c>
@@ -52841,7 +52895,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <v>42270</v>
       </c>
@@ -52882,7 +52936,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <v>42277</v>
       </c>
@@ -52923,7 +52977,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <v>42284</v>
       </c>
@@ -52964,7 +53018,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <v>42291</v>
       </c>
@@ -53005,7 +53059,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <v>42298</v>
       </c>
@@ -53046,7 +53100,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <v>42305</v>
       </c>
@@ -53087,7 +53141,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <v>42312</v>
       </c>
@@ -53128,7 +53182,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <v>42319</v>
       </c>
@@ -53169,7 +53223,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <v>42326</v>
       </c>
@@ -53210,7 +53264,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <v>42333</v>
       </c>
@@ -53251,7 +53305,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <v>42340</v>
       </c>
@@ -53292,7 +53346,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <v>42347</v>
       </c>
@@ -53333,7 +53387,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <v>42354</v>
       </c>
@@ -53374,7 +53428,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <v>42361</v>
       </c>
@@ -53415,7 +53469,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <v>42368</v>
       </c>
@@ -53456,7 +53510,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <v>42375</v>
       </c>
@@ -53497,7 +53551,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <v>42382</v>
       </c>
@@ -53538,7 +53592,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <v>42389</v>
       </c>
@@ -53579,7 +53633,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <v>42396</v>
       </c>
@@ -53620,7 +53674,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <v>42403</v>
       </c>
@@ -53661,7 +53715,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <v>42410</v>
       </c>
@@ -53702,7 +53756,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <v>42417</v>
       </c>
@@ -53743,7 +53797,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <v>42424</v>
       </c>
@@ -53784,7 +53838,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <v>42431</v>
       </c>
@@ -53825,7 +53879,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <v>42438</v>
       </c>
@@ -53866,7 +53920,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <v>42445</v>
       </c>
@@ -53907,7 +53961,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <v>42452</v>
       </c>
@@ -53948,7 +54002,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <v>42459</v>
       </c>
@@ -53989,7 +54043,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <v>42466</v>
       </c>
@@ -54030,7 +54084,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <v>42473</v>
       </c>
@@ -54071,7 +54125,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <v>42480</v>
       </c>
@@ -54112,7 +54166,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <v>42487</v>
       </c>
@@ -54153,7 +54207,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <v>42494</v>
       </c>
@@ -54194,7 +54248,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <v>42501</v>
       </c>
@@ -54235,7 +54289,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <v>42508</v>
       </c>
@@ -54276,7 +54330,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <v>42515</v>
       </c>
@@ -54317,7 +54371,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <v>42522</v>
       </c>
@@ -54358,7 +54412,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <v>42529</v>
       </c>
@@ -54399,7 +54453,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="8">
         <v>42536</v>
       </c>
@@ -54440,7 +54494,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" s="8">
         <v>42543</v>
       </c>
@@ -54481,7 +54535,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" s="8">
         <v>42550</v>
       </c>
@@ -54522,7 +54576,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262" s="8">
         <v>42557</v>
       </c>
@@ -54563,7 +54617,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="8">
         <v>42564</v>
       </c>
@@ -54604,7 +54658,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" s="8">
         <v>42571</v>
       </c>
@@ -54645,7 +54699,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" s="8">
         <v>42578</v>
       </c>
@@ -54686,7 +54740,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" s="8">
         <v>42585</v>
       </c>
@@ -54727,7 +54781,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" s="8">
         <v>42592</v>
       </c>
@@ -54768,7 +54822,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" s="8">
         <v>42599</v>
       </c>
@@ -54809,7 +54863,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" s="8">
         <v>42606</v>
       </c>
@@ -54850,7 +54904,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270" s="8">
         <v>42613</v>
       </c>
@@ -54891,7 +54945,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <v>42620</v>
       </c>
@@ -54932,7 +54986,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <v>42627</v>
       </c>
@@ -54973,7 +55027,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <v>42634</v>
       </c>
@@ -55014,7 +55068,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <v>42641</v>
       </c>
@@ -55055,7 +55109,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <v>42648</v>
       </c>
@@ -55096,7 +55150,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <v>42655</v>
       </c>
@@ -55137,7 +55191,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <v>42662</v>
       </c>
@@ -55178,7 +55232,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <v>42669</v>
       </c>
@@ -55219,7 +55273,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <v>42676</v>
       </c>
@@ -55260,7 +55314,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <v>42683</v>
       </c>
@@ -55301,7 +55355,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <v>42690</v>
       </c>
@@ -55342,7 +55396,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <v>42697</v>
       </c>
@@ -55383,7 +55437,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <v>42704</v>
       </c>
@@ -55424,7 +55478,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <v>42711</v>
       </c>
@@ -55465,7 +55519,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <v>42718</v>
       </c>
@@ -55506,7 +55560,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <v>42725</v>
       </c>
@@ -55547,7 +55601,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A287" s="8">
         <v>42732</v>
       </c>
@@ -55588,7 +55642,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A288" s="8">
         <v>42739</v>
       </c>
@@ -55629,7 +55683,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289" s="8">
         <v>42746</v>
       </c>
@@ -55670,7 +55724,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290" s="8">
         <v>42753</v>
       </c>
@@ -55711,7 +55765,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291" s="8">
         <v>42760</v>
       </c>
@@ -55752,7 +55806,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" s="8">
         <v>42767</v>
       </c>
@@ -55793,7 +55847,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293" s="8">
         <v>42774</v>
       </c>
@@ -55834,7 +55888,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294" s="8">
         <v>42781</v>
       </c>
@@ -55875,7 +55929,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295" s="8">
         <v>42788</v>
       </c>
@@ -55916,7 +55970,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296" s="8">
         <v>42795</v>
       </c>
@@ -55957,7 +56011,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297" s="8">
         <v>42802</v>
       </c>
@@ -55998,7 +56052,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298" s="8">
         <v>42809</v>
       </c>
@@ -56039,7 +56093,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299" s="8">
         <v>42816</v>
       </c>
@@ -56080,7 +56134,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300" s="8">
         <v>42823</v>
       </c>
@@ -56121,7 +56175,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301" s="8">
         <v>42830</v>
       </c>
@@ -56162,7 +56216,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302" s="8">
         <v>42837</v>
       </c>
@@ -56203,7 +56257,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303" s="8">
         <v>42844</v>
       </c>
@@ -56244,7 +56298,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304" s="8">
         <v>42851</v>
       </c>
@@ -56285,7 +56339,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305" s="8">
         <v>42858</v>
       </c>
@@ -56326,7 +56380,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306" s="8">
         <v>42865</v>
       </c>
@@ -56367,7 +56421,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307" s="8">
         <v>42872</v>
       </c>
@@ -56408,7 +56462,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308" s="8">
         <v>42879</v>
       </c>
@@ -56449,7 +56503,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309" s="8">
         <v>42886</v>
       </c>
@@ -56490,7 +56544,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310" s="8">
         <v>42893</v>
       </c>
@@ -56531,7 +56585,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" s="8">
         <v>42900</v>
       </c>
@@ -56572,7 +56626,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312" s="8">
         <v>42907</v>
       </c>
@@ -56613,7 +56667,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313" s="8">
         <v>42914</v>
       </c>
@@ -56654,7 +56708,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314" s="8">
         <v>42921</v>
       </c>
@@ -56695,7 +56749,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315" s="8">
         <v>42928</v>
       </c>
@@ -56736,7 +56790,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316" s="8">
         <v>42935</v>
       </c>
@@ -56777,7 +56831,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317" s="8">
         <v>42942</v>
       </c>
@@ -56818,7 +56872,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318" s="8">
         <v>42949</v>
       </c>
@@ -56859,7 +56913,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319" s="8">
         <v>42956</v>
       </c>
@@ -56900,7 +56954,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320" s="8">
         <v>42963</v>
       </c>
@@ -56941,7 +56995,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321" s="8">
         <v>42970</v>
       </c>
@@ -56982,7 +57036,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" s="8">
         <v>42977</v>
       </c>
@@ -57023,7 +57077,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" s="8">
         <v>42984</v>
       </c>
@@ -57064,7 +57118,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" s="8">
         <v>42991</v>
       </c>
@@ -57105,7 +57159,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325" s="8">
         <v>42998</v>
       </c>
@@ -57146,7 +57200,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A326" s="8">
         <v>43005</v>
       </c>
@@ -57187,7 +57241,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327" s="8">
         <v>43012</v>
       </c>
@@ -57228,7 +57282,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A328" s="8">
         <v>43019</v>
       </c>
@@ -57269,7 +57323,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" s="8">
         <v>43026</v>
       </c>
@@ -57310,7 +57364,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330" s="8">
         <v>43033</v>
       </c>
@@ -57351,7 +57405,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331" s="8">
         <v>43040</v>
       </c>
@@ -57392,7 +57446,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332" s="8">
         <v>43047</v>
       </c>
@@ -57433,7 +57487,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333" s="8">
         <v>43054</v>
       </c>
@@ -57474,7 +57528,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" s="8">
         <v>43061</v>
       </c>
@@ -57515,7 +57569,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" s="8">
         <v>43068</v>
       </c>
@@ -57556,7 +57610,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" s="8">
         <v>43075</v>
       </c>
@@ -57597,7 +57651,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337" s="8">
         <v>43082</v>
       </c>
@@ -57638,7 +57692,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" s="8">
         <v>43089</v>
       </c>
@@ -57679,7 +57733,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339" s="8">
         <v>43096</v>
       </c>
@@ -57720,7 +57774,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" s="8">
         <v>43103</v>
       </c>
@@ -57761,7 +57815,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341" s="8">
         <v>43110</v>
       </c>
@@ -57802,7 +57856,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342" s="8">
         <v>43117</v>
       </c>
@@ -57843,7 +57897,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="8">
         <v>43124</v>
       </c>
@@ -57884,7 +57938,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344" s="8">
         <v>43131</v>
       </c>
@@ -57925,7 +57979,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345" s="8">
         <v>43138</v>
       </c>
@@ -57966,7 +58020,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346" s="8">
         <v>43145</v>
       </c>
@@ -58007,7 +58061,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347" s="8">
         <v>43152</v>
       </c>
@@ -58048,7 +58102,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348" s="8">
         <v>43159</v>
       </c>
@@ -58089,7 +58143,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" s="8">
         <v>43166</v>
       </c>
@@ -58130,7 +58184,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350" s="8">
         <v>43173</v>
       </c>
@@ -58171,7 +58225,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" s="8">
         <v>43180</v>
       </c>
@@ -58212,7 +58266,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="8">
         <v>43187</v>
       </c>
@@ -58253,7 +58307,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="8">
         <v>43194</v>
       </c>
@@ -58294,7 +58348,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="8">
         <v>43201</v>
       </c>
@@ -58335,7 +58389,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="8">
         <v>43208</v>
       </c>
@@ -58376,7 +58430,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="8">
         <v>43215</v>
       </c>
@@ -58417,7 +58471,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="8">
         <v>43222</v>
       </c>
@@ -58458,7 +58512,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="8">
         <v>43229</v>
       </c>
@@ -58499,7 +58553,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="8">
         <v>43236</v>
       </c>
@@ -58540,7 +58594,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" s="8">
         <v>43243</v>
       </c>
@@ -58581,7 +58635,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" s="8">
         <v>43250</v>
       </c>
@@ -58622,7 +58676,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" s="8">
         <v>43257</v>
       </c>
@@ -58663,7 +58717,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" s="8">
         <v>43264</v>
       </c>
@@ -58704,7 +58758,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364" s="8">
         <v>43271</v>
       </c>
@@ -58745,7 +58799,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365" s="8">
         <v>43278</v>
       </c>
@@ -58786,7 +58840,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" s="8">
         <v>43285</v>
       </c>
@@ -58827,7 +58881,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" s="8">
         <v>43292</v>
       </c>
@@ -58868,7 +58922,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" s="8">
         <v>43299</v>
       </c>
@@ -58909,7 +58963,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A369" s="8">
         <v>43306</v>
       </c>
@@ -58950,7 +59004,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370" s="8">
         <v>43313</v>
       </c>
@@ -58991,7 +59045,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A371" s="8">
         <v>43320</v>
       </c>
@@ -59032,7 +59086,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A372" s="8">
         <v>43327</v>
       </c>
@@ -59073,7 +59127,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A373" s="8">
         <v>43334</v>
       </c>
@@ -59114,7 +59168,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A374" s="8">
         <v>43341</v>
       </c>
@@ -59155,7 +59209,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="8">
         <v>43348</v>
       </c>
@@ -59196,7 +59250,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="8">
         <v>43355</v>
       </c>
@@ -59237,7 +59291,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="8">
         <v>43362</v>
       </c>
@@ -59278,7 +59332,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="8">
         <v>43369</v>
       </c>
@@ -59319,7 +59373,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="8">
         <v>43376</v>
       </c>
@@ -59360,7 +59414,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="8">
         <v>43383</v>
       </c>
@@ -59401,7 +59455,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A381" s="8">
         <v>43390</v>
       </c>
@@ -59442,7 +59496,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A382" s="8">
         <v>43397</v>
       </c>
@@ -59483,7 +59537,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A383" s="8">
         <v>43404</v>
       </c>
@@ -59524,7 +59578,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A384" s="8">
         <v>43411</v>
       </c>
@@ -59565,7 +59619,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="8">
         <v>43418</v>
       </c>
@@ -59606,7 +59660,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="8">
         <v>43425</v>
       </c>
@@ -59647,7 +59701,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387" s="8">
         <v>43432</v>
       </c>
@@ -59688,7 +59742,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="8">
         <v>43439</v>
       </c>
@@ -59729,7 +59783,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389" s="8">
         <v>43446</v>
       </c>
@@ -59770,7 +59824,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390" s="8">
         <v>43453</v>
       </c>
@@ -59811,7 +59865,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A391" s="8">
         <v>43460</v>
       </c>
@@ -59852,7 +59906,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="8">
         <v>43467</v>
       </c>
@@ -59893,7 +59947,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="8">
         <v>43474</v>
       </c>
@@ -59934,7 +59988,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="8">
         <v>43481</v>
       </c>
@@ -59975,7 +60029,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="8">
         <v>43488</v>
       </c>
@@ -60016,7 +60070,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="8">
         <v>43495</v>
       </c>
@@ -60057,7 +60111,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="8">
         <v>43502</v>
       </c>
@@ -60098,7 +60152,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="8">
         <v>43509</v>
       </c>
@@ -60139,7 +60193,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="8">
         <v>43516</v>
       </c>
@@ -60180,7 +60234,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="8">
         <v>43523</v>
       </c>
@@ -60221,7 +60275,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="8">
         <v>43530</v>
       </c>
@@ -60262,7 +60316,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="8">
         <v>43537</v>
       </c>
@@ -60303,7 +60357,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="8">
         <v>43544</v>
       </c>
@@ -60344,7 +60398,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="8">
         <v>43551</v>
       </c>
@@ -60385,7 +60439,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="8">
         <v>43558</v>
       </c>
@@ -60426,7 +60480,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="8">
         <v>43565</v>
       </c>
@@ -60467,7 +60521,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A407" s="8">
         <v>43572</v>
       </c>
@@ -60508,7 +60562,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408" s="8">
         <v>43579</v>
       </c>
@@ -60549,7 +60603,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409" s="8">
         <v>43586</v>
       </c>
@@ -60590,7 +60644,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" s="8">
         <v>43593</v>
       </c>
@@ -60631,7 +60685,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="8">
         <v>43600</v>
       </c>
@@ -60672,7 +60726,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="8">
         <v>43607</v>
       </c>
@@ -60713,7 +60767,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="8">
         <v>43614</v>
       </c>
@@ -60754,7 +60808,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="8">
         <v>43621</v>
       </c>
@@ -60795,7 +60849,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A415" s="8">
         <v>43628</v>
       </c>
@@ -60836,7 +60890,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A416" s="8">
         <v>43635</v>
       </c>
@@ -60877,7 +60931,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A417" s="8">
         <v>43642</v>
       </c>
@@ -60918,7 +60972,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" s="8">
         <v>43649</v>
       </c>
@@ -60959,7 +61013,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419" s="8">
         <v>43656</v>
       </c>
@@ -61000,7 +61054,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420" s="8">
         <v>43663</v>
       </c>
@@ -61041,7 +61095,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" s="8">
         <v>43670</v>
       </c>
@@ -61082,7 +61136,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" s="8">
         <v>43677</v>
       </c>
@@ -61123,7 +61177,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423" s="8">
         <v>43684</v>
       </c>
@@ -61164,7 +61218,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424" s="8">
         <v>43691</v>
       </c>
@@ -61205,7 +61259,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425" s="8">
         <v>43698</v>
       </c>
@@ -61246,7 +61300,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426" s="8">
         <v>43705</v>
       </c>
@@ -61287,7 +61341,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" s="8">
         <v>43712</v>
       </c>
@@ -61328,7 +61382,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" s="8">
         <v>43719</v>
       </c>
@@ -61369,7 +61423,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429" s="8">
         <v>43726</v>
       </c>
@@ -61410,7 +61464,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430" s="8">
         <v>43733</v>
       </c>
@@ -61451,7 +61505,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A431" s="8">
         <v>43740</v>
       </c>
@@ -61492,7 +61546,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A432" s="8">
         <v>43747</v>
       </c>
@@ -61533,7 +61587,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A433" s="8">
         <v>43754</v>
       </c>
@@ -61574,7 +61628,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A434" s="8">
         <v>43761</v>
       </c>
@@ -61615,7 +61669,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A435" s="8">
         <v>43768</v>
       </c>
@@ -61656,7 +61710,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436" s="8">
         <v>43775</v>
       </c>
@@ -61697,7 +61751,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A437" s="8">
         <v>43782</v>
       </c>
@@ -61738,7 +61792,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="8">
         <v>43789</v>
       </c>
@@ -61779,7 +61833,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="8">
         <v>43796</v>
       </c>
@@ -61820,7 +61874,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A440" s="8">
         <v>43803</v>
       </c>
@@ -61861,7 +61915,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A441" s="8">
         <v>43810</v>
       </c>
@@ -61902,7 +61956,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A442" s="8">
         <v>43817</v>
       </c>
@@ -61943,7 +61997,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A443" s="8">
         <v>43831</v>
       </c>
@@ -61984,7 +62038,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A444" s="8">
         <v>43838</v>
       </c>
@@ -62025,7 +62079,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="8">
         <v>43845</v>
       </c>
@@ -62066,7 +62120,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="8">
         <v>43852</v>
       </c>
@@ -62107,7 +62161,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="8">
         <v>43859</v>
       </c>
@@ -62148,7 +62202,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A448" s="8">
         <v>43866</v>
       </c>
@@ -62189,7 +62243,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A449" s="8">
         <v>43873</v>
       </c>
@@ -62230,7 +62284,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A450" s="8">
         <v>43880</v>
       </c>
@@ -62271,7 +62325,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A451" s="8">
         <v>43887</v>
       </c>
@@ -62312,7 +62366,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="8">
         <v>43894</v>
       </c>
@@ -62353,7 +62407,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453" s="8">
         <v>43901</v>
       </c>
@@ -62394,7 +62448,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A454" s="8">
         <v>43908</v>
       </c>
@@ -62435,7 +62489,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A455" s="8">
         <v>43915</v>
       </c>
@@ -62476,7 +62530,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456" s="8">
         <v>43922</v>
       </c>
@@ -62517,7 +62571,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457" s="8">
         <v>43929</v>
       </c>
@@ -62558,7 +62612,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458" s="8">
         <v>43936</v>
       </c>
@@ -62599,7 +62653,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459" s="8">
         <v>43943</v>
       </c>
@@ -62640,7 +62694,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460" s="8">
         <v>43950</v>
       </c>
@@ -62681,7 +62735,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461" s="8">
         <v>43957</v>
       </c>
@@ -62722,7 +62776,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462" s="8">
         <v>43964</v>
       </c>
@@ -62763,7 +62817,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463" s="8">
         <v>43971</v>
       </c>
@@ -62804,7 +62858,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464" s="8">
         <v>43978</v>
       </c>
@@ -62845,7 +62899,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A465" s="8">
         <v>43985</v>
       </c>
@@ -62886,7 +62940,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A466" s="8">
         <v>43992</v>
       </c>
@@ -62927,7 +62981,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A467" s="8">
         <v>43999</v>
       </c>
@@ -62968,7 +63022,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A468" s="8">
         <v>44006</v>
       </c>
@@ -63009,7 +63063,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A469" s="8">
         <v>44013</v>
       </c>
@@ -63050,7 +63104,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A470" s="8">
         <v>44020</v>
       </c>
@@ -63091,7 +63145,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A471" s="8">
         <v>44027</v>
       </c>
@@ -63132,7 +63186,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="8">
         <v>44034</v>
       </c>
@@ -63173,7 +63227,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A473" s="8">
         <v>44041</v>
       </c>
@@ -63214,7 +63268,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="8">
         <v>44048</v>
       </c>
@@ -63255,7 +63309,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A475" s="8">
         <v>44055</v>
       </c>
@@ -63296,7 +63350,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="8">
         <v>44062</v>
       </c>
@@ -63337,7 +63391,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A477" s="8">
         <v>44069</v>
       </c>
@@ -63378,7 +63432,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A478" s="8">
         <v>44076</v>
       </c>
@@ -63419,7 +63473,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A479" s="8">
         <v>44083</v>
       </c>
@@ -63460,7 +63514,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A480" s="8">
         <v>44090</v>
       </c>
@@ -63501,7 +63555,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A481" s="8">
         <v>44097</v>
       </c>
@@ -63542,7 +63596,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A482" s="8">
         <v>44104</v>
       </c>
@@ -63583,7 +63637,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="8">
         <v>44111</v>
       </c>
@@ -63624,7 +63678,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A484" s="8">
         <v>44118</v>
       </c>
@@ -63665,7 +63719,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A485" s="8">
         <v>44125</v>
       </c>
@@ -63706,7 +63760,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="8">
         <v>44132</v>
       </c>
@@ -63747,7 +63801,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A487" s="8">
         <v>44139</v>
       </c>
@@ -63788,7 +63842,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A488" s="8">
         <v>44146</v>
       </c>
@@ -63829,7 +63883,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A489" s="8">
         <v>44153</v>
       </c>
@@ -63870,7 +63924,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A490" s="8">
         <v>44160</v>
       </c>
@@ -63911,7 +63965,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="8">
         <v>44167</v>
       </c>
@@ -63952,7 +64006,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A492" s="8">
         <v>44174</v>
       </c>
@@ -63993,7 +64047,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A493" s="8">
         <v>44181</v>
       </c>
@@ -64034,7 +64088,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A494" s="8">
         <v>44188</v>
       </c>
@@ -64075,7 +64129,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A495" s="8">
         <v>44195</v>
       </c>
@@ -64116,7 +64170,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A496" s="8">
         <v>44202</v>
       </c>
@@ -64157,7 +64211,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A497" s="8">
         <v>44209</v>
       </c>
@@ -64198,7 +64252,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A498" s="8">
         <v>44216</v>
       </c>
@@ -64239,7 +64293,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A499" s="8">
         <v>44223</v>
       </c>
@@ -64280,7 +64334,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A500" s="8">
         <v>44230</v>
       </c>
@@ -64321,7 +64375,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A501" s="8">
         <v>44237</v>
       </c>
@@ -64362,7 +64416,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A502" s="8">
         <v>44244</v>
       </c>
@@ -64403,7 +64457,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A503" s="8">
         <v>44251</v>
       </c>
@@ -64444,7 +64498,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A504" s="8">
         <v>44258</v>
       </c>
@@ -64485,7 +64539,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A505" s="8">
         <v>44265</v>
       </c>
@@ -64526,7 +64580,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A506" s="8">
         <v>44272</v>
       </c>
@@ -64567,7 +64621,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A507" s="8">
         <v>44279</v>
       </c>
@@ -64608,7 +64662,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="8">
         <v>44286</v>
       </c>
@@ -64649,7 +64703,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="8">
         <v>44293</v>
       </c>
@@ -64690,7 +64744,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A510" s="8">
         <v>44300</v>
       </c>
@@ -64731,7 +64785,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A511" s="8">
         <v>44307</v>
       </c>
@@ -64772,7 +64826,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A512" s="8">
         <v>44314</v>
       </c>
@@ -64813,7 +64867,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A513" s="8">
         <v>44321</v>
       </c>
@@ -64854,7 +64908,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A514" s="8">
         <v>44328</v>
       </c>
@@ -64895,7 +64949,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A515" s="8">
         <v>44335</v>
       </c>
@@ -64936,7 +64990,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A516" s="8">
         <v>44342</v>
       </c>
@@ -64977,7 +65031,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A517" s="8">
         <v>44349</v>
       </c>
@@ -65018,7 +65072,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A518" s="8">
         <v>44356</v>
       </c>
@@ -65059,7 +65113,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A519" s="8">
         <v>44363</v>
       </c>
@@ -65100,7 +65154,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A520" s="8">
         <v>44370</v>
       </c>
@@ -65141,7 +65195,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A521" s="8">
         <v>44377</v>
       </c>
@@ -65182,7 +65236,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A522" s="8">
         <v>44384</v>
       </c>
@@ -65223,7 +65277,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A523" s="8">
         <v>44391</v>
       </c>
@@ -65264,7 +65318,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A524" s="8">
         <v>44398</v>
       </c>
@@ -65305,7 +65359,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A525" s="8">
         <v>44405</v>
       </c>
@@ -65346,7 +65400,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A526" s="8">
         <v>44412</v>
       </c>
@@ -65387,7 +65441,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A527" s="8">
         <v>44419</v>
       </c>
@@ -65428,7 +65482,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A528" s="8">
         <v>44426</v>
       </c>
@@ -65469,7 +65523,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A529" s="8">
         <v>44433</v>
       </c>
@@ -65510,7 +65564,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A530" s="8">
         <v>44440</v>
       </c>
@@ -65551,7 +65605,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A531" s="8">
         <v>44447</v>
       </c>
@@ -65592,7 +65646,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A532" s="8">
         <v>44454</v>
       </c>
@@ -65633,7 +65687,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A533" s="8">
         <v>44461</v>
       </c>
@@ -65674,7 +65728,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A534" s="8">
         <v>44468</v>
       </c>
@@ -65715,7 +65769,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A535" s="8">
         <v>44475</v>
       </c>
@@ -65756,7 +65810,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A536" s="8">
         <v>44482</v>
       </c>
@@ -65797,7 +65851,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A537" s="8">
         <v>44489</v>
       </c>
@@ -65838,7 +65892,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A538" s="8">
         <v>44496</v>
       </c>
@@ -65879,7 +65933,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A539" s="8">
         <v>44503</v>
       </c>
@@ -65920,7 +65974,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A540" s="8">
         <v>44510</v>
       </c>
@@ -65961,7 +66015,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" s="8">
         <v>44517</v>
       </c>
@@ -66002,7 +66056,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A542" s="8">
         <v>44524</v>
       </c>
@@ -66043,7 +66097,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A543" s="8">
         <v>44531</v>
       </c>
@@ -66084,7 +66138,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A544" s="8">
         <v>44538</v>
       </c>
@@ -66125,7 +66179,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" s="8">
         <v>44545</v>
       </c>
@@ -66166,7 +66220,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" s="8">
         <v>44552</v>
       </c>
@@ -66207,7 +66261,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" s="8">
         <v>44566</v>
       </c>
@@ -66248,7 +66302,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" s="8">
         <v>44573</v>
       </c>
@@ -66289,7 +66343,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" s="8">
         <v>44580</v>
       </c>
@@ -66330,7 +66384,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" s="8">
         <v>44587</v>
       </c>
@@ -66371,7 +66425,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" s="8">
         <v>44594</v>
       </c>
@@ -66412,7 +66466,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A552" s="8">
         <v>44601</v>
       </c>
@@ -66453,7 +66507,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A553" s="8">
         <v>44608</v>
       </c>
@@ -66494,7 +66548,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A554" s="8">
         <v>44615</v>
       </c>
@@ -66535,7 +66589,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A555" s="8">
         <v>44622</v>
       </c>
@@ -66576,7 +66630,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A556" s="8">
         <v>44629</v>
       </c>
@@ -66617,7 +66671,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A557" s="8">
         <v>44636</v>
       </c>
@@ -66658,7 +66712,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A558" s="8">
         <v>44643</v>
       </c>
@@ -66699,7 +66753,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A559" s="8">
         <v>44650</v>
       </c>
@@ -66740,7 +66794,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A560" s="8">
         <v>44657</v>
       </c>
@@ -66781,7 +66835,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A561" s="8">
         <v>44664</v>
       </c>
@@ -66822,7 +66876,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A562" s="8">
         <v>44671</v>
       </c>
@@ -66863,7 +66917,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A563" s="8">
         <v>44678</v>
       </c>
@@ -66904,7 +66958,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A564" s="8">
         <v>44685</v>
       </c>
@@ -66945,7 +66999,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A565" s="8">
         <v>44692</v>
       </c>
@@ -66986,7 +67040,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A566" s="8">
         <v>44699</v>
       </c>
@@ -67027,7 +67081,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A567" s="8">
         <v>44706</v>
       </c>
@@ -67068,7 +67122,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A568" s="8">
         <v>44713</v>
       </c>
@@ -67109,7 +67163,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A569" s="8">
         <v>44720</v>
       </c>
@@ -67150,7 +67204,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A570" s="8">
         <v>44727</v>
       </c>
@@ -67191,7 +67245,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A571" s="8">
         <v>44734</v>
       </c>
@@ -67232,7 +67286,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A572" s="8">
         <v>44741</v>
       </c>
@@ -67273,7 +67327,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A573" s="8">
         <v>44748</v>
       </c>
@@ -67314,7 +67368,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A574" s="8">
         <v>44755</v>
       </c>
@@ -67355,7 +67409,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A575" s="8">
         <v>44762</v>
       </c>
@@ -67396,7 +67450,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A576" s="8">
         <v>44769</v>
       </c>
@@ -67437,7 +67491,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A577" s="8">
         <v>44776</v>
       </c>
@@ -67478,7 +67532,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A578" s="8">
         <v>44783</v>
       </c>
@@ -67519,7 +67573,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A579" s="8">
         <v>44790</v>
       </c>
@@ -67560,7 +67614,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A580" s="8">
         <v>44797</v>
       </c>
@@ -67601,7 +67655,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A581" s="8">
         <v>44804</v>
       </c>
@@ -67642,7 +67696,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A582" s="8">
         <v>44811</v>
       </c>
@@ -67683,7 +67737,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A583" s="8">
         <v>44818</v>
       </c>
@@ -67724,7 +67778,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A584" s="8">
         <v>44825</v>
       </c>
@@ -67765,7 +67819,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A585" s="8">
         <v>44832</v>
       </c>
@@ -67806,7 +67860,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A586" s="8">
         <v>44839</v>
       </c>
@@ -67847,7 +67901,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A587" s="8">
         <v>44846</v>
       </c>
@@ -67888,7 +67942,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A588" s="8">
         <v>44853</v>
       </c>
@@ -67929,7 +67983,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A589" s="8">
         <v>44860</v>
       </c>
@@ -67970,7 +68024,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A590" s="8">
         <v>44867</v>
       </c>
@@ -68011,7 +68065,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A591" s="8">
         <v>44874</v>
       </c>
@@ -68052,7 +68106,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A592" s="8">
         <v>44881</v>
       </c>
@@ -68093,7 +68147,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A593" s="8">
         <v>44888</v>
       </c>
@@ -68134,7 +68188,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A594" s="8">
         <v>44895</v>
       </c>
@@ -68175,7 +68229,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A595" s="8">
         <v>44902</v>
       </c>
@@ -68216,7 +68270,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A596" s="8">
         <v>44909</v>
       </c>
@@ -68257,7 +68311,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A597" s="8">
         <v>44916</v>
       </c>
@@ -68298,7 +68352,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A598" s="8">
         <v>44930</v>
       </c>
@@ -68339,7 +68393,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A599" s="8">
         <v>44937</v>
       </c>
@@ -68380,7 +68434,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A600" s="8">
         <v>44944</v>
       </c>
@@ -68421,7 +68475,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A601" s="8">
         <v>44951</v>
       </c>
@@ -68462,7 +68516,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A602" s="8">
         <v>44958</v>
       </c>
@@ -68503,7 +68557,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A603" s="8">
         <v>44965</v>
       </c>
@@ -68544,7 +68598,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A604" s="8">
         <v>44972</v>
       </c>
@@ -68585,7 +68639,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A605" s="8">
         <v>44979</v>
       </c>
@@ -68626,7 +68680,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A606" s="8">
         <v>44986</v>
       </c>
@@ -68667,7 +68721,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A607" s="8">
         <v>44993</v>
       </c>
@@ -68708,7 +68762,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A608" s="8">
         <v>45000</v>
       </c>
@@ -68749,7 +68803,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A609" s="8">
         <v>45007</v>
       </c>
@@ -68790,7 +68844,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A610" s="8">
         <v>45014</v>
       </c>
@@ -68831,7 +68885,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A611" s="8">
         <v>45021</v>
       </c>
@@ -68872,7 +68926,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A612" s="8">
         <v>45028</v>
       </c>
@@ -68913,7 +68967,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A613" s="8">
         <v>45035</v>
       </c>
@@ -68954,7 +69008,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A614" s="8">
         <v>45042</v>
       </c>
@@ -68995,7 +69049,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A615" s="8">
         <v>45049</v>
       </c>
@@ -69036,7 +69090,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A616" s="8">
         <v>45056</v>
       </c>
@@ -69077,7 +69131,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A617" s="8">
         <v>45063</v>
       </c>
@@ -69118,7 +69172,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A618" s="8">
         <v>45070</v>
       </c>
@@ -69159,7 +69213,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A619" s="8">
         <v>45077</v>
       </c>
@@ -69200,7 +69254,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A620" s="8">
         <v>45084</v>
       </c>
@@ -69241,7 +69295,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A621" s="8">
         <v>45091</v>
       </c>
@@ -69282,7 +69336,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A622" s="8">
         <v>45098</v>
       </c>
@@ -69323,7 +69377,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A623" s="8">
         <v>45105</v>
       </c>
@@ -69364,7 +69418,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A624" s="8">
         <v>45112</v>
       </c>
@@ -69405,7 +69459,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A625" s="8">
         <v>45119</v>
       </c>
@@ -69446,7 +69500,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A626" s="8">
         <v>45126</v>
       </c>
@@ -69487,7 +69541,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A627" s="8">
         <v>45133</v>
       </c>
@@ -69528,7 +69582,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A628" s="8">
         <v>45140</v>
       </c>
@@ -69569,7 +69623,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A629" s="8">
         <v>45147</v>
       </c>
@@ -69610,7 +69664,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="8">
         <v>45154</v>
       </c>
@@ -69651,7 +69705,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A631" s="8">
         <v>45161</v>
       </c>
@@ -69692,7 +69746,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A632" s="8">
         <v>45168</v>
       </c>
@@ -69733,7 +69787,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A633" s="8">
         <v>45175</v>
       </c>
@@ -69774,7 +69828,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A634" s="8">
         <v>45182</v>
       </c>
@@ -69815,7 +69869,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" s="8">
         <v>45189</v>
       </c>
@@ -69856,7 +69910,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A636" s="8">
         <v>45196</v>
       </c>
@@ -69897,7 +69951,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A637" s="8">
         <v>45203</v>
       </c>
@@ -69938,7 +69992,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A638" s="8">
         <v>45210</v>
       </c>
@@ -69979,7 +70033,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A639" s="8">
         <v>45217</v>
       </c>
@@ -70020,7 +70074,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" s="8">
         <v>45224</v>
       </c>
@@ -70061,7 +70115,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A641" s="8">
         <v>45231</v>
       </c>
@@ -70102,7 +70156,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A642" s="8">
         <v>45238</v>
       </c>
@@ -70143,7 +70197,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A643" s="8">
         <v>45245</v>
       </c>
@@ -70184,7 +70238,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A644" s="8">
         <v>45252</v>
       </c>
@@ -70225,7 +70279,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A645" s="8">
         <v>45259</v>
       </c>
@@ -70266,7 +70320,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" s="8">
         <v>45266</v>
       </c>
@@ -70307,7 +70361,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" s="8">
         <v>45273</v>
       </c>
@@ -70348,7 +70402,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" s="8">
         <v>45280</v>
       </c>
@@ -70389,7 +70443,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" s="8">
         <v>45294</v>
       </c>
@@ -70430,7 +70484,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" s="8">
         <v>45301</v>
       </c>
@@ -70471,7 +70525,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" s="8">
         <v>45308</v>
       </c>
@@ -70512,7 +70566,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A652" s="8">
         <v>45315</v>
       </c>
@@ -70553,7 +70607,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A653" s="8">
         <v>45322</v>
       </c>
@@ -70594,7 +70648,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A654" s="8">
         <v>45329</v>
       </c>
@@ -70635,7 +70689,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A655" s="8">
         <v>45336</v>
       </c>
@@ -70676,7 +70730,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A656" s="8">
         <v>45343</v>
       </c>
@@ -70717,7 +70771,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A657" s="8">
         <v>45350</v>
       </c>
@@ -70758,7 +70812,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A658" s="8">
         <v>45357</v>
       </c>
@@ -70799,7 +70853,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A659" s="8">
         <v>45364</v>
       </c>
@@ -70840,7 +70894,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="8">
         <v>45371</v>
       </c>
@@ -70881,7 +70935,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A661" s="8">
         <v>45378</v>
       </c>
@@ -70922,7 +70976,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A662" s="8">
         <v>45385</v>
       </c>
@@ -70963,7 +71017,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A663" s="8">
         <v>45392</v>
       </c>
@@ -71004,7 +71058,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A664" s="8">
         <v>45399</v>
       </c>
@@ -71045,7 +71099,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A665" s="8">
         <v>45406</v>
       </c>
@@ -71086,7 +71140,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A666" s="8">
         <v>45413</v>
       </c>
@@ -71127,7 +71181,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A667" s="8">
         <v>45420</v>
       </c>
@@ -71168,7 +71222,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A668" s="8">
         <v>45427</v>
       </c>
@@ -71209,7 +71263,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A669" s="8">
         <v>45434</v>
       </c>
@@ -71250,7 +71304,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A670" s="8">
         <v>45441</v>
       </c>
@@ -71291,7 +71345,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A671" s="8">
         <v>45448</v>
       </c>
@@ -71332,7 +71386,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A672" s="8">
         <v>45455</v>
       </c>
@@ -71373,7 +71427,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A673" s="8">
         <v>45462</v>
       </c>
@@ -71414,7 +71468,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A674" s="8">
         <v>45469</v>
       </c>
@@ -71455,7 +71509,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A675" s="8">
         <v>45476</v>
       </c>
@@ -71496,7 +71550,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A676" s="8">
         <v>45483</v>
       </c>
@@ -71537,7 +71591,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A677" s="8">
         <v>45490</v>
       </c>
@@ -71578,7 +71632,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A678" s="8">
         <v>45497</v>
       </c>
@@ -71619,7 +71673,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A679" s="8">
         <v>45504</v>
       </c>
@@ -71660,7 +71714,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A680" s="8">
         <v>45511</v>
       </c>
@@ -71701,7 +71755,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A681" s="8">
         <v>45518</v>
       </c>
@@ -71742,7 +71796,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A682" s="8">
         <v>45525</v>
       </c>
@@ -71783,7 +71837,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A683" s="8">
         <v>45532</v>
       </c>
@@ -71824,7 +71878,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A684" s="8">
         <v>45539</v>
       </c>
@@ -71865,7 +71919,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A685" s="8">
         <v>45546</v>
       </c>
@@ -71906,7 +71960,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A686" s="8">
         <v>45553</v>
       </c>
@@ -71947,7 +72001,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A687" s="8">
         <v>45560</v>
       </c>
@@ -71988,7 +72042,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A688" s="8">
         <v>45567</v>
       </c>
@@ -72029,7 +72083,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A689" s="8">
         <v>45574</v>
       </c>
@@ -72070,7 +72124,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A690" s="8">
         <v>45581</v>
       </c>
@@ -72111,7 +72165,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A691" s="8">
         <v>45588</v>
       </c>
@@ -72152,7 +72206,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A692" s="8">
         <v>45595</v>
       </c>
@@ -72193,7 +72247,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A693" s="8">
         <v>45602</v>
       </c>
@@ -72234,7 +72288,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A694" s="8">
         <v>45609</v>
       </c>
@@ -72275,7 +72329,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A695" s="8">
         <v>45616</v>
       </c>
@@ -72316,7 +72370,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A696" s="8">
         <v>45623</v>
       </c>
@@ -72357,7 +72411,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A697" s="8">
         <v>45630</v>
       </c>
@@ -72398,7 +72452,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="8">
         <v>45637</v>
       </c>
@@ -72439,7 +72493,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="8">
         <v>45644</v>
       </c>
@@ -72480,7 +72534,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="8">
         <v>45658</v>
       </c>
@@ -72521,7 +72575,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="8">
         <v>45665</v>
       </c>
@@ -72562,7 +72616,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="8">
         <v>45672</v>
       </c>
@@ -72603,7 +72657,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="8">
         <v>45679</v>
       </c>
@@ -72644,7 +72698,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="8">
         <v>45686</v>
       </c>
@@ -72685,7 +72739,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="8">
         <v>45693</v>
       </c>
@@ -72726,7 +72780,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="8">
         <v>45700</v>
       </c>
@@ -72767,7 +72821,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="8">
         <v>45707</v>
       </c>
@@ -72808,7 +72862,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="8">
         <v>45714</v>
       </c>
@@ -72849,7 +72903,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="8">
         <v>45721</v>
       </c>
@@ -72890,7 +72944,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="8">
         <v>45728</v>
       </c>
@@ -72931,7 +72985,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="8">
         <v>45735</v>
       </c>
@@ -72972,7 +73026,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="8">
         <v>45742</v>
       </c>
@@ -73013,7 +73067,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="8">
         <v>45749</v>
       </c>
@@ -73054,7 +73108,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A714" s="8">
         <v>45756</v>
       </c>
@@ -73095,7 +73149,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A715" s="8">
         <v>45763</v>
       </c>
@@ -73136,7 +73190,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A716" s="8">
         <v>45770</v>
       </c>
@@ -73177,7 +73231,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A717" s="8">
         <v>45777</v>
       </c>
@@ -73218,7 +73272,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A718" s="8">
         <v>45784</v>
       </c>
@@ -73259,7 +73313,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A719" s="8">
         <v>45791</v>
       </c>
@@ -73300,7 +73354,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A720" s="8">
         <v>45798</v>
       </c>
@@ -73341,7 +73395,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A721" s="8">
         <v>45805</v>
       </c>
@@ -73382,7 +73436,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A722" s="8">
         <v>45812</v>
       </c>
@@ -73423,7 +73477,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A723" s="8">
         <v>45819</v>
       </c>
@@ -73464,7 +73518,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A724" s="8">
         <v>45826</v>
       </c>
@@ -73505,7 +73559,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A725" s="8">
         <v>45833</v>
       </c>
@@ -73546,7 +73600,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A726" s="8">
         <v>45840</v>
       </c>
@@ -73587,7 +73641,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A727" s="8">
         <v>45847</v>
       </c>
@@ -73628,7 +73682,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A728" s="8">
         <v>45854</v>
       </c>
@@ -73669,7 +73723,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A729" s="8">
         <v>45861</v>
       </c>
@@ -73710,7 +73764,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A730" s="8">
         <v>45868</v>
       </c>
@@ -73751,7 +73805,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A731" s="8">
         <v>45875</v>
       </c>
@@ -73792,7 +73846,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A732" s="8">
         <v>45882</v>
       </c>
@@ -73833,7 +73887,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A733" s="8">
         <v>45889</v>
       </c>
@@ -73874,7 +73928,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A734" s="8">
         <v>45896</v>
       </c>
@@ -73915,7 +73969,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A735" s="8">
         <v>45903</v>
       </c>
@@ -73956,7 +74010,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A736" s="8">
         <v>45910</v>
       </c>
@@ -73997,7 +74051,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A737" s="8">
         <v>45917</v>
       </c>
@@ -74038,7 +74092,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A738" s="8">
         <v>45924</v>
       </c>
@@ -74079,7 +74133,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A739" s="8">
         <v>45931</v>
       </c>
@@ -74120,7 +74174,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A740" s="8">
         <v>45938</v>
       </c>
@@ -74161,7 +74215,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A741" s="8">
         <v>45945</v>
       </c>
@@ -74202,7 +74256,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A742" s="8">
         <v>45952</v>
       </c>
@@ -74243,7 +74297,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A743" s="8">
         <v>45959</v>
       </c>
@@ -74284,7 +74338,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A744" s="8">
         <v>45966</v>
       </c>
@@ -74325,7 +74379,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A745" s="8">
         <v>45973</v>
       </c>
@@ -74366,7 +74420,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A746" s="8">
         <v>45980</v>
       </c>
@@ -74407,7 +74461,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A747" s="8">
         <v>45987</v>
       </c>
@@ -74448,7 +74502,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A748" s="8">
         <v>45994</v>
       </c>
@@ -74489,7 +74543,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A749" s="8">
         <v>46001</v>
       </c>
@@ -74530,7 +74584,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A750" s="8">
         <v>46008</v>
       </c>
@@ -74571,7 +74625,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A751" s="8">
         <v>46015</v>
       </c>
@@ -74612,7 +74666,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A752" s="8">
         <v>46022</v>
       </c>
@@ -74653,7 +74707,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A753" s="8">
         <v>46029</v>
       </c>
@@ -74694,7 +74748,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A754" s="8">
         <v>46036</v>
       </c>
@@ -74735,7 +74789,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A755" s="8">
         <v>46043</v>
       </c>
@@ -74776,7 +74830,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A756" s="8">
         <v>46050</v>
       </c>
@@ -74817,7 +74871,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A757" s="8">
         <v>46057</v>
       </c>
@@ -74858,7 +74912,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A758" s="8">
         <v>46064</v>
       </c>
@@ -74899,7 +74953,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A759" s="8">
         <v>46071</v>
       </c>
@@ -74940,7 +74994,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A760" s="8">
         <v>46078</v>
       </c>
@@ -74981,7 +75035,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A761" s="8">
         <v>46085</v>
       </c>
@@ -75022,7 +75076,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A762" s="8">
         <v>46092</v>
       </c>
@@ -75063,7 +75117,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A763" s="8">
         <v>46099</v>
       </c>
@@ -75104,7 +75158,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A764" s="8">
         <v>46106</v>
       </c>
@@ -75145,7 +75199,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A765" s="8">
         <v>46113</v>
       </c>
@@ -75186,7 +75240,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A766" s="8">
         <v>46120</v>
       </c>
@@ -75227,7 +75281,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A767" s="8">
         <v>46127</v>
       </c>
@@ -75268,7 +75322,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A768" s="8">
         <v>46134</v>
       </c>
@@ -75309,7 +75363,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A769" s="8">
         <v>46141</v>
       </c>
@@ -75350,7 +75404,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A770" s="8">
         <v>46148</v>
       </c>
@@ -75391,7 +75445,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A771" s="8">
         <v>46155</v>
       </c>
@@ -75432,7 +75486,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A772" s="8">
         <v>46162</v>
       </c>
@@ -75473,7 +75527,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A773" s="8">
         <v>46169</v>
       </c>
@@ -75514,7 +75568,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A774" s="8">
         <v>46176</v>
       </c>
@@ -75555,7 +75609,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A775" s="8">
         <v>46183</v>
       </c>
@@ -75596,7 +75650,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A776" s="8">
         <v>46190</v>
       </c>
@@ -75637,7 +75691,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="777" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A777" s="8">
         <v>46197</v>
       </c>
@@ -75678,7 +75732,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="778" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A778" s="8">
         <v>46204</v>
       </c>
@@ -75719,7 +75773,7 @@
         <v>2602</v>
       </c>
     </row>
-    <row r="779" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A779" s="8">
         <v>46211</v>
       </c>
@@ -75758,6 +75812,47 @@
       </c>
       <c r="M779" s="11">
         <v>2723</v>
+      </c>
+    </row>
+    <row r="780" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A780" s="8">
+        <v>46218</v>
+      </c>
+      <c r="B780" s="8">
+        <v>46219</v>
+      </c>
+      <c r="C780" s="9">
+        <v>0.58333333333944504</v>
+      </c>
+      <c r="D780" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E780" s="10">
+        <v>4546.6400000000003</v>
+      </c>
+      <c r="F780" s="11">
+        <v>4873</v>
+      </c>
+      <c r="G780" s="11">
+        <v>6300</v>
+      </c>
+      <c r="H780" s="11">
+        <v>6272</v>
+      </c>
+      <c r="I780" s="11">
+        <v>7879</v>
+      </c>
+      <c r="J780" s="11">
+        <v>605</v>
+      </c>
+      <c r="K780" s="11">
+        <v>825</v>
+      </c>
+      <c r="L780" s="11">
+        <v>1037</v>
+      </c>
+      <c r="M780" s="11">
+        <v>2667</v>
       </c>
     </row>
   </sheetData>
@@ -75770,7 +75865,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75781,12 +75876,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
@@ -75805,7 +75900,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70403B94-C581-574D-A99F-E166A860129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27E30FC-979A-4389-8403-C5AA3F7F6F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25480" yWindow="600" windowWidth="25720" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -107,29 +107,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,7 +138,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,7 +146,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -195,35 +195,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -241,7 +241,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2627,6 +2627,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4972,6 +4975,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>4546.6400000000003</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>4373.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7353,6 +7359,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9698,6 +9707,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>4873</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>4824</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12079,6 +12091,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14424,6 +14439,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>5988</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16805,6 +16823,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19150,6 +19171,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>6272</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>5878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21531,6 +21555,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23876,6 +23903,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>7879</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>7598</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26257,6 +26287,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28602,6 +28635,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>607</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30985,6 +31021,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33330,6 +33369,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35713,6 +35755,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -38058,6 +38103,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>1037</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>1050</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40441,6 +40489,9 @@
                 <c:pt idx="778">
                   <c:v>46219</c:v>
                 </c:pt>
+                <c:pt idx="779">
+                  <c:v>46226</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42786,6 +42837,9 @@
                 </c:pt>
                 <c:pt idx="778">
                   <c:v>2667</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>2635</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43863,19 +43917,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M780"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M781"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.796875" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="10.5" style="11" customWidth="1"/>
     <col min="14" max="16384" width="7.5" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -43916,7 +43970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="8">
         <v>40716</v>
       </c>
@@ -43957,7 +44011,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="8">
         <v>40723</v>
       </c>
@@ -43998,7 +44052,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="8">
         <v>40730</v>
       </c>
@@ -44039,7 +44093,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="8">
         <v>40737</v>
       </c>
@@ -44080,7 +44134,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="8">
         <v>40744</v>
       </c>
@@ -44121,7 +44175,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="8">
         <v>40751</v>
       </c>
@@ -44162,7 +44216,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="8">
         <v>40758</v>
       </c>
@@ -44203,7 +44257,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="8">
         <v>40765</v>
       </c>
@@ -44244,7 +44298,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="8">
         <v>40772</v>
       </c>
@@ -44285,7 +44339,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="8">
         <v>40779</v>
       </c>
@@ -44326,7 +44380,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="8">
         <v>40786</v>
       </c>
@@ -44367,7 +44421,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="8">
         <v>40793</v>
       </c>
@@ -44408,7 +44462,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="8">
         <v>40800</v>
       </c>
@@ -44449,7 +44503,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="8">
         <v>40807</v>
       </c>
@@ -44490,7 +44544,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="8">
         <v>40814</v>
       </c>
@@ -44531,7 +44585,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" s="8">
         <v>40821</v>
       </c>
@@ -44572,7 +44626,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" s="8">
         <v>40828</v>
       </c>
@@ -44613,7 +44667,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="8">
         <v>40835</v>
       </c>
@@ -44654,7 +44708,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="8">
         <v>40842</v>
       </c>
@@ -44695,7 +44749,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="8">
         <v>40849</v>
       </c>
@@ -44736,7 +44790,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="8">
         <v>40856</v>
       </c>
@@ -44777,7 +44831,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="8">
         <v>40863</v>
       </c>
@@ -44818,7 +44872,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="8">
         <v>40870</v>
       </c>
@@ -44859,7 +44913,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="8">
         <v>40877</v>
       </c>
@@ -44900,7 +44954,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="8">
         <v>40884</v>
       </c>
@@ -44941,7 +44995,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="8">
         <v>40891</v>
       </c>
@@ -44982,7 +45036,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="8">
         <v>40898</v>
       </c>
@@ -45023,7 +45077,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="8">
         <v>40905</v>
       </c>
@@ -45064,7 +45118,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="8">
         <v>40912</v>
       </c>
@@ -45105,7 +45159,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="8">
         <v>40919</v>
       </c>
@@ -45146,7 +45200,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="8">
         <v>40926</v>
       </c>
@@ -45187,7 +45241,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="8">
         <v>40933</v>
       </c>
@@ -45228,7 +45282,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="8">
         <v>40940</v>
       </c>
@@ -45269,7 +45323,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="8">
         <v>40947</v>
       </c>
@@ -45310,7 +45364,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="8">
         <v>40954</v>
       </c>
@@ -45351,7 +45405,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="8">
         <v>40961</v>
       </c>
@@ -45392,7 +45446,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="8">
         <v>40968</v>
       </c>
@@ -45433,7 +45487,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="8">
         <v>40975</v>
       </c>
@@ -45474,7 +45528,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="8">
         <v>40982</v>
       </c>
@@ -45515,7 +45569,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="8">
         <v>40989</v>
       </c>
@@ -45556,7 +45610,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="8">
         <v>40996</v>
       </c>
@@ -45597,7 +45651,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" s="8">
         <v>41003</v>
       </c>
@@ -45638,7 +45692,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="8">
         <v>41010</v>
       </c>
@@ -45679,7 +45733,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" s="8">
         <v>41017</v>
       </c>
@@ -45720,7 +45774,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="8">
         <v>41024</v>
       </c>
@@ -45761,7 +45815,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" s="8">
         <v>41031</v>
       </c>
@@ -45802,7 +45856,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" s="8">
         <v>41038</v>
       </c>
@@ -45843,7 +45897,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A49" s="8">
         <v>41045</v>
       </c>
@@ -45884,7 +45938,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A50" s="8">
         <v>41052</v>
       </c>
@@ -45925,7 +45979,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A51" s="8">
         <v>41059</v>
       </c>
@@ -45966,7 +46020,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A52" s="8">
         <v>41066</v>
       </c>
@@ -46007,7 +46061,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A53" s="8">
         <v>41073</v>
       </c>
@@ -46048,7 +46102,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" s="8">
         <v>41080</v>
       </c>
@@ -46089,7 +46143,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" s="8">
         <v>41087</v>
       </c>
@@ -46130,7 +46184,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" s="8">
         <v>41094</v>
       </c>
@@ -46171,7 +46225,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" s="8">
         <v>41101</v>
       </c>
@@ -46212,7 +46266,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" s="8">
         <v>41108</v>
       </c>
@@ -46253,7 +46307,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59" s="8">
         <v>41115</v>
       </c>
@@ -46294,7 +46348,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" s="8">
         <v>41122</v>
       </c>
@@ -46335,7 +46389,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A61" s="8">
         <v>41129</v>
       </c>
@@ -46376,7 +46430,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62" s="8">
         <v>41136</v>
       </c>
@@ -46417,7 +46471,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A63" s="8">
         <v>41143</v>
       </c>
@@ -46458,7 +46512,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A64" s="8">
         <v>41150</v>
       </c>
@@ -46499,7 +46553,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A65" s="8">
         <v>41157</v>
       </c>
@@ -46540,7 +46594,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A66" s="8">
         <v>41164</v>
       </c>
@@ -46581,7 +46635,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A67" s="8">
         <v>41171</v>
       </c>
@@ -46622,7 +46676,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A68" s="8">
         <v>41178</v>
       </c>
@@ -46663,7 +46717,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A69" s="8">
         <v>41185</v>
       </c>
@@ -46704,7 +46758,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A70" s="8">
         <v>41192</v>
       </c>
@@ -46745,7 +46799,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A71" s="8">
         <v>41199</v>
       </c>
@@ -46786,7 +46840,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A72" s="8">
         <v>41206</v>
       </c>
@@ -46827,7 +46881,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A73" s="8">
         <v>41213</v>
       </c>
@@ -46868,7 +46922,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A74" s="8">
         <v>41220</v>
       </c>
@@ -46909,7 +46963,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A75" s="8">
         <v>41227</v>
       </c>
@@ -46950,7 +47004,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A76" s="8">
         <v>41234</v>
       </c>
@@ -46991,7 +47045,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A77" s="8">
         <v>41241</v>
       </c>
@@ -47032,7 +47086,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A78" s="8">
         <v>41248</v>
       </c>
@@ -47073,7 +47127,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A79" s="8">
         <v>41255</v>
       </c>
@@ -47114,7 +47168,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A80" s="8">
         <v>41262</v>
       </c>
@@ -47155,7 +47209,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A81" s="8">
         <v>41269</v>
       </c>
@@ -47196,7 +47250,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A82" s="8">
         <v>41276</v>
       </c>
@@ -47237,7 +47291,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A83" s="8">
         <v>41283</v>
       </c>
@@ -47278,7 +47332,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A84" s="8">
         <v>41290</v>
       </c>
@@ -47319,7 +47373,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A85" s="8">
         <v>41297</v>
       </c>
@@ -47360,7 +47414,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A86" s="8">
         <v>41304</v>
       </c>
@@ -47401,7 +47455,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A87" s="8">
         <v>41311</v>
       </c>
@@ -47442,7 +47496,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A88" s="8">
         <v>41318</v>
       </c>
@@ -47483,7 +47537,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A89" s="8">
         <v>41325</v>
       </c>
@@ -47524,7 +47578,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A90" s="8">
         <v>41332</v>
       </c>
@@ -47565,7 +47619,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A91" s="8">
         <v>41339</v>
       </c>
@@ -47606,7 +47660,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A92" s="8">
         <v>41346</v>
       </c>
@@ -47647,7 +47701,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A93" s="8">
         <v>41353</v>
       </c>
@@ -47688,7 +47742,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A94" s="8">
         <v>41360</v>
       </c>
@@ -47729,7 +47783,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A95" s="8">
         <v>41367</v>
       </c>
@@ -47770,7 +47824,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A96" s="8">
         <v>41374</v>
       </c>
@@ -47811,7 +47865,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A97" s="8">
         <v>41381</v>
       </c>
@@ -47852,7 +47906,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A98" s="8">
         <v>41388</v>
       </c>
@@ -47893,7 +47947,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A99" s="8">
         <v>41395</v>
       </c>
@@ -47934,7 +47988,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A100" s="8">
         <v>41402</v>
       </c>
@@ -47975,7 +48029,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A101" s="8">
         <v>41409</v>
       </c>
@@ -48016,7 +48070,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A102" s="8">
         <v>41416</v>
       </c>
@@ -48057,7 +48111,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A103" s="8">
         <v>41423</v>
       </c>
@@ -48098,7 +48152,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A104" s="8">
         <v>41430</v>
       </c>
@@ -48139,7 +48193,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A105" s="8">
         <v>41437</v>
       </c>
@@ -48180,7 +48234,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A106" s="8">
         <v>41444</v>
       </c>
@@ -48221,7 +48275,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A107" s="8">
         <v>41451</v>
       </c>
@@ -48262,7 +48316,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A108" s="8">
         <v>41458</v>
       </c>
@@ -48303,7 +48357,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A109" s="8">
         <v>41465</v>
       </c>
@@ -48344,7 +48398,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A110" s="8">
         <v>41472</v>
       </c>
@@ -48385,7 +48439,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A111" s="8">
         <v>41479</v>
       </c>
@@ -48426,7 +48480,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A112" s="8">
         <v>41486</v>
       </c>
@@ -48467,7 +48521,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A113" s="8">
         <v>41493</v>
       </c>
@@ -48508,7 +48562,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A114" s="8">
         <v>41500</v>
       </c>
@@ -48549,7 +48603,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A115" s="8">
         <v>41507</v>
       </c>
@@ -48590,7 +48644,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A116" s="8">
         <v>41514</v>
       </c>
@@ -48631,7 +48685,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A117" s="8">
         <v>41521</v>
       </c>
@@ -48672,7 +48726,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A118" s="8">
         <v>41528</v>
       </c>
@@ -48713,7 +48767,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A119" s="8">
         <v>41535</v>
       </c>
@@ -48754,7 +48808,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A120" s="8">
         <v>41542</v>
       </c>
@@ -48795,7 +48849,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A121" s="8">
         <v>41549</v>
       </c>
@@ -48836,7 +48890,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A122" s="8">
         <v>41556</v>
       </c>
@@ -48877,7 +48931,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A123" s="8">
         <v>41563</v>
       </c>
@@ -48918,7 +48972,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A124" s="8">
         <v>41570</v>
       </c>
@@ -48959,7 +49013,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A125" s="8">
         <v>41577</v>
       </c>
@@ -49000,7 +49054,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A126" s="8">
         <v>41584</v>
       </c>
@@ -49041,7 +49095,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A127" s="8">
         <v>41591</v>
       </c>
@@ -49082,7 +49136,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A128" s="8">
         <v>41598</v>
       </c>
@@ -49123,7 +49177,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A129" s="8">
         <v>41605</v>
       </c>
@@ -49164,7 +49218,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A130" s="8">
         <v>41612</v>
       </c>
@@ -49205,7 +49259,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A131" s="8">
         <v>41619</v>
       </c>
@@ -49246,7 +49300,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A132" s="8">
         <v>41626</v>
       </c>
@@ -49287,7 +49341,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A133" s="8">
         <v>41640</v>
       </c>
@@ -49328,7 +49382,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A134" s="8">
         <v>41647</v>
       </c>
@@ -49369,7 +49423,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A135" s="8">
         <v>41654</v>
       </c>
@@ -49410,7 +49464,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A136" s="8">
         <v>41661</v>
       </c>
@@ -49451,7 +49505,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A137" s="8">
         <v>41668</v>
       </c>
@@ -49492,7 +49546,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A138" s="8">
         <v>41675</v>
       </c>
@@ -49533,7 +49587,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A139" s="8">
         <v>41682</v>
       </c>
@@ -49574,7 +49628,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A140" s="8">
         <v>41689</v>
       </c>
@@ -49615,7 +49669,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A141" s="8">
         <v>41696</v>
       </c>
@@ -49656,7 +49710,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A142" s="8">
         <v>41703</v>
       </c>
@@ -49697,7 +49751,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A143" s="8">
         <v>41710</v>
       </c>
@@ -49738,7 +49792,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A144" s="8">
         <v>41717</v>
       </c>
@@ -49779,7 +49833,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A145" s="8">
         <v>41724</v>
       </c>
@@ -49820,7 +49874,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A146" s="8">
         <v>41731</v>
       </c>
@@ -49861,7 +49915,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A147" s="8">
         <v>41738</v>
       </c>
@@ -49902,7 +49956,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A148" s="8">
         <v>41745</v>
       </c>
@@ -49943,7 +49997,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A149" s="8">
         <v>41752</v>
       </c>
@@ -49984,7 +50038,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A150" s="8">
         <v>41759</v>
       </c>
@@ -50025,7 +50079,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A151" s="8">
         <v>41766</v>
       </c>
@@ -50066,7 +50120,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A152" s="8">
         <v>41773</v>
       </c>
@@ -50107,7 +50161,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A153" s="8">
         <v>41780</v>
       </c>
@@ -50148,7 +50202,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A154" s="8">
         <v>41787</v>
       </c>
@@ -50189,7 +50243,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A155" s="8">
         <v>41794</v>
       </c>
@@ -50230,7 +50284,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A156" s="8">
         <v>41801</v>
       </c>
@@ -50271,7 +50325,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A157" s="8">
         <v>41808</v>
       </c>
@@ -50312,7 +50366,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A158" s="8">
         <v>41815</v>
       </c>
@@ -50353,7 +50407,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A159" s="8">
         <v>41822</v>
       </c>
@@ -50394,7 +50448,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A160" s="8">
         <v>41829</v>
       </c>
@@ -50435,7 +50489,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A161" s="8">
         <v>41836</v>
       </c>
@@ -50476,7 +50530,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A162" s="8">
         <v>41843</v>
       </c>
@@ -50517,7 +50571,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A163" s="8">
         <v>41850</v>
       </c>
@@ -50558,7 +50612,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A164" s="8">
         <v>41857</v>
       </c>
@@ -50599,7 +50653,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A165" s="8">
         <v>41864</v>
       </c>
@@ -50640,7 +50694,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A166" s="8">
         <v>41871</v>
       </c>
@@ -50681,7 +50735,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A167" s="8">
         <v>41878</v>
       </c>
@@ -50722,7 +50776,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A168" s="8">
         <v>41885</v>
       </c>
@@ -50763,7 +50817,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A169" s="8">
         <v>41892</v>
       </c>
@@ -50804,7 +50858,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A170" s="8">
         <v>41899</v>
       </c>
@@ -50845,7 +50899,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A171" s="8">
         <v>41906</v>
       </c>
@@ -50886,7 +50940,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A172" s="8">
         <v>41913</v>
       </c>
@@ -50927,7 +50981,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A173" s="8">
         <v>41920</v>
       </c>
@@ -50968,7 +51022,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A174" s="8">
         <v>41927</v>
       </c>
@@ -51009,7 +51063,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A175" s="8">
         <v>41934</v>
       </c>
@@ -51050,7 +51104,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A176" s="8">
         <v>41941</v>
       </c>
@@ -51091,7 +51145,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A177" s="8">
         <v>41948</v>
       </c>
@@ -51132,7 +51186,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A178" s="8">
         <v>41955</v>
       </c>
@@ -51173,7 +51227,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A179" s="8">
         <v>41962</v>
       </c>
@@ -51214,7 +51268,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A180" s="8">
         <v>41969</v>
       </c>
@@ -51255,7 +51309,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A181" s="8">
         <v>41976</v>
       </c>
@@ -51296,7 +51350,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A182" s="8">
         <v>41983</v>
       </c>
@@ -51337,7 +51391,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A183" s="8">
         <v>41990</v>
       </c>
@@ -51378,7 +51432,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A184" s="8">
         <v>42011</v>
       </c>
@@ -51419,7 +51473,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A185" s="8">
         <v>42018</v>
       </c>
@@ -51460,7 +51514,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A186" s="8">
         <v>42025</v>
       </c>
@@ -51501,7 +51555,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A187" s="8">
         <v>42032</v>
       </c>
@@ -51542,7 +51596,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A188" s="8">
         <v>42039</v>
       </c>
@@ -51583,7 +51637,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A189" s="8">
         <v>42046</v>
       </c>
@@ -51624,7 +51678,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A190" s="8">
         <v>42053</v>
       </c>
@@ -51665,7 +51719,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A191" s="8">
         <v>42060</v>
       </c>
@@ -51706,7 +51760,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A192" s="8">
         <v>42067</v>
       </c>
@@ -51747,7 +51801,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A193" s="8">
         <v>42074</v>
       </c>
@@ -51788,7 +51842,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A194" s="8">
         <v>42081</v>
       </c>
@@ -51829,7 +51883,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A195" s="8">
         <v>42088</v>
       </c>
@@ -51870,7 +51924,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A196" s="8">
         <v>42095</v>
       </c>
@@ -51911,7 +51965,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A197" s="8">
         <v>42102</v>
       </c>
@@ -51952,7 +52006,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A198" s="8">
         <v>42109</v>
       </c>
@@ -51993,7 +52047,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A199" s="8">
         <v>42116</v>
       </c>
@@ -52034,7 +52088,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A200" s="8">
         <v>42123</v>
       </c>
@@ -52075,7 +52129,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A201" s="8">
         <v>42130</v>
       </c>
@@ -52116,7 +52170,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A202" s="8">
         <v>42137</v>
       </c>
@@ -52157,7 +52211,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A203" s="8">
         <v>42144</v>
       </c>
@@ -52198,7 +52252,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A204" s="8">
         <v>42151</v>
       </c>
@@ -52239,7 +52293,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A205" s="8">
         <v>42158</v>
       </c>
@@ -52280,7 +52334,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A206" s="8">
         <v>42165</v>
       </c>
@@ -52321,7 +52375,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A207" s="8">
         <v>42172</v>
       </c>
@@ -52362,7 +52416,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A208" s="8">
         <v>42179</v>
       </c>
@@ -52403,7 +52457,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A209" s="8">
         <v>42186</v>
       </c>
@@ -52444,7 +52498,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A210" s="8">
         <v>42193</v>
       </c>
@@ -52485,7 +52539,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A211" s="8">
         <v>42200</v>
       </c>
@@ -52526,7 +52580,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A212" s="8">
         <v>42207</v>
       </c>
@@ -52567,7 +52621,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A213" s="8">
         <v>42214</v>
       </c>
@@ -52608,7 +52662,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A214" s="8">
         <v>42221</v>
       </c>
@@ -52649,7 +52703,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A215" s="8">
         <v>42228</v>
       </c>
@@ -52690,7 +52744,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A216" s="8">
         <v>42235</v>
       </c>
@@ -52731,7 +52785,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A217" s="8">
         <v>42242</v>
       </c>
@@ -52772,7 +52826,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A218" s="8">
         <v>42249</v>
       </c>
@@ -52813,7 +52867,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A219" s="8">
         <v>42256</v>
       </c>
@@ -52854,7 +52908,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A220" s="8">
         <v>42263</v>
       </c>
@@ -52895,7 +52949,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A221" s="8">
         <v>42270</v>
       </c>
@@ -52936,7 +52990,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A222" s="8">
         <v>42277</v>
       </c>
@@ -52977,7 +53031,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A223" s="8">
         <v>42284</v>
       </c>
@@ -53018,7 +53072,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A224" s="8">
         <v>42291</v>
       </c>
@@ -53059,7 +53113,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A225" s="8">
         <v>42298</v>
       </c>
@@ -53100,7 +53154,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A226" s="8">
         <v>42305</v>
       </c>
@@ -53141,7 +53195,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A227" s="8">
         <v>42312</v>
       </c>
@@ -53182,7 +53236,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A228" s="8">
         <v>42319</v>
       </c>
@@ -53223,7 +53277,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A229" s="8">
         <v>42326</v>
       </c>
@@ -53264,7 +53318,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A230" s="8">
         <v>42333</v>
       </c>
@@ -53305,7 +53359,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A231" s="8">
         <v>42340</v>
       </c>
@@ -53346,7 +53400,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A232" s="8">
         <v>42347</v>
       </c>
@@ -53387,7 +53441,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A233" s="8">
         <v>42354</v>
       </c>
@@ -53428,7 +53482,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A234" s="8">
         <v>42361</v>
       </c>
@@ -53469,7 +53523,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A235" s="8">
         <v>42368</v>
       </c>
@@ -53510,7 +53564,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A236" s="8">
         <v>42375</v>
       </c>
@@ -53551,7 +53605,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A237" s="8">
         <v>42382</v>
       </c>
@@ -53592,7 +53646,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A238" s="8">
         <v>42389</v>
       </c>
@@ -53633,7 +53687,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A239" s="8">
         <v>42396</v>
       </c>
@@ -53674,7 +53728,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A240" s="8">
         <v>42403</v>
       </c>
@@ -53715,7 +53769,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A241" s="8">
         <v>42410</v>
       </c>
@@ -53756,7 +53810,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A242" s="8">
         <v>42417</v>
       </c>
@@ -53797,7 +53851,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A243" s="8">
         <v>42424</v>
       </c>
@@ -53838,7 +53892,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A244" s="8">
         <v>42431</v>
       </c>
@@ -53879,7 +53933,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A245" s="8">
         <v>42438</v>
       </c>
@@ -53920,7 +53974,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A246" s="8">
         <v>42445</v>
       </c>
@@ -53961,7 +54015,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A247" s="8">
         <v>42452</v>
       </c>
@@ -54002,7 +54056,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A248" s="8">
         <v>42459</v>
       </c>
@@ -54043,7 +54097,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A249" s="8">
         <v>42466</v>
       </c>
@@ -54084,7 +54138,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A250" s="8">
         <v>42473</v>
       </c>
@@ -54125,7 +54179,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A251" s="8">
         <v>42480</v>
       </c>
@@ -54166,7 +54220,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A252" s="8">
         <v>42487</v>
       </c>
@@ -54207,7 +54261,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A253" s="8">
         <v>42494</v>
       </c>
@@ -54248,7 +54302,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A254" s="8">
         <v>42501</v>
       </c>
@@ -54289,7 +54343,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A255" s="8">
         <v>42508</v>
       </c>
@@ -54330,7 +54384,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A256" s="8">
         <v>42515</v>
       </c>
@@ -54371,7 +54425,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A257" s="8">
         <v>42522</v>
       </c>
@@ -54412,7 +54466,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A258" s="8">
         <v>42529</v>
       </c>
@@ -54453,7 +54507,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A259" s="8">
         <v>42536</v>
       </c>
@@ -54494,7 +54548,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A260" s="8">
         <v>42543</v>
       </c>
@@ -54535,7 +54589,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A261" s="8">
         <v>42550</v>
       </c>
@@ -54576,7 +54630,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A262" s="8">
         <v>42557</v>
       </c>
@@ -54617,7 +54671,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A263" s="8">
         <v>42564</v>
       </c>
@@ -54658,7 +54712,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A264" s="8">
         <v>42571</v>
       </c>
@@ -54699,7 +54753,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A265" s="8">
         <v>42578</v>
       </c>
@@ -54740,7 +54794,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A266" s="8">
         <v>42585</v>
       </c>
@@ -54781,7 +54835,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A267" s="8">
         <v>42592</v>
       </c>
@@ -54822,7 +54876,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A268" s="8">
         <v>42599</v>
       </c>
@@ -54863,7 +54917,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A269" s="8">
         <v>42606</v>
       </c>
@@ -54904,7 +54958,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A270" s="8">
         <v>42613</v>
       </c>
@@ -54945,7 +54999,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A271" s="8">
         <v>42620</v>
       </c>
@@ -54986,7 +55040,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A272" s="8">
         <v>42627</v>
       </c>
@@ -55027,7 +55081,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A273" s="8">
         <v>42634</v>
       </c>
@@ -55068,7 +55122,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A274" s="8">
         <v>42641</v>
       </c>
@@ -55109,7 +55163,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A275" s="8">
         <v>42648</v>
       </c>
@@ -55150,7 +55204,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A276" s="8">
         <v>42655</v>
       </c>
@@ -55191,7 +55245,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A277" s="8">
         <v>42662</v>
       </c>
@@ -55232,7 +55286,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A278" s="8">
         <v>42669</v>
       </c>
@@ -55273,7 +55327,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A279" s="8">
         <v>42676</v>
       </c>
@@ -55314,7 +55368,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A280" s="8">
         <v>42683</v>
       </c>
@@ -55355,7 +55409,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A281" s="8">
         <v>42690</v>
       </c>
@@ -55396,7 +55450,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A282" s="8">
         <v>42697</v>
       </c>
@@ -55437,7 +55491,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A283" s="8">
         <v>42704</v>
       </c>
@@ -55478,7 +55532,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A284" s="8">
         <v>42711</v>
       </c>
@@ -55519,7 +55573,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A285" s="8">
         <v>42718</v>
       </c>
@@ -55560,7 +55614,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A286" s="8">
         <v>42725</v>
       </c>
@@ -55601,7 +55655,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A287" s="8">
         <v>42732</v>
       </c>
@@ -55642,7 +55696,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A288" s="8">
         <v>42739</v>
       </c>
@@ -55683,7 +55737,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A289" s="8">
         <v>42746</v>
       </c>
@@ -55724,7 +55778,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A290" s="8">
         <v>42753</v>
       </c>
@@ -55765,7 +55819,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A291" s="8">
         <v>42760</v>
       </c>
@@ -55806,7 +55860,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A292" s="8">
         <v>42767</v>
       </c>
@@ -55847,7 +55901,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A293" s="8">
         <v>42774</v>
       </c>
@@ -55888,7 +55942,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A294" s="8">
         <v>42781</v>
       </c>
@@ -55929,7 +55983,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A295" s="8">
         <v>42788</v>
       </c>
@@ -55970,7 +56024,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A296" s="8">
         <v>42795</v>
       </c>
@@ -56011,7 +56065,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A297" s="8">
         <v>42802</v>
       </c>
@@ -56052,7 +56106,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A298" s="8">
         <v>42809</v>
       </c>
@@ -56093,7 +56147,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A299" s="8">
         <v>42816</v>
       </c>
@@ -56134,7 +56188,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A300" s="8">
         <v>42823</v>
       </c>
@@ -56175,7 +56229,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A301" s="8">
         <v>42830</v>
       </c>
@@ -56216,7 +56270,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A302" s="8">
         <v>42837</v>
       </c>
@@ -56257,7 +56311,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A303" s="8">
         <v>42844</v>
       </c>
@@ -56298,7 +56352,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A304" s="8">
         <v>42851</v>
       </c>
@@ -56339,7 +56393,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A305" s="8">
         <v>42858</v>
       </c>
@@ -56380,7 +56434,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A306" s="8">
         <v>42865</v>
       </c>
@@ -56421,7 +56475,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A307" s="8">
         <v>42872</v>
       </c>
@@ -56462,7 +56516,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A308" s="8">
         <v>42879</v>
       </c>
@@ -56503,7 +56557,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A309" s="8">
         <v>42886</v>
       </c>
@@ -56544,7 +56598,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A310" s="8">
         <v>42893</v>
       </c>
@@ -56585,7 +56639,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A311" s="8">
         <v>42900</v>
       </c>
@@ -56626,7 +56680,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A312" s="8">
         <v>42907</v>
       </c>
@@ -56667,7 +56721,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A313" s="8">
         <v>42914</v>
       </c>
@@ -56708,7 +56762,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A314" s="8">
         <v>42921</v>
       </c>
@@ -56749,7 +56803,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A315" s="8">
         <v>42928</v>
       </c>
@@ -56790,7 +56844,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A316" s="8">
         <v>42935</v>
       </c>
@@ -56831,7 +56885,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A317" s="8">
         <v>42942</v>
       </c>
@@ -56872,7 +56926,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A318" s="8">
         <v>42949</v>
       </c>
@@ -56913,7 +56967,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A319" s="8">
         <v>42956</v>
       </c>
@@ -56954,7 +57008,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A320" s="8">
         <v>42963</v>
       </c>
@@ -56995,7 +57049,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A321" s="8">
         <v>42970</v>
       </c>
@@ -57036,7 +57090,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A322" s="8">
         <v>42977</v>
       </c>
@@ -57077,7 +57131,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A323" s="8">
         <v>42984</v>
       </c>
@@ -57118,7 +57172,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A324" s="8">
         <v>42991</v>
       </c>
@@ -57159,7 +57213,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A325" s="8">
         <v>42998</v>
       </c>
@@ -57200,7 +57254,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A326" s="8">
         <v>43005</v>
       </c>
@@ -57241,7 +57295,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A327" s="8">
         <v>43012</v>
       </c>
@@ -57282,7 +57336,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A328" s="8">
         <v>43019</v>
       </c>
@@ -57323,7 +57377,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A329" s="8">
         <v>43026</v>
       </c>
@@ -57364,7 +57418,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A330" s="8">
         <v>43033</v>
       </c>
@@ -57405,7 +57459,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A331" s="8">
         <v>43040</v>
       </c>
@@ -57446,7 +57500,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A332" s="8">
         <v>43047</v>
       </c>
@@ -57487,7 +57541,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A333" s="8">
         <v>43054</v>
       </c>
@@ -57528,7 +57582,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A334" s="8">
         <v>43061</v>
       </c>
@@ -57569,7 +57623,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A335" s="8">
         <v>43068</v>
       </c>
@@ -57610,7 +57664,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A336" s="8">
         <v>43075</v>
       </c>
@@ -57651,7 +57705,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A337" s="8">
         <v>43082</v>
       </c>
@@ -57692,7 +57746,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A338" s="8">
         <v>43089</v>
       </c>
@@ -57733,7 +57787,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A339" s="8">
         <v>43096</v>
       </c>
@@ -57774,7 +57828,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A340" s="8">
         <v>43103</v>
       </c>
@@ -57815,7 +57869,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A341" s="8">
         <v>43110</v>
       </c>
@@ -57856,7 +57910,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A342" s="8">
         <v>43117</v>
       </c>
@@ -57897,7 +57951,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A343" s="8">
         <v>43124</v>
       </c>
@@ -57938,7 +57992,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A344" s="8">
         <v>43131</v>
       </c>
@@ -57979,7 +58033,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A345" s="8">
         <v>43138</v>
       </c>
@@ -58020,7 +58074,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A346" s="8">
         <v>43145</v>
       </c>
@@ -58061,7 +58115,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A347" s="8">
         <v>43152</v>
       </c>
@@ -58102,7 +58156,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A348" s="8">
         <v>43159</v>
       </c>
@@ -58143,7 +58197,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A349" s="8">
         <v>43166</v>
       </c>
@@ -58184,7 +58238,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A350" s="8">
         <v>43173</v>
       </c>
@@ -58225,7 +58279,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A351" s="8">
         <v>43180</v>
       </c>
@@ -58266,7 +58320,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A352" s="8">
         <v>43187</v>
       </c>
@@ -58307,7 +58361,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A353" s="8">
         <v>43194</v>
       </c>
@@ -58348,7 +58402,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A354" s="8">
         <v>43201</v>
       </c>
@@ -58389,7 +58443,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A355" s="8">
         <v>43208</v>
       </c>
@@ -58430,7 +58484,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A356" s="8">
         <v>43215</v>
       </c>
@@ -58471,7 +58525,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A357" s="8">
         <v>43222</v>
       </c>
@@ -58512,7 +58566,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A358" s="8">
         <v>43229</v>
       </c>
@@ -58553,7 +58607,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A359" s="8">
         <v>43236</v>
       </c>
@@ -58594,7 +58648,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A360" s="8">
         <v>43243</v>
       </c>
@@ -58635,7 +58689,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A361" s="8">
         <v>43250</v>
       </c>
@@ -58676,7 +58730,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A362" s="8">
         <v>43257</v>
       </c>
@@ -58717,7 +58771,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A363" s="8">
         <v>43264</v>
       </c>
@@ -58758,7 +58812,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A364" s="8">
         <v>43271</v>
       </c>
@@ -58799,7 +58853,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A365" s="8">
         <v>43278</v>
       </c>
@@ -58840,7 +58894,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A366" s="8">
         <v>43285</v>
       </c>
@@ -58881,7 +58935,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A367" s="8">
         <v>43292</v>
       </c>
@@ -58922,7 +58976,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A368" s="8">
         <v>43299</v>
       </c>
@@ -58963,7 +59017,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A369" s="8">
         <v>43306</v>
       </c>
@@ -59004,7 +59058,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A370" s="8">
         <v>43313</v>
       </c>
@@ -59045,7 +59099,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A371" s="8">
         <v>43320</v>
       </c>
@@ -59086,7 +59140,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A372" s="8">
         <v>43327</v>
       </c>
@@ -59127,7 +59181,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A373" s="8">
         <v>43334</v>
       </c>
@@ -59168,7 +59222,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A374" s="8">
         <v>43341</v>
       </c>
@@ -59209,7 +59263,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A375" s="8">
         <v>43348</v>
       </c>
@@ -59250,7 +59304,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A376" s="8">
         <v>43355</v>
       </c>
@@ -59291,7 +59345,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A377" s="8">
         <v>43362</v>
       </c>
@@ -59332,7 +59386,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A378" s="8">
         <v>43369</v>
       </c>
@@ -59373,7 +59427,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A379" s="8">
         <v>43376</v>
       </c>
@@ -59414,7 +59468,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A380" s="8">
         <v>43383</v>
       </c>
@@ -59455,7 +59509,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A381" s="8">
         <v>43390</v>
       </c>
@@ -59496,7 +59550,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A382" s="8">
         <v>43397</v>
       </c>
@@ -59537,7 +59591,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A383" s="8">
         <v>43404</v>
       </c>
@@ -59578,7 +59632,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A384" s="8">
         <v>43411</v>
       </c>
@@ -59619,7 +59673,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A385" s="8">
         <v>43418</v>
       </c>
@@ -59660,7 +59714,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A386" s="8">
         <v>43425</v>
       </c>
@@ -59701,7 +59755,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A387" s="8">
         <v>43432</v>
       </c>
@@ -59742,7 +59796,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A388" s="8">
         <v>43439</v>
       </c>
@@ -59783,7 +59837,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A389" s="8">
         <v>43446</v>
       </c>
@@ -59824,7 +59878,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A390" s="8">
         <v>43453</v>
       </c>
@@ -59865,7 +59919,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A391" s="8">
         <v>43460</v>
       </c>
@@ -59906,7 +59960,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A392" s="8">
         <v>43467</v>
       </c>
@@ -59947,7 +60001,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A393" s="8">
         <v>43474</v>
       </c>
@@ -59988,7 +60042,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A394" s="8">
         <v>43481</v>
       </c>
@@ -60029,7 +60083,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A395" s="8">
         <v>43488</v>
       </c>
@@ -60070,7 +60124,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A396" s="8">
         <v>43495</v>
       </c>
@@ -60111,7 +60165,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A397" s="8">
         <v>43502</v>
       </c>
@@ -60152,7 +60206,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A398" s="8">
         <v>43509</v>
       </c>
@@ -60193,7 +60247,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A399" s="8">
         <v>43516</v>
       </c>
@@ -60234,7 +60288,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A400" s="8">
         <v>43523</v>
       </c>
@@ -60275,7 +60329,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A401" s="8">
         <v>43530</v>
       </c>
@@ -60316,7 +60370,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A402" s="8">
         <v>43537</v>
       </c>
@@ -60357,7 +60411,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A403" s="8">
         <v>43544</v>
       </c>
@@ -60398,7 +60452,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A404" s="8">
         <v>43551</v>
       </c>
@@ -60439,7 +60493,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A405" s="8">
         <v>43558</v>
       </c>
@@ -60480,7 +60534,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A406" s="8">
         <v>43565</v>
       </c>
@@ -60521,7 +60575,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A407" s="8">
         <v>43572</v>
       </c>
@@ -60562,7 +60616,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A408" s="8">
         <v>43579</v>
       </c>
@@ -60603,7 +60657,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A409" s="8">
         <v>43586</v>
       </c>
@@ -60644,7 +60698,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A410" s="8">
         <v>43593</v>
       </c>
@@ -60685,7 +60739,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A411" s="8">
         <v>43600</v>
       </c>
@@ -60726,7 +60780,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A412" s="8">
         <v>43607</v>
       </c>
@@ -60767,7 +60821,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A413" s="8">
         <v>43614</v>
       </c>
@@ -60808,7 +60862,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A414" s="8">
         <v>43621</v>
       </c>
@@ -60849,7 +60903,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A415" s="8">
         <v>43628</v>
       </c>
@@ -60890,7 +60944,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A416" s="8">
         <v>43635</v>
       </c>
@@ -60931,7 +60985,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A417" s="8">
         <v>43642</v>
       </c>
@@ -60972,7 +61026,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A418" s="8">
         <v>43649</v>
       </c>
@@ -61013,7 +61067,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A419" s="8">
         <v>43656</v>
       </c>
@@ -61054,7 +61108,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A420" s="8">
         <v>43663</v>
       </c>
@@ -61095,7 +61149,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A421" s="8">
         <v>43670</v>
       </c>
@@ -61136,7 +61190,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A422" s="8">
         <v>43677</v>
       </c>
@@ -61177,7 +61231,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A423" s="8">
         <v>43684</v>
       </c>
@@ -61218,7 +61272,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A424" s="8">
         <v>43691</v>
       </c>
@@ -61259,7 +61313,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A425" s="8">
         <v>43698</v>
       </c>
@@ -61300,7 +61354,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A426" s="8">
         <v>43705</v>
       </c>
@@ -61341,7 +61395,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A427" s="8">
         <v>43712</v>
       </c>
@@ -61382,7 +61436,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A428" s="8">
         <v>43719</v>
       </c>
@@ -61423,7 +61477,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A429" s="8">
         <v>43726</v>
       </c>
@@ -61464,7 +61518,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A430" s="8">
         <v>43733</v>
       </c>
@@ -61505,7 +61559,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A431" s="8">
         <v>43740</v>
       </c>
@@ -61546,7 +61600,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A432" s="8">
         <v>43747</v>
       </c>
@@ -61587,7 +61641,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A433" s="8">
         <v>43754</v>
       </c>
@@ -61628,7 +61682,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A434" s="8">
         <v>43761</v>
       </c>
@@ -61669,7 +61723,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A435" s="8">
         <v>43768</v>
       </c>
@@ -61710,7 +61764,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A436" s="8">
         <v>43775</v>
       </c>
@@ -61751,7 +61805,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A437" s="8">
         <v>43782</v>
       </c>
@@ -61792,7 +61846,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A438" s="8">
         <v>43789</v>
       </c>
@@ -61833,7 +61887,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A439" s="8">
         <v>43796</v>
       </c>
@@ -61874,7 +61928,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A440" s="8">
         <v>43803</v>
       </c>
@@ -61915,7 +61969,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A441" s="8">
         <v>43810</v>
       </c>
@@ -61956,7 +62010,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A442" s="8">
         <v>43817</v>
       </c>
@@ -61997,7 +62051,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A443" s="8">
         <v>43831</v>
       </c>
@@ -62038,7 +62092,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A444" s="8">
         <v>43838</v>
       </c>
@@ -62079,7 +62133,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A445" s="8">
         <v>43845</v>
       </c>
@@ -62120,7 +62174,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A446" s="8">
         <v>43852</v>
       </c>
@@ -62161,7 +62215,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A447" s="8">
         <v>43859</v>
       </c>
@@ -62202,7 +62256,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A448" s="8">
         <v>43866</v>
       </c>
@@ -62243,7 +62297,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A449" s="8">
         <v>43873</v>
       </c>
@@ -62284,7 +62338,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A450" s="8">
         <v>43880</v>
       </c>
@@ -62325,7 +62379,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A451" s="8">
         <v>43887</v>
       </c>
@@ -62366,7 +62420,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A452" s="8">
         <v>43894</v>
       </c>
@@ -62407,7 +62461,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A453" s="8">
         <v>43901</v>
       </c>
@@ -62448,7 +62502,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A454" s="8">
         <v>43908</v>
       </c>
@@ -62489,7 +62543,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A455" s="8">
         <v>43915</v>
       </c>
@@ -62530,7 +62584,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A456" s="8">
         <v>43922</v>
       </c>
@@ -62571,7 +62625,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A457" s="8">
         <v>43929</v>
       </c>
@@ -62612,7 +62666,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A458" s="8">
         <v>43936</v>
       </c>
@@ -62653,7 +62707,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A459" s="8">
         <v>43943</v>
       </c>
@@ -62694,7 +62748,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A460" s="8">
         <v>43950</v>
       </c>
@@ -62735,7 +62789,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A461" s="8">
         <v>43957</v>
       </c>
@@ -62776,7 +62830,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A462" s="8">
         <v>43964</v>
       </c>
@@ -62817,7 +62871,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A463" s="8">
         <v>43971</v>
       </c>
@@ -62858,7 +62912,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A464" s="8">
         <v>43978</v>
       </c>
@@ -62899,7 +62953,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A465" s="8">
         <v>43985</v>
       </c>
@@ -62940,7 +62994,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A466" s="8">
         <v>43992</v>
       </c>
@@ -62981,7 +63035,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A467" s="8">
         <v>43999</v>
       </c>
@@ -63022,7 +63076,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A468" s="8">
         <v>44006</v>
       </c>
@@ -63063,7 +63117,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A469" s="8">
         <v>44013</v>
       </c>
@@ -63104,7 +63158,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A470" s="8">
         <v>44020</v>
       </c>
@@ -63145,7 +63199,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A471" s="8">
         <v>44027</v>
       </c>
@@ -63186,7 +63240,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A472" s="8">
         <v>44034</v>
       </c>
@@ -63227,7 +63281,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A473" s="8">
         <v>44041</v>
       </c>
@@ -63268,7 +63322,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A474" s="8">
         <v>44048</v>
       </c>
@@ -63309,7 +63363,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A475" s="8">
         <v>44055</v>
       </c>
@@ -63350,7 +63404,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A476" s="8">
         <v>44062</v>
       </c>
@@ -63391,7 +63445,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A477" s="8">
         <v>44069</v>
       </c>
@@ -63432,7 +63486,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A478" s="8">
         <v>44076</v>
       </c>
@@ -63473,7 +63527,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A479" s="8">
         <v>44083</v>
       </c>
@@ -63514,7 +63568,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A480" s="8">
         <v>44090</v>
       </c>
@@ -63555,7 +63609,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A481" s="8">
         <v>44097</v>
       </c>
@@ -63596,7 +63650,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A482" s="8">
         <v>44104</v>
       </c>
@@ -63637,7 +63691,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A483" s="8">
         <v>44111</v>
       </c>
@@ -63678,7 +63732,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A484" s="8">
         <v>44118</v>
       </c>
@@ -63719,7 +63773,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A485" s="8">
         <v>44125</v>
       </c>
@@ -63760,7 +63814,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A486" s="8">
         <v>44132</v>
       </c>
@@ -63801,7 +63855,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A487" s="8">
         <v>44139</v>
       </c>
@@ -63842,7 +63896,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A488" s="8">
         <v>44146</v>
       </c>
@@ -63883,7 +63937,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A489" s="8">
         <v>44153</v>
       </c>
@@ -63924,7 +63978,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A490" s="8">
         <v>44160</v>
       </c>
@@ -63965,7 +64019,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A491" s="8">
         <v>44167</v>
       </c>
@@ -64006,7 +64060,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A492" s="8">
         <v>44174</v>
       </c>
@@ -64047,7 +64101,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A493" s="8">
         <v>44181</v>
       </c>
@@ -64088,7 +64142,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A494" s="8">
         <v>44188</v>
       </c>
@@ -64129,7 +64183,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A495" s="8">
         <v>44195</v>
       </c>
@@ -64170,7 +64224,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A496" s="8">
         <v>44202</v>
       </c>
@@ -64211,7 +64265,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A497" s="8">
         <v>44209</v>
       </c>
@@ -64252,7 +64306,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A498" s="8">
         <v>44216</v>
       </c>
@@ -64293,7 +64347,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A499" s="8">
         <v>44223</v>
       </c>
@@ -64334,7 +64388,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A500" s="8">
         <v>44230</v>
       </c>
@@ -64375,7 +64429,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A501" s="8">
         <v>44237</v>
       </c>
@@ -64416,7 +64470,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A502" s="8">
         <v>44244</v>
       </c>
@@ -64457,7 +64511,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A503" s="8">
         <v>44251</v>
       </c>
@@ -64498,7 +64552,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A504" s="8">
         <v>44258</v>
       </c>
@@ -64539,7 +64593,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A505" s="8">
         <v>44265</v>
       </c>
@@ -64580,7 +64634,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A506" s="8">
         <v>44272</v>
       </c>
@@ -64621,7 +64675,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A507" s="8">
         <v>44279</v>
       </c>
@@ -64662,7 +64716,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A508" s="8">
         <v>44286</v>
       </c>
@@ -64703,7 +64757,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A509" s="8">
         <v>44293</v>
       </c>
@@ -64744,7 +64798,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A510" s="8">
         <v>44300</v>
       </c>
@@ -64785,7 +64839,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A511" s="8">
         <v>44307</v>
       </c>
@@ -64826,7 +64880,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A512" s="8">
         <v>44314</v>
       </c>
@@ -64867,7 +64921,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A513" s="8">
         <v>44321</v>
       </c>
@@ -64908,7 +64962,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A514" s="8">
         <v>44328</v>
       </c>
@@ -64949,7 +65003,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A515" s="8">
         <v>44335</v>
       </c>
@@ -64990,7 +65044,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A516" s="8">
         <v>44342</v>
       </c>
@@ -65031,7 +65085,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A517" s="8">
         <v>44349</v>
       </c>
@@ -65072,7 +65126,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A518" s="8">
         <v>44356</v>
       </c>
@@ -65113,7 +65167,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A519" s="8">
         <v>44363</v>
       </c>
@@ -65154,7 +65208,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A520" s="8">
         <v>44370</v>
       </c>
@@ -65195,7 +65249,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A521" s="8">
         <v>44377</v>
       </c>
@@ -65236,7 +65290,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A522" s="8">
         <v>44384</v>
       </c>
@@ -65277,7 +65331,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A523" s="8">
         <v>44391</v>
       </c>
@@ -65318,7 +65372,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A524" s="8">
         <v>44398</v>
       </c>
@@ -65359,7 +65413,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A525" s="8">
         <v>44405</v>
       </c>
@@ -65400,7 +65454,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A526" s="8">
         <v>44412</v>
       </c>
@@ -65441,7 +65495,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A527" s="8">
         <v>44419</v>
       </c>
@@ -65482,7 +65536,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A528" s="8">
         <v>44426</v>
       </c>
@@ -65523,7 +65577,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A529" s="8">
         <v>44433</v>
       </c>
@@ -65564,7 +65618,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A530" s="8">
         <v>44440</v>
       </c>
@@ -65605,7 +65659,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A531" s="8">
         <v>44447</v>
       </c>
@@ -65646,7 +65700,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A532" s="8">
         <v>44454</v>
       </c>
@@ -65687,7 +65741,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A533" s="8">
         <v>44461</v>
       </c>
@@ -65728,7 +65782,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A534" s="8">
         <v>44468</v>
       </c>
@@ -65769,7 +65823,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A535" s="8">
         <v>44475</v>
       </c>
@@ -65810,7 +65864,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A536" s="8">
         <v>44482</v>
       </c>
@@ -65851,7 +65905,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A537" s="8">
         <v>44489</v>
       </c>
@@ -65892,7 +65946,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A538" s="8">
         <v>44496</v>
       </c>
@@ -65933,7 +65987,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A539" s="8">
         <v>44503</v>
       </c>
@@ -65974,7 +66028,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A540" s="8">
         <v>44510</v>
       </c>
@@ -66015,7 +66069,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A541" s="8">
         <v>44517</v>
       </c>
@@ -66056,7 +66110,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A542" s="8">
         <v>44524</v>
       </c>
@@ -66097,7 +66151,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A543" s="8">
         <v>44531</v>
       </c>
@@ -66138,7 +66192,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A544" s="8">
         <v>44538</v>
       </c>
@@ -66179,7 +66233,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A545" s="8">
         <v>44545</v>
       </c>
@@ -66220,7 +66274,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A546" s="8">
         <v>44552</v>
       </c>
@@ -66261,7 +66315,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A547" s="8">
         <v>44566</v>
       </c>
@@ -66302,7 +66356,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A548" s="8">
         <v>44573</v>
       </c>
@@ -66343,7 +66397,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A549" s="8">
         <v>44580</v>
       </c>
@@ -66384,7 +66438,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A550" s="8">
         <v>44587</v>
       </c>
@@ -66425,7 +66479,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A551" s="8">
         <v>44594</v>
       </c>
@@ -66466,7 +66520,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A552" s="8">
         <v>44601</v>
       </c>
@@ -66507,7 +66561,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A553" s="8">
         <v>44608</v>
       </c>
@@ -66548,7 +66602,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A554" s="8">
         <v>44615</v>
       </c>
@@ -66589,7 +66643,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A555" s="8">
         <v>44622</v>
       </c>
@@ -66630,7 +66684,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A556" s="8">
         <v>44629</v>
       </c>
@@ -66671,7 +66725,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A557" s="8">
         <v>44636</v>
       </c>
@@ -66712,7 +66766,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A558" s="8">
         <v>44643</v>
       </c>
@@ -66753,7 +66807,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A559" s="8">
         <v>44650</v>
       </c>
@@ -66794,7 +66848,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A560" s="8">
         <v>44657</v>
       </c>
@@ -66835,7 +66889,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A561" s="8">
         <v>44664</v>
       </c>
@@ -66876,7 +66930,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A562" s="8">
         <v>44671</v>
       </c>
@@ -66917,7 +66971,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A563" s="8">
         <v>44678</v>
       </c>
@@ -66958,7 +67012,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A564" s="8">
         <v>44685</v>
       </c>
@@ -66999,7 +67053,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A565" s="8">
         <v>44692</v>
       </c>
@@ -67040,7 +67094,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A566" s="8">
         <v>44699</v>
       </c>
@@ -67081,7 +67135,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A567" s="8">
         <v>44706</v>
       </c>
@@ -67122,7 +67176,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A568" s="8">
         <v>44713</v>
       </c>
@@ -67163,7 +67217,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A569" s="8">
         <v>44720</v>
       </c>
@@ -67204,7 +67258,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A570" s="8">
         <v>44727</v>
       </c>
@@ -67245,7 +67299,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A571" s="8">
         <v>44734</v>
       </c>
@@ -67286,7 +67340,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A572" s="8">
         <v>44741</v>
       </c>
@@ -67327,7 +67381,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A573" s="8">
         <v>44748</v>
       </c>
@@ -67368,7 +67422,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A574" s="8">
         <v>44755</v>
       </c>
@@ -67409,7 +67463,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A575" s="8">
         <v>44762</v>
       </c>
@@ -67450,7 +67504,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A576" s="8">
         <v>44769</v>
       </c>
@@ -67491,7 +67545,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A577" s="8">
         <v>44776</v>
       </c>
@@ -67532,7 +67586,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A578" s="8">
         <v>44783</v>
       </c>
@@ -67573,7 +67627,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A579" s="8">
         <v>44790</v>
       </c>
@@ -67614,7 +67668,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A580" s="8">
         <v>44797</v>
       </c>
@@ -67655,7 +67709,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A581" s="8">
         <v>44804</v>
       </c>
@@ -67696,7 +67750,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A582" s="8">
         <v>44811</v>
       </c>
@@ -67737,7 +67791,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A583" s="8">
         <v>44818</v>
       </c>
@@ -67778,7 +67832,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A584" s="8">
         <v>44825</v>
       </c>
@@ -67819,7 +67873,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A585" s="8">
         <v>44832</v>
       </c>
@@ -67860,7 +67914,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A586" s="8">
         <v>44839</v>
       </c>
@@ -67901,7 +67955,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A587" s="8">
         <v>44846</v>
       </c>
@@ -67942,7 +67996,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A588" s="8">
         <v>44853</v>
       </c>
@@ -67983,7 +68037,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A589" s="8">
         <v>44860</v>
       </c>
@@ -68024,7 +68078,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A590" s="8">
         <v>44867</v>
       </c>
@@ -68065,7 +68119,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A591" s="8">
         <v>44874</v>
       </c>
@@ -68106,7 +68160,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A592" s="8">
         <v>44881</v>
       </c>
@@ -68147,7 +68201,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A593" s="8">
         <v>44888</v>
       </c>
@@ -68188,7 +68242,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A594" s="8">
         <v>44895</v>
       </c>
@@ -68229,7 +68283,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A595" s="8">
         <v>44902</v>
       </c>
@@ -68270,7 +68324,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A596" s="8">
         <v>44909</v>
       </c>
@@ -68311,7 +68365,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A597" s="8">
         <v>44916</v>
       </c>
@@ -68352,7 +68406,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A598" s="8">
         <v>44930</v>
       </c>
@@ -68393,7 +68447,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A599" s="8">
         <v>44937</v>
       </c>
@@ -68434,7 +68488,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A600" s="8">
         <v>44944</v>
       </c>
@@ -68475,7 +68529,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A601" s="8">
         <v>44951</v>
       </c>
@@ -68516,7 +68570,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A602" s="8">
         <v>44958</v>
       </c>
@@ -68557,7 +68611,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A603" s="8">
         <v>44965</v>
       </c>
@@ -68598,7 +68652,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A604" s="8">
         <v>44972</v>
       </c>
@@ -68639,7 +68693,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A605" s="8">
         <v>44979</v>
       </c>
@@ -68680,7 +68734,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A606" s="8">
         <v>44986</v>
       </c>
@@ -68721,7 +68775,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A607" s="8">
         <v>44993</v>
       </c>
@@ -68762,7 +68816,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A608" s="8">
         <v>45000</v>
       </c>
@@ -68803,7 +68857,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A609" s="8">
         <v>45007</v>
       </c>
@@ -68844,7 +68898,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A610" s="8">
         <v>45014</v>
       </c>
@@ -68885,7 +68939,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A611" s="8">
         <v>45021</v>
       </c>
@@ -68926,7 +68980,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A612" s="8">
         <v>45028</v>
       </c>
@@ -68967,7 +69021,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A613" s="8">
         <v>45035</v>
       </c>
@@ -69008,7 +69062,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A614" s="8">
         <v>45042</v>
       </c>
@@ -69049,7 +69103,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A615" s="8">
         <v>45049</v>
       </c>
@@ -69090,7 +69144,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A616" s="8">
         <v>45056</v>
       </c>
@@ -69131,7 +69185,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A617" s="8">
         <v>45063</v>
       </c>
@@ -69172,7 +69226,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A618" s="8">
         <v>45070</v>
       </c>
@@ -69213,7 +69267,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A619" s="8">
         <v>45077</v>
       </c>
@@ -69254,7 +69308,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A620" s="8">
         <v>45084</v>
       </c>
@@ -69295,7 +69349,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A621" s="8">
         <v>45091</v>
       </c>
@@ -69336,7 +69390,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A622" s="8">
         <v>45098</v>
       </c>
@@ -69377,7 +69431,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A623" s="8">
         <v>45105</v>
       </c>
@@ -69418,7 +69472,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A624" s="8">
         <v>45112</v>
       </c>
@@ -69459,7 +69513,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A625" s="8">
         <v>45119</v>
       </c>
@@ -69500,7 +69554,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A626" s="8">
         <v>45126</v>
       </c>
@@ -69541,7 +69595,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A627" s="8">
         <v>45133</v>
       </c>
@@ -69582,7 +69636,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A628" s="8">
         <v>45140</v>
       </c>
@@ -69623,7 +69677,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A629" s="8">
         <v>45147</v>
       </c>
@@ -69664,7 +69718,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A630" s="8">
         <v>45154</v>
       </c>
@@ -69705,7 +69759,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A631" s="8">
         <v>45161</v>
       </c>
@@ -69746,7 +69800,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A632" s="8">
         <v>45168</v>
       </c>
@@ -69787,7 +69841,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A633" s="8">
         <v>45175</v>
       </c>
@@ -69828,7 +69882,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A634" s="8">
         <v>45182</v>
       </c>
@@ -69869,7 +69923,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A635" s="8">
         <v>45189</v>
       </c>
@@ -69910,7 +69964,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A636" s="8">
         <v>45196</v>
       </c>
@@ -69951,7 +70005,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A637" s="8">
         <v>45203</v>
       </c>
@@ -69992,7 +70046,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A638" s="8">
         <v>45210</v>
       </c>
@@ -70033,7 +70087,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A639" s="8">
         <v>45217</v>
       </c>
@@ -70074,7 +70128,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A640" s="8">
         <v>45224</v>
       </c>
@@ -70115,7 +70169,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A641" s="8">
         <v>45231</v>
       </c>
@@ -70156,7 +70210,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A642" s="8">
         <v>45238</v>
       </c>
@@ -70197,7 +70251,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A643" s="8">
         <v>45245</v>
       </c>
@@ -70238,7 +70292,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A644" s="8">
         <v>45252</v>
       </c>
@@ -70279,7 +70333,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A645" s="8">
         <v>45259</v>
       </c>
@@ -70320,7 +70374,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A646" s="8">
         <v>45266</v>
       </c>
@@ -70361,7 +70415,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A647" s="8">
         <v>45273</v>
       </c>
@@ -70402,7 +70456,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A648" s="8">
         <v>45280</v>
       </c>
@@ -70443,7 +70497,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A649" s="8">
         <v>45294</v>
       </c>
@@ -70484,7 +70538,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A650" s="8">
         <v>45301</v>
       </c>
@@ -70525,7 +70579,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A651" s="8">
         <v>45308</v>
       </c>
@@ -70566,7 +70620,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A652" s="8">
         <v>45315</v>
       </c>
@@ -70607,7 +70661,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A653" s="8">
         <v>45322</v>
       </c>
@@ -70648,7 +70702,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A654" s="8">
         <v>45329</v>
       </c>
@@ -70689,7 +70743,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A655" s="8">
         <v>45336</v>
       </c>
@@ -70730,7 +70784,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A656" s="8">
         <v>45343</v>
       </c>
@@ -70771,7 +70825,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A657" s="8">
         <v>45350</v>
       </c>
@@ -70812,7 +70866,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A658" s="8">
         <v>45357</v>
       </c>
@@ -70853,7 +70907,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A659" s="8">
         <v>45364</v>
       </c>
@@ -70894,7 +70948,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A660" s="8">
         <v>45371</v>
       </c>
@@ -70935,7 +70989,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A661" s="8">
         <v>45378</v>
       </c>
@@ -70976,7 +71030,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A662" s="8">
         <v>45385</v>
       </c>
@@ -71017,7 +71071,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A663" s="8">
         <v>45392</v>
       </c>
@@ -71058,7 +71112,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A664" s="8">
         <v>45399</v>
       </c>
@@ -71099,7 +71153,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A665" s="8">
         <v>45406</v>
       </c>
@@ -71140,7 +71194,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A666" s="8">
         <v>45413</v>
       </c>
@@ -71181,7 +71235,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A667" s="8">
         <v>45420</v>
       </c>
@@ -71222,7 +71276,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A668" s="8">
         <v>45427</v>
       </c>
@@ -71263,7 +71317,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A669" s="8">
         <v>45434</v>
       </c>
@@ -71304,7 +71358,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A670" s="8">
         <v>45441</v>
       </c>
@@ -71345,7 +71399,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A671" s="8">
         <v>45448</v>
       </c>
@@ -71386,7 +71440,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A672" s="8">
         <v>45455</v>
       </c>
@@ -71427,7 +71481,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A673" s="8">
         <v>45462</v>
       </c>
@@ -71468,7 +71522,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A674" s="8">
         <v>45469</v>
       </c>
@@ -71509,7 +71563,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A675" s="8">
         <v>45476</v>
       </c>
@@ -71550,7 +71604,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A676" s="8">
         <v>45483</v>
       </c>
@@ -71591,7 +71645,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A677" s="8">
         <v>45490</v>
       </c>
@@ -71632,7 +71686,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A678" s="8">
         <v>45497</v>
       </c>
@@ -71673,7 +71727,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A679" s="8">
         <v>45504</v>
       </c>
@@ -71714,7 +71768,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A680" s="8">
         <v>45511</v>
       </c>
@@ -71755,7 +71809,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A681" s="8">
         <v>45518</v>
       </c>
@@ -71796,7 +71850,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A682" s="8">
         <v>45525</v>
       </c>
@@ -71837,7 +71891,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A683" s="8">
         <v>45532</v>
       </c>
@@ -71878,7 +71932,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A684" s="8">
         <v>45539</v>
       </c>
@@ -71919,7 +71973,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A685" s="8">
         <v>45546</v>
       </c>
@@ -71960,7 +72014,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A686" s="8">
         <v>45553</v>
       </c>
@@ -72001,7 +72055,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A687" s="8">
         <v>45560</v>
       </c>
@@ -72042,7 +72096,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A688" s="8">
         <v>45567</v>
       </c>
@@ -72083,7 +72137,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A689" s="8">
         <v>45574</v>
       </c>
@@ -72124,7 +72178,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A690" s="8">
         <v>45581</v>
       </c>
@@ -72165,7 +72219,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A691" s="8">
         <v>45588</v>
       </c>
@@ -72206,7 +72260,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A692" s="8">
         <v>45595</v>
       </c>
@@ -72247,7 +72301,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A693" s="8">
         <v>45602</v>
       </c>
@@ -72288,7 +72342,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A694" s="8">
         <v>45609</v>
       </c>
@@ -72329,7 +72383,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A695" s="8">
         <v>45616</v>
       </c>
@@ -72370,7 +72424,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A696" s="8">
         <v>45623</v>
       </c>
@@ -72411,7 +72465,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A697" s="8">
         <v>45630</v>
       </c>
@@ -72452,7 +72506,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A698" s="8">
         <v>45637</v>
       </c>
@@ -72493,7 +72547,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A699" s="8">
         <v>45644</v>
       </c>
@@ -72534,7 +72588,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A700" s="8">
         <v>45658</v>
       </c>
@@ -72575,7 +72629,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A701" s="8">
         <v>45665</v>
       </c>
@@ -72616,7 +72670,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A702" s="8">
         <v>45672</v>
       </c>
@@ -72657,7 +72711,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A703" s="8">
         <v>45679</v>
       </c>
@@ -72698,7 +72752,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A704" s="8">
         <v>45686</v>
       </c>
@@ -72739,7 +72793,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A705" s="8">
         <v>45693</v>
       </c>
@@ -72780,7 +72834,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A706" s="8">
         <v>45700</v>
       </c>
@@ -72821,7 +72875,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A707" s="8">
         <v>45707</v>
       </c>
@@ -72862,7 +72916,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A708" s="8">
         <v>45714</v>
       </c>
@@ -72903,7 +72957,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A709" s="8">
         <v>45721</v>
       </c>
@@ -72944,7 +72998,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A710" s="8">
         <v>45728</v>
       </c>
@@ -72985,7 +73039,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A711" s="8">
         <v>45735</v>
       </c>
@@ -73026,7 +73080,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A712" s="8">
         <v>45742</v>
       </c>
@@ -73067,7 +73121,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A713" s="8">
         <v>45749</v>
       </c>
@@ -73108,7 +73162,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A714" s="8">
         <v>45756</v>
       </c>
@@ -73149,7 +73203,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A715" s="8">
         <v>45763</v>
       </c>
@@ -73190,7 +73244,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A716" s="8">
         <v>45770</v>
       </c>
@@ -73231,7 +73285,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A717" s="8">
         <v>45777</v>
       </c>
@@ -73272,7 +73326,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A718" s="8">
         <v>45784</v>
       </c>
@@ -73313,7 +73367,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A719" s="8">
         <v>45791</v>
       </c>
@@ -73354,7 +73408,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A720" s="8">
         <v>45798</v>
       </c>
@@ -73395,7 +73449,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A721" s="8">
         <v>45805</v>
       </c>
@@ -73436,7 +73490,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A722" s="8">
         <v>45812</v>
       </c>
@@ -73477,7 +73531,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A723" s="8">
         <v>45819</v>
       </c>
@@ -73518,7 +73572,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A724" s="8">
         <v>45826</v>
       </c>
@@ -73559,7 +73613,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A725" s="8">
         <v>45833</v>
       </c>
@@ -73600,7 +73654,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A726" s="8">
         <v>45840</v>
       </c>
@@ -73641,7 +73695,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A727" s="8">
         <v>45847</v>
       </c>
@@ -73682,7 +73736,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A728" s="8">
         <v>45854</v>
       </c>
@@ -73723,7 +73777,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A729" s="8">
         <v>45861</v>
       </c>
@@ -73764,7 +73818,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A730" s="8">
         <v>45868</v>
       </c>
@@ -73805,7 +73859,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A731" s="8">
         <v>45875</v>
       </c>
@@ -73846,7 +73900,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A732" s="8">
         <v>45882</v>
       </c>
@@ -73887,7 +73941,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A733" s="8">
         <v>45889</v>
       </c>
@@ -73928,7 +73982,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A734" s="8">
         <v>45896</v>
       </c>
@@ -73969,7 +74023,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A735" s="8">
         <v>45903</v>
       </c>
@@ -74010,7 +74064,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A736" s="8">
         <v>45910</v>
       </c>
@@ -74051,7 +74105,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A737" s="8">
         <v>45917</v>
       </c>
@@ -74092,7 +74146,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A738" s="8">
         <v>45924</v>
       </c>
@@ -74133,7 +74187,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A739" s="8">
         <v>45931</v>
       </c>
@@ -74174,7 +74228,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A740" s="8">
         <v>45938</v>
       </c>
@@ -74215,7 +74269,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A741" s="8">
         <v>45945</v>
       </c>
@@ -74256,7 +74310,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A742" s="8">
         <v>45952</v>
       </c>
@@ -74297,7 +74351,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A743" s="8">
         <v>45959</v>
       </c>
@@ -74338,7 +74392,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A744" s="8">
         <v>45966</v>
       </c>
@@ -74379,7 +74433,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A745" s="8">
         <v>45973</v>
       </c>
@@ -74420,7 +74474,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A746" s="8">
         <v>45980</v>
       </c>
@@ -74461,7 +74515,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A747" s="8">
         <v>45987</v>
       </c>
@@ -74502,7 +74556,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A748" s="8">
         <v>45994</v>
       </c>
@@ -74543,7 +74597,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A749" s="8">
         <v>46001</v>
       </c>
@@ -74584,7 +74638,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A750" s="8">
         <v>46008</v>
       </c>
@@ -74625,7 +74679,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A751" s="8">
         <v>46015</v>
       </c>
@@ -74666,7 +74720,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A752" s="8">
         <v>46022</v>
       </c>
@@ -74707,7 +74761,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A753" s="8">
         <v>46029</v>
       </c>
@@ -74748,7 +74802,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A754" s="8">
         <v>46036</v>
       </c>
@@ -74789,7 +74843,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A755" s="8">
         <v>46043</v>
       </c>
@@ -74830,7 +74884,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A756" s="8">
         <v>46050</v>
       </c>
@@ -74871,7 +74925,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A757" s="8">
         <v>46057</v>
       </c>
@@ -74912,7 +74966,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A758" s="8">
         <v>46064</v>
       </c>
@@ -74953,7 +75007,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A759" s="8">
         <v>46071</v>
       </c>
@@ -74994,7 +75048,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A760" s="8">
         <v>46078</v>
       </c>
@@ -75035,7 +75089,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A761" s="8">
         <v>46085</v>
       </c>
@@ -75076,7 +75130,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A762" s="8">
         <v>46092</v>
       </c>
@@ -75117,7 +75171,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A763" s="8">
         <v>46099</v>
       </c>
@@ -75158,7 +75212,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A764" s="8">
         <v>46106</v>
       </c>
@@ -75199,7 +75253,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A765" s="8">
         <v>46113</v>
       </c>
@@ -75240,7 +75294,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A766" s="8">
         <v>46120</v>
       </c>
@@ -75281,7 +75335,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A767" s="8">
         <v>46127</v>
       </c>
@@ -75322,7 +75376,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A768" s="8">
         <v>46134</v>
       </c>
@@ -75363,7 +75417,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A769" s="8">
         <v>46141</v>
       </c>
@@ -75404,7 +75458,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A770" s="8">
         <v>46148</v>
       </c>
@@ -75445,7 +75499,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A771" s="8">
         <v>46155</v>
       </c>
@@ -75486,7 +75540,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A772" s="8">
         <v>46162</v>
       </c>
@@ -75527,7 +75581,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A773" s="8">
         <v>46169</v>
       </c>
@@ -75568,7 +75622,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A774" s="8">
         <v>46176</v>
       </c>
@@ -75609,7 +75663,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A775" s="8">
         <v>46183</v>
       </c>
@@ -75650,7 +75704,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A776" s="8">
         <v>46190</v>
       </c>
@@ -75691,7 +75745,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="777" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A777" s="8">
         <v>46197</v>
       </c>
@@ -75732,7 +75786,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="778" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A778" s="8">
         <v>46204</v>
       </c>
@@ -75773,7 +75827,7 @@
         <v>2602</v>
       </c>
     </row>
-    <row r="779" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A779" s="8">
         <v>46211</v>
       </c>
@@ -75814,7 +75868,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="780" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A780" s="8">
         <v>46218</v>
       </c>
@@ -75853,6 +75907,47 @@
       </c>
       <c r="M780" s="11">
         <v>2667</v>
+      </c>
+    </row>
+    <row r="781" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A781" s="8">
+        <v>46225</v>
+      </c>
+      <c r="B781" s="8">
+        <v>46226</v>
+      </c>
+      <c r="C781" s="9">
+        <v>0.58333333334078497</v>
+      </c>
+      <c r="D781" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E781" s="10">
+        <v>4373.7</v>
+      </c>
+      <c r="F781" s="11">
+        <v>4824</v>
+      </c>
+      <c r="G781" s="11">
+        <v>5988</v>
+      </c>
+      <c r="H781" s="11">
+        <v>5878</v>
+      </c>
+      <c r="I781" s="11">
+        <v>7598</v>
+      </c>
+      <c r="J781" s="11">
+        <v>607</v>
+      </c>
+      <c r="K781" s="11">
+        <v>839</v>
+      </c>
+      <c r="L781" s="11">
+        <v>1050</v>
+      </c>
+      <c r="M781" s="11">
+        <v>2635</v>
       </c>
     </row>
   </sheetData>
@@ -75865,7 +75960,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75876,12 +75971,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
@@ -75900,7 +75995,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27E30FC-979A-4389-8403-C5AA3F7F6F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF97501-640E-144F-A48F-22CED107A883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26780" yWindow="4880" windowWidth="23880" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -107,29 +107,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,7 +138,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,7 +146,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -195,35 +195,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -241,7 +241,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2630,6 +2630,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4978,6 +4981,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>4373.7</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>4254.7299999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7362,6 +7368,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9710,6 +9719,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>4824</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>4667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12094,6 +12106,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14442,6 +14457,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>5988</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>5630</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16826,6 +16844,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19174,6 +19195,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>5878</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>5739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21558,6 +21582,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23906,6 +23933,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>7598</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>7578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26290,6 +26320,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28638,6 +28671,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>607</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>589</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -31024,6 +31060,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33372,6 +33411,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>839</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>859</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35758,6 +35800,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -38106,6 +38151,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>1103</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40492,6 +40540,9 @@
                 <c:pt idx="779">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="780">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42840,6 +42891,9 @@
                 </c:pt>
                 <c:pt idx="779">
                   <c:v>2635</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>2719</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43917,19 +43971,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M781"/>
-  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M782"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="10.5" style="11" customWidth="1"/>
     <col min="14" max="16384" width="7.5" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -43970,7 +44024,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>40716</v>
       </c>
@@ -44011,7 +44065,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>40723</v>
       </c>
@@ -44052,7 +44106,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>40730</v>
       </c>
@@ -44093,7 +44147,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>40737</v>
       </c>
@@ -44134,7 +44188,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>40744</v>
       </c>
@@ -44175,7 +44229,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>40751</v>
       </c>
@@ -44216,7 +44270,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>40758</v>
       </c>
@@ -44257,7 +44311,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>40765</v>
       </c>
@@ -44298,7 +44352,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>40772</v>
       </c>
@@ -44339,7 +44393,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>40779</v>
       </c>
@@ -44380,7 +44434,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>40786</v>
       </c>
@@ -44421,7 +44475,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>40793</v>
       </c>
@@ -44462,7 +44516,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>40800</v>
       </c>
@@ -44503,7 +44557,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>40807</v>
       </c>
@@ -44544,7 +44598,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>40814</v>
       </c>
@@ -44585,7 +44639,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>40821</v>
       </c>
@@ -44626,7 +44680,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>40828</v>
       </c>
@@ -44667,7 +44721,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>40835</v>
       </c>
@@ -44708,7 +44762,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>40842</v>
       </c>
@@ -44749,7 +44803,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>40849</v>
       </c>
@@ -44790,7 +44844,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>40856</v>
       </c>
@@ -44831,7 +44885,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>40863</v>
       </c>
@@ -44872,7 +44926,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>40870</v>
       </c>
@@ -44913,7 +44967,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>40877</v>
       </c>
@@ -44954,7 +45008,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>40884</v>
       </c>
@@ -44995,7 +45049,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>40891</v>
       </c>
@@ -45036,7 +45090,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>40898</v>
       </c>
@@ -45077,7 +45131,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>40905</v>
       </c>
@@ -45118,7 +45172,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>40912</v>
       </c>
@@ -45159,7 +45213,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>40919</v>
       </c>
@@ -45200,7 +45254,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>40926</v>
       </c>
@@ -45241,7 +45295,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>40933</v>
       </c>
@@ -45282,7 +45336,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>40940</v>
       </c>
@@ -45323,7 +45377,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>40947</v>
       </c>
@@ -45364,7 +45418,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>40954</v>
       </c>
@@ -45405,7 +45459,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>40961</v>
       </c>
@@ -45446,7 +45500,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>40968</v>
       </c>
@@ -45487,7 +45541,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>40975</v>
       </c>
@@ -45528,7 +45582,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>40982</v>
       </c>
@@ -45569,7 +45623,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>40989</v>
       </c>
@@ -45610,7 +45664,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>40996</v>
       </c>
@@ -45651,7 +45705,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>41003</v>
       </c>
@@ -45692,7 +45746,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>41010</v>
       </c>
@@ -45733,7 +45787,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>41017</v>
       </c>
@@ -45774,7 +45828,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>41024</v>
       </c>
@@ -45815,7 +45869,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>41031</v>
       </c>
@@ -45856,7 +45910,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>41038</v>
       </c>
@@ -45897,7 +45951,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>41045</v>
       </c>
@@ -45938,7 +45992,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>41052</v>
       </c>
@@ -45979,7 +46033,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>41059</v>
       </c>
@@ -46020,7 +46074,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>41066</v>
       </c>
@@ -46061,7 +46115,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>41073</v>
       </c>
@@ -46102,7 +46156,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>41080</v>
       </c>
@@ -46143,7 +46197,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>41087</v>
       </c>
@@ -46184,7 +46238,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>41094</v>
       </c>
@@ -46225,7 +46279,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>41101</v>
       </c>
@@ -46266,7 +46320,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>41108</v>
       </c>
@@ -46307,7 +46361,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>41115</v>
       </c>
@@ -46348,7 +46402,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>41122</v>
       </c>
@@ -46389,7 +46443,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>41129</v>
       </c>
@@ -46430,7 +46484,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>41136</v>
       </c>
@@ -46471,7 +46525,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>41143</v>
       </c>
@@ -46512,7 +46566,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>41150</v>
       </c>
@@ -46553,7 +46607,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>41157</v>
       </c>
@@ -46594,7 +46648,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>41164</v>
       </c>
@@ -46635,7 +46689,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>41171</v>
       </c>
@@ -46676,7 +46730,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>41178</v>
       </c>
@@ -46717,7 +46771,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>41185</v>
       </c>
@@ -46758,7 +46812,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>41192</v>
       </c>
@@ -46799,7 +46853,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>41199</v>
       </c>
@@ -46840,7 +46894,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>41206</v>
       </c>
@@ -46881,7 +46935,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>41213</v>
       </c>
@@ -46922,7 +46976,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>41220</v>
       </c>
@@ -46963,7 +47017,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>41227</v>
       </c>
@@ -47004,7 +47058,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>41234</v>
       </c>
@@ -47045,7 +47099,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>41241</v>
       </c>
@@ -47086,7 +47140,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>41248</v>
       </c>
@@ -47127,7 +47181,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>41255</v>
       </c>
@@ -47168,7 +47222,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>41262</v>
       </c>
@@ -47209,7 +47263,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>41269</v>
       </c>
@@ -47250,7 +47304,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>41276</v>
       </c>
@@ -47291,7 +47345,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>41283</v>
       </c>
@@ -47332,7 +47386,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>41290</v>
       </c>
@@ -47373,7 +47427,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>41297</v>
       </c>
@@ -47414,7 +47468,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>41304</v>
       </c>
@@ -47455,7 +47509,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>41311</v>
       </c>
@@ -47496,7 +47550,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>41318</v>
       </c>
@@ -47537,7 +47591,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>41325</v>
       </c>
@@ -47578,7 +47632,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>41332</v>
       </c>
@@ -47619,7 +47673,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>41339</v>
       </c>
@@ -47660,7 +47714,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>41346</v>
       </c>
@@ -47701,7 +47755,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>41353</v>
       </c>
@@ -47742,7 +47796,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>41360</v>
       </c>
@@ -47783,7 +47837,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>41367</v>
       </c>
@@ -47824,7 +47878,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>41374</v>
       </c>
@@ -47865,7 +47919,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>41381</v>
       </c>
@@ -47906,7 +47960,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>41388</v>
       </c>
@@ -47947,7 +48001,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>41395</v>
       </c>
@@ -47988,7 +48042,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>41402</v>
       </c>
@@ -48029,7 +48083,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>41409</v>
       </c>
@@ -48070,7 +48124,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>41416</v>
       </c>
@@ -48111,7 +48165,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>41423</v>
       </c>
@@ -48152,7 +48206,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>41430</v>
       </c>
@@ -48193,7 +48247,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>41437</v>
       </c>
@@ -48234,7 +48288,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>41444</v>
       </c>
@@ -48275,7 +48329,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>41451</v>
       </c>
@@ -48316,7 +48370,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>41458</v>
       </c>
@@ -48357,7 +48411,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>41465</v>
       </c>
@@ -48398,7 +48452,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>41472</v>
       </c>
@@ -48439,7 +48493,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>41479</v>
       </c>
@@ -48480,7 +48534,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>41486</v>
       </c>
@@ -48521,7 +48575,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>41493</v>
       </c>
@@ -48562,7 +48616,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="8">
         <v>41500</v>
       </c>
@@ -48603,7 +48657,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="8">
         <v>41507</v>
       </c>
@@ -48644,7 +48698,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="8">
         <v>41514</v>
       </c>
@@ -48685,7 +48739,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="8">
         <v>41521</v>
       </c>
@@ -48726,7 +48780,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="8">
         <v>41528</v>
       </c>
@@ -48767,7 +48821,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="8">
         <v>41535</v>
       </c>
@@ -48808,7 +48862,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="8">
         <v>41542</v>
       </c>
@@ -48849,7 +48903,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="8">
         <v>41549</v>
       </c>
@@ -48890,7 +48944,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="8">
         <v>41556</v>
       </c>
@@ -48931,7 +48985,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="8">
         <v>41563</v>
       </c>
@@ -48972,7 +49026,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="8">
         <v>41570</v>
       </c>
@@ -49013,7 +49067,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
         <v>41577</v>
       </c>
@@ -49054,7 +49108,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
         <v>41584</v>
       </c>
@@ -49095,7 +49149,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
         <v>41591</v>
       </c>
@@ -49136,7 +49190,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
         <v>41598</v>
       </c>
@@ -49177,7 +49231,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
         <v>41605</v>
       </c>
@@ -49218,7 +49272,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
         <v>41612</v>
       </c>
@@ -49259,7 +49313,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <v>41619</v>
       </c>
@@ -49300,7 +49354,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <v>41626</v>
       </c>
@@ -49341,7 +49395,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <v>41640</v>
       </c>
@@ -49382,7 +49436,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <v>41647</v>
       </c>
@@ -49423,7 +49477,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <v>41654</v>
       </c>
@@ -49464,7 +49518,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <v>41661</v>
       </c>
@@ -49505,7 +49559,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <v>41668</v>
       </c>
@@ -49546,7 +49600,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <v>41675</v>
       </c>
@@ -49587,7 +49641,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
         <v>41682</v>
       </c>
@@ -49628,7 +49682,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
         <v>41689</v>
       </c>
@@ -49669,7 +49723,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
         <v>41696</v>
       </c>
@@ -49710,7 +49764,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
         <v>41703</v>
       </c>
@@ -49751,7 +49805,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
         <v>41710</v>
       </c>
@@ -49792,7 +49846,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
         <v>41717</v>
       </c>
@@ -49833,7 +49887,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
         <v>41724</v>
       </c>
@@ -49874,7 +49928,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <v>41731</v>
       </c>
@@ -49915,7 +49969,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <v>41738</v>
       </c>
@@ -49956,7 +50010,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <v>41745</v>
       </c>
@@ -49997,7 +50051,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <v>41752</v>
       </c>
@@ -50038,7 +50092,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <v>41759</v>
       </c>
@@ -50079,7 +50133,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <v>41766</v>
       </c>
@@ -50120,7 +50174,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <v>41773</v>
       </c>
@@ -50161,7 +50215,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <v>41780</v>
       </c>
@@ -50202,7 +50256,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <v>41787</v>
       </c>
@@ -50243,7 +50297,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>41794</v>
       </c>
@@ -50284,7 +50338,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <v>41801</v>
       </c>
@@ -50325,7 +50379,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>41808</v>
       </c>
@@ -50366,7 +50420,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <v>41815</v>
       </c>
@@ -50407,7 +50461,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>41822</v>
       </c>
@@ -50448,7 +50502,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <v>41829</v>
       </c>
@@ -50489,7 +50543,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>41836</v>
       </c>
@@ -50530,7 +50584,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <v>41843</v>
       </c>
@@ -50571,7 +50625,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>41850</v>
       </c>
@@ -50612,7 +50666,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <v>41857</v>
       </c>
@@ -50653,7 +50707,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>41864</v>
       </c>
@@ -50694,7 +50748,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="8">
         <v>41871</v>
       </c>
@@ -50735,7 +50789,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>41878</v>
       </c>
@@ -50776,7 +50830,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
         <v>41885</v>
       </c>
@@ -50817,7 +50871,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>41892</v>
       </c>
@@ -50858,7 +50912,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="8">
         <v>41899</v>
       </c>
@@ -50899,7 +50953,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>41906</v>
       </c>
@@ -50940,7 +50994,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="8">
         <v>41913</v>
       </c>
@@ -50981,7 +51035,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" s="8">
         <v>41920</v>
       </c>
@@ -51022,7 +51076,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" s="8">
         <v>41927</v>
       </c>
@@ -51063,7 +51117,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" s="8">
         <v>41934</v>
       </c>
@@ -51104,7 +51158,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" s="8">
         <v>41941</v>
       </c>
@@ -51145,7 +51199,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <v>41948</v>
       </c>
@@ -51186,7 +51240,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" s="8">
         <v>41955</v>
       </c>
@@ -51227,7 +51281,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" s="8">
         <v>41962</v>
       </c>
@@ -51268,7 +51322,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" s="8">
         <v>41969</v>
       </c>
@@ -51309,7 +51363,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <v>41976</v>
       </c>
@@ -51350,7 +51404,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <v>41983</v>
       </c>
@@ -51391,7 +51445,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <v>41990</v>
       </c>
@@ -51432,7 +51486,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" s="8">
         <v>42011</v>
       </c>
@@ -51473,7 +51527,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <v>42018</v>
       </c>
@@ -51514,7 +51568,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <v>42025</v>
       </c>
@@ -51555,7 +51609,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <v>42032</v>
       </c>
@@ -51596,7 +51650,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <v>42039</v>
       </c>
@@ -51637,7 +51691,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <v>42046</v>
       </c>
@@ -51678,7 +51732,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <v>42053</v>
       </c>
@@ -51719,7 +51773,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <v>42060</v>
       </c>
@@ -51760,7 +51814,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <v>42067</v>
       </c>
@@ -51801,7 +51855,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <v>42074</v>
       </c>
@@ -51842,7 +51896,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <v>42081</v>
       </c>
@@ -51883,7 +51937,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <v>42088</v>
       </c>
@@ -51924,7 +51978,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <v>42095</v>
       </c>
@@ -51965,7 +52019,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <v>42102</v>
       </c>
@@ -52006,7 +52060,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <v>42109</v>
       </c>
@@ -52047,7 +52101,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <v>42116</v>
       </c>
@@ -52088,7 +52142,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <v>42123</v>
       </c>
@@ -52129,7 +52183,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <v>42130</v>
       </c>
@@ -52170,7 +52224,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <v>42137</v>
       </c>
@@ -52211,7 +52265,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <v>42144</v>
       </c>
@@ -52252,7 +52306,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <v>42151</v>
       </c>
@@ -52293,7 +52347,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <v>42158</v>
       </c>
@@ -52334,7 +52388,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <v>42165</v>
       </c>
@@ -52375,7 +52429,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <v>42172</v>
       </c>
@@ -52416,7 +52470,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <v>42179</v>
       </c>
@@ -52457,7 +52511,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <v>42186</v>
       </c>
@@ -52498,7 +52552,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <v>42193</v>
       </c>
@@ -52539,7 +52593,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <v>42200</v>
       </c>
@@ -52580,7 +52634,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <v>42207</v>
       </c>
@@ -52621,7 +52675,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <v>42214</v>
       </c>
@@ -52662,7 +52716,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <v>42221</v>
       </c>
@@ -52703,7 +52757,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <v>42228</v>
       </c>
@@ -52744,7 +52798,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <v>42235</v>
       </c>
@@ -52785,7 +52839,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <v>42242</v>
       </c>
@@ -52826,7 +52880,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <v>42249</v>
       </c>
@@ -52867,7 +52921,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <v>42256</v>
       </c>
@@ -52908,7 +52962,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <v>42263</v>
       </c>
@@ -52949,7 +53003,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <v>42270</v>
       </c>
@@ -52990,7 +53044,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <v>42277</v>
       </c>
@@ -53031,7 +53085,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <v>42284</v>
       </c>
@@ -53072,7 +53126,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <v>42291</v>
       </c>
@@ -53113,7 +53167,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <v>42298</v>
       </c>
@@ -53154,7 +53208,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <v>42305</v>
       </c>
@@ -53195,7 +53249,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <v>42312</v>
       </c>
@@ -53236,7 +53290,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <v>42319</v>
       </c>
@@ -53277,7 +53331,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <v>42326</v>
       </c>
@@ -53318,7 +53372,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <v>42333</v>
       </c>
@@ -53359,7 +53413,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <v>42340</v>
       </c>
@@ -53400,7 +53454,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <v>42347</v>
       </c>
@@ -53441,7 +53495,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <v>42354</v>
       </c>
@@ -53482,7 +53536,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <v>42361</v>
       </c>
@@ -53523,7 +53577,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <v>42368</v>
       </c>
@@ -53564,7 +53618,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <v>42375</v>
       </c>
@@ -53605,7 +53659,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <v>42382</v>
       </c>
@@ -53646,7 +53700,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <v>42389</v>
       </c>
@@ -53687,7 +53741,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <v>42396</v>
       </c>
@@ -53728,7 +53782,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <v>42403</v>
       </c>
@@ -53769,7 +53823,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <v>42410</v>
       </c>
@@ -53810,7 +53864,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <v>42417</v>
       </c>
@@ -53851,7 +53905,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <v>42424</v>
       </c>
@@ -53892,7 +53946,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <v>42431</v>
       </c>
@@ -53933,7 +53987,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <v>42438</v>
       </c>
@@ -53974,7 +54028,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <v>42445</v>
       </c>
@@ -54015,7 +54069,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <v>42452</v>
       </c>
@@ -54056,7 +54110,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <v>42459</v>
       </c>
@@ -54097,7 +54151,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <v>42466</v>
       </c>
@@ -54138,7 +54192,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <v>42473</v>
       </c>
@@ -54179,7 +54233,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <v>42480</v>
       </c>
@@ -54220,7 +54274,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <v>42487</v>
       </c>
@@ -54261,7 +54315,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <v>42494</v>
       </c>
@@ -54302,7 +54356,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <v>42501</v>
       </c>
@@ -54343,7 +54397,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <v>42508</v>
       </c>
@@ -54384,7 +54438,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <v>42515</v>
       </c>
@@ -54425,7 +54479,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <v>42522</v>
       </c>
@@ -54466,7 +54520,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <v>42529</v>
       </c>
@@ -54507,7 +54561,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="8">
         <v>42536</v>
       </c>
@@ -54548,7 +54602,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" s="8">
         <v>42543</v>
       </c>
@@ -54589,7 +54643,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" s="8">
         <v>42550</v>
       </c>
@@ -54630,7 +54684,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262" s="8">
         <v>42557</v>
       </c>
@@ -54671,7 +54725,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="8">
         <v>42564</v>
       </c>
@@ -54712,7 +54766,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" s="8">
         <v>42571</v>
       </c>
@@ -54753,7 +54807,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" s="8">
         <v>42578</v>
       </c>
@@ -54794,7 +54848,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" s="8">
         <v>42585</v>
       </c>
@@ -54835,7 +54889,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" s="8">
         <v>42592</v>
       </c>
@@ -54876,7 +54930,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" s="8">
         <v>42599</v>
       </c>
@@ -54917,7 +54971,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" s="8">
         <v>42606</v>
       </c>
@@ -54958,7 +55012,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270" s="8">
         <v>42613</v>
       </c>
@@ -54999,7 +55053,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <v>42620</v>
       </c>
@@ -55040,7 +55094,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <v>42627</v>
       </c>
@@ -55081,7 +55135,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <v>42634</v>
       </c>
@@ -55122,7 +55176,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <v>42641</v>
       </c>
@@ -55163,7 +55217,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <v>42648</v>
       </c>
@@ -55204,7 +55258,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <v>42655</v>
       </c>
@@ -55245,7 +55299,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <v>42662</v>
       </c>
@@ -55286,7 +55340,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <v>42669</v>
       </c>
@@ -55327,7 +55381,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <v>42676</v>
       </c>
@@ -55368,7 +55422,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <v>42683</v>
       </c>
@@ -55409,7 +55463,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <v>42690</v>
       </c>
@@ -55450,7 +55504,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <v>42697</v>
       </c>
@@ -55491,7 +55545,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <v>42704</v>
       </c>
@@ -55532,7 +55586,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <v>42711</v>
       </c>
@@ -55573,7 +55627,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <v>42718</v>
       </c>
@@ -55614,7 +55668,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <v>42725</v>
       </c>
@@ -55655,7 +55709,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A287" s="8">
         <v>42732</v>
       </c>
@@ -55696,7 +55750,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A288" s="8">
         <v>42739</v>
       </c>
@@ -55737,7 +55791,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289" s="8">
         <v>42746</v>
       </c>
@@ -55778,7 +55832,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290" s="8">
         <v>42753</v>
       </c>
@@ -55819,7 +55873,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291" s="8">
         <v>42760</v>
       </c>
@@ -55860,7 +55914,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" s="8">
         <v>42767</v>
       </c>
@@ -55901,7 +55955,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293" s="8">
         <v>42774</v>
       </c>
@@ -55942,7 +55996,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294" s="8">
         <v>42781</v>
       </c>
@@ -55983,7 +56037,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295" s="8">
         <v>42788</v>
       </c>
@@ -56024,7 +56078,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296" s="8">
         <v>42795</v>
       </c>
@@ -56065,7 +56119,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297" s="8">
         <v>42802</v>
       </c>
@@ -56106,7 +56160,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298" s="8">
         <v>42809</v>
       </c>
@@ -56147,7 +56201,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299" s="8">
         <v>42816</v>
       </c>
@@ -56188,7 +56242,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300" s="8">
         <v>42823</v>
       </c>
@@ -56229,7 +56283,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301" s="8">
         <v>42830</v>
       </c>
@@ -56270,7 +56324,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302" s="8">
         <v>42837</v>
       </c>
@@ -56311,7 +56365,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303" s="8">
         <v>42844</v>
       </c>
@@ -56352,7 +56406,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304" s="8">
         <v>42851</v>
       </c>
@@ -56393,7 +56447,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305" s="8">
         <v>42858</v>
       </c>
@@ -56434,7 +56488,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306" s="8">
         <v>42865</v>
       </c>
@@ -56475,7 +56529,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307" s="8">
         <v>42872</v>
       </c>
@@ -56516,7 +56570,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308" s="8">
         <v>42879</v>
       </c>
@@ -56557,7 +56611,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309" s="8">
         <v>42886</v>
       </c>
@@ -56598,7 +56652,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310" s="8">
         <v>42893</v>
       </c>
@@ -56639,7 +56693,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" s="8">
         <v>42900</v>
       </c>
@@ -56680,7 +56734,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312" s="8">
         <v>42907</v>
       </c>
@@ -56721,7 +56775,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313" s="8">
         <v>42914</v>
       </c>
@@ -56762,7 +56816,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314" s="8">
         <v>42921</v>
       </c>
@@ -56803,7 +56857,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315" s="8">
         <v>42928</v>
       </c>
@@ -56844,7 +56898,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316" s="8">
         <v>42935</v>
       </c>
@@ -56885,7 +56939,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317" s="8">
         <v>42942</v>
       </c>
@@ -56926,7 +56980,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318" s="8">
         <v>42949</v>
       </c>
@@ -56967,7 +57021,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319" s="8">
         <v>42956</v>
       </c>
@@ -57008,7 +57062,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320" s="8">
         <v>42963</v>
       </c>
@@ -57049,7 +57103,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321" s="8">
         <v>42970</v>
       </c>
@@ -57090,7 +57144,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" s="8">
         <v>42977</v>
       </c>
@@ -57131,7 +57185,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" s="8">
         <v>42984</v>
       </c>
@@ -57172,7 +57226,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" s="8">
         <v>42991</v>
       </c>
@@ -57213,7 +57267,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325" s="8">
         <v>42998</v>
       </c>
@@ -57254,7 +57308,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A326" s="8">
         <v>43005</v>
       </c>
@@ -57295,7 +57349,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327" s="8">
         <v>43012</v>
       </c>
@@ -57336,7 +57390,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A328" s="8">
         <v>43019</v>
       </c>
@@ -57377,7 +57431,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" s="8">
         <v>43026</v>
       </c>
@@ -57418,7 +57472,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330" s="8">
         <v>43033</v>
       </c>
@@ -57459,7 +57513,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331" s="8">
         <v>43040</v>
       </c>
@@ -57500,7 +57554,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332" s="8">
         <v>43047</v>
       </c>
@@ -57541,7 +57595,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333" s="8">
         <v>43054</v>
       </c>
@@ -57582,7 +57636,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" s="8">
         <v>43061</v>
       </c>
@@ -57623,7 +57677,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" s="8">
         <v>43068</v>
       </c>
@@ -57664,7 +57718,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" s="8">
         <v>43075</v>
       </c>
@@ -57705,7 +57759,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337" s="8">
         <v>43082</v>
       </c>
@@ -57746,7 +57800,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" s="8">
         <v>43089</v>
       </c>
@@ -57787,7 +57841,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339" s="8">
         <v>43096</v>
       </c>
@@ -57828,7 +57882,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" s="8">
         <v>43103</v>
       </c>
@@ -57869,7 +57923,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341" s="8">
         <v>43110</v>
       </c>
@@ -57910,7 +57964,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342" s="8">
         <v>43117</v>
       </c>
@@ -57951,7 +58005,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="8">
         <v>43124</v>
       </c>
@@ -57992,7 +58046,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344" s="8">
         <v>43131</v>
       </c>
@@ -58033,7 +58087,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345" s="8">
         <v>43138</v>
       </c>
@@ -58074,7 +58128,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346" s="8">
         <v>43145</v>
       </c>
@@ -58115,7 +58169,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347" s="8">
         <v>43152</v>
       </c>
@@ -58156,7 +58210,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348" s="8">
         <v>43159</v>
       </c>
@@ -58197,7 +58251,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" s="8">
         <v>43166</v>
       </c>
@@ -58238,7 +58292,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350" s="8">
         <v>43173</v>
       </c>
@@ -58279,7 +58333,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" s="8">
         <v>43180</v>
       </c>
@@ -58320,7 +58374,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="8">
         <v>43187</v>
       </c>
@@ -58361,7 +58415,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="8">
         <v>43194</v>
       </c>
@@ -58402,7 +58456,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="8">
         <v>43201</v>
       </c>
@@ -58443,7 +58497,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="8">
         <v>43208</v>
       </c>
@@ -58484,7 +58538,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="8">
         <v>43215</v>
       </c>
@@ -58525,7 +58579,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="8">
         <v>43222</v>
       </c>
@@ -58566,7 +58620,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="8">
         <v>43229</v>
       </c>
@@ -58607,7 +58661,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="8">
         <v>43236</v>
       </c>
@@ -58648,7 +58702,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" s="8">
         <v>43243</v>
       </c>
@@ -58689,7 +58743,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" s="8">
         <v>43250</v>
       </c>
@@ -58730,7 +58784,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" s="8">
         <v>43257</v>
       </c>
@@ -58771,7 +58825,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" s="8">
         <v>43264</v>
       </c>
@@ -58812,7 +58866,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364" s="8">
         <v>43271</v>
       </c>
@@ -58853,7 +58907,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365" s="8">
         <v>43278</v>
       </c>
@@ -58894,7 +58948,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" s="8">
         <v>43285</v>
       </c>
@@ -58935,7 +58989,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" s="8">
         <v>43292</v>
       </c>
@@ -58976,7 +59030,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" s="8">
         <v>43299</v>
       </c>
@@ -59017,7 +59071,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A369" s="8">
         <v>43306</v>
       </c>
@@ -59058,7 +59112,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370" s="8">
         <v>43313</v>
       </c>
@@ -59099,7 +59153,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A371" s="8">
         <v>43320</v>
       </c>
@@ -59140,7 +59194,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A372" s="8">
         <v>43327</v>
       </c>
@@ -59181,7 +59235,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A373" s="8">
         <v>43334</v>
       </c>
@@ -59222,7 +59276,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A374" s="8">
         <v>43341</v>
       </c>
@@ -59263,7 +59317,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="8">
         <v>43348</v>
       </c>
@@ -59304,7 +59358,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="8">
         <v>43355</v>
       </c>
@@ -59345,7 +59399,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="8">
         <v>43362</v>
       </c>
@@ -59386,7 +59440,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="8">
         <v>43369</v>
       </c>
@@ -59427,7 +59481,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="8">
         <v>43376</v>
       </c>
@@ -59468,7 +59522,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="8">
         <v>43383</v>
       </c>
@@ -59509,7 +59563,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A381" s="8">
         <v>43390</v>
       </c>
@@ -59550,7 +59604,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A382" s="8">
         <v>43397</v>
       </c>
@@ -59591,7 +59645,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A383" s="8">
         <v>43404</v>
       </c>
@@ -59632,7 +59686,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A384" s="8">
         <v>43411</v>
       </c>
@@ -59673,7 +59727,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="8">
         <v>43418</v>
       </c>
@@ -59714,7 +59768,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="8">
         <v>43425</v>
       </c>
@@ -59755,7 +59809,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387" s="8">
         <v>43432</v>
       </c>
@@ -59796,7 +59850,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="8">
         <v>43439</v>
       </c>
@@ -59837,7 +59891,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389" s="8">
         <v>43446</v>
       </c>
@@ -59878,7 +59932,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390" s="8">
         <v>43453</v>
       </c>
@@ -59919,7 +59973,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A391" s="8">
         <v>43460</v>
       </c>
@@ -59960,7 +60014,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="8">
         <v>43467</v>
       </c>
@@ -60001,7 +60055,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="8">
         <v>43474</v>
       </c>
@@ -60042,7 +60096,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="8">
         <v>43481</v>
       </c>
@@ -60083,7 +60137,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="8">
         <v>43488</v>
       </c>
@@ -60124,7 +60178,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="8">
         <v>43495</v>
       </c>
@@ -60165,7 +60219,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="8">
         <v>43502</v>
       </c>
@@ -60206,7 +60260,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="8">
         <v>43509</v>
       </c>
@@ -60247,7 +60301,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="8">
         <v>43516</v>
       </c>
@@ -60288,7 +60342,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="8">
         <v>43523</v>
       </c>
@@ -60329,7 +60383,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="8">
         <v>43530</v>
       </c>
@@ -60370,7 +60424,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="8">
         <v>43537</v>
       </c>
@@ -60411,7 +60465,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="8">
         <v>43544</v>
       </c>
@@ -60452,7 +60506,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="8">
         <v>43551</v>
       </c>
@@ -60493,7 +60547,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="8">
         <v>43558</v>
       </c>
@@ -60534,7 +60588,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="8">
         <v>43565</v>
       </c>
@@ -60575,7 +60629,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A407" s="8">
         <v>43572</v>
       </c>
@@ -60616,7 +60670,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408" s="8">
         <v>43579</v>
       </c>
@@ -60657,7 +60711,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409" s="8">
         <v>43586</v>
       </c>
@@ -60698,7 +60752,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" s="8">
         <v>43593</v>
       </c>
@@ -60739,7 +60793,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="8">
         <v>43600</v>
       </c>
@@ -60780,7 +60834,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="8">
         <v>43607</v>
       </c>
@@ -60821,7 +60875,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="8">
         <v>43614</v>
       </c>
@@ -60862,7 +60916,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="8">
         <v>43621</v>
       </c>
@@ -60903,7 +60957,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A415" s="8">
         <v>43628</v>
       </c>
@@ -60944,7 +60998,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A416" s="8">
         <v>43635</v>
       </c>
@@ -60985,7 +61039,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A417" s="8">
         <v>43642</v>
       </c>
@@ -61026,7 +61080,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" s="8">
         <v>43649</v>
       </c>
@@ -61067,7 +61121,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419" s="8">
         <v>43656</v>
       </c>
@@ -61108,7 +61162,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420" s="8">
         <v>43663</v>
       </c>
@@ -61149,7 +61203,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" s="8">
         <v>43670</v>
       </c>
@@ -61190,7 +61244,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" s="8">
         <v>43677</v>
       </c>
@@ -61231,7 +61285,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423" s="8">
         <v>43684</v>
       </c>
@@ -61272,7 +61326,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424" s="8">
         <v>43691</v>
       </c>
@@ -61313,7 +61367,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425" s="8">
         <v>43698</v>
       </c>
@@ -61354,7 +61408,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426" s="8">
         <v>43705</v>
       </c>
@@ -61395,7 +61449,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" s="8">
         <v>43712</v>
       </c>
@@ -61436,7 +61490,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" s="8">
         <v>43719</v>
       </c>
@@ -61477,7 +61531,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429" s="8">
         <v>43726</v>
       </c>
@@ -61518,7 +61572,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430" s="8">
         <v>43733</v>
       </c>
@@ -61559,7 +61613,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A431" s="8">
         <v>43740</v>
       </c>
@@ -61600,7 +61654,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A432" s="8">
         <v>43747</v>
       </c>
@@ -61641,7 +61695,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A433" s="8">
         <v>43754</v>
       </c>
@@ -61682,7 +61736,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A434" s="8">
         <v>43761</v>
       </c>
@@ -61723,7 +61777,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A435" s="8">
         <v>43768</v>
       </c>
@@ -61764,7 +61818,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436" s="8">
         <v>43775</v>
       </c>
@@ -61805,7 +61859,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A437" s="8">
         <v>43782</v>
       </c>
@@ -61846,7 +61900,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="8">
         <v>43789</v>
       </c>
@@ -61887,7 +61941,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="8">
         <v>43796</v>
       </c>
@@ -61928,7 +61982,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A440" s="8">
         <v>43803</v>
       </c>
@@ -61969,7 +62023,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A441" s="8">
         <v>43810</v>
       </c>
@@ -62010,7 +62064,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A442" s="8">
         <v>43817</v>
       </c>
@@ -62051,7 +62105,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A443" s="8">
         <v>43831</v>
       </c>
@@ -62092,7 +62146,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A444" s="8">
         <v>43838</v>
       </c>
@@ -62133,7 +62187,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="8">
         <v>43845</v>
       </c>
@@ -62174,7 +62228,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="8">
         <v>43852</v>
       </c>
@@ -62215,7 +62269,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="8">
         <v>43859</v>
       </c>
@@ -62256,7 +62310,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A448" s="8">
         <v>43866</v>
       </c>
@@ -62297,7 +62351,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A449" s="8">
         <v>43873</v>
       </c>
@@ -62338,7 +62392,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A450" s="8">
         <v>43880</v>
       </c>
@@ -62379,7 +62433,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A451" s="8">
         <v>43887</v>
       </c>
@@ -62420,7 +62474,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="8">
         <v>43894</v>
       </c>
@@ -62461,7 +62515,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453" s="8">
         <v>43901</v>
       </c>
@@ -62502,7 +62556,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A454" s="8">
         <v>43908</v>
       </c>
@@ -62543,7 +62597,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A455" s="8">
         <v>43915</v>
       </c>
@@ -62584,7 +62638,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456" s="8">
         <v>43922</v>
       </c>
@@ -62625,7 +62679,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457" s="8">
         <v>43929</v>
       </c>
@@ -62666,7 +62720,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458" s="8">
         <v>43936</v>
       </c>
@@ -62707,7 +62761,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459" s="8">
         <v>43943</v>
       </c>
@@ -62748,7 +62802,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460" s="8">
         <v>43950</v>
       </c>
@@ -62789,7 +62843,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461" s="8">
         <v>43957</v>
       </c>
@@ -62830,7 +62884,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462" s="8">
         <v>43964</v>
       </c>
@@ -62871,7 +62925,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463" s="8">
         <v>43971</v>
       </c>
@@ -62912,7 +62966,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464" s="8">
         <v>43978</v>
       </c>
@@ -62953,7 +63007,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A465" s="8">
         <v>43985</v>
       </c>
@@ -62994,7 +63048,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A466" s="8">
         <v>43992</v>
       </c>
@@ -63035,7 +63089,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A467" s="8">
         <v>43999</v>
       </c>
@@ -63076,7 +63130,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A468" s="8">
         <v>44006</v>
       </c>
@@ -63117,7 +63171,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A469" s="8">
         <v>44013</v>
       </c>
@@ -63158,7 +63212,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A470" s="8">
         <v>44020</v>
       </c>
@@ -63199,7 +63253,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A471" s="8">
         <v>44027</v>
       </c>
@@ -63240,7 +63294,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="8">
         <v>44034</v>
       </c>
@@ -63281,7 +63335,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A473" s="8">
         <v>44041</v>
       </c>
@@ -63322,7 +63376,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="8">
         <v>44048</v>
       </c>
@@ -63363,7 +63417,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A475" s="8">
         <v>44055</v>
       </c>
@@ -63404,7 +63458,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="8">
         <v>44062</v>
       </c>
@@ -63445,7 +63499,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A477" s="8">
         <v>44069</v>
       </c>
@@ -63486,7 +63540,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A478" s="8">
         <v>44076</v>
       </c>
@@ -63527,7 +63581,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A479" s="8">
         <v>44083</v>
       </c>
@@ -63568,7 +63622,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A480" s="8">
         <v>44090</v>
       </c>
@@ -63609,7 +63663,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A481" s="8">
         <v>44097</v>
       </c>
@@ -63650,7 +63704,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A482" s="8">
         <v>44104</v>
       </c>
@@ -63691,7 +63745,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="8">
         <v>44111</v>
       </c>
@@ -63732,7 +63786,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A484" s="8">
         <v>44118</v>
       </c>
@@ -63773,7 +63827,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A485" s="8">
         <v>44125</v>
       </c>
@@ -63814,7 +63868,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="8">
         <v>44132</v>
       </c>
@@ -63855,7 +63909,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A487" s="8">
         <v>44139</v>
       </c>
@@ -63896,7 +63950,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A488" s="8">
         <v>44146</v>
       </c>
@@ -63937,7 +63991,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A489" s="8">
         <v>44153</v>
       </c>
@@ -63978,7 +64032,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A490" s="8">
         <v>44160</v>
       </c>
@@ -64019,7 +64073,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="8">
         <v>44167</v>
       </c>
@@ -64060,7 +64114,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A492" s="8">
         <v>44174</v>
       </c>
@@ -64101,7 +64155,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A493" s="8">
         <v>44181</v>
       </c>
@@ -64142,7 +64196,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A494" s="8">
         <v>44188</v>
       </c>
@@ -64183,7 +64237,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A495" s="8">
         <v>44195</v>
       </c>
@@ -64224,7 +64278,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A496" s="8">
         <v>44202</v>
       </c>
@@ -64265,7 +64319,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A497" s="8">
         <v>44209</v>
       </c>
@@ -64306,7 +64360,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A498" s="8">
         <v>44216</v>
       </c>
@@ -64347,7 +64401,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A499" s="8">
         <v>44223</v>
       </c>
@@ -64388,7 +64442,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A500" s="8">
         <v>44230</v>
       </c>
@@ -64429,7 +64483,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A501" s="8">
         <v>44237</v>
       </c>
@@ -64470,7 +64524,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A502" s="8">
         <v>44244</v>
       </c>
@@ -64511,7 +64565,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A503" s="8">
         <v>44251</v>
       </c>
@@ -64552,7 +64606,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A504" s="8">
         <v>44258</v>
       </c>
@@ -64593,7 +64647,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A505" s="8">
         <v>44265</v>
       </c>
@@ -64634,7 +64688,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A506" s="8">
         <v>44272</v>
       </c>
@@ -64675,7 +64729,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A507" s="8">
         <v>44279</v>
       </c>
@@ -64716,7 +64770,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="8">
         <v>44286</v>
       </c>
@@ -64757,7 +64811,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="8">
         <v>44293</v>
       </c>
@@ -64798,7 +64852,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A510" s="8">
         <v>44300</v>
       </c>
@@ -64839,7 +64893,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A511" s="8">
         <v>44307</v>
       </c>
@@ -64880,7 +64934,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A512" s="8">
         <v>44314</v>
       </c>
@@ -64921,7 +64975,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A513" s="8">
         <v>44321</v>
       </c>
@@ -64962,7 +65016,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A514" s="8">
         <v>44328</v>
       </c>
@@ -65003,7 +65057,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A515" s="8">
         <v>44335</v>
       </c>
@@ -65044,7 +65098,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A516" s="8">
         <v>44342</v>
       </c>
@@ -65085,7 +65139,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A517" s="8">
         <v>44349</v>
       </c>
@@ -65126,7 +65180,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A518" s="8">
         <v>44356</v>
       </c>
@@ -65167,7 +65221,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A519" s="8">
         <v>44363</v>
       </c>
@@ -65208,7 +65262,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A520" s="8">
         <v>44370</v>
       </c>
@@ -65249,7 +65303,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A521" s="8">
         <v>44377</v>
       </c>
@@ -65290,7 +65344,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A522" s="8">
         <v>44384</v>
       </c>
@@ -65331,7 +65385,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A523" s="8">
         <v>44391</v>
       </c>
@@ -65372,7 +65426,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A524" s="8">
         <v>44398</v>
       </c>
@@ -65413,7 +65467,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A525" s="8">
         <v>44405</v>
       </c>
@@ -65454,7 +65508,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A526" s="8">
         <v>44412</v>
       </c>
@@ -65495,7 +65549,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A527" s="8">
         <v>44419</v>
       </c>
@@ -65536,7 +65590,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A528" s="8">
         <v>44426</v>
       </c>
@@ -65577,7 +65631,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A529" s="8">
         <v>44433</v>
       </c>
@@ -65618,7 +65672,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A530" s="8">
         <v>44440</v>
       </c>
@@ -65659,7 +65713,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A531" s="8">
         <v>44447</v>
       </c>
@@ -65700,7 +65754,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A532" s="8">
         <v>44454</v>
       </c>
@@ -65741,7 +65795,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A533" s="8">
         <v>44461</v>
       </c>
@@ -65782,7 +65836,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A534" s="8">
         <v>44468</v>
       </c>
@@ -65823,7 +65877,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A535" s="8">
         <v>44475</v>
       </c>
@@ -65864,7 +65918,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A536" s="8">
         <v>44482</v>
       </c>
@@ -65905,7 +65959,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A537" s="8">
         <v>44489</v>
       </c>
@@ -65946,7 +66000,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A538" s="8">
         <v>44496</v>
       </c>
@@ -65987,7 +66041,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A539" s="8">
         <v>44503</v>
       </c>
@@ -66028,7 +66082,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A540" s="8">
         <v>44510</v>
       </c>
@@ -66069,7 +66123,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" s="8">
         <v>44517</v>
       </c>
@@ -66110,7 +66164,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A542" s="8">
         <v>44524</v>
       </c>
@@ -66151,7 +66205,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A543" s="8">
         <v>44531</v>
       </c>
@@ -66192,7 +66246,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A544" s="8">
         <v>44538</v>
       </c>
@@ -66233,7 +66287,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" s="8">
         <v>44545</v>
       </c>
@@ -66274,7 +66328,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" s="8">
         <v>44552</v>
       </c>
@@ -66315,7 +66369,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" s="8">
         <v>44566</v>
       </c>
@@ -66356,7 +66410,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" s="8">
         <v>44573</v>
       </c>
@@ -66397,7 +66451,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" s="8">
         <v>44580</v>
       </c>
@@ -66438,7 +66492,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" s="8">
         <v>44587</v>
       </c>
@@ -66479,7 +66533,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" s="8">
         <v>44594</v>
       </c>
@@ -66520,7 +66574,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A552" s="8">
         <v>44601</v>
       </c>
@@ -66561,7 +66615,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A553" s="8">
         <v>44608</v>
       </c>
@@ -66602,7 +66656,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A554" s="8">
         <v>44615</v>
       </c>
@@ -66643,7 +66697,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A555" s="8">
         <v>44622</v>
       </c>
@@ -66684,7 +66738,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A556" s="8">
         <v>44629</v>
       </c>
@@ -66725,7 +66779,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A557" s="8">
         <v>44636</v>
       </c>
@@ -66766,7 +66820,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A558" s="8">
         <v>44643</v>
       </c>
@@ -66807,7 +66861,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A559" s="8">
         <v>44650</v>
       </c>
@@ -66848,7 +66902,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A560" s="8">
         <v>44657</v>
       </c>
@@ -66889,7 +66943,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A561" s="8">
         <v>44664</v>
       </c>
@@ -66930,7 +66984,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A562" s="8">
         <v>44671</v>
       </c>
@@ -66971,7 +67025,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A563" s="8">
         <v>44678</v>
       </c>
@@ -67012,7 +67066,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A564" s="8">
         <v>44685</v>
       </c>
@@ -67053,7 +67107,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A565" s="8">
         <v>44692</v>
       </c>
@@ -67094,7 +67148,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A566" s="8">
         <v>44699</v>
       </c>
@@ -67135,7 +67189,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A567" s="8">
         <v>44706</v>
       </c>
@@ -67176,7 +67230,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A568" s="8">
         <v>44713</v>
       </c>
@@ -67217,7 +67271,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A569" s="8">
         <v>44720</v>
       </c>
@@ -67258,7 +67312,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A570" s="8">
         <v>44727</v>
       </c>
@@ -67299,7 +67353,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A571" s="8">
         <v>44734</v>
       </c>
@@ -67340,7 +67394,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A572" s="8">
         <v>44741</v>
       </c>
@@ -67381,7 +67435,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A573" s="8">
         <v>44748</v>
       </c>
@@ -67422,7 +67476,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A574" s="8">
         <v>44755</v>
       </c>
@@ -67463,7 +67517,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A575" s="8">
         <v>44762</v>
       </c>
@@ -67504,7 +67558,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A576" s="8">
         <v>44769</v>
       </c>
@@ -67545,7 +67599,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A577" s="8">
         <v>44776</v>
       </c>
@@ -67586,7 +67640,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A578" s="8">
         <v>44783</v>
       </c>
@@ -67627,7 +67681,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A579" s="8">
         <v>44790</v>
       </c>
@@ -67668,7 +67722,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A580" s="8">
         <v>44797</v>
       </c>
@@ -67709,7 +67763,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A581" s="8">
         <v>44804</v>
       </c>
@@ -67750,7 +67804,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A582" s="8">
         <v>44811</v>
       </c>
@@ -67791,7 +67845,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A583" s="8">
         <v>44818</v>
       </c>
@@ -67832,7 +67886,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A584" s="8">
         <v>44825</v>
       </c>
@@ -67873,7 +67927,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A585" s="8">
         <v>44832</v>
       </c>
@@ -67914,7 +67968,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A586" s="8">
         <v>44839</v>
       </c>
@@ -67955,7 +68009,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A587" s="8">
         <v>44846</v>
       </c>
@@ -67996,7 +68050,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A588" s="8">
         <v>44853</v>
       </c>
@@ -68037,7 +68091,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A589" s="8">
         <v>44860</v>
       </c>
@@ -68078,7 +68132,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A590" s="8">
         <v>44867</v>
       </c>
@@ -68119,7 +68173,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A591" s="8">
         <v>44874</v>
       </c>
@@ -68160,7 +68214,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A592" s="8">
         <v>44881</v>
       </c>
@@ -68201,7 +68255,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A593" s="8">
         <v>44888</v>
       </c>
@@ -68242,7 +68296,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A594" s="8">
         <v>44895</v>
       </c>
@@ -68283,7 +68337,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A595" s="8">
         <v>44902</v>
       </c>
@@ -68324,7 +68378,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A596" s="8">
         <v>44909</v>
       </c>
@@ -68365,7 +68419,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A597" s="8">
         <v>44916</v>
       </c>
@@ -68406,7 +68460,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A598" s="8">
         <v>44930</v>
       </c>
@@ -68447,7 +68501,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A599" s="8">
         <v>44937</v>
       </c>
@@ -68488,7 +68542,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A600" s="8">
         <v>44944</v>
       </c>
@@ -68529,7 +68583,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A601" s="8">
         <v>44951</v>
       </c>
@@ -68570,7 +68624,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A602" s="8">
         <v>44958</v>
       </c>
@@ -68611,7 +68665,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A603" s="8">
         <v>44965</v>
       </c>
@@ -68652,7 +68706,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A604" s="8">
         <v>44972</v>
       </c>
@@ -68693,7 +68747,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A605" s="8">
         <v>44979</v>
       </c>
@@ -68734,7 +68788,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A606" s="8">
         <v>44986</v>
       </c>
@@ -68775,7 +68829,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A607" s="8">
         <v>44993</v>
       </c>
@@ -68816,7 +68870,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A608" s="8">
         <v>45000</v>
       </c>
@@ -68857,7 +68911,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A609" s="8">
         <v>45007</v>
       </c>
@@ -68898,7 +68952,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A610" s="8">
         <v>45014</v>
       </c>
@@ -68939,7 +68993,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A611" s="8">
         <v>45021</v>
       </c>
@@ -68980,7 +69034,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A612" s="8">
         <v>45028</v>
       </c>
@@ -69021,7 +69075,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A613" s="8">
         <v>45035</v>
       </c>
@@ -69062,7 +69116,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A614" s="8">
         <v>45042</v>
       </c>
@@ -69103,7 +69157,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A615" s="8">
         <v>45049</v>
       </c>
@@ -69144,7 +69198,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A616" s="8">
         <v>45056</v>
       </c>
@@ -69185,7 +69239,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A617" s="8">
         <v>45063</v>
       </c>
@@ -69226,7 +69280,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A618" s="8">
         <v>45070</v>
       </c>
@@ -69267,7 +69321,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A619" s="8">
         <v>45077</v>
       </c>
@@ -69308,7 +69362,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A620" s="8">
         <v>45084</v>
       </c>
@@ -69349,7 +69403,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A621" s="8">
         <v>45091</v>
       </c>
@@ -69390,7 +69444,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A622" s="8">
         <v>45098</v>
       </c>
@@ -69431,7 +69485,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A623" s="8">
         <v>45105</v>
       </c>
@@ -69472,7 +69526,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A624" s="8">
         <v>45112</v>
       </c>
@@ -69513,7 +69567,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A625" s="8">
         <v>45119</v>
       </c>
@@ -69554,7 +69608,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A626" s="8">
         <v>45126</v>
       </c>
@@ -69595,7 +69649,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A627" s="8">
         <v>45133</v>
       </c>
@@ -69636,7 +69690,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A628" s="8">
         <v>45140</v>
       </c>
@@ -69677,7 +69731,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A629" s="8">
         <v>45147</v>
       </c>
@@ -69718,7 +69772,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="8">
         <v>45154</v>
       </c>
@@ -69759,7 +69813,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A631" s="8">
         <v>45161</v>
       </c>
@@ -69800,7 +69854,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A632" s="8">
         <v>45168</v>
       </c>
@@ -69841,7 +69895,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A633" s="8">
         <v>45175</v>
       </c>
@@ -69882,7 +69936,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A634" s="8">
         <v>45182</v>
       </c>
@@ -69923,7 +69977,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" s="8">
         <v>45189</v>
       </c>
@@ -69964,7 +70018,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A636" s="8">
         <v>45196</v>
       </c>
@@ -70005,7 +70059,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A637" s="8">
         <v>45203</v>
       </c>
@@ -70046,7 +70100,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A638" s="8">
         <v>45210</v>
       </c>
@@ -70087,7 +70141,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A639" s="8">
         <v>45217</v>
       </c>
@@ -70128,7 +70182,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" s="8">
         <v>45224</v>
       </c>
@@ -70169,7 +70223,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A641" s="8">
         <v>45231</v>
       </c>
@@ -70210,7 +70264,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A642" s="8">
         <v>45238</v>
       </c>
@@ -70251,7 +70305,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A643" s="8">
         <v>45245</v>
       </c>
@@ -70292,7 +70346,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A644" s="8">
         <v>45252</v>
       </c>
@@ -70333,7 +70387,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A645" s="8">
         <v>45259</v>
       </c>
@@ -70374,7 +70428,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" s="8">
         <v>45266</v>
       </c>
@@ -70415,7 +70469,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" s="8">
         <v>45273</v>
       </c>
@@ -70456,7 +70510,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" s="8">
         <v>45280</v>
       </c>
@@ -70497,7 +70551,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" s="8">
         <v>45294</v>
       </c>
@@ -70538,7 +70592,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" s="8">
         <v>45301</v>
       </c>
@@ -70579,7 +70633,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" s="8">
         <v>45308</v>
       </c>
@@ -70620,7 +70674,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A652" s="8">
         <v>45315</v>
       </c>
@@ -70661,7 +70715,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A653" s="8">
         <v>45322</v>
       </c>
@@ -70702,7 +70756,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A654" s="8">
         <v>45329</v>
       </c>
@@ -70743,7 +70797,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A655" s="8">
         <v>45336</v>
       </c>
@@ -70784,7 +70838,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A656" s="8">
         <v>45343</v>
       </c>
@@ -70825,7 +70879,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A657" s="8">
         <v>45350</v>
       </c>
@@ -70866,7 +70920,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A658" s="8">
         <v>45357</v>
       </c>
@@ -70907,7 +70961,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A659" s="8">
         <v>45364</v>
       </c>
@@ -70948,7 +71002,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="8">
         <v>45371</v>
       </c>
@@ -70989,7 +71043,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A661" s="8">
         <v>45378</v>
       </c>
@@ -71030,7 +71084,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A662" s="8">
         <v>45385</v>
       </c>
@@ -71071,7 +71125,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A663" s="8">
         <v>45392</v>
       </c>
@@ -71112,7 +71166,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A664" s="8">
         <v>45399</v>
       </c>
@@ -71153,7 +71207,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A665" s="8">
         <v>45406</v>
       </c>
@@ -71194,7 +71248,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A666" s="8">
         <v>45413</v>
       </c>
@@ -71235,7 +71289,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A667" s="8">
         <v>45420</v>
       </c>
@@ -71276,7 +71330,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A668" s="8">
         <v>45427</v>
       </c>
@@ -71317,7 +71371,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A669" s="8">
         <v>45434</v>
       </c>
@@ -71358,7 +71412,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A670" s="8">
         <v>45441</v>
       </c>
@@ -71399,7 +71453,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A671" s="8">
         <v>45448</v>
       </c>
@@ -71440,7 +71494,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A672" s="8">
         <v>45455</v>
       </c>
@@ -71481,7 +71535,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A673" s="8">
         <v>45462</v>
       </c>
@@ -71522,7 +71576,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A674" s="8">
         <v>45469</v>
       </c>
@@ -71563,7 +71617,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A675" s="8">
         <v>45476</v>
       </c>
@@ -71604,7 +71658,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A676" s="8">
         <v>45483</v>
       </c>
@@ -71645,7 +71699,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A677" s="8">
         <v>45490</v>
       </c>
@@ -71686,7 +71740,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A678" s="8">
         <v>45497</v>
       </c>
@@ -71727,7 +71781,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A679" s="8">
         <v>45504</v>
       </c>
@@ -71768,7 +71822,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A680" s="8">
         <v>45511</v>
       </c>
@@ -71809,7 +71863,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A681" s="8">
         <v>45518</v>
       </c>
@@ -71850,7 +71904,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A682" s="8">
         <v>45525</v>
       </c>
@@ -71891,7 +71945,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A683" s="8">
         <v>45532</v>
       </c>
@@ -71932,7 +71986,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A684" s="8">
         <v>45539</v>
       </c>
@@ -71973,7 +72027,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A685" s="8">
         <v>45546</v>
       </c>
@@ -72014,7 +72068,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A686" s="8">
         <v>45553</v>
       </c>
@@ -72055,7 +72109,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A687" s="8">
         <v>45560</v>
       </c>
@@ -72096,7 +72150,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A688" s="8">
         <v>45567</v>
       </c>
@@ -72137,7 +72191,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A689" s="8">
         <v>45574</v>
       </c>
@@ -72178,7 +72232,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A690" s="8">
         <v>45581</v>
       </c>
@@ -72219,7 +72273,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A691" s="8">
         <v>45588</v>
       </c>
@@ -72260,7 +72314,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A692" s="8">
         <v>45595</v>
       </c>
@@ -72301,7 +72355,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A693" s="8">
         <v>45602</v>
       </c>
@@ -72342,7 +72396,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A694" s="8">
         <v>45609</v>
       </c>
@@ -72383,7 +72437,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A695" s="8">
         <v>45616</v>
       </c>
@@ -72424,7 +72478,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A696" s="8">
         <v>45623</v>
       </c>
@@ -72465,7 +72519,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A697" s="8">
         <v>45630</v>
       </c>
@@ -72506,7 +72560,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="8">
         <v>45637</v>
       </c>
@@ -72547,7 +72601,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="8">
         <v>45644</v>
       </c>
@@ -72588,7 +72642,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="8">
         <v>45658</v>
       </c>
@@ -72629,7 +72683,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="8">
         <v>45665</v>
       </c>
@@ -72670,7 +72724,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="8">
         <v>45672</v>
       </c>
@@ -72711,7 +72765,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="8">
         <v>45679</v>
       </c>
@@ -72752,7 +72806,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="8">
         <v>45686</v>
       </c>
@@ -72793,7 +72847,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="8">
         <v>45693</v>
       </c>
@@ -72834,7 +72888,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="8">
         <v>45700</v>
       </c>
@@ -72875,7 +72929,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="8">
         <v>45707</v>
       </c>
@@ -72916,7 +72970,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="8">
         <v>45714</v>
       </c>
@@ -72957,7 +73011,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="8">
         <v>45721</v>
       </c>
@@ -72998,7 +73052,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="8">
         <v>45728</v>
       </c>
@@ -73039,7 +73093,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="8">
         <v>45735</v>
       </c>
@@ -73080,7 +73134,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="8">
         <v>45742</v>
       </c>
@@ -73121,7 +73175,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="8">
         <v>45749</v>
       </c>
@@ -73162,7 +73216,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A714" s="8">
         <v>45756</v>
       </c>
@@ -73203,7 +73257,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A715" s="8">
         <v>45763</v>
       </c>
@@ -73244,7 +73298,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A716" s="8">
         <v>45770</v>
       </c>
@@ -73285,7 +73339,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A717" s="8">
         <v>45777</v>
       </c>
@@ -73326,7 +73380,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A718" s="8">
         <v>45784</v>
       </c>
@@ -73367,7 +73421,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A719" s="8">
         <v>45791</v>
       </c>
@@ -73408,7 +73462,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A720" s="8">
         <v>45798</v>
       </c>
@@ -73449,7 +73503,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A721" s="8">
         <v>45805</v>
       </c>
@@ -73490,7 +73544,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A722" s="8">
         <v>45812</v>
       </c>
@@ -73531,7 +73585,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A723" s="8">
         <v>45819</v>
       </c>
@@ -73572,7 +73626,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A724" s="8">
         <v>45826</v>
       </c>
@@ -73613,7 +73667,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A725" s="8">
         <v>45833</v>
       </c>
@@ -73654,7 +73708,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A726" s="8">
         <v>45840</v>
       </c>
@@ -73695,7 +73749,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A727" s="8">
         <v>45847</v>
       </c>
@@ -73736,7 +73790,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A728" s="8">
         <v>45854</v>
       </c>
@@ -73777,7 +73831,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A729" s="8">
         <v>45861</v>
       </c>
@@ -73818,7 +73872,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A730" s="8">
         <v>45868</v>
       </c>
@@ -73859,7 +73913,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A731" s="8">
         <v>45875</v>
       </c>
@@ -73900,7 +73954,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A732" s="8">
         <v>45882</v>
       </c>
@@ -73941,7 +73995,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A733" s="8">
         <v>45889</v>
       </c>
@@ -73982,7 +74036,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A734" s="8">
         <v>45896</v>
       </c>
@@ -74023,7 +74077,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A735" s="8">
         <v>45903</v>
       </c>
@@ -74064,7 +74118,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A736" s="8">
         <v>45910</v>
       </c>
@@ -74105,7 +74159,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A737" s="8">
         <v>45917</v>
       </c>
@@ -74146,7 +74200,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A738" s="8">
         <v>45924</v>
       </c>
@@ -74187,7 +74241,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A739" s="8">
         <v>45931</v>
       </c>
@@ -74228,7 +74282,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A740" s="8">
         <v>45938</v>
       </c>
@@ -74269,7 +74323,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A741" s="8">
         <v>45945</v>
       </c>
@@ -74310,7 +74364,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A742" s="8">
         <v>45952</v>
       </c>
@@ -74351,7 +74405,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A743" s="8">
         <v>45959</v>
       </c>
@@ -74392,7 +74446,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A744" s="8">
         <v>45966</v>
       </c>
@@ -74433,7 +74487,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A745" s="8">
         <v>45973</v>
       </c>
@@ -74474,7 +74528,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A746" s="8">
         <v>45980</v>
       </c>
@@ -74515,7 +74569,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A747" s="8">
         <v>45987</v>
       </c>
@@ -74556,7 +74610,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A748" s="8">
         <v>45994</v>
       </c>
@@ -74597,7 +74651,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A749" s="8">
         <v>46001</v>
       </c>
@@ -74638,7 +74692,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A750" s="8">
         <v>46008</v>
       </c>
@@ -74679,7 +74733,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A751" s="8">
         <v>46015</v>
       </c>
@@ -74720,7 +74774,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A752" s="8">
         <v>46022</v>
       </c>
@@ -74761,7 +74815,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A753" s="8">
         <v>46029</v>
       </c>
@@ -74802,7 +74856,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A754" s="8">
         <v>46036</v>
       </c>
@@ -74843,7 +74897,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A755" s="8">
         <v>46043</v>
       </c>
@@ -74884,7 +74938,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A756" s="8">
         <v>46050</v>
       </c>
@@ -74925,7 +74979,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A757" s="8">
         <v>46057</v>
       </c>
@@ -74966,7 +75020,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A758" s="8">
         <v>46064</v>
       </c>
@@ -75007,7 +75061,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A759" s="8">
         <v>46071</v>
       </c>
@@ -75048,7 +75102,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A760" s="8">
         <v>46078</v>
       </c>
@@ -75089,7 +75143,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A761" s="8">
         <v>46085</v>
       </c>
@@ -75130,7 +75184,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A762" s="8">
         <v>46092</v>
       </c>
@@ -75171,7 +75225,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A763" s="8">
         <v>46099</v>
       </c>
@@ -75212,7 +75266,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A764" s="8">
         <v>46106</v>
       </c>
@@ -75253,7 +75307,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A765" s="8">
         <v>46113</v>
       </c>
@@ -75294,7 +75348,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A766" s="8">
         <v>46120</v>
       </c>
@@ -75335,7 +75389,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A767" s="8">
         <v>46127</v>
       </c>
@@ -75376,7 +75430,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A768" s="8">
         <v>46134</v>
       </c>
@@ -75417,7 +75471,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A769" s="8">
         <v>46141</v>
       </c>
@@ -75458,7 +75512,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A770" s="8">
         <v>46148</v>
       </c>
@@ -75499,7 +75553,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A771" s="8">
         <v>46155</v>
       </c>
@@ -75540,7 +75594,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A772" s="8">
         <v>46162</v>
       </c>
@@ -75581,7 +75635,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A773" s="8">
         <v>46169</v>
       </c>
@@ -75622,7 +75676,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A774" s="8">
         <v>46176</v>
       </c>
@@ -75663,7 +75717,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A775" s="8">
         <v>46183</v>
       </c>
@@ -75704,7 +75758,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A776" s="8">
         <v>46190</v>
       </c>
@@ -75745,7 +75799,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="777" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A777" s="8">
         <v>46197</v>
       </c>
@@ -75786,7 +75840,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="778" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A778" s="8">
         <v>46204</v>
       </c>
@@ -75827,7 +75881,7 @@
         <v>2602</v>
       </c>
     </row>
-    <row r="779" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A779" s="8">
         <v>46211</v>
       </c>
@@ -75868,7 +75922,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="780" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A780" s="8">
         <v>46218</v>
       </c>
@@ -75909,7 +75963,7 @@
         <v>2667</v>
       </c>
     </row>
-    <row r="781" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A781" s="8">
         <v>46225</v>
       </c>
@@ -75948,6 +76002,47 @@
       </c>
       <c r="M781" s="11">
         <v>2635</v>
+      </c>
+    </row>
+    <row r="782" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A782" s="8">
+        <v>46232</v>
+      </c>
+      <c r="B782" s="8">
+        <v>46233</v>
+      </c>
+      <c r="C782" s="9">
+        <v>0.583333333342125</v>
+      </c>
+      <c r="D782" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E782" s="10">
+        <v>4254.7299999999996</v>
+      </c>
+      <c r="F782" s="11">
+        <v>4667</v>
+      </c>
+      <c r="G782" s="11">
+        <v>5630</v>
+      </c>
+      <c r="H782" s="11">
+        <v>5739</v>
+      </c>
+      <c r="I782" s="11">
+        <v>7578</v>
+      </c>
+      <c r="J782" s="11">
+        <v>589</v>
+      </c>
+      <c r="K782" s="11">
+        <v>859</v>
+      </c>
+      <c r="L782" s="11">
+        <v>1103</v>
+      </c>
+      <c r="M782" s="11">
+        <v>2719</v>
       </c>
     </row>
   </sheetData>
@@ -75960,7 +76055,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -75971,12 +76066,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
@@ -75995,7 +76090,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF97501-640E-144F-A48F-22CED107A883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E957BC7-E7BE-4403-8862-38C7F3D8B459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26780" yWindow="4880" windowWidth="23880" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -107,29 +107,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,7 +138,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,7 +146,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -195,35 +195,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -241,7 +241,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2633,6 +2633,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4984,6 +4987,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>4254.7299999999996</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>4297.46</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7371,6 +7377,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9722,6 +9731,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>4667</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>4653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12109,6 +12121,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14460,6 +14475,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>5630</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>5506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16847,6 +16865,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19198,6 +19219,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>5739</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>5894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21585,6 +21609,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23936,6 +23963,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>7578</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>7893</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26323,6 +26353,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28674,6 +28707,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>589</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>583</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -31063,6 +31099,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33414,6 +33453,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>859</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>839</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35803,6 +35845,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -38154,6 +38199,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>1103</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>1096</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40543,6 +40591,9 @@
                 <c:pt idx="780">
                   <c:v>46233</c:v>
                 </c:pt>
+                <c:pt idx="781">
+                  <c:v>46240</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42894,6 +42945,9 @@
                 </c:pt>
                 <c:pt idx="780">
                   <c:v>2719</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>2773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -43971,19 +44025,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M782"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M783"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.796875" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="10.5" style="11" customWidth="1"/>
     <col min="14" max="16384" width="7.5" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -44024,7 +44078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="8">
         <v>40716</v>
       </c>
@@ -44065,7 +44119,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="8">
         <v>40723</v>
       </c>
@@ -44106,7 +44160,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="8">
         <v>40730</v>
       </c>
@@ -44147,7 +44201,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="8">
         <v>40737</v>
       </c>
@@ -44188,7 +44242,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="8">
         <v>40744</v>
       </c>
@@ -44229,7 +44283,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="8">
         <v>40751</v>
       </c>
@@ -44270,7 +44324,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="8">
         <v>40758</v>
       </c>
@@ -44311,7 +44365,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="8">
         <v>40765</v>
       </c>
@@ -44352,7 +44406,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="8">
         <v>40772</v>
       </c>
@@ -44393,7 +44447,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="8">
         <v>40779</v>
       </c>
@@ -44434,7 +44488,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="8">
         <v>40786</v>
       </c>
@@ -44475,7 +44529,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="8">
         <v>40793</v>
       </c>
@@ -44516,7 +44570,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="8">
         <v>40800</v>
       </c>
@@ -44557,7 +44611,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="8">
         <v>40807</v>
       </c>
@@ -44598,7 +44652,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="8">
         <v>40814</v>
       </c>
@@ -44639,7 +44693,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" s="8">
         <v>40821</v>
       </c>
@@ -44680,7 +44734,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" s="8">
         <v>40828</v>
       </c>
@@ -44721,7 +44775,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="8">
         <v>40835</v>
       </c>
@@ -44762,7 +44816,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="8">
         <v>40842</v>
       </c>
@@ -44803,7 +44857,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="8">
         <v>40849</v>
       </c>
@@ -44844,7 +44898,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="8">
         <v>40856</v>
       </c>
@@ -44885,7 +44939,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="8">
         <v>40863</v>
       </c>
@@ -44926,7 +44980,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="8">
         <v>40870</v>
       </c>
@@ -44967,7 +45021,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="8">
         <v>40877</v>
       </c>
@@ -45008,7 +45062,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="8">
         <v>40884</v>
       </c>
@@ -45049,7 +45103,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="8">
         <v>40891</v>
       </c>
@@ -45090,7 +45144,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="8">
         <v>40898</v>
       </c>
@@ -45131,7 +45185,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="8">
         <v>40905</v>
       </c>
@@ -45172,7 +45226,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="8">
         <v>40912</v>
       </c>
@@ -45213,7 +45267,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="8">
         <v>40919</v>
       </c>
@@ -45254,7 +45308,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="8">
         <v>40926</v>
       </c>
@@ -45295,7 +45349,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="8">
         <v>40933</v>
       </c>
@@ -45336,7 +45390,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="8">
         <v>40940</v>
       </c>
@@ -45377,7 +45431,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="8">
         <v>40947</v>
       </c>
@@ -45418,7 +45472,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="8">
         <v>40954</v>
       </c>
@@ -45459,7 +45513,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="8">
         <v>40961</v>
       </c>
@@ -45500,7 +45554,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="8">
         <v>40968</v>
       </c>
@@ -45541,7 +45595,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="8">
         <v>40975</v>
       </c>
@@ -45582,7 +45636,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="8">
         <v>40982</v>
       </c>
@@ -45623,7 +45677,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="8">
         <v>40989</v>
       </c>
@@ -45664,7 +45718,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="8">
         <v>40996</v>
       </c>
@@ -45705,7 +45759,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" s="8">
         <v>41003</v>
       </c>
@@ -45746,7 +45800,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="8">
         <v>41010</v>
       </c>
@@ -45787,7 +45841,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" s="8">
         <v>41017</v>
       </c>
@@ -45828,7 +45882,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="8">
         <v>41024</v>
       </c>
@@ -45869,7 +45923,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" s="8">
         <v>41031</v>
       </c>
@@ -45910,7 +45964,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" s="8">
         <v>41038</v>
       </c>
@@ -45951,7 +46005,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A49" s="8">
         <v>41045</v>
       </c>
@@ -45992,7 +46046,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A50" s="8">
         <v>41052</v>
       </c>
@@ -46033,7 +46087,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A51" s="8">
         <v>41059</v>
       </c>
@@ -46074,7 +46128,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A52" s="8">
         <v>41066</v>
       </c>
@@ -46115,7 +46169,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A53" s="8">
         <v>41073</v>
       </c>
@@ -46156,7 +46210,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" s="8">
         <v>41080</v>
       </c>
@@ -46197,7 +46251,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" s="8">
         <v>41087</v>
       </c>
@@ -46238,7 +46292,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" s="8">
         <v>41094</v>
       </c>
@@ -46279,7 +46333,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" s="8">
         <v>41101</v>
       </c>
@@ -46320,7 +46374,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" s="8">
         <v>41108</v>
       </c>
@@ -46361,7 +46415,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59" s="8">
         <v>41115</v>
       </c>
@@ -46402,7 +46456,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" s="8">
         <v>41122</v>
       </c>
@@ -46443,7 +46497,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A61" s="8">
         <v>41129</v>
       </c>
@@ -46484,7 +46538,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62" s="8">
         <v>41136</v>
       </c>
@@ -46525,7 +46579,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A63" s="8">
         <v>41143</v>
       </c>
@@ -46566,7 +46620,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A64" s="8">
         <v>41150</v>
       </c>
@@ -46607,7 +46661,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A65" s="8">
         <v>41157</v>
       </c>
@@ -46648,7 +46702,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A66" s="8">
         <v>41164</v>
       </c>
@@ -46689,7 +46743,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A67" s="8">
         <v>41171</v>
       </c>
@@ -46730,7 +46784,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A68" s="8">
         <v>41178</v>
       </c>
@@ -46771,7 +46825,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A69" s="8">
         <v>41185</v>
       </c>
@@ -46812,7 +46866,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A70" s="8">
         <v>41192</v>
       </c>
@@ -46853,7 +46907,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A71" s="8">
         <v>41199</v>
       </c>
@@ -46894,7 +46948,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A72" s="8">
         <v>41206</v>
       </c>
@@ -46935,7 +46989,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A73" s="8">
         <v>41213</v>
       </c>
@@ -46976,7 +47030,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A74" s="8">
         <v>41220</v>
       </c>
@@ -47017,7 +47071,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A75" s="8">
         <v>41227</v>
       </c>
@@ -47058,7 +47112,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A76" s="8">
         <v>41234</v>
       </c>
@@ -47099,7 +47153,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A77" s="8">
         <v>41241</v>
       </c>
@@ -47140,7 +47194,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A78" s="8">
         <v>41248</v>
       </c>
@@ -47181,7 +47235,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A79" s="8">
         <v>41255</v>
       </c>
@@ -47222,7 +47276,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A80" s="8">
         <v>41262</v>
       </c>
@@ -47263,7 +47317,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A81" s="8">
         <v>41269</v>
       </c>
@@ -47304,7 +47358,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A82" s="8">
         <v>41276</v>
       </c>
@@ -47345,7 +47399,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A83" s="8">
         <v>41283</v>
       </c>
@@ -47386,7 +47440,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A84" s="8">
         <v>41290</v>
       </c>
@@ -47427,7 +47481,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A85" s="8">
         <v>41297</v>
       </c>
@@ -47468,7 +47522,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A86" s="8">
         <v>41304</v>
       </c>
@@ -47509,7 +47563,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A87" s="8">
         <v>41311</v>
       </c>
@@ -47550,7 +47604,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A88" s="8">
         <v>41318</v>
       </c>
@@ -47591,7 +47645,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A89" s="8">
         <v>41325</v>
       </c>
@@ -47632,7 +47686,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A90" s="8">
         <v>41332</v>
       </c>
@@ -47673,7 +47727,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A91" s="8">
         <v>41339</v>
       </c>
@@ -47714,7 +47768,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A92" s="8">
         <v>41346</v>
       </c>
@@ -47755,7 +47809,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A93" s="8">
         <v>41353</v>
       </c>
@@ -47796,7 +47850,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A94" s="8">
         <v>41360</v>
       </c>
@@ -47837,7 +47891,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A95" s="8">
         <v>41367</v>
       </c>
@@ -47878,7 +47932,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A96" s="8">
         <v>41374</v>
       </c>
@@ -47919,7 +47973,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A97" s="8">
         <v>41381</v>
       </c>
@@ -47960,7 +48014,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A98" s="8">
         <v>41388</v>
       </c>
@@ -48001,7 +48055,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A99" s="8">
         <v>41395</v>
       </c>
@@ -48042,7 +48096,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A100" s="8">
         <v>41402</v>
       </c>
@@ -48083,7 +48137,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A101" s="8">
         <v>41409</v>
       </c>
@@ -48124,7 +48178,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A102" s="8">
         <v>41416</v>
       </c>
@@ -48165,7 +48219,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A103" s="8">
         <v>41423</v>
       </c>
@@ -48206,7 +48260,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A104" s="8">
         <v>41430</v>
       </c>
@@ -48247,7 +48301,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A105" s="8">
         <v>41437</v>
       </c>
@@ -48288,7 +48342,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A106" s="8">
         <v>41444</v>
       </c>
@@ -48329,7 +48383,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A107" s="8">
         <v>41451</v>
       </c>
@@ -48370,7 +48424,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A108" s="8">
         <v>41458</v>
       </c>
@@ -48411,7 +48465,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A109" s="8">
         <v>41465</v>
       </c>
@@ -48452,7 +48506,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A110" s="8">
         <v>41472</v>
       </c>
@@ -48493,7 +48547,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A111" s="8">
         <v>41479</v>
       </c>
@@ -48534,7 +48588,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A112" s="8">
         <v>41486</v>
       </c>
@@ -48575,7 +48629,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A113" s="8">
         <v>41493</v>
       </c>
@@ -48616,7 +48670,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A114" s="8">
         <v>41500</v>
       </c>
@@ -48657,7 +48711,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A115" s="8">
         <v>41507</v>
       </c>
@@ -48698,7 +48752,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A116" s="8">
         <v>41514</v>
       </c>
@@ -48739,7 +48793,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A117" s="8">
         <v>41521</v>
       </c>
@@ -48780,7 +48834,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A118" s="8">
         <v>41528</v>
       </c>
@@ -48821,7 +48875,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A119" s="8">
         <v>41535</v>
       </c>
@@ -48862,7 +48916,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A120" s="8">
         <v>41542</v>
       </c>
@@ -48903,7 +48957,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A121" s="8">
         <v>41549</v>
       </c>
@@ -48944,7 +48998,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A122" s="8">
         <v>41556</v>
       </c>
@@ -48985,7 +49039,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A123" s="8">
         <v>41563</v>
       </c>
@@ -49026,7 +49080,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A124" s="8">
         <v>41570</v>
       </c>
@@ -49067,7 +49121,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A125" s="8">
         <v>41577</v>
       </c>
@@ -49108,7 +49162,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A126" s="8">
         <v>41584</v>
       </c>
@@ -49149,7 +49203,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A127" s="8">
         <v>41591</v>
       </c>
@@ -49190,7 +49244,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A128" s="8">
         <v>41598</v>
       </c>
@@ -49231,7 +49285,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A129" s="8">
         <v>41605</v>
       </c>
@@ -49272,7 +49326,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A130" s="8">
         <v>41612</v>
       </c>
@@ -49313,7 +49367,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A131" s="8">
         <v>41619</v>
       </c>
@@ -49354,7 +49408,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A132" s="8">
         <v>41626</v>
       </c>
@@ -49395,7 +49449,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A133" s="8">
         <v>41640</v>
       </c>
@@ -49436,7 +49490,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A134" s="8">
         <v>41647</v>
       </c>
@@ -49477,7 +49531,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A135" s="8">
         <v>41654</v>
       </c>
@@ -49518,7 +49572,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A136" s="8">
         <v>41661</v>
       </c>
@@ -49559,7 +49613,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A137" s="8">
         <v>41668</v>
       </c>
@@ -49600,7 +49654,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A138" s="8">
         <v>41675</v>
       </c>
@@ -49641,7 +49695,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A139" s="8">
         <v>41682</v>
       </c>
@@ -49682,7 +49736,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A140" s="8">
         <v>41689</v>
       </c>
@@ -49723,7 +49777,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A141" s="8">
         <v>41696</v>
       </c>
@@ -49764,7 +49818,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A142" s="8">
         <v>41703</v>
       </c>
@@ -49805,7 +49859,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A143" s="8">
         <v>41710</v>
       </c>
@@ -49846,7 +49900,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A144" s="8">
         <v>41717</v>
       </c>
@@ -49887,7 +49941,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A145" s="8">
         <v>41724</v>
       </c>
@@ -49928,7 +49982,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A146" s="8">
         <v>41731</v>
       </c>
@@ -49969,7 +50023,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A147" s="8">
         <v>41738</v>
       </c>
@@ -50010,7 +50064,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A148" s="8">
         <v>41745</v>
       </c>
@@ -50051,7 +50105,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A149" s="8">
         <v>41752</v>
       </c>
@@ -50092,7 +50146,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A150" s="8">
         <v>41759</v>
       </c>
@@ -50133,7 +50187,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A151" s="8">
         <v>41766</v>
       </c>
@@ -50174,7 +50228,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A152" s="8">
         <v>41773</v>
       </c>
@@ -50215,7 +50269,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A153" s="8">
         <v>41780</v>
       </c>
@@ -50256,7 +50310,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A154" s="8">
         <v>41787</v>
       </c>
@@ -50297,7 +50351,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A155" s="8">
         <v>41794</v>
       </c>
@@ -50338,7 +50392,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A156" s="8">
         <v>41801</v>
       </c>
@@ -50379,7 +50433,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A157" s="8">
         <v>41808</v>
       </c>
@@ -50420,7 +50474,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A158" s="8">
         <v>41815</v>
       </c>
@@ -50461,7 +50515,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A159" s="8">
         <v>41822</v>
       </c>
@@ -50502,7 +50556,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A160" s="8">
         <v>41829</v>
       </c>
@@ -50543,7 +50597,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A161" s="8">
         <v>41836</v>
       </c>
@@ -50584,7 +50638,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A162" s="8">
         <v>41843</v>
       </c>
@@ -50625,7 +50679,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A163" s="8">
         <v>41850</v>
       </c>
@@ -50666,7 +50720,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A164" s="8">
         <v>41857</v>
       </c>
@@ -50707,7 +50761,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A165" s="8">
         <v>41864</v>
       </c>
@@ -50748,7 +50802,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A166" s="8">
         <v>41871</v>
       </c>
@@ -50789,7 +50843,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A167" s="8">
         <v>41878</v>
       </c>
@@ -50830,7 +50884,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A168" s="8">
         <v>41885</v>
       </c>
@@ -50871,7 +50925,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A169" s="8">
         <v>41892</v>
       </c>
@@ -50912,7 +50966,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A170" s="8">
         <v>41899</v>
       </c>
@@ -50953,7 +51007,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A171" s="8">
         <v>41906</v>
       </c>
@@ -50994,7 +51048,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A172" s="8">
         <v>41913</v>
       </c>
@@ -51035,7 +51089,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A173" s="8">
         <v>41920</v>
       </c>
@@ -51076,7 +51130,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A174" s="8">
         <v>41927</v>
       </c>
@@ -51117,7 +51171,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A175" s="8">
         <v>41934</v>
       </c>
@@ -51158,7 +51212,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A176" s="8">
         <v>41941</v>
       </c>
@@ -51199,7 +51253,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A177" s="8">
         <v>41948</v>
       </c>
@@ -51240,7 +51294,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A178" s="8">
         <v>41955</v>
       </c>
@@ -51281,7 +51335,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A179" s="8">
         <v>41962</v>
       </c>
@@ -51322,7 +51376,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A180" s="8">
         <v>41969</v>
       </c>
@@ -51363,7 +51417,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A181" s="8">
         <v>41976</v>
       </c>
@@ -51404,7 +51458,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A182" s="8">
         <v>41983</v>
       </c>
@@ -51445,7 +51499,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A183" s="8">
         <v>41990</v>
       </c>
@@ -51486,7 +51540,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A184" s="8">
         <v>42011</v>
       </c>
@@ -51527,7 +51581,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A185" s="8">
         <v>42018</v>
       </c>
@@ -51568,7 +51622,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A186" s="8">
         <v>42025</v>
       </c>
@@ -51609,7 +51663,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A187" s="8">
         <v>42032</v>
       </c>
@@ -51650,7 +51704,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A188" s="8">
         <v>42039</v>
       </c>
@@ -51691,7 +51745,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A189" s="8">
         <v>42046</v>
       </c>
@@ -51732,7 +51786,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A190" s="8">
         <v>42053</v>
       </c>
@@ -51773,7 +51827,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A191" s="8">
         <v>42060</v>
       </c>
@@ -51814,7 +51868,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A192" s="8">
         <v>42067</v>
       </c>
@@ -51855,7 +51909,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A193" s="8">
         <v>42074</v>
       </c>
@@ -51896,7 +51950,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A194" s="8">
         <v>42081</v>
       </c>
@@ -51937,7 +51991,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A195" s="8">
         <v>42088</v>
       </c>
@@ -51978,7 +52032,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A196" s="8">
         <v>42095</v>
       </c>
@@ -52019,7 +52073,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A197" s="8">
         <v>42102</v>
       </c>
@@ -52060,7 +52114,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A198" s="8">
         <v>42109</v>
       </c>
@@ -52101,7 +52155,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A199" s="8">
         <v>42116</v>
       </c>
@@ -52142,7 +52196,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A200" s="8">
         <v>42123</v>
       </c>
@@ -52183,7 +52237,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A201" s="8">
         <v>42130</v>
       </c>
@@ -52224,7 +52278,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A202" s="8">
         <v>42137</v>
       </c>
@@ -52265,7 +52319,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A203" s="8">
         <v>42144</v>
       </c>
@@ -52306,7 +52360,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A204" s="8">
         <v>42151</v>
       </c>
@@ -52347,7 +52401,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A205" s="8">
         <v>42158</v>
       </c>
@@ -52388,7 +52442,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A206" s="8">
         <v>42165</v>
       </c>
@@ -52429,7 +52483,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A207" s="8">
         <v>42172</v>
       </c>
@@ -52470,7 +52524,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A208" s="8">
         <v>42179</v>
       </c>
@@ -52511,7 +52565,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A209" s="8">
         <v>42186</v>
       </c>
@@ -52552,7 +52606,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A210" s="8">
         <v>42193</v>
       </c>
@@ -52593,7 +52647,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A211" s="8">
         <v>42200</v>
       </c>
@@ -52634,7 +52688,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A212" s="8">
         <v>42207</v>
       </c>
@@ -52675,7 +52729,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A213" s="8">
         <v>42214</v>
       </c>
@@ -52716,7 +52770,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A214" s="8">
         <v>42221</v>
       </c>
@@ -52757,7 +52811,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A215" s="8">
         <v>42228</v>
       </c>
@@ -52798,7 +52852,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A216" s="8">
         <v>42235</v>
       </c>
@@ -52839,7 +52893,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A217" s="8">
         <v>42242</v>
       </c>
@@ -52880,7 +52934,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A218" s="8">
         <v>42249</v>
       </c>
@@ -52921,7 +52975,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A219" s="8">
         <v>42256</v>
       </c>
@@ -52962,7 +53016,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A220" s="8">
         <v>42263</v>
       </c>
@@ -53003,7 +53057,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A221" s="8">
         <v>42270</v>
       </c>
@@ -53044,7 +53098,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A222" s="8">
         <v>42277</v>
       </c>
@@ -53085,7 +53139,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A223" s="8">
         <v>42284</v>
       </c>
@@ -53126,7 +53180,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A224" s="8">
         <v>42291</v>
       </c>
@@ -53167,7 +53221,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A225" s="8">
         <v>42298</v>
       </c>
@@ -53208,7 +53262,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A226" s="8">
         <v>42305</v>
       </c>
@@ -53249,7 +53303,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A227" s="8">
         <v>42312</v>
       </c>
@@ -53290,7 +53344,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A228" s="8">
         <v>42319</v>
       </c>
@@ -53331,7 +53385,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A229" s="8">
         <v>42326</v>
       </c>
@@ -53372,7 +53426,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A230" s="8">
         <v>42333</v>
       </c>
@@ -53413,7 +53467,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A231" s="8">
         <v>42340</v>
       </c>
@@ -53454,7 +53508,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A232" s="8">
         <v>42347</v>
       </c>
@@ -53495,7 +53549,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A233" s="8">
         <v>42354</v>
       </c>
@@ -53536,7 +53590,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A234" s="8">
         <v>42361</v>
       </c>
@@ -53577,7 +53631,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A235" s="8">
         <v>42368</v>
       </c>
@@ -53618,7 +53672,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A236" s="8">
         <v>42375</v>
       </c>
@@ -53659,7 +53713,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A237" s="8">
         <v>42382</v>
       </c>
@@ -53700,7 +53754,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A238" s="8">
         <v>42389</v>
       </c>
@@ -53741,7 +53795,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A239" s="8">
         <v>42396</v>
       </c>
@@ -53782,7 +53836,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A240" s="8">
         <v>42403</v>
       </c>
@@ -53823,7 +53877,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A241" s="8">
         <v>42410</v>
       </c>
@@ -53864,7 +53918,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A242" s="8">
         <v>42417</v>
       </c>
@@ -53905,7 +53959,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A243" s="8">
         <v>42424</v>
       </c>
@@ -53946,7 +54000,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A244" s="8">
         <v>42431</v>
       </c>
@@ -53987,7 +54041,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A245" s="8">
         <v>42438</v>
       </c>
@@ -54028,7 +54082,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A246" s="8">
         <v>42445</v>
       </c>
@@ -54069,7 +54123,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A247" s="8">
         <v>42452</v>
       </c>
@@ -54110,7 +54164,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A248" s="8">
         <v>42459</v>
       </c>
@@ -54151,7 +54205,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A249" s="8">
         <v>42466</v>
       </c>
@@ -54192,7 +54246,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A250" s="8">
         <v>42473</v>
       </c>
@@ -54233,7 +54287,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A251" s="8">
         <v>42480</v>
       </c>
@@ -54274,7 +54328,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A252" s="8">
         <v>42487</v>
       </c>
@@ -54315,7 +54369,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A253" s="8">
         <v>42494</v>
       </c>
@@ -54356,7 +54410,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A254" s="8">
         <v>42501</v>
       </c>
@@ -54397,7 +54451,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A255" s="8">
         <v>42508</v>
       </c>
@@ -54438,7 +54492,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A256" s="8">
         <v>42515</v>
       </c>
@@ -54479,7 +54533,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A257" s="8">
         <v>42522</v>
       </c>
@@ -54520,7 +54574,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A258" s="8">
         <v>42529</v>
       </c>
@@ -54561,7 +54615,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A259" s="8">
         <v>42536</v>
       </c>
@@ -54602,7 +54656,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A260" s="8">
         <v>42543</v>
       </c>
@@ -54643,7 +54697,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A261" s="8">
         <v>42550</v>
       </c>
@@ -54684,7 +54738,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A262" s="8">
         <v>42557</v>
       </c>
@@ -54725,7 +54779,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A263" s="8">
         <v>42564</v>
       </c>
@@ -54766,7 +54820,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A264" s="8">
         <v>42571</v>
       </c>
@@ -54807,7 +54861,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A265" s="8">
         <v>42578</v>
       </c>
@@ -54848,7 +54902,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A266" s="8">
         <v>42585</v>
       </c>
@@ -54889,7 +54943,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A267" s="8">
         <v>42592</v>
       </c>
@@ -54930,7 +54984,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A268" s="8">
         <v>42599</v>
       </c>
@@ -54971,7 +55025,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A269" s="8">
         <v>42606</v>
       </c>
@@ -55012,7 +55066,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A270" s="8">
         <v>42613</v>
       </c>
@@ -55053,7 +55107,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A271" s="8">
         <v>42620</v>
       </c>
@@ -55094,7 +55148,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A272" s="8">
         <v>42627</v>
       </c>
@@ -55135,7 +55189,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A273" s="8">
         <v>42634</v>
       </c>
@@ -55176,7 +55230,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A274" s="8">
         <v>42641</v>
       </c>
@@ -55217,7 +55271,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A275" s="8">
         <v>42648</v>
       </c>
@@ -55258,7 +55312,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A276" s="8">
         <v>42655</v>
       </c>
@@ -55299,7 +55353,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A277" s="8">
         <v>42662</v>
       </c>
@@ -55340,7 +55394,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A278" s="8">
         <v>42669</v>
       </c>
@@ -55381,7 +55435,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A279" s="8">
         <v>42676</v>
       </c>
@@ -55422,7 +55476,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A280" s="8">
         <v>42683</v>
       </c>
@@ -55463,7 +55517,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A281" s="8">
         <v>42690</v>
       </c>
@@ -55504,7 +55558,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A282" s="8">
         <v>42697</v>
       </c>
@@ -55545,7 +55599,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A283" s="8">
         <v>42704</v>
       </c>
@@ -55586,7 +55640,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A284" s="8">
         <v>42711</v>
       </c>
@@ -55627,7 +55681,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A285" s="8">
         <v>42718</v>
       </c>
@@ -55668,7 +55722,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A286" s="8">
         <v>42725</v>
       </c>
@@ -55709,7 +55763,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A287" s="8">
         <v>42732</v>
       </c>
@@ -55750,7 +55804,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A288" s="8">
         <v>42739</v>
       </c>
@@ -55791,7 +55845,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A289" s="8">
         <v>42746</v>
       </c>
@@ -55832,7 +55886,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A290" s="8">
         <v>42753</v>
       </c>
@@ -55873,7 +55927,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A291" s="8">
         <v>42760</v>
       </c>
@@ -55914,7 +55968,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A292" s="8">
         <v>42767</v>
       </c>
@@ -55955,7 +56009,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A293" s="8">
         <v>42774</v>
       </c>
@@ -55996,7 +56050,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A294" s="8">
         <v>42781</v>
       </c>
@@ -56037,7 +56091,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A295" s="8">
         <v>42788</v>
       </c>
@@ -56078,7 +56132,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A296" s="8">
         <v>42795</v>
       </c>
@@ -56119,7 +56173,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A297" s="8">
         <v>42802</v>
       </c>
@@ -56160,7 +56214,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A298" s="8">
         <v>42809</v>
       </c>
@@ -56201,7 +56255,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A299" s="8">
         <v>42816</v>
       </c>
@@ -56242,7 +56296,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A300" s="8">
         <v>42823</v>
       </c>
@@ -56283,7 +56337,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A301" s="8">
         <v>42830</v>
       </c>
@@ -56324,7 +56378,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A302" s="8">
         <v>42837</v>
       </c>
@@ -56365,7 +56419,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A303" s="8">
         <v>42844</v>
       </c>
@@ -56406,7 +56460,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A304" s="8">
         <v>42851</v>
       </c>
@@ -56447,7 +56501,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A305" s="8">
         <v>42858</v>
       </c>
@@ -56488,7 +56542,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A306" s="8">
         <v>42865</v>
       </c>
@@ -56529,7 +56583,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A307" s="8">
         <v>42872</v>
       </c>
@@ -56570,7 +56624,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A308" s="8">
         <v>42879</v>
       </c>
@@ -56611,7 +56665,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A309" s="8">
         <v>42886</v>
       </c>
@@ -56652,7 +56706,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A310" s="8">
         <v>42893</v>
       </c>
@@ -56693,7 +56747,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A311" s="8">
         <v>42900</v>
       </c>
@@ -56734,7 +56788,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A312" s="8">
         <v>42907</v>
       </c>
@@ -56775,7 +56829,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A313" s="8">
         <v>42914</v>
       </c>
@@ -56816,7 +56870,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A314" s="8">
         <v>42921</v>
       </c>
@@ -56857,7 +56911,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A315" s="8">
         <v>42928</v>
       </c>
@@ -56898,7 +56952,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A316" s="8">
         <v>42935</v>
       </c>
@@ -56939,7 +56993,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A317" s="8">
         <v>42942</v>
       </c>
@@ -56980,7 +57034,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A318" s="8">
         <v>42949</v>
       </c>
@@ -57021,7 +57075,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A319" s="8">
         <v>42956</v>
       </c>
@@ -57062,7 +57116,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A320" s="8">
         <v>42963</v>
       </c>
@@ -57103,7 +57157,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A321" s="8">
         <v>42970</v>
       </c>
@@ -57144,7 +57198,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A322" s="8">
         <v>42977</v>
       </c>
@@ -57185,7 +57239,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A323" s="8">
         <v>42984</v>
       </c>
@@ -57226,7 +57280,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A324" s="8">
         <v>42991</v>
       </c>
@@ -57267,7 +57321,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A325" s="8">
         <v>42998</v>
       </c>
@@ -57308,7 +57362,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A326" s="8">
         <v>43005</v>
       </c>
@@ -57349,7 +57403,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A327" s="8">
         <v>43012</v>
       </c>
@@ -57390,7 +57444,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A328" s="8">
         <v>43019</v>
       </c>
@@ -57431,7 +57485,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A329" s="8">
         <v>43026</v>
       </c>
@@ -57472,7 +57526,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A330" s="8">
         <v>43033</v>
       </c>
@@ -57513,7 +57567,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A331" s="8">
         <v>43040</v>
       </c>
@@ -57554,7 +57608,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A332" s="8">
         <v>43047</v>
       </c>
@@ -57595,7 +57649,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A333" s="8">
         <v>43054</v>
       </c>
@@ -57636,7 +57690,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A334" s="8">
         <v>43061</v>
       </c>
@@ -57677,7 +57731,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A335" s="8">
         <v>43068</v>
       </c>
@@ -57718,7 +57772,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A336" s="8">
         <v>43075</v>
       </c>
@@ -57759,7 +57813,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A337" s="8">
         <v>43082</v>
       </c>
@@ -57800,7 +57854,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A338" s="8">
         <v>43089</v>
       </c>
@@ -57841,7 +57895,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A339" s="8">
         <v>43096</v>
       </c>
@@ -57882,7 +57936,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A340" s="8">
         <v>43103</v>
       </c>
@@ -57923,7 +57977,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A341" s="8">
         <v>43110</v>
       </c>
@@ -57964,7 +58018,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A342" s="8">
         <v>43117</v>
       </c>
@@ -58005,7 +58059,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A343" s="8">
         <v>43124</v>
       </c>
@@ -58046,7 +58100,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A344" s="8">
         <v>43131</v>
       </c>
@@ -58087,7 +58141,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A345" s="8">
         <v>43138</v>
       </c>
@@ -58128,7 +58182,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A346" s="8">
         <v>43145</v>
       </c>
@@ -58169,7 +58223,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A347" s="8">
         <v>43152</v>
       </c>
@@ -58210,7 +58264,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A348" s="8">
         <v>43159</v>
       </c>
@@ -58251,7 +58305,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A349" s="8">
         <v>43166</v>
       </c>
@@ -58292,7 +58346,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A350" s="8">
         <v>43173</v>
       </c>
@@ -58333,7 +58387,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A351" s="8">
         <v>43180</v>
       </c>
@@ -58374,7 +58428,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A352" s="8">
         <v>43187</v>
       </c>
@@ -58415,7 +58469,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A353" s="8">
         <v>43194</v>
       </c>
@@ -58456,7 +58510,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A354" s="8">
         <v>43201</v>
       </c>
@@ -58497,7 +58551,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A355" s="8">
         <v>43208</v>
       </c>
@@ -58538,7 +58592,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A356" s="8">
         <v>43215</v>
       </c>
@@ -58579,7 +58633,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A357" s="8">
         <v>43222</v>
       </c>
@@ -58620,7 +58674,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A358" s="8">
         <v>43229</v>
       </c>
@@ -58661,7 +58715,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A359" s="8">
         <v>43236</v>
       </c>
@@ -58702,7 +58756,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A360" s="8">
         <v>43243</v>
       </c>
@@ -58743,7 +58797,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A361" s="8">
         <v>43250</v>
       </c>
@@ -58784,7 +58838,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A362" s="8">
         <v>43257</v>
       </c>
@@ -58825,7 +58879,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A363" s="8">
         <v>43264</v>
       </c>
@@ -58866,7 +58920,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A364" s="8">
         <v>43271</v>
       </c>
@@ -58907,7 +58961,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A365" s="8">
         <v>43278</v>
       </c>
@@ -58948,7 +59002,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A366" s="8">
         <v>43285</v>
       </c>
@@ -58989,7 +59043,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A367" s="8">
         <v>43292</v>
       </c>
@@ -59030,7 +59084,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A368" s="8">
         <v>43299</v>
       </c>
@@ -59071,7 +59125,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A369" s="8">
         <v>43306</v>
       </c>
@@ -59112,7 +59166,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A370" s="8">
         <v>43313</v>
       </c>
@@ -59153,7 +59207,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A371" s="8">
         <v>43320</v>
       </c>
@@ -59194,7 +59248,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A372" s="8">
         <v>43327</v>
       </c>
@@ -59235,7 +59289,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A373" s="8">
         <v>43334</v>
       </c>
@@ -59276,7 +59330,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A374" s="8">
         <v>43341</v>
       </c>
@@ -59317,7 +59371,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A375" s="8">
         <v>43348</v>
       </c>
@@ -59358,7 +59412,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A376" s="8">
         <v>43355</v>
       </c>
@@ -59399,7 +59453,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A377" s="8">
         <v>43362</v>
       </c>
@@ -59440,7 +59494,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A378" s="8">
         <v>43369</v>
       </c>
@@ -59481,7 +59535,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A379" s="8">
         <v>43376</v>
       </c>
@@ -59522,7 +59576,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A380" s="8">
         <v>43383</v>
       </c>
@@ -59563,7 +59617,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A381" s="8">
         <v>43390</v>
       </c>
@@ -59604,7 +59658,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A382" s="8">
         <v>43397</v>
       </c>
@@ -59645,7 +59699,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A383" s="8">
         <v>43404</v>
       </c>
@@ -59686,7 +59740,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A384" s="8">
         <v>43411</v>
       </c>
@@ -59727,7 +59781,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A385" s="8">
         <v>43418</v>
       </c>
@@ -59768,7 +59822,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A386" s="8">
         <v>43425</v>
       </c>
@@ -59809,7 +59863,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A387" s="8">
         <v>43432</v>
       </c>
@@ -59850,7 +59904,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A388" s="8">
         <v>43439</v>
       </c>
@@ -59891,7 +59945,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A389" s="8">
         <v>43446</v>
       </c>
@@ -59932,7 +59986,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A390" s="8">
         <v>43453</v>
       </c>
@@ -59973,7 +60027,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A391" s="8">
         <v>43460</v>
       </c>
@@ -60014,7 +60068,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A392" s="8">
         <v>43467</v>
       </c>
@@ -60055,7 +60109,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A393" s="8">
         <v>43474</v>
       </c>
@@ -60096,7 +60150,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A394" s="8">
         <v>43481</v>
       </c>
@@ -60137,7 +60191,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A395" s="8">
         <v>43488</v>
       </c>
@@ -60178,7 +60232,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A396" s="8">
         <v>43495</v>
       </c>
@@ -60219,7 +60273,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A397" s="8">
         <v>43502</v>
       </c>
@@ -60260,7 +60314,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A398" s="8">
         <v>43509</v>
       </c>
@@ -60301,7 +60355,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A399" s="8">
         <v>43516</v>
       </c>
@@ -60342,7 +60396,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A400" s="8">
         <v>43523</v>
       </c>
@@ -60383,7 +60437,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A401" s="8">
         <v>43530</v>
       </c>
@@ -60424,7 +60478,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A402" s="8">
         <v>43537</v>
       </c>
@@ -60465,7 +60519,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A403" s="8">
         <v>43544</v>
       </c>
@@ -60506,7 +60560,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A404" s="8">
         <v>43551</v>
       </c>
@@ -60547,7 +60601,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A405" s="8">
         <v>43558</v>
       </c>
@@ -60588,7 +60642,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A406" s="8">
         <v>43565</v>
       </c>
@@ -60629,7 +60683,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A407" s="8">
         <v>43572</v>
       </c>
@@ -60670,7 +60724,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A408" s="8">
         <v>43579</v>
       </c>
@@ -60711,7 +60765,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A409" s="8">
         <v>43586</v>
       </c>
@@ -60752,7 +60806,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A410" s="8">
         <v>43593</v>
       </c>
@@ -60793,7 +60847,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A411" s="8">
         <v>43600</v>
       </c>
@@ -60834,7 +60888,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A412" s="8">
         <v>43607</v>
       </c>
@@ -60875,7 +60929,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A413" s="8">
         <v>43614</v>
       </c>
@@ -60916,7 +60970,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A414" s="8">
         <v>43621</v>
       </c>
@@ -60957,7 +61011,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A415" s="8">
         <v>43628</v>
       </c>
@@ -60998,7 +61052,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A416" s="8">
         <v>43635</v>
       </c>
@@ -61039,7 +61093,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A417" s="8">
         <v>43642</v>
       </c>
@@ -61080,7 +61134,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A418" s="8">
         <v>43649</v>
       </c>
@@ -61121,7 +61175,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A419" s="8">
         <v>43656</v>
       </c>
@@ -61162,7 +61216,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A420" s="8">
         <v>43663</v>
       </c>
@@ -61203,7 +61257,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A421" s="8">
         <v>43670</v>
       </c>
@@ -61244,7 +61298,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A422" s="8">
         <v>43677</v>
       </c>
@@ -61285,7 +61339,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A423" s="8">
         <v>43684</v>
       </c>
@@ -61326,7 +61380,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A424" s="8">
         <v>43691</v>
       </c>
@@ -61367,7 +61421,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A425" s="8">
         <v>43698</v>
       </c>
@@ -61408,7 +61462,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A426" s="8">
         <v>43705</v>
       </c>
@@ -61449,7 +61503,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A427" s="8">
         <v>43712</v>
       </c>
@@ -61490,7 +61544,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A428" s="8">
         <v>43719</v>
       </c>
@@ -61531,7 +61585,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A429" s="8">
         <v>43726</v>
       </c>
@@ -61572,7 +61626,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A430" s="8">
         <v>43733</v>
       </c>
@@ -61613,7 +61667,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A431" s="8">
         <v>43740</v>
       </c>
@@ -61654,7 +61708,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A432" s="8">
         <v>43747</v>
       </c>
@@ -61695,7 +61749,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A433" s="8">
         <v>43754</v>
       </c>
@@ -61736,7 +61790,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A434" s="8">
         <v>43761</v>
       </c>
@@ -61777,7 +61831,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A435" s="8">
         <v>43768</v>
       </c>
@@ -61818,7 +61872,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A436" s="8">
         <v>43775</v>
       </c>
@@ -61859,7 +61913,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A437" s="8">
         <v>43782</v>
       </c>
@@ -61900,7 +61954,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A438" s="8">
         <v>43789</v>
       </c>
@@ -61941,7 +61995,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A439" s="8">
         <v>43796</v>
       </c>
@@ -61982,7 +62036,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A440" s="8">
         <v>43803</v>
       </c>
@@ -62023,7 +62077,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A441" s="8">
         <v>43810</v>
       </c>
@@ -62064,7 +62118,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A442" s="8">
         <v>43817</v>
       </c>
@@ -62105,7 +62159,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A443" s="8">
         <v>43831</v>
       </c>
@@ -62146,7 +62200,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A444" s="8">
         <v>43838</v>
       </c>
@@ -62187,7 +62241,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A445" s="8">
         <v>43845</v>
       </c>
@@ -62228,7 +62282,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A446" s="8">
         <v>43852</v>
       </c>
@@ -62269,7 +62323,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A447" s="8">
         <v>43859</v>
       </c>
@@ -62310,7 +62364,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A448" s="8">
         <v>43866</v>
       </c>
@@ -62351,7 +62405,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A449" s="8">
         <v>43873</v>
       </c>
@@ -62392,7 +62446,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A450" s="8">
         <v>43880</v>
       </c>
@@ -62433,7 +62487,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A451" s="8">
         <v>43887</v>
       </c>
@@ -62474,7 +62528,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A452" s="8">
         <v>43894</v>
       </c>
@@ -62515,7 +62569,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A453" s="8">
         <v>43901</v>
       </c>
@@ -62556,7 +62610,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A454" s="8">
         <v>43908</v>
       </c>
@@ -62597,7 +62651,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A455" s="8">
         <v>43915</v>
       </c>
@@ -62638,7 +62692,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A456" s="8">
         <v>43922</v>
       </c>
@@ -62679,7 +62733,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A457" s="8">
         <v>43929</v>
       </c>
@@ -62720,7 +62774,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A458" s="8">
         <v>43936</v>
       </c>
@@ -62761,7 +62815,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A459" s="8">
         <v>43943</v>
       </c>
@@ -62802,7 +62856,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A460" s="8">
         <v>43950</v>
       </c>
@@ -62843,7 +62897,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A461" s="8">
         <v>43957</v>
       </c>
@@ -62884,7 +62938,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A462" s="8">
         <v>43964</v>
       </c>
@@ -62925,7 +62979,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A463" s="8">
         <v>43971</v>
       </c>
@@ -62966,7 +63020,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A464" s="8">
         <v>43978</v>
       </c>
@@ -63007,7 +63061,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A465" s="8">
         <v>43985</v>
       </c>
@@ -63048,7 +63102,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A466" s="8">
         <v>43992</v>
       </c>
@@ -63089,7 +63143,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A467" s="8">
         <v>43999</v>
       </c>
@@ -63130,7 +63184,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A468" s="8">
         <v>44006</v>
       </c>
@@ -63171,7 +63225,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A469" s="8">
         <v>44013</v>
       </c>
@@ -63212,7 +63266,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A470" s="8">
         <v>44020</v>
       </c>
@@ -63253,7 +63307,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A471" s="8">
         <v>44027</v>
       </c>
@@ -63294,7 +63348,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A472" s="8">
         <v>44034</v>
       </c>
@@ -63335,7 +63389,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A473" s="8">
         <v>44041</v>
       </c>
@@ -63376,7 +63430,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A474" s="8">
         <v>44048</v>
       </c>
@@ -63417,7 +63471,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A475" s="8">
         <v>44055</v>
       </c>
@@ -63458,7 +63512,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A476" s="8">
         <v>44062</v>
       </c>
@@ -63499,7 +63553,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A477" s="8">
         <v>44069</v>
       </c>
@@ -63540,7 +63594,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A478" s="8">
         <v>44076</v>
       </c>
@@ -63581,7 +63635,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A479" s="8">
         <v>44083</v>
       </c>
@@ -63622,7 +63676,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A480" s="8">
         <v>44090</v>
       </c>
@@ -63663,7 +63717,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A481" s="8">
         <v>44097</v>
       </c>
@@ -63704,7 +63758,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A482" s="8">
         <v>44104</v>
       </c>
@@ -63745,7 +63799,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A483" s="8">
         <v>44111</v>
       </c>
@@ -63786,7 +63840,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A484" s="8">
         <v>44118</v>
       </c>
@@ -63827,7 +63881,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A485" s="8">
         <v>44125</v>
       </c>
@@ -63868,7 +63922,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A486" s="8">
         <v>44132</v>
       </c>
@@ -63909,7 +63963,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A487" s="8">
         <v>44139</v>
       </c>
@@ -63950,7 +64004,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A488" s="8">
         <v>44146</v>
       </c>
@@ -63991,7 +64045,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A489" s="8">
         <v>44153</v>
       </c>
@@ -64032,7 +64086,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A490" s="8">
         <v>44160</v>
       </c>
@@ -64073,7 +64127,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A491" s="8">
         <v>44167</v>
       </c>
@@ -64114,7 +64168,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A492" s="8">
         <v>44174</v>
       </c>
@@ -64155,7 +64209,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A493" s="8">
         <v>44181</v>
       </c>
@@ -64196,7 +64250,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A494" s="8">
         <v>44188</v>
       </c>
@@ -64237,7 +64291,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A495" s="8">
         <v>44195</v>
       </c>
@@ -64278,7 +64332,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A496" s="8">
         <v>44202</v>
       </c>
@@ -64319,7 +64373,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A497" s="8">
         <v>44209</v>
       </c>
@@ -64360,7 +64414,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A498" s="8">
         <v>44216</v>
       </c>
@@ -64401,7 +64455,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A499" s="8">
         <v>44223</v>
       </c>
@@ -64442,7 +64496,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A500" s="8">
         <v>44230</v>
       </c>
@@ -64483,7 +64537,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A501" s="8">
         <v>44237</v>
       </c>
@@ -64524,7 +64578,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A502" s="8">
         <v>44244</v>
       </c>
@@ -64565,7 +64619,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A503" s="8">
         <v>44251</v>
       </c>
@@ -64606,7 +64660,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A504" s="8">
         <v>44258</v>
       </c>
@@ -64647,7 +64701,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A505" s="8">
         <v>44265</v>
       </c>
@@ -64688,7 +64742,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A506" s="8">
         <v>44272</v>
       </c>
@@ -64729,7 +64783,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A507" s="8">
         <v>44279</v>
       </c>
@@ -64770,7 +64824,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A508" s="8">
         <v>44286</v>
       </c>
@@ -64811,7 +64865,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A509" s="8">
         <v>44293</v>
       </c>
@@ -64852,7 +64906,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A510" s="8">
         <v>44300</v>
       </c>
@@ -64893,7 +64947,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A511" s="8">
         <v>44307</v>
       </c>
@@ -64934,7 +64988,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A512" s="8">
         <v>44314</v>
       </c>
@@ -64975,7 +65029,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A513" s="8">
         <v>44321</v>
       </c>
@@ -65016,7 +65070,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A514" s="8">
         <v>44328</v>
       </c>
@@ -65057,7 +65111,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A515" s="8">
         <v>44335</v>
       </c>
@@ -65098,7 +65152,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A516" s="8">
         <v>44342</v>
       </c>
@@ -65139,7 +65193,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A517" s="8">
         <v>44349</v>
       </c>
@@ -65180,7 +65234,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A518" s="8">
         <v>44356</v>
       </c>
@@ -65221,7 +65275,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A519" s="8">
         <v>44363</v>
       </c>
@@ -65262,7 +65316,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A520" s="8">
         <v>44370</v>
       </c>
@@ -65303,7 +65357,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A521" s="8">
         <v>44377</v>
       </c>
@@ -65344,7 +65398,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A522" s="8">
         <v>44384</v>
       </c>
@@ -65385,7 +65439,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A523" s="8">
         <v>44391</v>
       </c>
@@ -65426,7 +65480,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A524" s="8">
         <v>44398</v>
       </c>
@@ -65467,7 +65521,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A525" s="8">
         <v>44405</v>
       </c>
@@ -65508,7 +65562,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A526" s="8">
         <v>44412</v>
       </c>
@@ -65549,7 +65603,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A527" s="8">
         <v>44419</v>
       </c>
@@ -65590,7 +65644,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A528" s="8">
         <v>44426</v>
       </c>
@@ -65631,7 +65685,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A529" s="8">
         <v>44433</v>
       </c>
@@ -65672,7 +65726,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A530" s="8">
         <v>44440</v>
       </c>
@@ -65713,7 +65767,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A531" s="8">
         <v>44447</v>
       </c>
@@ -65754,7 +65808,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A532" s="8">
         <v>44454</v>
       </c>
@@ -65795,7 +65849,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A533" s="8">
         <v>44461</v>
       </c>
@@ -65836,7 +65890,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A534" s="8">
         <v>44468</v>
       </c>
@@ -65877,7 +65931,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A535" s="8">
         <v>44475</v>
       </c>
@@ -65918,7 +65972,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A536" s="8">
         <v>44482</v>
       </c>
@@ -65959,7 +66013,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A537" s="8">
         <v>44489</v>
       </c>
@@ -66000,7 +66054,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A538" s="8">
         <v>44496</v>
       </c>
@@ -66041,7 +66095,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A539" s="8">
         <v>44503</v>
       </c>
@@ -66082,7 +66136,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A540" s="8">
         <v>44510</v>
       </c>
@@ -66123,7 +66177,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A541" s="8">
         <v>44517</v>
       </c>
@@ -66164,7 +66218,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A542" s="8">
         <v>44524</v>
       </c>
@@ -66205,7 +66259,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A543" s="8">
         <v>44531</v>
       </c>
@@ -66246,7 +66300,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A544" s="8">
         <v>44538</v>
       </c>
@@ -66287,7 +66341,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A545" s="8">
         <v>44545</v>
       </c>
@@ -66328,7 +66382,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A546" s="8">
         <v>44552</v>
       </c>
@@ -66369,7 +66423,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A547" s="8">
         <v>44566</v>
       </c>
@@ -66410,7 +66464,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A548" s="8">
         <v>44573</v>
       </c>
@@ -66451,7 +66505,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A549" s="8">
         <v>44580</v>
       </c>
@@ -66492,7 +66546,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A550" s="8">
         <v>44587</v>
       </c>
@@ -66533,7 +66587,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A551" s="8">
         <v>44594</v>
       </c>
@@ -66574,7 +66628,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A552" s="8">
         <v>44601</v>
       </c>
@@ -66615,7 +66669,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A553" s="8">
         <v>44608</v>
       </c>
@@ -66656,7 +66710,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A554" s="8">
         <v>44615</v>
       </c>
@@ -66697,7 +66751,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A555" s="8">
         <v>44622</v>
       </c>
@@ -66738,7 +66792,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A556" s="8">
         <v>44629</v>
       </c>
@@ -66779,7 +66833,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A557" s="8">
         <v>44636</v>
       </c>
@@ -66820,7 +66874,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A558" s="8">
         <v>44643</v>
       </c>
@@ -66861,7 +66915,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A559" s="8">
         <v>44650</v>
       </c>
@@ -66902,7 +66956,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A560" s="8">
         <v>44657</v>
       </c>
@@ -66943,7 +66997,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A561" s="8">
         <v>44664</v>
       </c>
@@ -66984,7 +67038,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A562" s="8">
         <v>44671</v>
       </c>
@@ -67025,7 +67079,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A563" s="8">
         <v>44678</v>
       </c>
@@ -67066,7 +67120,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A564" s="8">
         <v>44685</v>
       </c>
@@ -67107,7 +67161,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A565" s="8">
         <v>44692</v>
       </c>
@@ -67148,7 +67202,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A566" s="8">
         <v>44699</v>
       </c>
@@ -67189,7 +67243,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A567" s="8">
         <v>44706</v>
       </c>
@@ -67230,7 +67284,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A568" s="8">
         <v>44713</v>
       </c>
@@ -67271,7 +67325,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A569" s="8">
         <v>44720</v>
       </c>
@@ -67312,7 +67366,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A570" s="8">
         <v>44727</v>
       </c>
@@ -67353,7 +67407,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A571" s="8">
         <v>44734</v>
       </c>
@@ -67394,7 +67448,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A572" s="8">
         <v>44741</v>
       </c>
@@ -67435,7 +67489,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A573" s="8">
         <v>44748</v>
       </c>
@@ -67476,7 +67530,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A574" s="8">
         <v>44755</v>
       </c>
@@ -67517,7 +67571,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A575" s="8">
         <v>44762</v>
       </c>
@@ -67558,7 +67612,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A576" s="8">
         <v>44769</v>
       </c>
@@ -67599,7 +67653,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A577" s="8">
         <v>44776</v>
       </c>
@@ -67640,7 +67694,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A578" s="8">
         <v>44783</v>
       </c>
@@ -67681,7 +67735,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A579" s="8">
         <v>44790</v>
       </c>
@@ -67722,7 +67776,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A580" s="8">
         <v>44797</v>
       </c>
@@ -67763,7 +67817,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A581" s="8">
         <v>44804</v>
       </c>
@@ -67804,7 +67858,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A582" s="8">
         <v>44811</v>
       </c>
@@ -67845,7 +67899,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A583" s="8">
         <v>44818</v>
       </c>
@@ -67886,7 +67940,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A584" s="8">
         <v>44825</v>
       </c>
@@ -67927,7 +67981,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A585" s="8">
         <v>44832</v>
       </c>
@@ -67968,7 +68022,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A586" s="8">
         <v>44839</v>
       </c>
@@ -68009,7 +68063,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A587" s="8">
         <v>44846</v>
       </c>
@@ -68050,7 +68104,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A588" s="8">
         <v>44853</v>
       </c>
@@ -68091,7 +68145,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A589" s="8">
         <v>44860</v>
       </c>
@@ -68132,7 +68186,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A590" s="8">
         <v>44867</v>
       </c>
@@ -68173,7 +68227,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A591" s="8">
         <v>44874</v>
       </c>
@@ -68214,7 +68268,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A592" s="8">
         <v>44881</v>
       </c>
@@ -68255,7 +68309,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A593" s="8">
         <v>44888</v>
       </c>
@@ -68296,7 +68350,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A594" s="8">
         <v>44895</v>
       </c>
@@ -68337,7 +68391,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A595" s="8">
         <v>44902</v>
       </c>
@@ -68378,7 +68432,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A596" s="8">
         <v>44909</v>
       </c>
@@ -68419,7 +68473,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A597" s="8">
         <v>44916</v>
       </c>
@@ -68460,7 +68514,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A598" s="8">
         <v>44930</v>
       </c>
@@ -68501,7 +68555,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A599" s="8">
         <v>44937</v>
       </c>
@@ -68542,7 +68596,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A600" s="8">
         <v>44944</v>
       </c>
@@ -68583,7 +68637,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A601" s="8">
         <v>44951</v>
       </c>
@@ -68624,7 +68678,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A602" s="8">
         <v>44958</v>
       </c>
@@ -68665,7 +68719,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A603" s="8">
         <v>44965</v>
       </c>
@@ -68706,7 +68760,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A604" s="8">
         <v>44972</v>
       </c>
@@ -68747,7 +68801,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A605" s="8">
         <v>44979</v>
       </c>
@@ -68788,7 +68842,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A606" s="8">
         <v>44986</v>
       </c>
@@ -68829,7 +68883,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A607" s="8">
         <v>44993</v>
       </c>
@@ -68870,7 +68924,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A608" s="8">
         <v>45000</v>
       </c>
@@ -68911,7 +68965,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A609" s="8">
         <v>45007</v>
       </c>
@@ -68952,7 +69006,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A610" s="8">
         <v>45014</v>
       </c>
@@ -68993,7 +69047,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A611" s="8">
         <v>45021</v>
       </c>
@@ -69034,7 +69088,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A612" s="8">
         <v>45028</v>
       </c>
@@ -69075,7 +69129,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A613" s="8">
         <v>45035</v>
       </c>
@@ -69116,7 +69170,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A614" s="8">
         <v>45042</v>
       </c>
@@ -69157,7 +69211,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A615" s="8">
         <v>45049</v>
       </c>
@@ -69198,7 +69252,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A616" s="8">
         <v>45056</v>
       </c>
@@ -69239,7 +69293,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A617" s="8">
         <v>45063</v>
       </c>
@@ -69280,7 +69334,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A618" s="8">
         <v>45070</v>
       </c>
@@ -69321,7 +69375,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A619" s="8">
         <v>45077</v>
       </c>
@@ -69362,7 +69416,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A620" s="8">
         <v>45084</v>
       </c>
@@ -69403,7 +69457,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A621" s="8">
         <v>45091</v>
       </c>
@@ -69444,7 +69498,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A622" s="8">
         <v>45098</v>
       </c>
@@ -69485,7 +69539,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A623" s="8">
         <v>45105</v>
       </c>
@@ -69526,7 +69580,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A624" s="8">
         <v>45112</v>
       </c>
@@ -69567,7 +69621,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A625" s="8">
         <v>45119</v>
       </c>
@@ -69608,7 +69662,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A626" s="8">
         <v>45126</v>
       </c>
@@ -69649,7 +69703,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A627" s="8">
         <v>45133</v>
       </c>
@@ -69690,7 +69744,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A628" s="8">
         <v>45140</v>
       </c>
@@ -69731,7 +69785,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A629" s="8">
         <v>45147</v>
       </c>
@@ -69772,7 +69826,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A630" s="8">
         <v>45154</v>
       </c>
@@ -69813,7 +69867,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A631" s="8">
         <v>45161</v>
       </c>
@@ -69854,7 +69908,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A632" s="8">
         <v>45168</v>
       </c>
@@ -69895,7 +69949,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A633" s="8">
         <v>45175</v>
       </c>
@@ -69936,7 +69990,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A634" s="8">
         <v>45182</v>
       </c>
@@ -69977,7 +70031,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A635" s="8">
         <v>45189</v>
       </c>
@@ -70018,7 +70072,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A636" s="8">
         <v>45196</v>
       </c>
@@ -70059,7 +70113,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A637" s="8">
         <v>45203</v>
       </c>
@@ -70100,7 +70154,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A638" s="8">
         <v>45210</v>
       </c>
@@ -70141,7 +70195,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A639" s="8">
         <v>45217</v>
       </c>
@@ -70182,7 +70236,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A640" s="8">
         <v>45224</v>
       </c>
@@ -70223,7 +70277,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A641" s="8">
         <v>45231</v>
       </c>
@@ -70264,7 +70318,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A642" s="8">
         <v>45238</v>
       </c>
@@ -70305,7 +70359,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A643" s="8">
         <v>45245</v>
       </c>
@@ -70346,7 +70400,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A644" s="8">
         <v>45252</v>
       </c>
@@ -70387,7 +70441,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A645" s="8">
         <v>45259</v>
       </c>
@@ -70428,7 +70482,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A646" s="8">
         <v>45266</v>
       </c>
@@ -70469,7 +70523,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A647" s="8">
         <v>45273</v>
       </c>
@@ -70510,7 +70564,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A648" s="8">
         <v>45280</v>
       </c>
@@ -70551,7 +70605,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A649" s="8">
         <v>45294</v>
       </c>
@@ -70592,7 +70646,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A650" s="8">
         <v>45301</v>
       </c>
@@ -70633,7 +70687,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A651" s="8">
         <v>45308</v>
       </c>
@@ -70674,7 +70728,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A652" s="8">
         <v>45315</v>
       </c>
@@ -70715,7 +70769,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A653" s="8">
         <v>45322</v>
       </c>
@@ -70756,7 +70810,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A654" s="8">
         <v>45329</v>
       </c>
@@ -70797,7 +70851,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A655" s="8">
         <v>45336</v>
       </c>
@@ -70838,7 +70892,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A656" s="8">
         <v>45343</v>
       </c>
@@ -70879,7 +70933,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A657" s="8">
         <v>45350</v>
       </c>
@@ -70920,7 +70974,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A658" s="8">
         <v>45357</v>
       </c>
@@ -70961,7 +71015,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A659" s="8">
         <v>45364</v>
       </c>
@@ -71002,7 +71056,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A660" s="8">
         <v>45371</v>
       </c>
@@ -71043,7 +71097,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A661" s="8">
         <v>45378</v>
       </c>
@@ -71084,7 +71138,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A662" s="8">
         <v>45385</v>
       </c>
@@ -71125,7 +71179,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A663" s="8">
         <v>45392</v>
       </c>
@@ -71166,7 +71220,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A664" s="8">
         <v>45399</v>
       </c>
@@ -71207,7 +71261,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A665" s="8">
         <v>45406</v>
       </c>
@@ -71248,7 +71302,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A666" s="8">
         <v>45413</v>
       </c>
@@ -71289,7 +71343,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A667" s="8">
         <v>45420</v>
       </c>
@@ -71330,7 +71384,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A668" s="8">
         <v>45427</v>
       </c>
@@ -71371,7 +71425,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A669" s="8">
         <v>45434</v>
       </c>
@@ -71412,7 +71466,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A670" s="8">
         <v>45441</v>
       </c>
@@ -71453,7 +71507,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A671" s="8">
         <v>45448</v>
       </c>
@@ -71494,7 +71548,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A672" s="8">
         <v>45455</v>
       </c>
@@ -71535,7 +71589,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A673" s="8">
         <v>45462</v>
       </c>
@@ -71576,7 +71630,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A674" s="8">
         <v>45469</v>
       </c>
@@ -71617,7 +71671,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A675" s="8">
         <v>45476</v>
       </c>
@@ -71658,7 +71712,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A676" s="8">
         <v>45483</v>
       </c>
@@ -71699,7 +71753,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A677" s="8">
         <v>45490</v>
       </c>
@@ -71740,7 +71794,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A678" s="8">
         <v>45497</v>
       </c>
@@ -71781,7 +71835,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A679" s="8">
         <v>45504</v>
       </c>
@@ -71822,7 +71876,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A680" s="8">
         <v>45511</v>
       </c>
@@ -71863,7 +71917,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A681" s="8">
         <v>45518</v>
       </c>
@@ -71904,7 +71958,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A682" s="8">
         <v>45525</v>
       </c>
@@ -71945,7 +71999,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A683" s="8">
         <v>45532</v>
       </c>
@@ -71986,7 +72040,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A684" s="8">
         <v>45539</v>
       </c>
@@ -72027,7 +72081,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A685" s="8">
         <v>45546</v>
       </c>
@@ -72068,7 +72122,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A686" s="8">
         <v>45553</v>
       </c>
@@ -72109,7 +72163,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A687" s="8">
         <v>45560</v>
       </c>
@@ -72150,7 +72204,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A688" s="8">
         <v>45567</v>
       </c>
@@ -72191,7 +72245,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A689" s="8">
         <v>45574</v>
       </c>
@@ -72232,7 +72286,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A690" s="8">
         <v>45581</v>
       </c>
@@ -72273,7 +72327,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A691" s="8">
         <v>45588</v>
       </c>
@@ -72314,7 +72368,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A692" s="8">
         <v>45595</v>
       </c>
@@ -72355,7 +72409,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A693" s="8">
         <v>45602</v>
       </c>
@@ -72396,7 +72450,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A694" s="8">
         <v>45609</v>
       </c>
@@ -72437,7 +72491,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A695" s="8">
         <v>45616</v>
       </c>
@@ -72478,7 +72532,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A696" s="8">
         <v>45623</v>
       </c>
@@ -72519,7 +72573,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A697" s="8">
         <v>45630</v>
       </c>
@@ -72560,7 +72614,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A698" s="8">
         <v>45637</v>
       </c>
@@ -72601,7 +72655,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A699" s="8">
         <v>45644</v>
       </c>
@@ -72642,7 +72696,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A700" s="8">
         <v>45658</v>
       </c>
@@ -72683,7 +72737,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A701" s="8">
         <v>45665</v>
       </c>
@@ -72724,7 +72778,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A702" s="8">
         <v>45672</v>
       </c>
@@ -72765,7 +72819,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A703" s="8">
         <v>45679</v>
       </c>
@@ -72806,7 +72860,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A704" s="8">
         <v>45686</v>
       </c>
@@ -72847,7 +72901,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A705" s="8">
         <v>45693</v>
       </c>
@@ -72888,7 +72942,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A706" s="8">
         <v>45700</v>
       </c>
@@ -72929,7 +72983,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A707" s="8">
         <v>45707</v>
       </c>
@@ -72970,7 +73024,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A708" s="8">
         <v>45714</v>
       </c>
@@ -73011,7 +73065,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A709" s="8">
         <v>45721</v>
       </c>
@@ -73052,7 +73106,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A710" s="8">
         <v>45728</v>
       </c>
@@ -73093,7 +73147,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A711" s="8">
         <v>45735</v>
       </c>
@@ -73134,7 +73188,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A712" s="8">
         <v>45742</v>
       </c>
@@ -73175,7 +73229,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A713" s="8">
         <v>45749</v>
       </c>
@@ -73216,7 +73270,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A714" s="8">
         <v>45756</v>
       </c>
@@ -73257,7 +73311,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A715" s="8">
         <v>45763</v>
       </c>
@@ -73298,7 +73352,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A716" s="8">
         <v>45770</v>
       </c>
@@ -73339,7 +73393,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A717" s="8">
         <v>45777</v>
       </c>
@@ -73380,7 +73434,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A718" s="8">
         <v>45784</v>
       </c>
@@ -73421,7 +73475,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A719" s="8">
         <v>45791</v>
       </c>
@@ -73462,7 +73516,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A720" s="8">
         <v>45798</v>
       </c>
@@ -73503,7 +73557,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A721" s="8">
         <v>45805</v>
       </c>
@@ -73544,7 +73598,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A722" s="8">
         <v>45812</v>
       </c>
@@ -73585,7 +73639,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A723" s="8">
         <v>45819</v>
       </c>
@@ -73626,7 +73680,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A724" s="8">
         <v>45826</v>
       </c>
@@ -73667,7 +73721,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A725" s="8">
         <v>45833</v>
       </c>
@@ -73708,7 +73762,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A726" s="8">
         <v>45840</v>
       </c>
@@ -73749,7 +73803,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A727" s="8">
         <v>45847</v>
       </c>
@@ -73790,7 +73844,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A728" s="8">
         <v>45854</v>
       </c>
@@ -73831,7 +73885,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A729" s="8">
         <v>45861</v>
       </c>
@@ -73872,7 +73926,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A730" s="8">
         <v>45868</v>
       </c>
@@ -73913,7 +73967,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A731" s="8">
         <v>45875</v>
       </c>
@@ -73954,7 +74008,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A732" s="8">
         <v>45882</v>
       </c>
@@ -73995,7 +74049,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A733" s="8">
         <v>45889</v>
       </c>
@@ -74036,7 +74090,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A734" s="8">
         <v>45896</v>
       </c>
@@ -74077,7 +74131,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A735" s="8">
         <v>45903</v>
       </c>
@@ -74118,7 +74172,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A736" s="8">
         <v>45910</v>
       </c>
@@ -74159,7 +74213,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A737" s="8">
         <v>45917</v>
       </c>
@@ -74200,7 +74254,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A738" s="8">
         <v>45924</v>
       </c>
@@ -74241,7 +74295,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A739" s="8">
         <v>45931</v>
       </c>
@@ -74282,7 +74336,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A740" s="8">
         <v>45938</v>
       </c>
@@ -74323,7 +74377,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A741" s="8">
         <v>45945</v>
       </c>
@@ -74364,7 +74418,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A742" s="8">
         <v>45952</v>
       </c>
@@ -74405,7 +74459,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A743" s="8">
         <v>45959</v>
       </c>
@@ -74446,7 +74500,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A744" s="8">
         <v>45966</v>
       </c>
@@ -74487,7 +74541,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A745" s="8">
         <v>45973</v>
       </c>
@@ -74528,7 +74582,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A746" s="8">
         <v>45980</v>
       </c>
@@ -74569,7 +74623,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A747" s="8">
         <v>45987</v>
       </c>
@@ -74610,7 +74664,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A748" s="8">
         <v>45994</v>
       </c>
@@ -74651,7 +74705,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A749" s="8">
         <v>46001</v>
       </c>
@@ -74692,7 +74746,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A750" s="8">
         <v>46008</v>
       </c>
@@ -74733,7 +74787,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A751" s="8">
         <v>46015</v>
       </c>
@@ -74774,7 +74828,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A752" s="8">
         <v>46022</v>
       </c>
@@ -74815,7 +74869,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A753" s="8">
         <v>46029</v>
       </c>
@@ -74856,7 +74910,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A754" s="8">
         <v>46036</v>
       </c>
@@ -74897,7 +74951,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A755" s="8">
         <v>46043</v>
       </c>
@@ -74938,7 +74992,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A756" s="8">
         <v>46050</v>
       </c>
@@ -74979,7 +75033,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A757" s="8">
         <v>46057</v>
       </c>
@@ -75020,7 +75074,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A758" s="8">
         <v>46064</v>
       </c>
@@ -75061,7 +75115,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A759" s="8">
         <v>46071</v>
       </c>
@@ -75102,7 +75156,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A760" s="8">
         <v>46078</v>
       </c>
@@ -75143,7 +75197,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A761" s="8">
         <v>46085</v>
       </c>
@@ -75184,7 +75238,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A762" s="8">
         <v>46092</v>
       </c>
@@ -75225,7 +75279,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A763" s="8">
         <v>46099</v>
       </c>
@@ -75266,7 +75320,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A764" s="8">
         <v>46106</v>
       </c>
@@ -75307,7 +75361,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A765" s="8">
         <v>46113</v>
       </c>
@@ -75348,7 +75402,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A766" s="8">
         <v>46120</v>
       </c>
@@ -75389,7 +75443,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A767" s="8">
         <v>46127</v>
       </c>
@@ -75430,7 +75484,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A768" s="8">
         <v>46134</v>
       </c>
@@ -75471,7 +75525,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A769" s="8">
         <v>46141</v>
       </c>
@@ -75512,7 +75566,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A770" s="8">
         <v>46148</v>
       </c>
@@ -75553,7 +75607,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A771" s="8">
         <v>46155</v>
       </c>
@@ -75594,7 +75648,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A772" s="8">
         <v>46162</v>
       </c>
@@ -75635,7 +75689,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A773" s="8">
         <v>46169</v>
       </c>
@@ -75676,7 +75730,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A774" s="8">
         <v>46176</v>
       </c>
@@ -75717,7 +75771,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A775" s="8">
         <v>46183</v>
       </c>
@@ -75758,7 +75812,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A776" s="8">
         <v>46190</v>
       </c>
@@ -75799,7 +75853,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="777" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A777" s="8">
         <v>46197</v>
       </c>
@@ -75840,7 +75894,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="778" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A778" s="8">
         <v>46204</v>
       </c>
@@ -75881,7 +75935,7 @@
         <v>2602</v>
       </c>
     </row>
-    <row r="779" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A779" s="8">
         <v>46211</v>
       </c>
@@ -75922,7 +75976,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="780" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A780" s="8">
         <v>46218</v>
       </c>
@@ -75963,7 +76017,7 @@
         <v>2667</v>
       </c>
     </row>
-    <row r="781" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A781" s="8">
         <v>46225</v>
       </c>
@@ -76004,7 +76058,7 @@
         <v>2635</v>
       </c>
     </row>
-    <row r="782" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A782" s="8">
         <v>46232</v>
       </c>
@@ -76043,6 +76097,47 @@
       </c>
       <c r="M782" s="11">
         <v>2719</v>
+      </c>
+    </row>
+    <row r="783" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A783" s="8">
+        <v>46239</v>
+      </c>
+      <c r="B783" s="8">
+        <v>46240</v>
+      </c>
+      <c r="C783" s="9">
+        <v>0.58333333334346504</v>
+      </c>
+      <c r="D783" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E783" s="10">
+        <v>4297.46</v>
+      </c>
+      <c r="F783" s="11">
+        <v>4653</v>
+      </c>
+      <c r="G783" s="11">
+        <v>5506</v>
+      </c>
+      <c r="H783" s="11">
+        <v>5894</v>
+      </c>
+      <c r="I783" s="11">
+        <v>7893</v>
+      </c>
+      <c r="J783" s="11">
+        <v>583</v>
+      </c>
+      <c r="K783" s="11">
+        <v>839</v>
+      </c>
+      <c r="L783" s="11">
+        <v>1096</v>
+      </c>
+      <c r="M783" s="11">
+        <v>2773</v>
       </c>
     </row>
   </sheetData>
@@ -76055,7 +76150,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -76066,12 +76161,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
@@ -76090,7 +76185,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E957BC7-E7BE-4403-8862-38C7F3D8B459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FB1CD2-7A6C-46E4-9084-87DB6B339C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -2636,6 +2636,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4990,6 +4993,9 @@
                 </c:pt>
                 <c:pt idx="781">
                   <c:v>4297.46</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>4339</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7380,6 +7386,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9734,6 +9743,9 @@
                 </c:pt>
                 <c:pt idx="781">
                   <c:v>4653</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>4425</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12124,6 +12136,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14479,10 +14494,13 @@
                 <c:pt idx="781">
                   <c:v>5506</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>5080</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-7388-468B-8576-2C5D46BD4D58}"/>
@@ -16868,6 +16886,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19223,10 +19244,13 @@
                 <c:pt idx="781">
                   <c:v>5894</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>6244</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-7388-468B-8576-2C5D46BD4D58}"/>
@@ -21612,6 +21636,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23967,10 +23994,13 @@
                 <c:pt idx="781">
                   <c:v>7893</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>8706</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-7388-468B-8576-2C5D46BD4D58}"/>
@@ -26356,6 +26386,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28711,10 +28744,13 @@
                 <c:pt idx="781">
                   <c:v>583</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>574</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-7388-468B-8576-2C5D46BD4D58}"/>
@@ -31102,6 +31138,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33457,10 +33496,13 @@
                 <c:pt idx="781">
                   <c:v>839</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>830</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-7388-468B-8576-2C5D46BD4D58}"/>
@@ -35848,6 +35890,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -38203,10 +38248,13 @@
                 <c:pt idx="781">
                   <c:v>1096</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>1088</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-7388-468B-8576-2C5D46BD4D58}"/>
@@ -40594,6 +40642,9 @@
                 <c:pt idx="781">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -42949,10 +43000,13 @@
                 <c:pt idx="781">
                   <c:v>2773</c:v>
                 </c:pt>
+                <c:pt idx="782">
+                  <c:v>2884</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000008-7388-468B-8576-2C5D46BD4D58}"/>
@@ -44025,7 +44079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M783"/>
+  <dimension ref="A1:M784"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
@@ -76138,6 +76192,47 @@
       </c>
       <c r="M783" s="11">
         <v>2773</v>
+      </c>
+    </row>
+    <row r="784" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A784" s="8">
+        <v>46246</v>
+      </c>
+      <c r="B784" s="8">
+        <v>46247</v>
+      </c>
+      <c r="C784" s="9">
+        <v>0.58333333334480497</v>
+      </c>
+      <c r="D784" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E784" s="10">
+        <v>4339</v>
+      </c>
+      <c r="F784" s="11">
+        <v>4425</v>
+      </c>
+      <c r="G784" s="11">
+        <v>5080</v>
+      </c>
+      <c r="H784" s="11">
+        <v>6244</v>
+      </c>
+      <c r="I784" s="11">
+        <v>8706</v>
+      </c>
+      <c r="J784" s="11">
+        <v>574</v>
+      </c>
+      <c r="K784" s="11">
+        <v>830</v>
+      </c>
+      <c r="L784" s="11">
+        <v>1088</v>
+      </c>
+      <c r="M784" s="11">
+        <v>2884</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FB1CD2-7A6C-46E4-9084-87DB6B339C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFCD0E1-5B20-4579-BA1C-E629C3D12009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -2639,6 +2639,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4995,7 +4998,10 @@
                   <c:v>4297.46</c:v>
                 </c:pt>
                 <c:pt idx="782">
-                  <c:v>4339</c:v>
+                  <c:v>4338.6000000000004</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>4526</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7389,6 +7395,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9746,6 +9755,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>4425</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>4401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12139,6 +12151,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14496,6 +14511,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>5080</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>4955</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16889,6 +16907,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19246,6 +19267,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>6244</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>6802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21639,6 +21663,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -23996,6 +24023,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>8706</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>9507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26389,6 +26419,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28746,6 +28779,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>574</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>591</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -31141,6 +31177,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33498,6 +33537,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>822</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35893,6 +35935,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -38250,6 +38295,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>1088</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>1126</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -40645,6 +40693,9 @@
                 <c:pt idx="782">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="783">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -43002,6 +43053,9 @@
                 </c:pt>
                 <c:pt idx="782">
                   <c:v>2884</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>3039</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -44079,7 +44133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M784"/>
+  <dimension ref="A1:M785"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
@@ -76208,7 +76262,7 @@
         <v>15</v>
       </c>
       <c r="E784" s="10">
-        <v>4339</v>
+        <v>4338.6000000000004</v>
       </c>
       <c r="F784" s="11">
         <v>4425</v>
@@ -76233,6 +76287,47 @@
       </c>
       <c r="M784" s="11">
         <v>2884</v>
+      </c>
+    </row>
+    <row r="785" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A785" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B785" s="8">
+        <v>46254</v>
+      </c>
+      <c r="C785" s="9">
+        <v>0.58333333334614501</v>
+      </c>
+      <c r="D785" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E785" s="10">
+        <v>4526</v>
+      </c>
+      <c r="F785" s="11">
+        <v>4401</v>
+      </c>
+      <c r="G785" s="11">
+        <v>4955</v>
+      </c>
+      <c r="H785" s="11">
+        <v>6802</v>
+      </c>
+      <c r="I785" s="11">
+        <v>9507</v>
+      </c>
+      <c r="J785" s="11">
+        <v>591</v>
+      </c>
+      <c r="K785" s="11">
+        <v>822</v>
+      </c>
+      <c r="L785" s="11">
+        <v>1126</v>
+      </c>
+      <c r="M785" s="11">
+        <v>3039</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/freight/world container index.xlsx
+++ b/data_lake/freight/world container index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFCD0E1-5B20-4579-BA1C-E629C3D12009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE7384D-4CC7-F547-BFF9-AF0CA35E671F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17980" yWindow="780" windowWidth="18020" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="19">
   <si>
     <t>WCI Composite</t>
   </si>
@@ -107,29 +107,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,7 +138,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -146,7 +146,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -195,35 +195,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -241,7 +241,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2642,6 +2642,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5001,7 +5004,10 @@
                   <c:v>4338.6000000000004</c:v>
                 </c:pt>
                 <c:pt idx="783">
-                  <c:v>4526</c:v>
+                  <c:v>4526.1899999999996</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>4472.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7398,6 +7404,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9758,6 +9767,9 @@
                 </c:pt>
                 <c:pt idx="783">
                   <c:v>4401</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>4287</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12154,6 +12166,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14514,6 +14529,9 @@
                 </c:pt>
                 <c:pt idx="783">
                   <c:v>4955</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>2866</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16910,6 +16928,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -19270,6 +19291,9 @@
                 </c:pt>
                 <c:pt idx="783">
                   <c:v>6802</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>6818</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21666,6 +21690,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -24026,6 +24053,9 @@
                 </c:pt>
                 <c:pt idx="783">
                   <c:v>9507</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>9333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -26422,6 +26452,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -28782,6 +28815,9 @@
                 </c:pt>
                 <c:pt idx="783">
                   <c:v>591</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>588</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -31180,6 +31216,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -33539,6 +33578,9 @@
                   <c:v>830</c:v>
                 </c:pt>
                 <c:pt idx="783">
+                  <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="784">
                   <c:v>822</c:v>
                 </c:pt>
               </c:numCache>
@@ -35938,6 +35980,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -38297,6 +38342,9 @@
                   <c:v>1088</c:v>
                 </c:pt>
                 <c:pt idx="783">
+                  <c:v>1126</c:v>
+                </c:pt>
+                <c:pt idx="784">
                   <c:v>1126</c:v>
                 </c:pt>
               </c:numCache>
@@ -40696,6 +40744,9 @@
                 <c:pt idx="783">
                   <c:v>46254</c:v>
                 </c:pt>
+                <c:pt idx="784">
+                  <c:v>46261</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -43056,6 +43107,9 @@
                 </c:pt>
                 <c:pt idx="783">
                   <c:v>3039</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>3010</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -44133,19 +44187,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M785"/>
-  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M786"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="10.5" style="11" customWidth="1"/>
     <col min="14" max="16384" width="7.5" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -44186,7 +44240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>40716</v>
       </c>
@@ -44227,7 +44281,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>40723</v>
       </c>
@@ -44268,7 +44322,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>40730</v>
       </c>
@@ -44309,7 +44363,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>40737</v>
       </c>
@@ -44350,7 +44404,7 @@
         <v>2572.9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>40744</v>
       </c>
@@ -44391,7 +44445,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>40751</v>
       </c>
@@ -44432,7 +44486,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>40758</v>
       </c>
@@ -44473,7 +44527,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>40765</v>
       </c>
@@ -44514,7 +44568,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>40772</v>
       </c>
@@ -44555,7 +44609,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>40779</v>
       </c>
@@ -44596,7 +44650,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>40786</v>
       </c>
@@ -44637,7 +44691,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>40793</v>
       </c>
@@ -44678,7 +44732,7 @@
         <v>2572</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>40800</v>
       </c>
@@ -44719,7 +44773,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>40807</v>
       </c>
@@ -44760,7 +44814,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>40814</v>
       </c>
@@ -44801,7 +44855,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>40821</v>
       </c>
@@ -44842,7 +44896,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>40828</v>
       </c>
@@ -44883,7 +44937,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>40835</v>
       </c>
@@ -44924,7 +44978,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>40842</v>
       </c>
@@ -44965,7 +45019,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>40849</v>
       </c>
@@ -45006,7 +45060,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>40856</v>
       </c>
@@ -45047,7 +45101,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>40863</v>
       </c>
@@ -45088,7 +45142,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>40870</v>
       </c>
@@ -45129,7 +45183,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>40877</v>
       </c>
@@ -45170,7 +45224,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>40884</v>
       </c>
@@ -45211,7 +45265,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>40891</v>
       </c>
@@ -45252,7 +45306,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>40898</v>
       </c>
@@ -45293,7 +45347,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>40905</v>
       </c>
@@ -45334,7 +45388,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>40912</v>
       </c>
@@ -45375,7 +45429,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>40919</v>
       </c>
@@ -45416,7 +45470,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>40926</v>
       </c>
@@ -45457,7 +45511,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>40933</v>
       </c>
@@ -45498,7 +45552,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>40940</v>
       </c>
@@ -45539,7 +45593,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>40947</v>
       </c>
@@ -45580,7 +45634,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>40954</v>
       </c>
@@ -45621,7 +45675,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>40961</v>
       </c>
@@ -45662,7 +45716,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>40968</v>
       </c>
@@ -45703,7 +45757,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>40975</v>
       </c>
@@ -45744,7 +45798,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>40982</v>
       </c>
@@ -45785,7 +45839,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>40989</v>
       </c>
@@ -45826,7 +45880,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>40996</v>
       </c>
@@ -45867,7 +45921,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>41003</v>
       </c>
@@ -45908,7 +45962,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>41010</v>
       </c>
@@ -45949,7 +46003,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>41017</v>
       </c>
@@ -45990,7 +46044,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>41024</v>
       </c>
@@ -46031,7 +46085,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>41031</v>
       </c>
@@ -46072,7 +46126,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>41038</v>
       </c>
@@ -46113,7 +46167,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>41045</v>
       </c>
@@ -46154,7 +46208,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>41052</v>
       </c>
@@ -46195,7 +46249,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>41059</v>
       </c>
@@ -46236,7 +46290,7 @@
         <v>2605</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>41066</v>
       </c>
@@ -46277,7 +46331,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>41073</v>
       </c>
@@ -46318,7 +46372,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>41080</v>
       </c>
@@ -46359,7 +46413,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>41087</v>
       </c>
@@ -46400,7 +46454,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>41094</v>
       </c>
@@ -46441,7 +46495,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>41101</v>
       </c>
@@ -46482,7 +46536,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>41108</v>
       </c>
@@ -46523,7 +46577,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>41115</v>
       </c>
@@ -46564,7 +46618,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>41122</v>
       </c>
@@ -46605,7 +46659,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>41129</v>
       </c>
@@ -46646,7 +46700,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>41136</v>
       </c>
@@ -46687,7 +46741,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>41143</v>
       </c>
@@ -46728,7 +46782,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>41150</v>
       </c>
@@ -46769,7 +46823,7 @@
         <v>2656</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>41157</v>
       </c>
@@ -46810,7 +46864,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>41164</v>
       </c>
@@ -46851,7 +46905,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>41171</v>
       </c>
@@ -46892,7 +46946,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>41178</v>
       </c>
@@ -46933,7 +46987,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>41185</v>
       </c>
@@ -46974,7 +47028,7 @@
         <v>2428</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>41192</v>
       </c>
@@ -47015,7 +47069,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>41199</v>
       </c>
@@ -47056,7 +47110,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>41206</v>
       </c>
@@ -47097,7 +47151,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>41213</v>
       </c>
@@ -47138,7 +47192,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>41220</v>
       </c>
@@ -47179,7 +47233,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>41227</v>
       </c>
@@ -47220,7 +47274,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>41234</v>
       </c>
@@ -47261,7 +47315,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>41241</v>
       </c>
@@ -47302,7 +47356,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>41248</v>
       </c>
@@ -47343,7 +47397,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>41255</v>
       </c>
@@ -47384,7 +47438,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>41262</v>
       </c>
@@ -47425,7 +47479,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>41269</v>
       </c>
@@ -47466,7 +47520,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>41276</v>
       </c>
@@ -47507,7 +47561,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>41283</v>
       </c>
@@ -47548,7 +47602,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>41290</v>
       </c>
@@ -47589,7 +47643,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>41297</v>
       </c>
@@ -47630,7 +47684,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>41304</v>
       </c>
@@ -47671,7 +47725,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>41311</v>
       </c>
@@ -47712,7 +47766,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>41318</v>
       </c>
@@ -47753,7 +47807,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>41325</v>
       </c>
@@ -47794,7 +47848,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>41332</v>
       </c>
@@ -47835,7 +47889,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>41339</v>
       </c>
@@ -47876,7 +47930,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>41346</v>
       </c>
@@ -47917,7 +47971,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>41353</v>
       </c>
@@ -47958,7 +48012,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>41360</v>
       </c>
@@ -47999,7 +48053,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>41367</v>
       </c>
@@ -48040,7 +48094,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>41374</v>
       </c>
@@ -48081,7 +48135,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>41381</v>
       </c>
@@ -48122,7 +48176,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>41388</v>
       </c>
@@ -48163,7 +48217,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>41395</v>
       </c>
@@ -48204,7 +48258,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>41402</v>
       </c>
@@ -48245,7 +48299,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>41409</v>
       </c>
@@ -48286,7 +48340,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>41416</v>
       </c>
@@ -48327,7 +48381,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>41423</v>
       </c>
@@ -48368,7 +48422,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>41430</v>
       </c>
@@ -48409,7 +48463,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>41437</v>
       </c>
@@ -48450,7 +48504,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>41444</v>
       </c>
@@ -48491,7 +48545,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>41451</v>
       </c>
@@ -48532,7 +48586,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>41458</v>
       </c>
@@ -48573,7 +48627,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>41465</v>
       </c>
@@ -48614,7 +48668,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>41472</v>
       </c>
@@ -48655,7 +48709,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>41479</v>
       </c>
@@ -48696,7 +48750,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>41486</v>
       </c>
@@ -48737,7 +48791,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>41493</v>
       </c>
@@ -48778,7 +48832,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="8">
         <v>41500</v>
       </c>
@@ -48819,7 +48873,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="8">
         <v>41507</v>
       </c>
@@ -48860,7 +48914,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="8">
         <v>41514</v>
       </c>
@@ -48901,7 +48955,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="8">
         <v>41521</v>
       </c>
@@ -48942,7 +48996,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="8">
         <v>41528</v>
       </c>
@@ -48983,7 +49037,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="8">
         <v>41535</v>
       </c>
@@ -49024,7 +49078,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="8">
         <v>41542</v>
       </c>
@@ -49065,7 +49119,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="8">
         <v>41549</v>
       </c>
@@ -49106,7 +49160,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="8">
         <v>41556</v>
       </c>
@@ -49147,7 +49201,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="8">
         <v>41563</v>
       </c>
@@ -49188,7 +49242,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="8">
         <v>41570</v>
       </c>
@@ -49229,7 +49283,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
         <v>41577</v>
       </c>
@@ -49270,7 +49324,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
         <v>41584</v>
       </c>
@@ -49311,7 +49365,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
         <v>41591</v>
       </c>
@@ -49352,7 +49406,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
         <v>41598</v>
       </c>
@@ -49393,7 +49447,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
         <v>41605</v>
       </c>
@@ -49434,7 +49488,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
         <v>41612</v>
       </c>
@@ -49475,7 +49529,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <v>41619</v>
       </c>
@@ -49516,7 +49570,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <v>41626</v>
       </c>
@@ -49557,7 +49611,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <v>41640</v>
       </c>
@@ -49598,7 +49652,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <v>41647</v>
       </c>
@@ -49639,7 +49693,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <v>41654</v>
       </c>
@@ -49680,7 +49734,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <v>41661</v>
       </c>
@@ -49721,7 +49775,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <v>41668</v>
       </c>
@@ -49762,7 +49816,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <v>41675</v>
       </c>
@@ -49803,7 +49857,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
         <v>41682</v>
       </c>
@@ -49844,7 +49898,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
         <v>41689</v>
       </c>
@@ -49885,7 +49939,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
         <v>41696</v>
       </c>
@@ -49926,7 +49980,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
         <v>41703</v>
       </c>
@@ -49967,7 +50021,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
         <v>41710</v>
       </c>
@@ -50008,7 +50062,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
         <v>41717</v>
       </c>
@@ -50049,7 +50103,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
         <v>41724</v>
       </c>
@@ -50090,7 +50144,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <v>41731</v>
       </c>
@@ -50131,7 +50185,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <v>41738</v>
       </c>
@@ -50172,7 +50226,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <v>41745</v>
       </c>
@@ -50213,7 +50267,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <v>41752</v>
       </c>
@@ -50254,7 +50308,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <v>41759</v>
       </c>
@@ -50295,7 +50349,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <v>41766</v>
       </c>
@@ -50336,7 +50390,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <v>41773</v>
       </c>
@@ -50377,7 +50431,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <v>41780</v>
       </c>
@@ -50418,7 +50472,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <v>41787</v>
       </c>
@@ -50459,7 +50513,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>41794</v>
       </c>
@@ -50500,7 +50554,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <v>41801</v>
       </c>
@@ -50541,7 +50595,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>41808</v>
       </c>
@@ -50582,7 +50636,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <v>41815</v>
       </c>
@@ -50623,7 +50677,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>41822</v>
       </c>
@@ -50664,7 +50718,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <v>41829</v>
       </c>
@@ -50705,7 +50759,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>41836</v>
       </c>
@@ -50746,7 +50800,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <v>41843</v>
       </c>
@@ -50787,7 +50841,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>41850</v>
       </c>
@@ -50828,7 +50882,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <v>41857</v>
       </c>
@@ -50869,7 +50923,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>41864</v>
       </c>
@@ -50910,7 +50964,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166" s="8">
         <v>41871</v>
       </c>
@@ -50951,7 +51005,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>41878</v>
       </c>
@@ -50992,7 +51046,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
         <v>41885</v>
       </c>
@@ -51033,7 +51087,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>41892</v>
       </c>
@@ -51074,7 +51128,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170" s="8">
         <v>41899</v>
       </c>
@@ -51115,7 +51169,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>41906</v>
       </c>
@@ -51156,7 +51210,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172" s="8">
         <v>41913</v>
       </c>
@@ -51197,7 +51251,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173" s="8">
         <v>41920</v>
       </c>
@@ -51238,7 +51292,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174" s="8">
         <v>41927</v>
       </c>
@@ -51279,7 +51333,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175" s="8">
         <v>41934</v>
       </c>
@@ -51320,7 +51374,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176" s="8">
         <v>41941</v>
       </c>
@@ -51361,7 +51415,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <v>41948</v>
       </c>
@@ -51402,7 +51456,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178" s="8">
         <v>41955</v>
       </c>
@@ -51443,7 +51497,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179" s="8">
         <v>41962</v>
       </c>
@@ -51484,7 +51538,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180" s="8">
         <v>41969</v>
       </c>
@@ -51525,7 +51579,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <v>41976</v>
       </c>
@@ -51566,7 +51620,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <v>41983</v>
       </c>
@@ -51607,7 +51661,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <v>41990</v>
       </c>
@@ -51648,7 +51702,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184" s="8">
         <v>42011</v>
       </c>
@@ -51689,7 +51743,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <v>42018</v>
       </c>
@@ -51730,7 +51784,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <v>42025</v>
       </c>
@@ -51771,7 +51825,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <v>42032</v>
       </c>
@@ -51812,7 +51866,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <v>42039</v>
       </c>
@@ -51853,7 +51907,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <v>42046</v>
       </c>
@@ -51894,7 +51948,7 @@
         <v>2333</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <v>42053</v>
       </c>
@@ -51935,7 +51989,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <v>42060</v>
       </c>
@@ -51976,7 +52030,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <v>42067</v>
       </c>
@@ -52017,7 +52071,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <v>42074</v>
       </c>
@@ -52058,7 +52112,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <v>42081</v>
       </c>
@@ -52099,7 +52153,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <v>42088</v>
       </c>
@@ -52140,7 +52194,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <v>42095</v>
       </c>
@@ -52181,7 +52235,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <v>42102</v>
       </c>
@@ -52222,7 +52276,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <v>42109</v>
       </c>
@@ -52263,7 +52317,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <v>42116</v>
       </c>
@@ -52304,7 +52358,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <v>42123</v>
       </c>
@@ -52345,7 +52399,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <v>42130</v>
       </c>
@@ -52386,7 +52440,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <v>42137</v>
       </c>
@@ -52427,7 +52481,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <v>42144</v>
       </c>
@@ -52468,7 +52522,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <v>42151</v>
       </c>
@@ -52509,7 +52563,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <v>42158</v>
       </c>
@@ -52550,7 +52604,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <v>42165</v>
       </c>
@@ -52591,7 +52645,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <v>42172</v>
       </c>
@@ -52632,7 +52686,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <v>42179</v>
       </c>
@@ -52673,7 +52727,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <v>42186</v>
       </c>
@@ -52714,7 +52768,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <v>42193</v>
       </c>
@@ -52755,7 +52809,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <v>42200</v>
       </c>
@@ -52796,7 +52850,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <v>42207</v>
       </c>
@@ -52837,7 +52891,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <v>42214</v>
       </c>
@@ -52878,7 +52932,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <v>42221</v>
       </c>
@@ -52919,7 +52973,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <v>42228</v>
       </c>
@@ -52960,7 +53014,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <v>42235</v>
       </c>
@@ -53001,7 +53055,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <v>42242</v>
       </c>
@@ -53042,7 +53096,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <v>42249</v>
       </c>
@@ -53083,7 +53137,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <v>42256</v>
       </c>
@@ -53124,7 +53178,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <v>42263</v>
       </c>
@@ -53165,7 +53219,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <v>42270</v>
       </c>
@@ -53206,7 +53260,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <v>42277</v>
       </c>
@@ -53247,7 +53301,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <v>42284</v>
       </c>
@@ -53288,7 +53342,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <v>42291</v>
       </c>
@@ -53329,7 +53383,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <v>42298</v>
       </c>
@@ -53370,7 +53424,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <v>42305</v>
       </c>
@@ -53411,7 +53465,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <v>42312</v>
       </c>
@@ -53452,7 +53506,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <v>42319</v>
       </c>
@@ -53493,7 +53547,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <v>42326</v>
       </c>
@@ -53534,7 +53588,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <v>42333</v>
       </c>
@@ -53575,7 +53629,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <v>42340</v>
       </c>
@@ -53616,7 +53670,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <v>42347</v>
       </c>
@@ -53657,7 +53711,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <v>42354</v>
       </c>
@@ -53698,7 +53752,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <v>42361</v>
       </c>
@@ -53739,7 +53793,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <v>42368</v>
       </c>
@@ -53780,7 +53834,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <v>42375</v>
       </c>
@@ -53821,7 +53875,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <v>42382</v>
       </c>
@@ -53862,7 +53916,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <v>42389</v>
       </c>
@@ -53903,7 +53957,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <v>42396</v>
       </c>
@@ -53944,7 +53998,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <v>42403</v>
       </c>
@@ -53985,7 +54039,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <v>42410</v>
       </c>
@@ -54026,7 +54080,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <v>42417</v>
       </c>
@@ -54067,7 +54121,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <v>42424</v>
       </c>
@@ -54108,7 +54162,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <v>42431</v>
       </c>
@@ -54149,7 +54203,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <v>42438</v>
       </c>
@@ -54190,7 +54244,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <v>42445</v>
       </c>
@@ -54231,7 +54285,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <v>42452</v>
       </c>
@@ -54272,7 +54326,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <v>42459</v>
       </c>
@@ -54313,7 +54367,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <v>42466</v>
       </c>
@@ -54354,7 +54408,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <v>42473</v>
       </c>
@@ -54395,7 +54449,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <v>42480</v>
       </c>
@@ -54436,7 +54490,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <v>42487</v>
       </c>
@@ -54477,7 +54531,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <v>42494</v>
       </c>
@@ -54518,7 +54572,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <v>42501</v>
       </c>
@@ -54559,7 +54613,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <v>42508</v>
       </c>
@@ -54600,7 +54654,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <v>42515</v>
       </c>
@@ -54641,7 +54695,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <v>42522</v>
       </c>
@@ -54682,7 +54736,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <v>42529</v>
       </c>
@@ -54723,7 +54777,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259" s="8">
         <v>42536</v>
       </c>
@@ -54764,7 +54818,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" s="8">
         <v>42543</v>
       </c>
@@ -54805,7 +54859,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261" s="8">
         <v>42550</v>
       </c>
@@ -54846,7 +54900,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262" s="8">
         <v>42557</v>
       </c>
@@ -54887,7 +54941,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263" s="8">
         <v>42564</v>
       </c>
@@ -54928,7 +54982,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264" s="8">
         <v>42571</v>
       </c>
@@ -54969,7 +55023,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265" s="8">
         <v>42578</v>
       </c>
@@ -55010,7 +55064,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266" s="8">
         <v>42585</v>
       </c>
@@ -55051,7 +55105,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267" s="8">
         <v>42592</v>
       </c>
@@ -55092,7 +55146,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268" s="8">
         <v>42599</v>
       </c>
@@ -55133,7 +55187,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269" s="8">
         <v>42606</v>
       </c>
@@ -55174,7 +55228,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270" s="8">
         <v>42613</v>
       </c>
@@ -55215,7 +55269,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <v>42620</v>
       </c>
@@ -55256,7 +55310,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <v>42627</v>
       </c>
@@ -55297,7 +55351,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <v>42634</v>
       </c>
@@ -55338,7 +55392,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <v>42641</v>
       </c>
@@ -55379,7 +55433,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <v>42648</v>
       </c>
@@ -55420,7 +55474,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <v>42655</v>
       </c>
@@ -55461,7 +55515,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <v>42662</v>
       </c>
@@ -55502,7 +55556,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <v>42669</v>
       </c>
@@ -55543,7 +55597,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <v>42676</v>
       </c>
@@ -55584,7 +55638,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <v>42683</v>
       </c>
@@ -55625,7 +55679,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <v>42690</v>
       </c>
@@ -55666,7 +55720,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <v>42697</v>
       </c>
@@ -55707,7 +55761,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <v>42704</v>
       </c>
@@ -55748,7 +55802,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <v>42711</v>
       </c>
@@ -55789,7 +55843,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <v>42718</v>
       </c>
@@ -55830,7 +55884,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <v>42725</v>
       </c>
@@ -55871,7 +55925,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A287" s="8">
         <v>42732</v>
       </c>
@@ -55912,7 +55966,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A288" s="8">
         <v>42739</v>
       </c>
@@ -55953,7 +56007,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289" s="8">
         <v>42746</v>
       </c>
@@ -55994,7 +56048,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290" s="8">
         <v>42753</v>
       </c>
@@ -56035,7 +56089,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291" s="8">
         <v>42760</v>
       </c>
@@ -56076,7 +56130,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" s="8">
         <v>42767</v>
       </c>
@@ -56117,7 +56171,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293" s="8">
         <v>42774</v>
       </c>
@@ -56158,7 +56212,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294" s="8">
         <v>42781</v>
       </c>
@@ -56199,7 +56253,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295" s="8">
         <v>42788</v>
       </c>
@@ -56240,7 +56294,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296" s="8">
         <v>42795</v>
       </c>
@@ -56281,7 +56335,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297" s="8">
         <v>42802</v>
       </c>
@@ -56322,7 +56376,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298" s="8">
         <v>42809</v>
       </c>
@@ -56363,7 +56417,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299" s="8">
         <v>42816</v>
       </c>
@@ -56404,7 +56458,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300" s="8">
         <v>42823</v>
       </c>
@@ -56445,7 +56499,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301" s="8">
         <v>42830</v>
       </c>
@@ -56486,7 +56540,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302" s="8">
         <v>42837</v>
       </c>
@@ -56527,7 +56581,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303" s="8">
         <v>42844</v>
       </c>
@@ -56568,7 +56622,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304" s="8">
         <v>42851</v>
       </c>
@@ -56609,7 +56663,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305" s="8">
         <v>42858</v>
       </c>
@@ -56650,7 +56704,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306" s="8">
         <v>42865</v>
       </c>
@@ -56691,7 +56745,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307" s="8">
         <v>42872</v>
       </c>
@@ -56732,7 +56786,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308" s="8">
         <v>42879</v>
       </c>
@@ -56773,7 +56827,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309" s="8">
         <v>42886</v>
       </c>
@@ -56814,7 +56868,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310" s="8">
         <v>42893</v>
       </c>
@@ -56855,7 +56909,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" s="8">
         <v>42900</v>
       </c>
@@ -56896,7 +56950,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312" s="8">
         <v>42907</v>
       </c>
@@ -56937,7 +56991,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313" s="8">
         <v>42914</v>
       </c>
@@ -56978,7 +57032,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314" s="8">
         <v>42921</v>
       </c>
@@ -57019,7 +57073,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315" s="8">
         <v>42928</v>
       </c>
@@ -57060,7 +57114,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316" s="8">
         <v>42935</v>
       </c>
@@ -57101,7 +57155,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317" s="8">
         <v>42942</v>
       </c>
@@ -57142,7 +57196,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318" s="8">
         <v>42949</v>
       </c>
@@ -57183,7 +57237,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319" s="8">
         <v>42956</v>
       </c>
@@ -57224,7 +57278,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320" s="8">
         <v>42963</v>
       </c>
@@ -57265,7 +57319,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321" s="8">
         <v>42970</v>
       </c>
@@ -57306,7 +57360,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322" s="8">
         <v>42977</v>
       </c>
@@ -57347,7 +57401,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323" s="8">
         <v>42984</v>
       </c>
@@ -57388,7 +57442,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324" s="8">
         <v>42991</v>
       </c>
@@ -57429,7 +57483,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325" s="8">
         <v>42998</v>
       </c>
@@ -57470,7 +57524,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A326" s="8">
         <v>43005</v>
       </c>
@@ -57511,7 +57565,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327" s="8">
         <v>43012</v>
       </c>
@@ -57552,7 +57606,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A328" s="8">
         <v>43019</v>
       </c>
@@ -57593,7 +57647,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" s="8">
         <v>43026</v>
       </c>
@@ -57634,7 +57688,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330" s="8">
         <v>43033</v>
       </c>
@@ -57675,7 +57729,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331" s="8">
         <v>43040</v>
       </c>
@@ -57716,7 +57770,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332" s="8">
         <v>43047</v>
       </c>
@@ -57757,7 +57811,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333" s="8">
         <v>43054</v>
       </c>
@@ -57798,7 +57852,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334" s="8">
         <v>43061</v>
       </c>
@@ -57839,7 +57893,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335" s="8">
         <v>43068</v>
       </c>
@@ -57880,7 +57934,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336" s="8">
         <v>43075</v>
       </c>
@@ -57921,7 +57975,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337" s="8">
         <v>43082</v>
       </c>
@@ -57962,7 +58016,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338" s="8">
         <v>43089</v>
       </c>
@@ -58003,7 +58057,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339" s="8">
         <v>43096</v>
       </c>
@@ -58044,7 +58098,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340" s="8">
         <v>43103</v>
       </c>
@@ -58085,7 +58139,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341" s="8">
         <v>43110</v>
       </c>
@@ -58126,7 +58180,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342" s="8">
         <v>43117</v>
       </c>
@@ -58167,7 +58221,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343" s="8">
         <v>43124</v>
       </c>
@@ -58208,7 +58262,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344" s="8">
         <v>43131</v>
       </c>
@@ -58249,7 +58303,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345" s="8">
         <v>43138</v>
       </c>
@@ -58290,7 +58344,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346" s="8">
         <v>43145</v>
       </c>
@@ -58331,7 +58385,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347" s="8">
         <v>43152</v>
       </c>
@@ -58372,7 +58426,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348" s="8">
         <v>43159</v>
       </c>
@@ -58413,7 +58467,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349" s="8">
         <v>43166</v>
       </c>
@@ -58454,7 +58508,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350" s="8">
         <v>43173</v>
       </c>
@@ -58495,7 +58549,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351" s="8">
         <v>43180</v>
       </c>
@@ -58536,7 +58590,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352" s="8">
         <v>43187</v>
       </c>
@@ -58577,7 +58631,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353" s="8">
         <v>43194</v>
       </c>
@@ -58618,7 +58672,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354" s="8">
         <v>43201</v>
       </c>
@@ -58659,7 +58713,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355" s="8">
         <v>43208</v>
       </c>
@@ -58700,7 +58754,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356" s="8">
         <v>43215</v>
       </c>
@@ -58741,7 +58795,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357" s="8">
         <v>43222</v>
       </c>
@@ -58782,7 +58836,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358" s="8">
         <v>43229</v>
       </c>
@@ -58823,7 +58877,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359" s="8">
         <v>43236</v>
       </c>
@@ -58864,7 +58918,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360" s="8">
         <v>43243</v>
       </c>
@@ -58905,7 +58959,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361" s="8">
         <v>43250</v>
       </c>
@@ -58946,7 +59000,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362" s="8">
         <v>43257</v>
       </c>
@@ -58987,7 +59041,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363" s="8">
         <v>43264</v>
       </c>
@@ -59028,7 +59082,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364" s="8">
         <v>43271</v>
       </c>
@@ -59069,7 +59123,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365" s="8">
         <v>43278</v>
       </c>
@@ -59110,7 +59164,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366" s="8">
         <v>43285</v>
       </c>
@@ -59151,7 +59205,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367" s="8">
         <v>43292</v>
       </c>
@@ -59192,7 +59246,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368" s="8">
         <v>43299</v>
       </c>
@@ -59233,7 +59287,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A369" s="8">
         <v>43306</v>
       </c>
@@ -59274,7 +59328,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370" s="8">
         <v>43313</v>
       </c>
@@ -59315,7 +59369,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A371" s="8">
         <v>43320</v>
       </c>
@@ -59356,7 +59410,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A372" s="8">
         <v>43327</v>
       </c>
@@ -59397,7 +59451,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A373" s="8">
         <v>43334</v>
       </c>
@@ -59438,7 +59492,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A374" s="8">
         <v>43341</v>
       </c>
@@ -59479,7 +59533,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375" s="8">
         <v>43348</v>
       </c>
@@ -59520,7 +59574,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376" s="8">
         <v>43355</v>
       </c>
@@ -59561,7 +59615,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377" s="8">
         <v>43362</v>
       </c>
@@ -59602,7 +59656,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378" s="8">
         <v>43369</v>
       </c>
@@ -59643,7 +59697,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379" s="8">
         <v>43376</v>
       </c>
@@ -59684,7 +59738,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380" s="8">
         <v>43383</v>
       </c>
@@ -59725,7 +59779,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A381" s="8">
         <v>43390</v>
       </c>
@@ -59766,7 +59820,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A382" s="8">
         <v>43397</v>
       </c>
@@ -59807,7 +59861,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A383" s="8">
         <v>43404</v>
       </c>
@@ -59848,7 +59902,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A384" s="8">
         <v>43411</v>
       </c>
@@ -59889,7 +59943,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385" s="8">
         <v>43418</v>
       </c>
@@ -59930,7 +59984,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386" s="8">
         <v>43425</v>
       </c>
@@ -59971,7 +60025,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387" s="8">
         <v>43432</v>
       </c>
@@ -60012,7 +60066,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388" s="8">
         <v>43439</v>
       </c>
@@ -60053,7 +60107,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389" s="8">
         <v>43446</v>
       </c>
@@ -60094,7 +60148,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390" s="8">
         <v>43453</v>
       </c>
@@ -60135,7 +60189,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A391" s="8">
         <v>43460</v>
       </c>
@@ -60176,7 +60230,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392" s="8">
         <v>43467</v>
       </c>
@@ -60217,7 +60271,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393" s="8">
         <v>43474</v>
       </c>
@@ -60258,7 +60312,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394" s="8">
         <v>43481</v>
       </c>
@@ -60299,7 +60353,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395" s="8">
         <v>43488</v>
       </c>
@@ -60340,7 +60394,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396" s="8">
         <v>43495</v>
       </c>
@@ -60381,7 +60435,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397" s="8">
         <v>43502</v>
       </c>
@@ -60422,7 +60476,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398" s="8">
         <v>43509</v>
       </c>
@@ -60463,7 +60517,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399" s="8">
         <v>43516</v>
       </c>
@@ -60504,7 +60558,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400" s="8">
         <v>43523</v>
       </c>
@@ -60545,7 +60599,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401" s="8">
         <v>43530</v>
       </c>
@@ -60586,7 +60640,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402" s="8">
         <v>43537</v>
       </c>
@@ -60627,7 +60681,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403" s="8">
         <v>43544</v>
       </c>
@@ -60668,7 +60722,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404" s="8">
         <v>43551</v>
       </c>
@@ -60709,7 +60763,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405" s="8">
         <v>43558</v>
       </c>
@@ -60750,7 +60804,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406" s="8">
         <v>43565</v>
       </c>
@@ -60791,7 +60845,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A407" s="8">
         <v>43572</v>
       </c>
@@ -60832,7 +60886,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408" s="8">
         <v>43579</v>
       </c>
@@ -60873,7 +60927,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409" s="8">
         <v>43586</v>
       </c>
@@ -60914,7 +60968,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" s="8">
         <v>43593</v>
       </c>
@@ -60955,7 +61009,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" s="8">
         <v>43600</v>
       </c>
@@ -60996,7 +61050,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" s="8">
         <v>43607</v>
       </c>
@@ -61037,7 +61091,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" s="8">
         <v>43614</v>
       </c>
@@ -61078,7 +61132,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414" s="8">
         <v>43621</v>
       </c>
@@ -61119,7 +61173,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A415" s="8">
         <v>43628</v>
       </c>
@@ -61160,7 +61214,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A416" s="8">
         <v>43635</v>
       </c>
@@ -61201,7 +61255,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A417" s="8">
         <v>43642</v>
       </c>
@@ -61242,7 +61296,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" s="8">
         <v>43649</v>
       </c>
@@ -61283,7 +61337,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419" s="8">
         <v>43656</v>
       </c>
@@ -61324,7 +61378,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420" s="8">
         <v>43663</v>
       </c>
@@ -61365,7 +61419,7 @@
         <v>2393</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" s="8">
         <v>43670</v>
       </c>
@@ -61406,7 +61460,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" s="8">
         <v>43677</v>
       </c>
@@ -61447,7 +61501,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423" s="8">
         <v>43684</v>
       </c>
@@ -61488,7 +61542,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424" s="8">
         <v>43691</v>
       </c>
@@ -61529,7 +61583,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425" s="8">
         <v>43698</v>
       </c>
@@ -61570,7 +61624,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426" s="8">
         <v>43705</v>
       </c>
@@ -61611,7 +61665,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" s="8">
         <v>43712</v>
       </c>
@@ -61652,7 +61706,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428" s="8">
         <v>43719</v>
       </c>
@@ -61693,7 +61747,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429" s="8">
         <v>43726</v>
       </c>
@@ -61734,7 +61788,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430" s="8">
         <v>43733</v>
       </c>
@@ -61775,7 +61829,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A431" s="8">
         <v>43740</v>
       </c>
@@ -61816,7 +61870,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A432" s="8">
         <v>43747</v>
       </c>
@@ -61857,7 +61911,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A433" s="8">
         <v>43754</v>
       </c>
@@ -61898,7 +61952,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A434" s="8">
         <v>43761</v>
       </c>
@@ -61939,7 +61993,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A435" s="8">
         <v>43768</v>
       </c>
@@ -61980,7 +62034,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436" s="8">
         <v>43775</v>
       </c>
@@ -62021,7 +62075,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A437" s="8">
         <v>43782</v>
       </c>
@@ -62062,7 +62116,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438" s="8">
         <v>43789</v>
       </c>
@@ -62103,7 +62157,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439" s="8">
         <v>43796</v>
       </c>
@@ -62144,7 +62198,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A440" s="8">
         <v>43803</v>
       </c>
@@ -62185,7 +62239,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A441" s="8">
         <v>43810</v>
       </c>
@@ -62226,7 +62280,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A442" s="8">
         <v>43817</v>
       </c>
@@ -62267,7 +62321,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A443" s="8">
         <v>43831</v>
       </c>
@@ -62308,7 +62362,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A444" s="8">
         <v>43838</v>
       </c>
@@ -62349,7 +62403,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445" s="8">
         <v>43845</v>
       </c>
@@ -62390,7 +62444,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446" s="8">
         <v>43852</v>
       </c>
@@ -62431,7 +62485,7 @@
         <v>2410</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447" s="8">
         <v>43859</v>
       </c>
@@ -62472,7 +62526,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A448" s="8">
         <v>43866</v>
       </c>
@@ -62513,7 +62567,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A449" s="8">
         <v>43873</v>
       </c>
@@ -62554,7 +62608,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A450" s="8">
         <v>43880</v>
       </c>
@@ -62595,7 +62649,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A451" s="8">
         <v>43887</v>
       </c>
@@ -62636,7 +62690,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452" s="8">
         <v>43894</v>
       </c>
@@ -62677,7 +62731,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453" s="8">
         <v>43901</v>
       </c>
@@ -62718,7 +62772,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A454" s="8">
         <v>43908</v>
       </c>
@@ -62759,7 +62813,7 @@
         <v>2513</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A455" s="8">
         <v>43915</v>
       </c>
@@ -62800,7 +62854,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456" s="8">
         <v>43922</v>
       </c>
@@ -62841,7 +62895,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457" s="8">
         <v>43929</v>
       </c>
@@ -62882,7 +62936,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458" s="8">
         <v>43936</v>
       </c>
@@ -62923,7 +62977,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459" s="8">
         <v>43943</v>
       </c>
@@ -62964,7 +63018,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460" s="8">
         <v>43950</v>
       </c>
@@ -63005,7 +63059,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461" s="8">
         <v>43957</v>
       </c>
@@ -63046,7 +63100,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462" s="8">
         <v>43964</v>
       </c>
@@ -63087,7 +63141,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463" s="8">
         <v>43971</v>
       </c>
@@ -63128,7 +63182,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464" s="8">
         <v>43978</v>
       </c>
@@ -63169,7 +63223,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A465" s="8">
         <v>43985</v>
       </c>
@@ -63210,7 +63264,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A466" s="8">
         <v>43992</v>
       </c>
@@ -63251,7 +63305,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A467" s="8">
         <v>43999</v>
       </c>
@@ -63292,7 +63346,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A468" s="8">
         <v>44006</v>
       </c>
@@ -63333,7 +63387,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A469" s="8">
         <v>44013</v>
       </c>
@@ -63374,7 +63428,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A470" s="8">
         <v>44020</v>
       </c>
@@ -63415,7 +63469,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A471" s="8">
         <v>44027</v>
       </c>
@@ -63456,7 +63510,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A472" s="8">
         <v>44034</v>
       </c>
@@ -63497,7 +63551,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A473" s="8">
         <v>44041</v>
       </c>
@@ -63538,7 +63592,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A474" s="8">
         <v>44048</v>
       </c>
@@ -63579,7 +63633,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A475" s="8">
         <v>44055</v>
       </c>
@@ -63620,7 +63674,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A476" s="8">
         <v>44062</v>
       </c>
@@ -63661,7 +63715,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A477" s="8">
         <v>44069</v>
       </c>
@@ -63702,7 +63756,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A478" s="8">
         <v>44076</v>
       </c>
@@ -63743,7 +63797,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A479" s="8">
         <v>44083</v>
       </c>
@@ -63784,7 +63838,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A480" s="8">
         <v>44090</v>
       </c>
@@ -63825,7 +63879,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A481" s="8">
         <v>44097</v>
       </c>
@@ -63866,7 +63920,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A482" s="8">
         <v>44104</v>
       </c>
@@ -63907,7 +63961,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A483" s="8">
         <v>44111</v>
       </c>
@@ -63948,7 +64002,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A484" s="8">
         <v>44118</v>
       </c>
@@ -63989,7 +64043,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A485" s="8">
         <v>44125</v>
       </c>
@@ -64030,7 +64084,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A486" s="8">
         <v>44132</v>
       </c>
@@ -64071,7 +64125,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A487" s="8">
         <v>44139</v>
       </c>
@@ -64112,7 +64166,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A488" s="8">
         <v>44146</v>
       </c>
@@ -64153,7 +64207,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A489" s="8">
         <v>44153</v>
       </c>
@@ -64194,7 +64248,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A490" s="8">
         <v>44160</v>
       </c>
@@ -64235,7 +64289,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A491" s="8">
         <v>44167</v>
       </c>
@@ -64276,7 +64330,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A492" s="8">
         <v>44174</v>
       </c>
@@ -64317,7 +64371,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A493" s="8">
         <v>44181</v>
       </c>
@@ -64358,7 +64412,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A494" s="8">
         <v>44188</v>
       </c>
@@ -64399,7 +64453,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A495" s="8">
         <v>44195</v>
       </c>
@@ -64440,7 +64494,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A496" s="8">
         <v>44202</v>
       </c>
@@ -64481,7 +64535,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A497" s="8">
         <v>44209</v>
       </c>
@@ -64522,7 +64576,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A498" s="8">
         <v>44216</v>
       </c>
@@ -64563,7 +64617,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A499" s="8">
         <v>44223</v>
       </c>
@@ -64604,7 +64658,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A500" s="8">
         <v>44230</v>
       </c>
@@ -64645,7 +64699,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A501" s="8">
         <v>44237</v>
       </c>
@@ -64686,7 +64740,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A502" s="8">
         <v>44244</v>
       </c>
@@ -64727,7 +64781,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A503" s="8">
         <v>44251</v>
       </c>
@@ -64768,7 +64822,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A504" s="8">
         <v>44258</v>
       </c>
@@ -64809,7 +64863,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A505" s="8">
         <v>44265</v>
       </c>
@@ -64850,7 +64904,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A506" s="8">
         <v>44272</v>
       </c>
@@ -64891,7 +64945,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A507" s="8">
         <v>44279</v>
       </c>
@@ -64932,7 +64986,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A508" s="8">
         <v>44286</v>
       </c>
@@ -64973,7 +65027,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A509" s="8">
         <v>44293</v>
       </c>
@@ -65014,7 +65068,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A510" s="8">
         <v>44300</v>
       </c>
@@ -65055,7 +65109,7 @@
         <v>2623</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A511" s="8">
         <v>44307</v>
       </c>
@@ -65096,7 +65150,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A512" s="8">
         <v>44314</v>
       </c>
@@ -65137,7 +65191,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A513" s="8">
         <v>44321</v>
       </c>
@@ -65178,7 +65232,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A514" s="8">
         <v>44328</v>
       </c>
@@ -65219,7 +65273,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A515" s="8">
         <v>44335</v>
       </c>
@@ -65260,7 +65314,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A516" s="8">
         <v>44342</v>
       </c>
@@ -65301,7 +65355,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A517" s="8">
         <v>44349</v>
       </c>
@@ -65342,7 +65396,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A518" s="8">
         <v>44356</v>
       </c>
@@ -65383,7 +65437,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A519" s="8">
         <v>44363</v>
       </c>
@@ -65424,7 +65478,7 @@
         <v>4607</v>
       </c>
     </row>
-    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A520" s="8">
         <v>44370</v>
       </c>
@@ -65465,7 +65519,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A521" s="8">
         <v>44377</v>
       </c>
@@ -65506,7 +65560,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A522" s="8">
         <v>44384</v>
       </c>
@@ -65547,7 +65601,7 @@
         <v>5336</v>
       </c>
     </row>
-    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A523" s="8">
         <v>44391</v>
       </c>
@@ -65588,7 +65642,7 @@
         <v>5362</v>
       </c>
     </row>
-    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A524" s="8">
         <v>44398</v>
       </c>
@@ -65629,7 +65683,7 @@
         <v>5364</v>
       </c>
     </row>
-    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A525" s="8">
         <v>44405</v>
       </c>
@@ -65670,7 +65724,7 @@
         <v>5624</v>
       </c>
     </row>
-    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A526" s="8">
         <v>44412</v>
       </c>
@@ -65711,7 +65765,7 @@
         <v>6417</v>
       </c>
     </row>
-    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A527" s="8">
         <v>44419</v>
       </c>
@@ -65752,7 +65806,7 @@
         <v>6390</v>
       </c>
     </row>
-    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A528" s="8">
         <v>44426</v>
       </c>
@@ -65793,7 +65847,7 @@
         <v>6435</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A529" s="8">
         <v>44433</v>
       </c>
@@ -65834,7 +65888,7 @@
         <v>6461</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A530" s="8">
         <v>44440</v>
       </c>
@@ -65875,7 +65929,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A531" s="8">
         <v>44447</v>
       </c>
@@ -65916,7 +65970,7 @@
         <v>6160</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A532" s="8">
         <v>44454</v>
       </c>
@@ -65957,7 +66011,7 @@
         <v>6162</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A533" s="8">
         <v>44461</v>
       </c>
@@ -65998,7 +66052,7 @@
         <v>6179</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A534" s="8">
         <v>44468</v>
       </c>
@@ -66039,7 +66093,7 @@
         <v>6192</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A535" s="8">
         <v>44475</v>
       </c>
@@ -66080,7 +66134,7 @@
         <v>6209</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A536" s="8">
         <v>44482</v>
       </c>
@@ -66121,7 +66175,7 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A537" s="8">
         <v>44489</v>
       </c>
@@ -66162,7 +66216,7 @@
         <v>6157</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A538" s="8">
         <v>44496</v>
       </c>
@@ -66203,7 +66257,7 @@
         <v>6161</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A539" s="8">
         <v>44503</v>
       </c>
@@ -66244,7 +66298,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A540" s="8">
         <v>44510</v>
       </c>
@@ -66285,7 +66339,7 @@
         <v>6255</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A541" s="8">
         <v>44517</v>
       </c>
@@ -66326,7 +66380,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A542" s="8">
         <v>44524</v>
       </c>
@@ -66367,7 +66421,7 @@
         <v>6232</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A543" s="8">
         <v>44531</v>
       </c>
@@ -66408,7 +66462,7 @@
         <v>6214</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A544" s="8">
         <v>44538</v>
       </c>
@@ -66449,7 +66503,7 @@
         <v>6283</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A545" s="8">
         <v>44545</v>
       </c>
@@ -66490,7 +66544,7 @@
         <v>6272</v>
       </c>
     </row>
-    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A546" s="8">
         <v>44552</v>
       </c>
@@ -66531,7 +66585,7 @@
         <v>6290</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A547" s="8">
         <v>44566</v>
       </c>
@@ -66572,7 +66626,7 @@
         <v>6280</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A548" s="8">
         <v>44573</v>
       </c>
@@ -66613,7 +66667,7 @@
         <v>6233</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A549" s="8">
         <v>44580</v>
       </c>
@@ -66654,7 +66708,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A550" s="8">
         <v>44587</v>
       </c>
@@ -66695,7 +66749,7 @@
         <v>6315</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A551" s="8">
         <v>44594</v>
       </c>
@@ -66736,7 +66790,7 @@
         <v>6455</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A552" s="8">
         <v>44601</v>
       </c>
@@ -66777,7 +66831,7 @@
         <v>6453</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A553" s="8">
         <v>44608</v>
       </c>
@@ -66818,7 +66872,7 @@
         <v>6514</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A554" s="8">
         <v>44615</v>
       </c>
@@ -66859,7 +66913,7 @@
         <v>6518</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A555" s="8">
         <v>44622</v>
       </c>
@@ -66900,7 +66954,7 @@
         <v>6476</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A556" s="8">
         <v>44629</v>
       </c>
@@ -66941,7 +66995,7 @@
         <v>6494</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A557" s="8">
         <v>44636</v>
       </c>
@@ -66982,7 +67036,7 @@
         <v>6491</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A558" s="8">
         <v>44643</v>
       </c>
@@ -67023,7 +67077,7 @@
         <v>6793</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A559" s="8">
         <v>44650</v>
       </c>
@@ -67064,7 +67118,7 @@
         <v>6680</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A560" s="8">
         <v>44657</v>
       </c>
@@ -67105,7 +67159,7 @@
         <v>6903</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A561" s="8">
         <v>44664</v>
       </c>
@@ -67146,7 +67200,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A562" s="8">
         <v>44671</v>
       </c>
@@ -67187,7 +67241,7 @@
         <v>6934</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A563" s="8">
         <v>44678</v>
       </c>
@@ -67228,7 +67282,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A564" s="8">
         <v>44685</v>
       </c>
@@ -67269,7 +67323,7 @@
         <v>7212</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A565" s="8">
         <v>44692</v>
       </c>
@@ -67310,7 +67364,7 @@
         <v>7201</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A566" s="8">
         <v>44699</v>
       </c>
@@ -67351,7 +67405,7 @@
         <v>7189</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A567" s="8">
         <v>44706</v>
       </c>
@@ -67392,7 +67446,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A568" s="8">
         <v>44713</v>
       </c>
@@ -67433,7 +67487,7 @@
         <v>7186</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A569" s="8">
         <v>44720</v>
       </c>
@@ -67474,7 +67528,7 @@
         <v>7100</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A570" s="8">
         <v>44727</v>
       </c>
@@ -67515,7 +67569,7 @@
         <v>6938</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A571" s="8">
         <v>44734</v>
       </c>
@@ -67556,7 +67610,7 @@
         <v>6849</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A572" s="8">
         <v>44741</v>
       </c>
@@ -67597,7 +67651,7 @@
         <v>6783</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A573" s="8">
         <v>44748</v>
       </c>
@@ -67638,7 +67692,7 @@
         <v>6801</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A574" s="8">
         <v>44755</v>
       </c>
@@ -67679,7 +67733,7 @@
         <v>6929</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A575" s="8">
         <v>44762</v>
       </c>
@@ -67720,7 +67774,7 @@
         <v>6926</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A576" s="8">
         <v>44769</v>
       </c>
@@ -67761,7 +67815,7 @@
         <v>6921</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A577" s="8">
         <v>44776</v>
       </c>
@@ -67802,7 +67856,7 @@
         <v>6939</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A578" s="8">
         <v>44783</v>
       </c>
@@ -67843,7 +67897,7 @@
         <v>6945</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A579" s="8">
         <v>44790</v>
       </c>
@@ -67884,7 +67938,7 @@
         <v>6936</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A580" s="8">
         <v>44797</v>
       </c>
@@ -67925,7 +67979,7 @@
         <v>6922</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A581" s="8">
         <v>44804</v>
       </c>
@@ -67966,7 +68020,7 @@
         <v>6839</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A582" s="8">
         <v>44811</v>
       </c>
@@ -68007,7 +68061,7 @@
         <v>6688</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A583" s="8">
         <v>44818</v>
       </c>
@@ -68048,7 +68102,7 @@
         <v>6607</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A584" s="8">
         <v>44825</v>
       </c>
@@ -68089,7 +68143,7 @@
         <v>6737</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A585" s="8">
         <v>44832</v>
       </c>
@@ -68130,7 +68184,7 @@
         <v>7038</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A586" s="8">
         <v>44839</v>
       </c>
@@ -68171,7 +68225,7 @@
         <v>7252</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A587" s="8">
         <v>44846</v>
       </c>
@@ -68212,7 +68266,7 @@
         <v>7295</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A588" s="8">
         <v>44853</v>
       </c>
@@ -68253,7 +68307,7 @@
         <v>7264</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A589" s="8">
         <v>44860</v>
       </c>
@@ -68294,7 +68348,7 @@
         <v>7284</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A590" s="8">
         <v>44867</v>
       </c>
@@ -68335,7 +68389,7 @@
         <v>7426</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A591" s="8">
         <v>44874</v>
       </c>
@@ -68376,7 +68430,7 @@
         <v>7336</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A592" s="8">
         <v>44881</v>
       </c>
@@ -68417,7 +68471,7 @@
         <v>7363</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A593" s="8">
         <v>44888</v>
       </c>
@@ -68458,7 +68512,7 @@
         <v>7224</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A594" s="8">
         <v>44895</v>
       </c>
@@ -68499,7 +68553,7 @@
         <v>7240</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A595" s="8">
         <v>44902</v>
       </c>
@@ -68540,7 +68594,7 @@
         <v>7151</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A596" s="8">
         <v>44909</v>
       </c>
@@ -68581,7 +68635,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A597" s="8">
         <v>44916</v>
       </c>
@@ -68622,7 +68676,7 @@
         <v>6989</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A598" s="8">
         <v>44930</v>
       </c>
@@ -68663,7 +68717,7 @@
         <v>6589</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A599" s="8">
         <v>44937</v>
       </c>
@@ -68704,7 +68758,7 @@
         <v>6363</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A600" s="8">
         <v>44944</v>
       </c>
@@ -68745,7 +68799,7 @@
         <v>6296</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A601" s="8">
         <v>44951</v>
       </c>
@@ -68786,7 +68840,7 @@
         <v>6322</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A602" s="8">
         <v>44958</v>
       </c>
@@ -68827,7 +68881,7 @@
         <v>6262</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A603" s="8">
         <v>44965</v>
       </c>
@@ -68868,7 +68922,7 @@
         <v>6010</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A604" s="8">
         <v>44972</v>
       </c>
@@ -68909,7 +68963,7 @@
         <v>5675</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A605" s="8">
         <v>44979</v>
       </c>
@@ -68950,7 +69004,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A606" s="8">
         <v>44986</v>
       </c>
@@ -68991,7 +69045,7 @@
         <v>5573</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A607" s="8">
         <v>44993</v>
       </c>
@@ -69032,7 +69086,7 @@
         <v>5377</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A608" s="8">
         <v>45000</v>
       </c>
@@ -69073,7 +69127,7 @@
         <v>5326</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A609" s="8">
         <v>45007</v>
       </c>
@@ -69114,7 +69168,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A610" s="8">
         <v>45014</v>
       </c>
@@ -69155,7 +69209,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A611" s="8">
         <v>45021</v>
       </c>
@@ -69196,7 +69250,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A612" s="8">
         <v>45028</v>
       </c>
@@ -69237,7 +69291,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A613" s="8">
         <v>45035</v>
       </c>
@@ -69278,7 +69332,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A614" s="8">
         <v>45042</v>
       </c>
@@ -69319,7 +69373,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A615" s="8">
         <v>45049</v>
       </c>
@@ -69360,7 +69414,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A616" s="8">
         <v>45056</v>
       </c>
@@ -69401,7 +69455,7 @@
         <v>4530</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A617" s="8">
         <v>45063</v>
       </c>
@@ -69442,7 +69496,7 @@
         <v>4434</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A618" s="8">
         <v>45070</v>
       </c>
@@ -69483,7 +69537,7 @@
         <v>3969</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A619" s="8">
         <v>45077</v>
       </c>
@@ -69524,7 +69578,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A620" s="8">
         <v>45084</v>
       </c>
@@ -69565,7 +69619,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A621" s="8">
         <v>45091</v>
       </c>
@@ -69606,7 +69660,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A622" s="8">
         <v>45098</v>
       </c>
@@ -69647,7 +69701,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A623" s="8">
         <v>45105</v>
       </c>
@@ -69688,7 +69742,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A624" s="8">
         <v>45112</v>
       </c>
@@ -69729,7 +69783,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A625" s="8">
         <v>45119</v>
       </c>
@@ -69770,7 +69824,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A626" s="8">
         <v>45126</v>
       </c>
@@ -69811,7 +69865,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A627" s="8">
         <v>45133</v>
       </c>
@@ -69852,7 +69906,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A628" s="8">
         <v>45140</v>
       </c>
@@ -69893,7 +69947,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A629" s="8">
         <v>45147</v>
       </c>
@@ -69934,7 +69988,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A630" s="8">
         <v>45154</v>
       </c>
@@ -69975,7 +70029,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A631" s="8">
         <v>45161</v>
       </c>
@@ -70016,7 +70070,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A632" s="8">
         <v>45168</v>
       </c>
@@ -70057,7 +70111,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A633" s="8">
         <v>45175</v>
       </c>
@@ -70098,7 +70152,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A634" s="8">
         <v>45182</v>
       </c>
@@ -70139,7 +70193,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" s="8">
         <v>45189</v>
       </c>
@@ -70180,7 +70234,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A636" s="8">
         <v>45196</v>
       </c>
@@ -70221,7 +70275,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A637" s="8">
         <v>45203</v>
       </c>
@@ -70262,7 +70316,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A638" s="8">
         <v>45210</v>
       </c>
@@ -70303,7 +70357,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A639" s="8">
         <v>45217</v>
       </c>
@@ -70344,7 +70398,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" s="8">
         <v>45224</v>
       </c>
@@ -70385,7 +70439,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A641" s="8">
         <v>45231</v>
       </c>
@@ -70426,7 +70480,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A642" s="8">
         <v>45238</v>
       </c>
@@ -70467,7 +70521,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A643" s="8">
         <v>45245</v>
       </c>
@@ -70508,7 +70562,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A644" s="8">
         <v>45252</v>
       </c>
@@ -70549,7 +70603,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A645" s="8">
         <v>45259</v>
       </c>
@@ -70590,7 +70644,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" s="8">
         <v>45266</v>
       </c>
@@ -70631,7 +70685,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" s="8">
         <v>45273</v>
       </c>
@@ -70672,7 +70726,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" s="8">
         <v>45280</v>
       </c>
@@ -70713,7 +70767,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" s="8">
         <v>45294</v>
       </c>
@@ -70754,7 +70808,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" s="8">
         <v>45301</v>
       </c>
@@ -70795,7 +70849,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" s="8">
         <v>45308</v>
       </c>
@@ -70836,7 +70890,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A652" s="8">
         <v>45315</v>
       </c>
@@ -70877,7 +70931,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A653" s="8">
         <v>45322</v>
       </c>
@@ -70918,7 +70972,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A654" s="8">
         <v>45329</v>
       </c>
@@ -70959,7 +71013,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A655" s="8">
         <v>45336</v>
       </c>
@@ -71000,7 +71054,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A656" s="8">
         <v>45343</v>
       </c>
@@ -71041,7 +71095,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A657" s="8">
         <v>45350</v>
       </c>
@@ -71082,7 +71136,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A658" s="8">
         <v>45357</v>
       </c>
@@ -71123,7 +71177,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A659" s="8">
         <v>45364</v>
       </c>
@@ -71164,7 +71218,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A660" s="8">
         <v>45371</v>
       </c>
@@ -71205,7 +71259,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A661" s="8">
         <v>45378</v>
       </c>
@@ -71246,7 +71300,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A662" s="8">
         <v>45385</v>
       </c>
@@ -71287,7 +71341,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A663" s="8">
         <v>45392</v>
       </c>
@@ -71328,7 +71382,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A664" s="8">
         <v>45399</v>
       </c>
@@ -71369,7 +71423,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="665" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A665" s="8">
         <v>45406</v>
       </c>
@@ -71410,7 +71464,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="666" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A666" s="8">
         <v>45413</v>
       </c>
@@ -71451,7 +71505,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="667" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A667" s="8">
         <v>45420</v>
       </c>
@@ -71492,7 +71546,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="668" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A668" s="8">
         <v>45427</v>
       </c>
@@ -71533,7 +71587,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A669" s="8">
         <v>45434</v>
       </c>
@@ -71574,7 +71628,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A670" s="8">
         <v>45441</v>
       </c>
@@ -71615,7 +71669,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A671" s="8">
         <v>45448</v>
       </c>
@@ -71656,7 +71710,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A672" s="8">
         <v>45455</v>
       </c>
@@ -71697,7 +71751,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A673" s="8">
         <v>45462</v>
       </c>
@@ -71738,7 +71792,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A674" s="8">
         <v>45469</v>
       </c>
@@ -71779,7 +71833,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A675" s="8">
         <v>45476</v>
       </c>
@@ -71820,7 +71874,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A676" s="8">
         <v>45483</v>
       </c>
@@ -71861,7 +71915,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A677" s="8">
         <v>45490</v>
       </c>
@@ -71902,7 +71956,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A678" s="8">
         <v>45497</v>
       </c>
@@ -71943,7 +71997,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A679" s="8">
         <v>45504</v>
       </c>
@@ -71984,7 +72038,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A680" s="8">
         <v>45511</v>
       </c>
@@ -72025,7 +72079,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A681" s="8">
         <v>45518</v>
       </c>
@@ -72066,7 +72120,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A682" s="8">
         <v>45525</v>
       </c>
@@ -72107,7 +72161,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A683" s="8">
         <v>45532</v>
       </c>
@@ -72148,7 +72202,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A684" s="8">
         <v>45539</v>
       </c>
@@ -72189,7 +72243,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A685" s="8">
         <v>45546</v>
       </c>
@@ -72230,7 +72284,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="686" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A686" s="8">
         <v>45553</v>
       </c>
@@ -72271,7 +72325,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A687" s="8">
         <v>45560</v>
       </c>
@@ -72312,7 +72366,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="688" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A688" s="8">
         <v>45567</v>
       </c>
@@ -72353,7 +72407,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="689" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A689" s="8">
         <v>45574</v>
       </c>
@@ -72394,7 +72448,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="690" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A690" s="8">
         <v>45581</v>
       </c>
@@ -72435,7 +72489,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="691" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A691" s="8">
         <v>45588</v>
       </c>
@@ -72476,7 +72530,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="692" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A692" s="8">
         <v>45595</v>
       </c>
@@ -72517,7 +72571,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="693" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A693" s="8">
         <v>45602</v>
       </c>
@@ -72558,7 +72612,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="694" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A694" s="8">
         <v>45609</v>
       </c>
@@ -72599,7 +72653,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="695" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A695" s="8">
         <v>45616</v>
       </c>
@@ -72640,7 +72694,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="696" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A696" s="8">
         <v>45623</v>
       </c>
@@ -72681,7 +72735,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="697" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A697" s="8">
         <v>45630</v>
       </c>
@@ -72722,7 +72776,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="698" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A698" s="8">
         <v>45637</v>
       </c>
@@ -72763,7 +72817,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="699" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A699" s="8">
         <v>45644</v>
       </c>
@@ -72804,7 +72858,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="700" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A700" s="8">
         <v>45658</v>
       </c>
@@ -72845,7 +72899,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="701" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A701" s="8">
         <v>45665</v>
       </c>
@@ -72886,7 +72940,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="702" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A702" s="8">
         <v>45672</v>
       </c>
@@ -72927,7 +72981,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="703" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A703" s="8">
         <v>45679</v>
       </c>
@@ -72968,7 +73022,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="704" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" s="8">
         <v>45686</v>
       </c>
@@ -73009,7 +73063,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A705" s="8">
         <v>45693</v>
       </c>
@@ -73050,7 +73104,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A706" s="8">
         <v>45700</v>
       </c>
@@ -73091,7 +73145,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A707" s="8">
         <v>45707</v>
       </c>
@@ -73132,7 +73186,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="708" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A708" s="8">
         <v>45714</v>
       </c>
@@ -73173,7 +73227,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A709" s="8">
         <v>45721</v>
       </c>
@@ -73214,7 +73268,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A710" s="8">
         <v>45728</v>
       </c>
@@ -73255,7 +73309,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A711" s="8">
         <v>45735</v>
       </c>
@@ -73296,7 +73350,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A712" s="8">
         <v>45742</v>
       </c>
@@ -73337,7 +73391,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A713" s="8">
         <v>45749</v>
       </c>
@@ -73378,7 +73432,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="714" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A714" s="8">
         <v>45756</v>
       </c>
@@ -73419,7 +73473,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="715" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A715" s="8">
         <v>45763</v>
       </c>
@@ -73460,7 +73514,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A716" s="8">
         <v>45770</v>
       </c>
@@ -73501,7 +73555,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A717" s="8">
         <v>45777</v>
       </c>
@@ -73542,7 +73596,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A718" s="8">
         <v>45784</v>
       </c>
@@ -73583,7 +73637,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A719" s="8">
         <v>45791</v>
       </c>
@@ -73624,7 +73678,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A720" s="8">
         <v>45798</v>
       </c>
@@ -73665,7 +73719,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="721" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A721" s="8">
         <v>45805</v>
       </c>
@@ -73706,7 +73760,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A722" s="8">
         <v>45812</v>
       </c>
@@ -73747,7 +73801,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="723" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A723" s="8">
         <v>45819</v>
       </c>
@@ -73788,7 +73842,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="724" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A724" s="8">
         <v>45826</v>
       </c>
@@ -73829,7 +73883,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A725" s="8">
         <v>45833</v>
       </c>
@@ -73870,7 +73924,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="726" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A726" s="8">
         <v>45840</v>
       </c>
@@ -73911,7 +73965,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="727" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A727" s="8">
         <v>45847</v>
       </c>
@@ -73952,7 +74006,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="728" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A728" s="8">
         <v>45854</v>
       </c>
@@ -73993,7 +74047,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="729" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A729" s="8">
         <v>45861</v>
       </c>
@@ -74034,7 +74088,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="730" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A730" s="8">
         <v>45868</v>
       </c>
@@ -74075,7 +74129,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A731" s="8">
         <v>45875</v>
       </c>
@@ -74116,7 +74170,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A732" s="8">
         <v>45882</v>
       </c>
@@ -74157,7 +74211,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="733" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A733" s="8">
         <v>45889</v>
       </c>
@@ -74198,7 +74252,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="734" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A734" s="8">
         <v>45896</v>
       </c>
@@ -74239,7 +74293,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="735" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A735" s="8">
         <v>45903</v>
       </c>
@@ -74280,7 +74334,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="736" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A736" s="8">
         <v>45910</v>
       </c>
@@ -74321,7 +74375,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="737" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A737" s="8">
         <v>45917</v>
       </c>
@@ -74362,7 +74416,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="738" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A738" s="8">
         <v>45924</v>
       </c>
@@ -74403,7 +74457,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="739" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A739" s="8">
         <v>45931</v>
       </c>
@@ -74444,7 +74498,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A740" s="8">
         <v>45938</v>
       </c>
@@ -74485,7 +74539,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="741" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A741" s="8">
         <v>45945</v>
       </c>
@@ -74526,7 +74580,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="742" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A742" s="8">
         <v>45952</v>
       </c>
@@ -74567,7 +74621,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A743" s="8">
         <v>45959</v>
       </c>
@@ -74608,7 +74662,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="744" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A744" s="8">
         <v>45966</v>
       </c>
@@ -74649,7 +74703,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="745" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A745" s="8">
         <v>45973</v>
       </c>
@@ -74690,7 +74744,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="746" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A746" s="8">
         <v>45980</v>
       </c>
@@ -74731,7 +74785,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="747" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A747" s="8">
         <v>45987</v>
       </c>
@@ -74772,7 +74826,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A748" s="8">
         <v>45994</v>
       </c>
@@ -74813,7 +74867,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="749" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A749" s="8">
         <v>46001</v>
       </c>
@@ -74854,7 +74908,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A750" s="8">
         <v>46008</v>
       </c>
@@ -74895,7 +74949,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A751" s="8">
         <v>46015</v>
       </c>
@@ -74936,7 +74990,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A752" s="8">
         <v>46022</v>
       </c>
@@ -74977,7 +75031,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A753" s="8">
         <v>46029</v>
       </c>
@@ -75018,7 +75072,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A754" s="8">
         <v>46036</v>
       </c>
@@ -75059,7 +75113,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="755" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A755" s="8">
         <v>46043</v>
       </c>
@@ -75100,7 +75154,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="756" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A756" s="8">
         <v>46050</v>
       </c>
@@ -75141,7 +75195,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A757" s="8">
         <v>46057</v>
       </c>
@@ -75182,7 +75236,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A758" s="8">
         <v>46064</v>
       </c>
@@ -75223,7 +75277,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A759" s="8">
         <v>46071</v>
       </c>
@@ -75264,7 +75318,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A760" s="8">
         <v>46078</v>
       </c>
@@ -75305,7 +75359,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A761" s="8">
         <v>46085</v>
       </c>
@@ -75346,7 +75400,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A762" s="8">
         <v>46092</v>
       </c>
@@ -75387,7 +75441,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A763" s="8">
         <v>46099</v>
       </c>
@@ -75428,7 +75482,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="764" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A764" s="8">
         <v>46106</v>
       </c>
@@ -75469,7 +75523,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A765" s="8">
         <v>46113</v>
       </c>
@@ -75510,7 +75564,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A766" s="8">
         <v>46120</v>
       </c>
@@ -75551,7 +75605,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="767" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A767" s="8">
         <v>46127</v>
       </c>
@@ -75592,7 +75646,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A768" s="8">
         <v>46134</v>
       </c>
@@ -75633,7 +75687,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A769" s="8">
         <v>46141</v>
       </c>
@@ -75674,7 +75728,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A770" s="8">
         <v>46148</v>
       </c>
@@ -75715,7 +75769,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A771" s="8">
         <v>46155</v>
       </c>
@@ -75756,7 +75810,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="772" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A772" s="8">
         <v>46162</v>
       </c>
@@ -75797,7 +75851,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A773" s="8">
         <v>46169</v>
       </c>
@@ -75838,7 +75892,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="774" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A774" s="8">
         <v>46176</v>
       </c>
@@ -75879,7 +75933,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="775" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A775" s="8">
         <v>46183</v>
       </c>
@@ -75920,7 +75974,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="776" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A776" s="8">
         <v>46190</v>
       </c>
@@ -75961,7 +76015,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="777" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A777" s="8">
         <v>46197</v>
       </c>
@@ -76002,7 +76056,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="778" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A778" s="8">
         <v>46204</v>
       </c>
@@ -76043,7 +76097,7 @@
         <v>2602</v>
       </c>
     </row>
-    <row r="779" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A779" s="8">
         <v>46211</v>
       </c>
@@ -76084,7 +76138,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="780" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A780" s="8">
         <v>46218</v>
       </c>
@@ -76125,7 +76179,7 @@
         <v>2667</v>
       </c>
     </row>
-    <row r="781" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A781" s="8">
         <v>46225</v>
       </c>
@@ -76166,7 +76220,7 @@
         <v>2635</v>
       </c>
     </row>
-    <row r="782" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A782" s="8">
         <v>46232</v>
       </c>
@@ -76207,7 +76261,7 @@
         <v>2719</v>
       </c>
     </row>
-    <row r="783" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A783" s="8">
         <v>46239</v>
       </c>
@@ -76248,7 +76302,7 @@
         <v>2773</v>
       </c>
     </row>
-    <row r="784" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A784" s="8">
         <v>46246</v>
       </c>
@@ -76289,7 +76343,7 @@
         <v>2884</v>
       </c>
     </row>
-    <row r="785" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A785" s="8">
         <v>46253</v>
       </c>
@@ -76303,7 +76357,7 @@
         <v>15</v>
       </c>
       <c r="E785" s="10">
-        <v>4526</v>
+        <v>4526.1899999999996</v>
       </c>
       <c r="F785" s="11">
         <v>4401</v>
@@ -76328,6 +76382,47 @@
       </c>
       <c r="M785" s="11">
         <v>3039</v>
+      </c>
+    </row>
+    <row r="786" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A786" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B786" s="8">
+        <v>46261</v>
+      </c>
+      <c r="C786" s="9">
+        <v>0.58333333334748505</v>
+      </c>
+      <c r="D786" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E786" s="10">
+        <v>4472.88</v>
+      </c>
+      <c r="F786" s="11">
+        <v>4287</v>
+      </c>
+      <c r="G786" s="11">
+        <v>2866</v>
+      </c>
+      <c r="H786" s="11">
+        <v>6818</v>
+      </c>
+      <c r="I786" s="11">
+        <v>9333</v>
+      </c>
+      <c r="J786" s="11">
+        <v>588</v>
+      </c>
+      <c r="K786" s="11">
+        <v>822</v>
+      </c>
+      <c r="L786" s="11">
+        <v>1126</v>
+      </c>
+      <c r="M786" s="11">
+        <v>3010</v>
       </c>
     </row>
   </sheetData>
@@ -76340,7 +76435,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BC2DE8-BCE4-43AE-95F3-3DF06CDF8905}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -76351,12 +76446,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C789BCF2-DC16-4FFC-AF71-3351D156D960}">
   <dimension ref="B2:N3"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
@@ -76375,7 +76470,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
